--- a/rtss-pre1917/src/main/resources/immigration.xlsx
+++ b/rtss-pre1917/src/main/resources/immigration.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9971648-A584-405C-B209-3AB884825442}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99BCCDA4-09F5-4BD8-AB8C-8B3AF2C02E8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{F5C0FC2C-9C7B-4145-981E-7BD1765E4EE3}"/>
   </bookViews>
@@ -114,9 +114,6 @@
   </si>
   <si>
     <t>в приграничную полосу на другой её стороне.</t>
-  </si>
-  <si>
-    <t>NBER, "International Migrations", ред. W. Wilcox, Volume I - Statistics, NY 1929, стр.  794-795, 798-803</t>
   </si>
   <si>
     <t>Движение иностранцев через границы России по паспортам, по странам.</t>
@@ -245,7 +242,10 @@
     <t>verify</t>
   </si>
   <si>
-    <t>verify-d</t>
+    <t>NBER, "International Migrations", ред. W. Wilcox, Volume I - Statistics, NY 1929, стр.  794-795, 798-804</t>
+  </si>
+  <si>
+    <t>verify-diff</t>
   </si>
 </sst>
 </file>
@@ -319,7 +319,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -331,41 +331,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="3" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -690,31 +673,31 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="2"/>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9" t="s">
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9" t="s">
+      <c r="F5" s="16"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="I5" s="9"/>
-      <c r="J5" s="9"/>
+      <c r="I5" s="16"/>
+      <c r="J5" s="16"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="3" t="s">
@@ -749,615 +732,615 @@
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="13">
+      <c r="A7" s="9">
         <f t="shared" ref="A7:A20" si="0">A8-1</f>
         <v>1881</v>
       </c>
-      <c r="B7" s="10">
+      <c r="B7" s="1">
         <f t="shared" ref="B7:B21" si="1">C7-D7</f>
         <v>46700</v>
       </c>
-      <c r="C7" s="17">
+      <c r="C7" s="11">
         <v>273857</v>
       </c>
-      <c r="D7" s="17">
+      <c r="D7" s="11">
         <v>227157</v>
       </c>
-      <c r="E7" s="10">
+      <c r="E7" s="1">
         <f t="shared" ref="E7:E21" si="2">F7-G7</f>
         <v>46867</v>
       </c>
-      <c r="F7" s="17">
+      <c r="F7" s="11">
         <v>225335</v>
       </c>
-      <c r="G7" s="17">
+      <c r="G7" s="11">
         <v>178468</v>
       </c>
-      <c r="H7" s="10">
+      <c r="H7" s="1">
         <f t="shared" ref="H7:H21" si="3">B7-E7</f>
         <v>-167</v>
       </c>
-      <c r="I7" s="10">
+      <c r="I7" s="1">
         <f t="shared" ref="I7:I21" si="4">C7-F7</f>
         <v>48522</v>
       </c>
-      <c r="J7" s="10">
+      <c r="J7" s="1">
         <f t="shared" ref="J7:J21" si="5">D7-G7</f>
         <v>48689</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="13">
+      <c r="A8" s="9">
         <f t="shared" si="0"/>
         <v>1882</v>
       </c>
-      <c r="B8" s="10">
+      <c r="B8" s="1">
         <f t="shared" si="1"/>
         <v>67597</v>
       </c>
-      <c r="C8" s="17">
+      <c r="C8" s="11">
         <v>306654</v>
       </c>
-      <c r="D8" s="17">
+      <c r="D8" s="11">
         <v>239057</v>
       </c>
-      <c r="E8" s="10">
+      <c r="E8" s="1">
         <f t="shared" si="2"/>
         <v>59018</v>
       </c>
-      <c r="F8" s="17">
+      <c r="F8" s="11">
         <v>272069</v>
       </c>
-      <c r="G8" s="17">
+      <c r="G8" s="11">
         <v>213051</v>
       </c>
-      <c r="H8" s="10">
+      <c r="H8" s="1">
         <f t="shared" si="3"/>
         <v>8579</v>
       </c>
-      <c r="I8" s="10">
+      <c r="I8" s="1">
         <f t="shared" si="4"/>
         <v>34585</v>
       </c>
-      <c r="J8" s="10">
+      <c r="J8" s="1">
         <f t="shared" si="5"/>
         <v>26006</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="13">
+      <c r="A9" s="9">
         <f t="shared" si="0"/>
         <v>1883</v>
       </c>
-      <c r="B9" s="10">
+      <c r="B9" s="1">
         <f t="shared" si="1"/>
         <v>55451</v>
       </c>
-      <c r="C9" s="17">
+      <c r="C9" s="11">
         <v>265002</v>
       </c>
-      <c r="D9" s="17">
+      <c r="D9" s="11">
         <v>209551</v>
       </c>
-      <c r="E9" s="10">
+      <c r="E9" s="1">
         <f t="shared" si="2"/>
         <v>47674</v>
       </c>
-      <c r="F9" s="17">
+      <c r="F9" s="11">
         <v>231748</v>
       </c>
-      <c r="G9" s="17">
+      <c r="G9" s="11">
         <v>184074</v>
       </c>
-      <c r="H9" s="10">
+      <c r="H9" s="1">
         <f t="shared" si="3"/>
         <v>7777</v>
       </c>
-      <c r="I9" s="10">
+      <c r="I9" s="1">
         <f t="shared" si="4"/>
         <v>33254</v>
       </c>
-      <c r="J9" s="10">
+      <c r="J9" s="1">
         <f t="shared" si="5"/>
         <v>25477</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="13">
+      <c r="A10" s="9">
         <f t="shared" si="0"/>
         <v>1884</v>
       </c>
-      <c r="B10" s="10">
+      <c r="B10" s="1">
         <f t="shared" si="1"/>
         <v>45084</v>
       </c>
-      <c r="C10" s="17">
+      <c r="C10" s="11">
         <v>243201</v>
       </c>
-      <c r="D10" s="17">
+      <c r="D10" s="11">
         <v>198117</v>
       </c>
-      <c r="E10" s="10">
+      <c r="E10" s="1">
         <f t="shared" si="2"/>
         <v>37662</v>
       </c>
-      <c r="F10" s="17">
+      <c r="F10" s="11">
         <v>209276</v>
       </c>
-      <c r="G10" s="17">
+      <c r="G10" s="11">
         <v>171614</v>
       </c>
-      <c r="H10" s="10">
+      <c r="H10" s="1">
         <f t="shared" si="3"/>
         <v>7422</v>
       </c>
-      <c r="I10" s="10">
+      <c r="I10" s="1">
         <f t="shared" si="4"/>
         <v>33925</v>
       </c>
-      <c r="J10" s="10">
+      <c r="J10" s="1">
         <f t="shared" si="5"/>
         <v>26503</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="13">
+      <c r="A11" s="9">
         <f t="shared" si="0"/>
         <v>1885</v>
       </c>
-      <c r="B11" s="10">
+      <c r="B11" s="1">
         <f t="shared" si="1"/>
         <v>58808</v>
       </c>
-      <c r="C11" s="17">
+      <c r="C11" s="11">
         <v>259616</v>
       </c>
-      <c r="D11" s="17">
+      <c r="D11" s="11">
         <v>200808</v>
       </c>
-      <c r="E11" s="10">
+      <c r="E11" s="1">
         <f t="shared" si="2"/>
         <v>50986</v>
       </c>
-      <c r="F11" s="17">
+      <c r="F11" s="11">
         <v>222297</v>
       </c>
-      <c r="G11" s="17">
+      <c r="G11" s="11">
         <v>171311</v>
       </c>
-      <c r="H11" s="10">
+      <c r="H11" s="1">
         <f t="shared" si="3"/>
         <v>7822</v>
       </c>
-      <c r="I11" s="10">
+      <c r="I11" s="1">
         <f t="shared" si="4"/>
         <v>37319</v>
       </c>
-      <c r="J11" s="10">
+      <c r="J11" s="1">
         <f t="shared" si="5"/>
         <v>29497</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="13">
+      <c r="A12" s="9">
         <f t="shared" si="0"/>
         <v>1886</v>
       </c>
-      <c r="B12" s="10">
+      <c r="B12" s="1">
         <f t="shared" si="1"/>
         <v>59536</v>
       </c>
-      <c r="C12" s="17">
+      <c r="C12" s="11">
         <v>237777</v>
       </c>
-      <c r="D12" s="17">
+      <c r="D12" s="11">
         <v>178241</v>
       </c>
-      <c r="E12" s="10">
+      <c r="E12" s="1">
         <f t="shared" si="2"/>
         <v>42795</v>
       </c>
-      <c r="F12" s="17">
+      <c r="F12" s="11">
         <v>197489</v>
       </c>
-      <c r="G12" s="17">
+      <c r="G12" s="11">
         <v>154694</v>
       </c>
-      <c r="H12" s="10">
+      <c r="H12" s="1">
         <f t="shared" si="3"/>
         <v>16741</v>
       </c>
-      <c r="I12" s="10">
+      <c r="I12" s="1">
         <f t="shared" si="4"/>
         <v>40288</v>
       </c>
-      <c r="J12" s="10">
+      <c r="J12" s="1">
         <f t="shared" si="5"/>
         <v>23547</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="13">
+      <c r="A13" s="9">
         <f t="shared" si="0"/>
         <v>1887</v>
       </c>
-      <c r="B13" s="10">
+      <c r="B13" s="1">
         <f t="shared" si="1"/>
         <v>21546</v>
       </c>
-      <c r="C13" s="17">
+      <c r="C13" s="11">
         <v>250516</v>
       </c>
-      <c r="D13" s="17">
+      <c r="D13" s="11">
         <v>228970</v>
       </c>
-      <c r="E13" s="10">
+      <c r="E13" s="1">
         <f t="shared" si="2"/>
         <v>11321</v>
       </c>
-      <c r="F13" s="17">
+      <c r="F13" s="11">
         <v>206454</v>
       </c>
-      <c r="G13" s="17">
+      <c r="G13" s="11">
         <v>195133</v>
       </c>
-      <c r="H13" s="10">
+      <c r="H13" s="1">
         <f t="shared" si="3"/>
         <v>10225</v>
       </c>
-      <c r="I13" s="10">
+      <c r="I13" s="1">
         <f t="shared" si="4"/>
         <v>44062</v>
       </c>
-      <c r="J13" s="10">
+      <c r="J13" s="1">
         <f t="shared" si="5"/>
         <v>33837</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="13">
+      <c r="A14" s="9">
         <f t="shared" si="0"/>
         <v>1888</v>
       </c>
-      <c r="B14" s="10">
+      <c r="B14" s="1">
         <f t="shared" si="1"/>
         <v>21899</v>
       </c>
-      <c r="C14" s="17">
+      <c r="C14" s="11">
         <v>272478</v>
       </c>
-      <c r="D14" s="17">
+      <c r="D14" s="11">
         <v>250579</v>
       </c>
-      <c r="E14" s="10">
+      <c r="E14" s="1">
         <f t="shared" si="2"/>
         <v>9990</v>
       </c>
-      <c r="F14" s="17">
+      <c r="F14" s="11">
         <v>227533</v>
       </c>
-      <c r="G14" s="17">
+      <c r="G14" s="11">
         <v>217543</v>
       </c>
-      <c r="H14" s="10">
+      <c r="H14" s="1">
         <f t="shared" si="3"/>
         <v>11909</v>
       </c>
-      <c r="I14" s="10">
+      <c r="I14" s="1">
         <f t="shared" si="4"/>
         <v>44945</v>
       </c>
-      <c r="J14" s="10">
+      <c r="J14" s="1">
         <f t="shared" si="5"/>
         <v>33036</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="13">
+      <c r="A15" s="9">
         <f t="shared" si="0"/>
         <v>1889</v>
       </c>
-      <c r="B15" s="10">
+      <c r="B15" s="1">
         <f t="shared" si="1"/>
         <v>18009</v>
       </c>
-      <c r="C15" s="17">
+      <c r="C15" s="11">
         <v>323931</v>
       </c>
-      <c r="D15" s="17">
+      <c r="D15" s="11">
         <v>305922</v>
       </c>
-      <c r="E15" s="10">
+      <c r="E15" s="1">
         <f t="shared" si="2"/>
         <v>7547</v>
       </c>
-      <c r="F15" s="17">
+      <c r="F15" s="11">
         <v>274578</v>
       </c>
-      <c r="G15" s="17">
+      <c r="G15" s="11">
         <v>267031</v>
       </c>
-      <c r="H15" s="10">
+      <c r="H15" s="1">
         <f t="shared" si="3"/>
         <v>10462</v>
       </c>
-      <c r="I15" s="10">
+      <c r="I15" s="1">
         <f t="shared" si="4"/>
         <v>49353</v>
       </c>
-      <c r="J15" s="10">
+      <c r="J15" s="1">
         <f t="shared" si="5"/>
         <v>38891</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="13">
+      <c r="A16" s="9">
         <f t="shared" si="0"/>
         <v>1890</v>
       </c>
-      <c r="B16" s="10">
+      <c r="B16" s="1">
         <f t="shared" si="1"/>
         <v>19534</v>
       </c>
-      <c r="C16" s="17">
+      <c r="C16" s="11">
         <v>306090</v>
       </c>
-      <c r="D16" s="17">
+      <c r="D16" s="11">
         <v>286556</v>
       </c>
-      <c r="E16" s="10">
+      <c r="E16" s="1">
         <f t="shared" si="2"/>
         <v>4703</v>
       </c>
-      <c r="F16" s="17">
+      <c r="F16" s="11">
         <v>253479</v>
       </c>
-      <c r="G16" s="17">
+      <c r="G16" s="11">
         <v>248776</v>
       </c>
-      <c r="H16" s="10">
+      <c r="H16" s="1">
         <f t="shared" si="3"/>
         <v>14831</v>
       </c>
-      <c r="I16" s="10">
+      <c r="I16" s="1">
         <f t="shared" si="4"/>
         <v>52611</v>
       </c>
-      <c r="J16" s="10">
+      <c r="J16" s="1">
         <f t="shared" si="5"/>
         <v>37780</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="13">
+      <c r="A17" s="9">
         <f t="shared" si="0"/>
         <v>1891</v>
       </c>
-      <c r="B17" s="10">
+      <c r="B17" s="1">
         <f t="shared" si="1"/>
         <v>4623</v>
       </c>
-      <c r="C17" s="17">
+      <c r="C17" s="11">
         <v>268501</v>
       </c>
-      <c r="D17" s="17">
+      <c r="D17" s="11">
         <v>263878</v>
       </c>
-      <c r="E17" s="10">
+      <c r="E17" s="1">
         <f t="shared" si="2"/>
         <v>-6697</v>
       </c>
-      <c r="F17" s="17">
+      <c r="F17" s="11">
         <v>215642</v>
       </c>
-      <c r="G17" s="17">
+      <c r="G17" s="11">
         <v>222339</v>
       </c>
-      <c r="H17" s="10">
+      <c r="H17" s="1">
         <f t="shared" si="3"/>
         <v>11320</v>
       </c>
-      <c r="I17" s="10">
+      <c r="I17" s="1">
         <f t="shared" si="4"/>
         <v>52859</v>
       </c>
-      <c r="J17" s="10">
+      <c r="J17" s="1">
         <f t="shared" si="5"/>
         <v>41539</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="13">
+      <c r="A18" s="9">
         <f t="shared" si="0"/>
         <v>1892</v>
       </c>
-      <c r="B18" s="10">
+      <c r="B18" s="1">
         <f t="shared" si="1"/>
         <v>17735</v>
       </c>
-      <c r="C18" s="17">
+      <c r="C18" s="11">
         <v>228624</v>
       </c>
-      <c r="D18" s="17">
+      <c r="D18" s="11">
         <v>210889</v>
       </c>
-      <c r="E18" s="10">
+      <c r="E18" s="1">
         <f t="shared" si="2"/>
         <v>458</v>
       </c>
-      <c r="F18" s="17">
+      <c r="F18" s="11">
         <v>173222</v>
       </c>
-      <c r="G18" s="17">
+      <c r="G18" s="11">
         <v>172764</v>
       </c>
-      <c r="H18" s="10">
+      <c r="H18" s="1">
         <f t="shared" si="3"/>
         <v>17277</v>
       </c>
-      <c r="I18" s="10">
+      <c r="I18" s="1">
         <f t="shared" si="4"/>
         <v>55402</v>
       </c>
-      <c r="J18" s="10">
+      <c r="J18" s="1">
         <f t="shared" si="5"/>
         <v>38125</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="13">
+      <c r="A19" s="9">
         <f t="shared" si="0"/>
         <v>1893</v>
       </c>
-      <c r="B19" s="10">
+      <c r="B19" s="1">
         <f t="shared" si="1"/>
         <v>21197</v>
       </c>
-      <c r="C19" s="17">
+      <c r="C19" s="11">
         <v>248137</v>
       </c>
-      <c r="D19" s="17">
+      <c r="D19" s="11">
         <v>226940</v>
       </c>
-      <c r="E19" s="10">
+      <c r="E19" s="1">
         <f t="shared" si="2"/>
         <v>1989</v>
       </c>
-      <c r="F19" s="17">
+      <c r="F19" s="11">
         <v>184993</v>
       </c>
-      <c r="G19" s="17">
+      <c r="G19" s="11">
         <v>183004</v>
       </c>
-      <c r="H19" s="10">
+      <c r="H19" s="1">
         <f t="shared" si="3"/>
         <v>19208</v>
       </c>
-      <c r="I19" s="10">
+      <c r="I19" s="1">
         <f t="shared" si="4"/>
         <v>63144</v>
       </c>
-      <c r="J19" s="10">
+      <c r="J19" s="1">
         <f t="shared" si="5"/>
         <v>43936</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="13">
+      <c r="A20" s="9">
         <f t="shared" si="0"/>
         <v>1894</v>
       </c>
-      <c r="B20" s="10">
+      <c r="B20" s="1">
         <f t="shared" si="1"/>
         <v>22621</v>
       </c>
-      <c r="C20" s="17">
+      <c r="C20" s="11">
         <v>256775</v>
       </c>
-      <c r="D20" s="17">
+      <c r="D20" s="11">
         <v>234154</v>
       </c>
-      <c r="E20" s="10">
+      <c r="E20" s="1">
         <f t="shared" si="2"/>
         <v>7921</v>
       </c>
-      <c r="F20" s="17">
+      <c r="F20" s="11">
         <v>192387</v>
       </c>
-      <c r="G20" s="17">
+      <c r="G20" s="11">
         <v>184466</v>
       </c>
-      <c r="H20" s="10">
+      <c r="H20" s="1">
         <f t="shared" si="3"/>
         <v>14700</v>
       </c>
-      <c r="I20" s="10">
+      <c r="I20" s="1">
         <f t="shared" si="4"/>
         <v>64388</v>
       </c>
-      <c r="J20" s="10">
+      <c r="J20" s="1">
         <f t="shared" si="5"/>
         <v>49688</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="13">
+      <c r="A21" s="9">
         <f>A22-1</f>
         <v>1895</v>
       </c>
-      <c r="B21" s="10">
+      <c r="B21" s="1">
         <f t="shared" si="1"/>
         <v>37966</v>
       </c>
-      <c r="C21" s="17">
+      <c r="C21" s="11">
         <v>273324</v>
       </c>
-      <c r="D21" s="17">
+      <c r="D21" s="11">
         <v>235358</v>
       </c>
-      <c r="E21" s="10">
+      <c r="E21" s="1">
         <f t="shared" si="2"/>
         <v>17062</v>
       </c>
-      <c r="F21" s="17">
+      <c r="F21" s="11">
         <v>198223</v>
       </c>
-      <c r="G21" s="17">
+      <c r="G21" s="11">
         <v>181161</v>
       </c>
-      <c r="H21" s="10">
+      <c r="H21" s="1">
         <f t="shared" si="3"/>
         <v>20904</v>
       </c>
-      <c r="I21" s="10">
+      <c r="I21" s="1">
         <f t="shared" si="4"/>
         <v>75101</v>
       </c>
-      <c r="J21" s="10">
+      <c r="J21" s="1">
         <f t="shared" si="5"/>
         <v>54197</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="14">
+      <c r="A22" s="9">
         <v>1896</v>
       </c>
-      <c r="B22" s="10">
+      <c r="B22" s="1">
         <f>C22-D22</f>
         <v>12174</v>
       </c>
-      <c r="C22" s="10">
+      <c r="C22" s="1">
         <v>268727</v>
       </c>
-      <c r="D22" s="10">
+      <c r="D22" s="1">
         <v>256553</v>
       </c>
-      <c r="E22" s="10">
+      <c r="E22" s="1">
         <f>F22-G22</f>
         <v>6906</v>
       </c>
-      <c r="F22" s="10">
+      <c r="F22" s="1">
         <v>218121</v>
       </c>
-      <c r="G22" s="10">
+      <c r="G22" s="1">
         <v>211215</v>
       </c>
-      <c r="H22" s="10">
+      <c r="H22" s="1">
         <f>B22-E22</f>
         <v>5268</v>
       </c>
-      <c r="I22" s="10">
+      <c r="I22" s="1">
         <f t="shared" ref="I22:J22" si="6">C22-F22</f>
         <v>50606</v>
       </c>
-      <c r="J22" s="10">
+      <c r="J22" s="1">
         <f t="shared" si="6"/>
         <v>45338</v>
       </c>
       <c r="O22" s="1"/>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="15">
+      <c r="A23" s="9">
         <f>A22+1</f>
         <v>1897</v>
       </c>
@@ -1396,7 +1379,7 @@
       <c r="O23" s="1"/>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="15">
+      <c r="A24" s="9">
         <f t="shared" ref="A24:A41" si="12">A23+1</f>
         <v>1898</v>
       </c>
@@ -1435,7 +1418,7 @@
       <c r="O24" s="1"/>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="15">
+      <c r="A25" s="9">
         <f t="shared" si="12"/>
         <v>1899</v>
       </c>
@@ -1474,7 +1457,7 @@
       <c r="O25" s="1"/>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="15">
+      <c r="A26" s="9">
         <f t="shared" si="12"/>
         <v>1900</v>
       </c>
@@ -1513,7 +1496,7 @@
       <c r="O26" s="1"/>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="15">
+      <c r="A27" s="9">
         <f t="shared" si="12"/>
         <v>1901</v>
       </c>
@@ -1552,7 +1535,7 @@
       <c r="O27" s="1"/>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="15">
+      <c r="A28" s="9">
         <f t="shared" si="12"/>
         <v>1902</v>
       </c>
@@ -1591,7 +1574,7 @@
       <c r="O28" s="1"/>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="15">
+      <c r="A29" s="9">
         <f t="shared" si="12"/>
         <v>1903</v>
       </c>
@@ -1630,7 +1613,7 @@
       <c r="O29" s="1"/>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="15">
+      <c r="A30" s="9">
         <f t="shared" si="12"/>
         <v>1904</v>
       </c>
@@ -1669,7 +1652,7 @@
       <c r="O30" s="1"/>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="15">
+      <c r="A31" s="9">
         <f t="shared" si="12"/>
         <v>1905</v>
       </c>
@@ -1708,7 +1691,7 @@
       <c r="O31" s="1"/>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="15">
+      <c r="A32" s="9">
         <f t="shared" si="12"/>
         <v>1906</v>
       </c>
@@ -1747,7 +1730,7 @@
       <c r="O32" s="1"/>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="15">
+      <c r="A33" s="9">
         <f t="shared" si="12"/>
         <v>1907</v>
       </c>
@@ -1786,7 +1769,7 @@
       <c r="O33" s="1"/>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="15">
+      <c r="A34" s="9">
         <f t="shared" si="12"/>
         <v>1908</v>
       </c>
@@ -1825,7 +1808,7 @@
       <c r="O34" s="1"/>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="15">
+      <c r="A35" s="9">
         <f t="shared" si="12"/>
         <v>1909</v>
       </c>
@@ -1864,7 +1847,7 @@
       <c r="O35" s="1"/>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="15">
+      <c r="A36" s="9">
         <f t="shared" si="12"/>
         <v>1910</v>
       </c>
@@ -1903,7 +1886,7 @@
       <c r="O36" s="1"/>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="15">
+      <c r="A37" s="9">
         <f t="shared" si="12"/>
         <v>1911</v>
       </c>
@@ -1942,7 +1925,7 @@
       <c r="O37" s="1"/>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" s="15">
+      <c r="A38" s="9">
         <f t="shared" si="12"/>
         <v>1912</v>
       </c>
@@ -1981,7 +1964,7 @@
       <c r="O38" s="1"/>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" s="15">
+      <c r="A39" s="9">
         <f t="shared" si="12"/>
         <v>1913</v>
       </c>
@@ -2020,7 +2003,7 @@
       <c r="O39" s="1"/>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" s="15">
+      <c r="A40" s="9">
         <f t="shared" si="12"/>
         <v>1914</v>
       </c>
@@ -2059,7 +2042,7 @@
       <c r="O40" s="1"/>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A41" s="15">
+      <c r="A41" s="9">
         <f t="shared" si="12"/>
         <v>1915</v>
       </c>
@@ -2098,7 +2081,7 @@
       <c r="O41" s="1"/>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A42" s="16" t="s">
+      <c r="A42" s="10" t="s">
         <v>4</v>
       </c>
       <c r="B42" s="5">
@@ -2122,8 +2105,8 @@
       <c r="O42" s="1"/>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A43" s="16" t="s">
-        <v>53</v>
+      <c r="A43" s="10" t="s">
+        <v>52</v>
       </c>
       <c r="B43" s="5">
         <f>SUM(B7:B21)</f>
@@ -2146,8 +2129,8 @@
       <c r="O43" s="1"/>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A44" s="16" t="s">
-        <v>54</v>
+      <c r="A44" s="10" t="s">
+        <v>53</v>
       </c>
       <c r="B44" s="5">
         <f>B42+B43</f>
@@ -2174,7 +2157,7 @@
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O46" s="1"/>
     </row>
@@ -2183,7 +2166,7 @@
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M48" s="6"/>
       <c r="O48" s="1"/>
@@ -2199,53 +2182,53 @@
         <v>8</v>
       </c>
       <c r="H50" t="s">
+        <v>21</v>
+      </c>
+      <c r="K50" t="s">
         <v>22</v>
       </c>
-      <c r="K50" t="s">
+      <c r="N50" t="s">
         <v>23</v>
-      </c>
-      <c r="N50" t="s">
-        <v>24</v>
       </c>
       <c r="O50" s="1"/>
       <c r="Q50" t="s">
+        <v>24</v>
+      </c>
+      <c r="T50" t="s">
         <v>25</v>
       </c>
-      <c r="T50" t="s">
+      <c r="W50" t="s">
         <v>26</v>
       </c>
-      <c r="W50" t="s">
+      <c r="Z50" t="s">
         <v>27</v>
       </c>
-      <c r="Z50" t="s">
+      <c r="AC50" t="s">
         <v>28</v>
-      </c>
-      <c r="AC50" t="s">
-        <v>29</v>
       </c>
       <c r="AF50" t="s">
         <v>9</v>
       </c>
       <c r="AI50" t="s">
+        <v>29</v>
+      </c>
+      <c r="AL50" t="s">
         <v>30</v>
       </c>
-      <c r="AL50" t="s">
+      <c r="AO50" t="s">
         <v>31</v>
       </c>
-      <c r="AO50" t="s">
+      <c r="AR50" t="s">
         <v>32</v>
       </c>
-      <c r="AR50" t="s">
+      <c r="AU50" t="s">
         <v>33</v>
       </c>
-      <c r="AU50" t="s">
+      <c r="AX50" t="s">
         <v>34</v>
       </c>
-      <c r="AX50" t="s">
+      <c r="BA50" t="s">
         <v>35</v>
-      </c>
-      <c r="BA50" t="s">
-        <v>36</v>
       </c>
       <c r="BD50" t="s">
         <v>12</v>
@@ -2254,22 +2237,22 @@
         <v>10</v>
       </c>
       <c r="BJ50" t="s">
+        <v>36</v>
+      </c>
+      <c r="BM50" t="s">
         <v>37</v>
       </c>
-      <c r="BM50" t="s">
-        <v>38</v>
-      </c>
       <c r="BP50" t="s">
+        <v>57</v>
+      </c>
+      <c r="BS50" t="s">
+        <v>39</v>
+      </c>
+      <c r="BV50" t="s">
         <v>58</v>
       </c>
-      <c r="BS50" t="s">
-        <v>40</v>
-      </c>
-      <c r="BV50" t="s">
+      <c r="BZ50" t="s">
         <v>59</v>
-      </c>
-      <c r="BZ50" t="s">
-        <v>60</v>
       </c>
       <c r="CD50" t="s">
         <v>61</v>
@@ -2504,27 +2487,27 @@
       <c r="BX51" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="BZ51" s="23" t="s">
+      <c r="BZ51" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="CA51" s="23" t="s">
+      <c r="CA51" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="CB51" s="23" t="s">
+      <c r="CB51" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="CD51" s="23" t="s">
+      <c r="CD51" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="CE51" s="23" t="s">
+      <c r="CE51" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="CF51" s="23" t="s">
+      <c r="CF51" s="15" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="52" spans="1:84" x14ac:dyDescent="0.55000000000000004">
-      <c r="A52" s="19">
+      <c r="A52" s="9">
         <f t="shared" ref="A52:A65" si="13">A53-1</f>
         <v>1881</v>
       </c>
@@ -2532,170 +2515,170 @@
         <f t="shared" ref="B52:B66" si="14">C52-D52</f>
         <v>31266</v>
       </c>
-      <c r="C52" s="17">
+      <c r="C52" s="11">
         <v>112831</v>
       </c>
-      <c r="D52" s="17">
+      <c r="D52" s="11">
         <v>81565</v>
       </c>
       <c r="E52" s="1">
         <f t="shared" ref="E52:E66" si="15">F52-G52</f>
         <v>15527</v>
       </c>
-      <c r="F52" s="17">
+      <c r="F52" s="11">
         <v>94439</v>
       </c>
-      <c r="G52" s="17">
+      <c r="G52" s="11">
         <v>78912</v>
       </c>
       <c r="H52" s="1">
         <f t="shared" ref="H52:H66" si="16">I52-J52</f>
         <v>-366</v>
       </c>
-      <c r="I52" s="17">
+      <c r="I52" s="11">
         <v>2918</v>
       </c>
-      <c r="J52" s="17">
+      <c r="J52" s="11">
         <v>3284</v>
       </c>
       <c r="K52" s="1">
         <f t="shared" ref="K52:K66" si="17">L52-M52</f>
         <v>-294</v>
       </c>
-      <c r="L52" s="17">
+      <c r="L52" s="11">
         <v>1498</v>
       </c>
-      <c r="M52" s="17">
+      <c r="M52" s="11">
         <v>1792</v>
       </c>
       <c r="N52" s="1">
         <f t="shared" ref="N52:N66" si="18">O52-P52</f>
         <v>7</v>
       </c>
-      <c r="O52" s="17">
+      <c r="O52" s="11">
         <v>330</v>
       </c>
-      <c r="P52" s="17">
+      <c r="P52" s="11">
         <v>323</v>
       </c>
       <c r="Q52" s="1">
         <f t="shared" ref="Q52:Q66" si="19">R52-S52</f>
         <v>-159</v>
       </c>
-      <c r="R52" s="17">
+      <c r="R52" s="11">
         <v>639</v>
       </c>
-      <c r="S52" s="17">
+      <c r="S52" s="11">
         <v>798</v>
       </c>
       <c r="T52" s="1">
         <f t="shared" ref="T52:T66" si="20">U52-V52</f>
         <v>-3</v>
       </c>
-      <c r="U52" s="17">
+      <c r="U52" s="11">
         <v>321</v>
       </c>
-      <c r="V52" s="17">
+      <c r="V52" s="11">
         <v>324</v>
       </c>
       <c r="W52" s="1">
         <f t="shared" ref="W52:W66" si="21">X52-Y52</f>
         <v>-55</v>
       </c>
-      <c r="X52" s="17">
+      <c r="X52" s="11">
         <v>101</v>
       </c>
-      <c r="Y52" s="17">
+      <c r="Y52" s="11">
         <v>156</v>
       </c>
       <c r="Z52" s="1">
         <f t="shared" ref="Z52:Z66" si="22">AA52-AB52</f>
         <v>58</v>
       </c>
-      <c r="AA52" s="20">
+      <c r="AA52" s="13">
         <v>1373</v>
       </c>
-      <c r="AB52" s="21">
+      <c r="AB52" s="14">
         <v>1315</v>
       </c>
       <c r="AC52" s="1">
         <f t="shared" ref="AC52:AC66" si="23">AD52-AE52</f>
         <v>-76</v>
       </c>
-      <c r="AD52" s="20">
+      <c r="AD52" s="13">
         <v>560</v>
       </c>
-      <c r="AE52" s="18">
+      <c r="AE52" s="12">
         <v>636</v>
       </c>
       <c r="AF52" s="1">
         <f t="shared" ref="AF52:AF66" si="24">AG52-AH52</f>
         <v>119</v>
       </c>
-      <c r="AG52" s="20">
+      <c r="AG52" s="13">
         <v>2294</v>
       </c>
-      <c r="AH52" s="21">
+      <c r="AH52" s="14">
         <v>2175</v>
       </c>
       <c r="AI52" s="1">
         <f t="shared" ref="AI52:AI66" si="25">AJ52-AK52</f>
         <v>598</v>
       </c>
-      <c r="AJ52" s="21">
+      <c r="AJ52" s="14">
         <v>3059</v>
       </c>
-      <c r="AK52" s="21">
+      <c r="AK52" s="14">
         <v>2461</v>
       </c>
       <c r="AL52" s="1">
         <f t="shared" ref="AL52:AL66" si="26">AM52-AN52</f>
         <v>-18</v>
       </c>
-      <c r="AM52" s="18">
+      <c r="AM52" s="12">
         <v>339</v>
       </c>
-      <c r="AN52" s="20">
+      <c r="AN52" s="13">
         <v>357</v>
       </c>
       <c r="AO52" s="1">
         <f t="shared" ref="AO52:AO66" si="27">AP52-AQ52</f>
         <v>122</v>
       </c>
-      <c r="AP52" s="18">
+      <c r="AP52" s="12">
         <v>391</v>
       </c>
-      <c r="AQ52" s="20">
+      <c r="AQ52" s="13">
         <v>269</v>
       </c>
       <c r="AR52" s="1">
         <f t="shared" ref="AR52:AR66" si="28">AS52-AT52</f>
         <v>-27</v>
       </c>
-      <c r="AS52" s="20">
+      <c r="AS52" s="13">
         <v>40</v>
       </c>
-      <c r="AT52" s="20">
+      <c r="AT52" s="13">
         <v>67</v>
       </c>
       <c r="AU52" s="1">
         <f t="shared" ref="AU52:AU66" si="29">AV52-AW52</f>
         <v>6</v>
       </c>
-      <c r="AV52" s="20">
+      <c r="AV52" s="13">
         <v>33</v>
       </c>
-      <c r="AW52" s="20">
+      <c r="AW52" s="13">
         <v>27</v>
       </c>
       <c r="AX52" s="1">
         <f t="shared" ref="AX52:AX66" si="30">AY52-AZ52</f>
         <v>-2</v>
       </c>
-      <c r="AY52" s="20">
+      <c r="AY52" s="13">
         <v>2</v>
       </c>
-      <c r="AZ52" s="20">
+      <c r="AZ52" s="13">
         <v>4</v>
       </c>
       <c r="BA52" s="1">
@@ -2805,7 +2788,7 @@
       </c>
     </row>
     <row r="53" spans="1:84" x14ac:dyDescent="0.55000000000000004">
-      <c r="A53" s="19">
+      <c r="A53" s="9">
         <f t="shared" si="13"/>
         <v>1882</v>
       </c>
@@ -2813,170 +2796,170 @@
         <f t="shared" si="14"/>
         <v>19184</v>
       </c>
-      <c r="C53" s="17">
+      <c r="C53" s="11">
         <v>99693</v>
       </c>
-      <c r="D53" s="17">
+      <c r="D53" s="11">
         <v>80509</v>
       </c>
       <c r="E53" s="1">
         <f t="shared" si="15"/>
         <v>37463</v>
       </c>
-      <c r="F53" s="17">
+      <c r="F53" s="11">
         <v>141179</v>
       </c>
-      <c r="G53" s="17">
+      <c r="G53" s="11">
         <v>103716</v>
       </c>
       <c r="H53" s="1">
         <f t="shared" si="16"/>
         <v>-493</v>
       </c>
-      <c r="I53" s="17">
+      <c r="I53" s="11">
         <v>4897</v>
       </c>
-      <c r="J53" s="17">
+      <c r="J53" s="11">
         <v>5390</v>
       </c>
       <c r="K53" s="1">
         <f t="shared" si="17"/>
         <v>599</v>
       </c>
-      <c r="L53" s="17">
+      <c r="L53" s="11">
         <v>3624</v>
       </c>
-      <c r="M53" s="17">
+      <c r="M53" s="11">
         <v>3025</v>
       </c>
       <c r="N53" s="1">
         <f t="shared" si="18"/>
         <v>-11</v>
       </c>
-      <c r="O53" s="17">
+      <c r="O53" s="11">
         <v>397</v>
       </c>
-      <c r="P53" s="17">
+      <c r="P53" s="11">
         <v>408</v>
       </c>
       <c r="Q53" s="1">
         <f t="shared" si="19"/>
         <v>-781</v>
       </c>
-      <c r="R53" s="17">
+      <c r="R53" s="11">
         <v>2860</v>
       </c>
-      <c r="S53" s="17">
+      <c r="S53" s="11">
         <v>3641</v>
       </c>
       <c r="T53" s="1">
         <f t="shared" si="20"/>
         <v>79</v>
       </c>
-      <c r="U53" s="17">
+      <c r="U53" s="11">
         <v>370</v>
       </c>
-      <c r="V53" s="17">
+      <c r="V53" s="11">
         <v>291</v>
       </c>
       <c r="W53" s="1">
         <f t="shared" si="21"/>
         <v>-56</v>
       </c>
-      <c r="X53" s="17">
+      <c r="X53" s="11">
         <v>162</v>
       </c>
-      <c r="Y53" s="17">
+      <c r="Y53" s="11">
         <v>218</v>
       </c>
       <c r="Z53" s="1">
         <f t="shared" si="22"/>
         <v>387</v>
       </c>
-      <c r="AA53" s="21">
+      <c r="AA53" s="14">
         <v>1594</v>
       </c>
-      <c r="AB53" s="21">
+      <c r="AB53" s="14">
         <v>1207</v>
       </c>
       <c r="AC53" s="1">
         <f t="shared" si="23"/>
         <v>-2</v>
       </c>
-      <c r="AD53" s="21">
+      <c r="AD53" s="14">
         <v>1013</v>
       </c>
-      <c r="AE53" s="17">
+      <c r="AE53" s="11">
         <v>1015</v>
       </c>
       <c r="AF53" s="1">
         <f t="shared" si="24"/>
         <v>526</v>
       </c>
-      <c r="AG53" s="21">
+      <c r="AG53" s="14">
         <v>4848</v>
       </c>
-      <c r="AH53" s="21">
+      <c r="AH53" s="14">
         <v>4322</v>
       </c>
       <c r="AI53" s="1">
         <f t="shared" si="25"/>
         <v>419</v>
       </c>
-      <c r="AJ53" s="21">
+      <c r="AJ53" s="14">
         <v>4693</v>
       </c>
-      <c r="AK53" s="21">
+      <c r="AK53" s="14">
         <v>4274</v>
       </c>
       <c r="AL53" s="1">
         <f t="shared" si="26"/>
         <v>-21</v>
       </c>
-      <c r="AM53" s="18">
+      <c r="AM53" s="12">
         <v>296</v>
       </c>
-      <c r="AN53" s="20">
+      <c r="AN53" s="13">
         <v>317</v>
       </c>
       <c r="AO53" s="1">
         <f t="shared" si="27"/>
         <v>17</v>
       </c>
-      <c r="AP53" s="18">
+      <c r="AP53" s="12">
         <v>359</v>
       </c>
-      <c r="AQ53" s="20">
+      <c r="AQ53" s="13">
         <v>342</v>
       </c>
       <c r="AR53" s="1">
         <f t="shared" si="28"/>
         <v>5</v>
       </c>
-      <c r="AS53" s="20">
+      <c r="AS53" s="13">
         <v>87</v>
       </c>
-      <c r="AT53" s="20">
+      <c r="AT53" s="13">
         <v>82</v>
       </c>
       <c r="AU53" s="1">
         <f t="shared" si="29"/>
         <v>4</v>
       </c>
-      <c r="AV53" s="20">
+      <c r="AV53" s="13">
         <v>29</v>
       </c>
-      <c r="AW53" s="20">
+      <c r="AW53" s="13">
         <v>25</v>
       </c>
       <c r="AX53" s="1">
         <f t="shared" si="30"/>
         <v>-2</v>
       </c>
-      <c r="AY53" s="20">
+      <c r="AY53" s="13">
         <v>5</v>
       </c>
-      <c r="AZ53" s="20">
+      <c r="AZ53" s="13">
         <v>7</v>
       </c>
       <c r="BA53" s="1">
@@ -3086,7 +3069,7 @@
       </c>
     </row>
     <row r="54" spans="1:84" x14ac:dyDescent="0.55000000000000004">
-      <c r="A54" s="19">
+      <c r="A54" s="9">
         <f t="shared" si="13"/>
         <v>1883</v>
       </c>
@@ -3094,170 +3077,170 @@
         <f t="shared" si="14"/>
         <v>15565</v>
       </c>
-      <c r="C54" s="17">
+      <c r="C54" s="11">
         <v>72639</v>
       </c>
-      <c r="D54" s="17">
+      <c r="D54" s="11">
         <v>57074</v>
       </c>
       <c r="E54" s="1">
         <f t="shared" si="15"/>
         <v>28795</v>
       </c>
-      <c r="F54" s="17">
+      <c r="F54" s="11">
         <v>135851</v>
       </c>
-      <c r="G54" s="17">
+      <c r="G54" s="11">
         <v>107056</v>
       </c>
       <c r="H54" s="1">
         <f t="shared" si="16"/>
         <v>1223</v>
       </c>
-      <c r="I54" s="17">
+      <c r="I54" s="11">
         <v>3128</v>
       </c>
-      <c r="J54" s="17">
+      <c r="J54" s="11">
         <v>1905</v>
       </c>
       <c r="K54" s="1">
         <f t="shared" si="17"/>
         <v>154</v>
       </c>
-      <c r="L54" s="17">
+      <c r="L54" s="11">
         <v>2546</v>
       </c>
-      <c r="M54" s="17">
+      <c r="M54" s="11">
         <v>2392</v>
       </c>
       <c r="N54" s="1">
         <f t="shared" si="18"/>
         <v>88</v>
       </c>
-      <c r="O54" s="17">
+      <c r="O54" s="11">
         <v>590</v>
       </c>
-      <c r="P54" s="17">
+      <c r="P54" s="11">
         <v>502</v>
       </c>
       <c r="Q54" s="1">
         <f t="shared" si="19"/>
         <v>93</v>
       </c>
-      <c r="R54" s="17">
+      <c r="R54" s="11">
         <v>674</v>
       </c>
-      <c r="S54" s="17">
+      <c r="S54" s="11">
         <v>581</v>
       </c>
       <c r="T54" s="1">
         <f t="shared" si="20"/>
         <v>-1</v>
       </c>
-      <c r="U54" s="17">
+      <c r="U54" s="11">
         <v>108</v>
       </c>
-      <c r="V54" s="17">
+      <c r="V54" s="11">
         <v>109</v>
       </c>
       <c r="W54" s="1">
         <f t="shared" si="21"/>
         <v>-6</v>
       </c>
-      <c r="X54" s="17">
+      <c r="X54" s="11">
         <v>53</v>
       </c>
-      <c r="Y54" s="17">
+      <c r="Y54" s="11">
         <v>59</v>
       </c>
       <c r="Z54" s="1">
         <f t="shared" si="22"/>
         <v>34</v>
       </c>
-      <c r="AA54" s="21">
+      <c r="AA54" s="14">
         <v>1197</v>
       </c>
-      <c r="AB54" s="21">
+      <c r="AB54" s="14">
         <v>1163</v>
       </c>
       <c r="AC54" s="1">
         <f t="shared" si="23"/>
         <v>90</v>
       </c>
-      <c r="AD54" s="21">
+      <c r="AD54" s="14">
         <v>1122</v>
       </c>
-      <c r="AE54" s="17">
+      <c r="AE54" s="11">
         <v>1032</v>
       </c>
       <c r="AF54" s="1">
         <f t="shared" si="24"/>
         <v>-489</v>
       </c>
-      <c r="AG54" s="21">
+      <c r="AG54" s="14">
         <v>3805</v>
       </c>
-      <c r="AH54" s="21">
+      <c r="AH54" s="14">
         <v>4294</v>
       </c>
       <c r="AI54" s="1">
         <f t="shared" si="25"/>
         <v>279</v>
       </c>
-      <c r="AJ54" s="21">
+      <c r="AJ54" s="14">
         <v>3642</v>
       </c>
-      <c r="AK54" s="21">
+      <c r="AK54" s="14">
         <v>3363</v>
       </c>
       <c r="AL54" s="1">
         <f t="shared" si="26"/>
         <v>46</v>
       </c>
-      <c r="AM54" s="18">
+      <c r="AM54" s="12">
         <v>232</v>
       </c>
-      <c r="AN54" s="20">
+      <c r="AN54" s="13">
         <v>186</v>
       </c>
       <c r="AO54" s="1">
         <f t="shared" si="27"/>
         <v>78</v>
       </c>
-      <c r="AP54" s="18">
+      <c r="AP54" s="12">
         <v>372</v>
       </c>
-      <c r="AQ54" s="20">
+      <c r="AQ54" s="13">
         <v>294</v>
       </c>
       <c r="AR54" s="1">
         <f t="shared" si="28"/>
         <v>85</v>
       </c>
-      <c r="AS54" s="20">
+      <c r="AS54" s="13">
         <v>194</v>
       </c>
-      <c r="AT54" s="20">
+      <c r="AT54" s="13">
         <v>109</v>
       </c>
       <c r="AU54" s="1">
         <f t="shared" si="29"/>
         <v>2</v>
       </c>
-      <c r="AV54" s="20">
+      <c r="AV54" s="13">
         <v>27</v>
       </c>
-      <c r="AW54" s="20">
+      <c r="AW54" s="13">
         <v>25</v>
       </c>
       <c r="AX54" s="1">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="AY54" s="20">
+      <c r="AY54" s="13">
         <v>0</v>
       </c>
-      <c r="AZ54" s="20">
+      <c r="AZ54" s="13">
         <v>0</v>
       </c>
       <c r="BA54" s="1">
@@ -3367,7 +3350,7 @@
       </c>
     </row>
     <row r="55" spans="1:84" x14ac:dyDescent="0.55000000000000004">
-      <c r="A55" s="19">
+      <c r="A55" s="9">
         <f t="shared" si="13"/>
         <v>1884</v>
       </c>
@@ -3375,170 +3358,170 @@
         <f t="shared" si="14"/>
         <v>9047</v>
       </c>
-      <c r="C55" s="17">
+      <c r="C55" s="11">
         <v>61712</v>
       </c>
-      <c r="D55" s="17">
+      <c r="D55" s="11">
         <v>52665</v>
       </c>
       <c r="E55" s="1">
         <f t="shared" si="15"/>
         <v>26116</v>
       </c>
-      <c r="F55" s="17">
+      <c r="F55" s="11">
         <v>126409</v>
       </c>
-      <c r="G55" s="17">
+      <c r="G55" s="11">
         <v>100293</v>
       </c>
       <c r="H55" s="1">
         <f t="shared" si="16"/>
         <v>281</v>
       </c>
-      <c r="I55" s="17">
+      <c r="I55" s="11">
         <v>1692</v>
       </c>
-      <c r="J55" s="17">
+      <c r="J55" s="11">
         <v>1411</v>
       </c>
       <c r="K55" s="1">
         <f t="shared" si="17"/>
         <v>-371</v>
       </c>
-      <c r="L55" s="17">
+      <c r="L55" s="11">
         <v>1761</v>
       </c>
-      <c r="M55" s="17">
+      <c r="M55" s="11">
         <v>2132</v>
       </c>
       <c r="N55" s="1">
         <f t="shared" si="18"/>
         <v>59</v>
       </c>
-      <c r="O55" s="17">
+      <c r="O55" s="11">
         <v>653</v>
       </c>
-      <c r="P55" s="17">
+      <c r="P55" s="11">
         <v>594</v>
       </c>
       <c r="Q55" s="1">
         <f t="shared" si="19"/>
         <v>29</v>
       </c>
-      <c r="R55" s="17">
+      <c r="R55" s="11">
         <v>699</v>
       </c>
-      <c r="S55" s="17">
+      <c r="S55" s="11">
         <v>670</v>
       </c>
       <c r="T55" s="1">
         <f t="shared" si="20"/>
         <v>45</v>
       </c>
-      <c r="U55" s="17">
+      <c r="U55" s="11">
         <v>202</v>
       </c>
-      <c r="V55" s="17">
+      <c r="V55" s="11">
         <v>157</v>
       </c>
       <c r="W55" s="1">
         <f t="shared" si="21"/>
         <v>12</v>
       </c>
-      <c r="X55" s="17">
+      <c r="X55" s="11">
         <v>78</v>
       </c>
-      <c r="Y55" s="17">
+      <c r="Y55" s="11">
         <v>66</v>
       </c>
       <c r="Z55" s="1">
         <f t="shared" si="22"/>
         <v>102</v>
       </c>
-      <c r="AA55" s="20">
+      <c r="AA55" s="13">
         <v>974</v>
       </c>
-      <c r="AB55" s="20">
+      <c r="AB55" s="13">
         <v>872</v>
       </c>
       <c r="AC55" s="1">
         <f t="shared" si="23"/>
         <v>83</v>
       </c>
-      <c r="AD55" s="20">
+      <c r="AD55" s="13">
         <v>958</v>
       </c>
-      <c r="AE55" s="18">
+      <c r="AE55" s="12">
         <v>875</v>
       </c>
       <c r="AF55" s="1">
         <f t="shared" si="24"/>
         <v>237</v>
       </c>
-      <c r="AG55" s="21">
+      <c r="AG55" s="14">
         <v>4101</v>
       </c>
-      <c r="AH55" s="21">
+      <c r="AH55" s="14">
         <v>3864</v>
       </c>
       <c r="AI55" s="1">
         <f t="shared" si="25"/>
         <v>298</v>
       </c>
-      <c r="AJ55" s="21">
+      <c r="AJ55" s="14">
         <v>4018</v>
       </c>
-      <c r="AK55" s="21">
+      <c r="AK55" s="14">
         <v>3720</v>
       </c>
       <c r="AL55" s="1">
         <f t="shared" si="26"/>
         <v>67</v>
       </c>
-      <c r="AM55" s="18">
+      <c r="AM55" s="12">
         <v>265</v>
       </c>
-      <c r="AN55" s="20">
+      <c r="AN55" s="13">
         <v>198</v>
       </c>
       <c r="AO55" s="1">
         <f t="shared" si="27"/>
         <v>-83</v>
       </c>
-      <c r="AP55" s="18">
+      <c r="AP55" s="12">
         <v>327</v>
       </c>
-      <c r="AQ55" s="20">
+      <c r="AQ55" s="13">
         <v>410</v>
       </c>
       <c r="AR55" s="1">
         <f t="shared" si="28"/>
         <v>17</v>
       </c>
-      <c r="AS55" s="20">
+      <c r="AS55" s="13">
         <v>113</v>
       </c>
-      <c r="AT55" s="20">
+      <c r="AT55" s="13">
         <v>96</v>
       </c>
       <c r="AU55" s="1">
         <f t="shared" si="29"/>
         <v>-24</v>
       </c>
-      <c r="AV55" s="20">
+      <c r="AV55" s="13">
         <v>18</v>
       </c>
-      <c r="AW55" s="20">
+      <c r="AW55" s="13">
         <v>42</v>
       </c>
       <c r="AX55" s="1">
         <f t="shared" si="30"/>
         <v>9</v>
       </c>
-      <c r="AY55" s="20">
+      <c r="AY55" s="13">
         <v>12</v>
       </c>
-      <c r="AZ55" s="20">
+      <c r="AZ55" s="13">
         <v>3</v>
       </c>
       <c r="BA55" s="1">
@@ -3648,7 +3631,7 @@
       </c>
     </row>
     <row r="56" spans="1:84" x14ac:dyDescent="0.55000000000000004">
-      <c r="A56" s="19">
+      <c r="A56" s="9">
         <f t="shared" si="13"/>
         <v>1885</v>
       </c>
@@ -3656,170 +3639,170 @@
         <f t="shared" si="14"/>
         <v>15529</v>
       </c>
-      <c r="C56" s="17">
+      <c r="C56" s="11">
         <v>68337</v>
       </c>
-      <c r="D56" s="17">
+      <c r="D56" s="11">
         <v>52808</v>
       </c>
       <c r="E56" s="1">
         <f t="shared" si="15"/>
         <v>31366</v>
       </c>
-      <c r="F56" s="17">
+      <c r="F56" s="11">
         <v>129010</v>
       </c>
-      <c r="G56" s="17">
+      <c r="G56" s="11">
         <v>97644</v>
       </c>
       <c r="H56" s="1">
         <f t="shared" si="16"/>
         <v>2181</v>
       </c>
-      <c r="I56" s="17">
+      <c r="I56" s="11">
         <v>4717</v>
       </c>
-      <c r="J56" s="17">
+      <c r="J56" s="11">
         <v>2536</v>
       </c>
       <c r="K56" s="1">
         <f t="shared" si="17"/>
         <v>537</v>
       </c>
-      <c r="L56" s="17">
+      <c r="L56" s="11">
         <v>2919</v>
       </c>
-      <c r="M56" s="17">
+      <c r="M56" s="11">
         <v>2382</v>
       </c>
       <c r="N56" s="1">
         <f t="shared" si="18"/>
         <v>145</v>
       </c>
-      <c r="O56" s="17">
+      <c r="O56" s="11">
         <v>511</v>
       </c>
-      <c r="P56" s="17">
+      <c r="P56" s="11">
         <v>366</v>
       </c>
       <c r="Q56" s="1">
         <f t="shared" si="19"/>
         <v>218</v>
       </c>
-      <c r="R56" s="17">
+      <c r="R56" s="11">
         <v>1169</v>
       </c>
-      <c r="S56" s="17">
+      <c r="S56" s="11">
         <v>951</v>
       </c>
       <c r="T56" s="1">
         <f t="shared" si="20"/>
         <v>63</v>
       </c>
-      <c r="U56" s="17">
+      <c r="U56" s="11">
         <v>381</v>
       </c>
-      <c r="V56" s="17">
+      <c r="V56" s="11">
         <v>318</v>
       </c>
       <c r="W56" s="1">
         <f t="shared" si="21"/>
         <v>-43</v>
       </c>
-      <c r="X56" s="17">
+      <c r="X56" s="11">
         <v>217</v>
       </c>
-      <c r="Y56" s="17">
+      <c r="Y56" s="11">
         <v>260</v>
       </c>
       <c r="Z56" s="1">
         <f t="shared" si="22"/>
         <v>-121</v>
       </c>
-      <c r="AA56" s="21">
+      <c r="AA56" s="14">
         <v>1063</v>
       </c>
-      <c r="AB56" s="21">
+      <c r="AB56" s="14">
         <v>1184</v>
       </c>
       <c r="AC56" s="1">
         <f t="shared" si="23"/>
         <v>-90</v>
       </c>
-      <c r="AD56" s="20">
+      <c r="AD56" s="13">
         <v>983</v>
       </c>
-      <c r="AE56" s="17">
+      <c r="AE56" s="11">
         <v>1073</v>
       </c>
       <c r="AF56" s="1">
         <f t="shared" si="24"/>
         <v>33</v>
       </c>
-      <c r="AG56" s="21">
+      <c r="AG56" s="14">
         <v>3222</v>
       </c>
-      <c r="AH56" s="21">
+      <c r="AH56" s="14">
         <v>3189</v>
       </c>
       <c r="AI56" s="1">
         <f t="shared" si="25"/>
         <v>39</v>
       </c>
-      <c r="AJ56" s="21">
+      <c r="AJ56" s="14">
         <v>3987</v>
       </c>
-      <c r="AK56" s="21">
+      <c r="AK56" s="14">
         <v>3948</v>
       </c>
       <c r="AL56" s="1">
         <f t="shared" si="26"/>
         <v>17</v>
       </c>
-      <c r="AM56" s="18">
+      <c r="AM56" s="12">
         <v>265</v>
       </c>
-      <c r="AN56" s="20">
+      <c r="AN56" s="13">
         <v>248</v>
       </c>
       <c r="AO56" s="1">
         <f t="shared" si="27"/>
         <v>358</v>
       </c>
-      <c r="AP56" s="18">
+      <c r="AP56" s="12">
         <v>670</v>
       </c>
-      <c r="AQ56" s="20">
+      <c r="AQ56" s="13">
         <v>312</v>
       </c>
       <c r="AR56" s="1">
         <f t="shared" si="28"/>
         <v>13</v>
       </c>
-      <c r="AS56" s="20">
+      <c r="AS56" s="13">
         <v>83</v>
       </c>
-      <c r="AT56" s="20">
+      <c r="AT56" s="13">
         <v>70</v>
       </c>
       <c r="AU56" s="1">
         <f t="shared" si="29"/>
         <v>-19</v>
       </c>
-      <c r="AV56" s="20">
+      <c r="AV56" s="13">
         <v>103</v>
       </c>
-      <c r="AW56" s="20">
+      <c r="AW56" s="13">
         <v>122</v>
       </c>
       <c r="AX56" s="1">
         <f t="shared" si="30"/>
         <v>-3</v>
       </c>
-      <c r="AY56" s="20">
+      <c r="AY56" s="13">
         <v>8</v>
       </c>
-      <c r="AZ56" s="20">
+      <c r="AZ56" s="13">
         <v>11</v>
       </c>
       <c r="BA56" s="1">
@@ -3929,7 +3912,7 @@
       </c>
     </row>
     <row r="57" spans="1:84" x14ac:dyDescent="0.55000000000000004">
-      <c r="A57" s="19">
+      <c r="A57" s="9">
         <f t="shared" si="13"/>
         <v>1886</v>
       </c>
@@ -3937,170 +3920,170 @@
         <f t="shared" si="14"/>
         <v>10819</v>
       </c>
-      <c r="C57" s="17">
+      <c r="C57" s="11">
         <v>58598</v>
       </c>
-      <c r="D57" s="17">
+      <c r="D57" s="11">
         <v>47779</v>
       </c>
       <c r="E57" s="1">
         <f t="shared" si="15"/>
         <v>29461</v>
       </c>
-      <c r="F57" s="17">
+      <c r="F57" s="11">
         <v>116083</v>
       </c>
-      <c r="G57" s="17">
+      <c r="G57" s="11">
         <v>86622</v>
       </c>
       <c r="H57" s="1">
         <f t="shared" si="16"/>
         <v>285</v>
       </c>
-      <c r="I57" s="17">
+      <c r="I57" s="11">
         <v>3380</v>
       </c>
-      <c r="J57" s="17">
+      <c r="J57" s="11">
         <v>3095</v>
       </c>
       <c r="K57" s="1">
         <f t="shared" si="17"/>
         <v>229</v>
       </c>
-      <c r="L57" s="17">
+      <c r="L57" s="11">
         <v>2803</v>
       </c>
-      <c r="M57" s="17">
+      <c r="M57" s="11">
         <v>2574</v>
       </c>
       <c r="N57" s="1">
         <f t="shared" si="18"/>
         <v>414</v>
       </c>
-      <c r="O57" s="17">
+      <c r="O57" s="11">
         <v>827</v>
       </c>
-      <c r="P57" s="17">
+      <c r="P57" s="11">
         <v>413</v>
       </c>
       <c r="Q57" s="1">
         <f t="shared" si="19"/>
         <v>223</v>
       </c>
-      <c r="R57" s="17">
+      <c r="R57" s="11">
         <v>1142</v>
       </c>
-      <c r="S57" s="17">
+      <c r="S57" s="11">
         <v>919</v>
       </c>
       <c r="T57" s="1">
         <f t="shared" si="20"/>
         <v>-93</v>
       </c>
-      <c r="U57" s="17">
+      <c r="U57" s="11">
         <v>417</v>
       </c>
-      <c r="V57" s="17">
+      <c r="V57" s="11">
         <v>510</v>
       </c>
       <c r="W57" s="1">
         <f t="shared" si="21"/>
         <v>11</v>
       </c>
-      <c r="X57" s="17">
+      <c r="X57" s="11">
         <v>163</v>
       </c>
-      <c r="Y57" s="17">
+      <c r="Y57" s="11">
         <v>152</v>
       </c>
       <c r="Z57" s="1">
         <f t="shared" si="22"/>
         <v>317</v>
       </c>
-      <c r="AA57" s="21">
+      <c r="AA57" s="14">
         <v>1183</v>
       </c>
-      <c r="AB57" s="20">
+      <c r="AB57" s="13">
         <v>866</v>
       </c>
       <c r="AC57" s="1">
         <f t="shared" si="23"/>
         <v>-8</v>
       </c>
-      <c r="AD57" s="20">
+      <c r="AD57" s="13">
         <v>800</v>
       </c>
-      <c r="AE57" s="18">
+      <c r="AE57" s="12">
         <v>808</v>
       </c>
       <c r="AF57" s="1">
         <f t="shared" si="24"/>
         <v>-70</v>
       </c>
-      <c r="AG57" s="20">
+      <c r="AG57" s="13">
         <v>2771</v>
       </c>
-      <c r="AH57" s="21">
+      <c r="AH57" s="14">
         <v>2841</v>
       </c>
       <c r="AI57" s="1">
         <f t="shared" si="25"/>
         <v>879</v>
       </c>
-      <c r="AJ57" s="21">
+      <c r="AJ57" s="14">
         <v>4324</v>
       </c>
-      <c r="AK57" s="21">
+      <c r="AK57" s="14">
         <v>3445</v>
       </c>
       <c r="AL57" s="1">
         <f t="shared" si="26"/>
         <v>43</v>
       </c>
-      <c r="AM57" s="18">
+      <c r="AM57" s="12">
         <v>278</v>
       </c>
-      <c r="AN57" s="20">
+      <c r="AN57" s="13">
         <v>235</v>
       </c>
       <c r="AO57" s="1">
         <f t="shared" si="27"/>
         <v>150</v>
       </c>
-      <c r="AP57" s="18">
+      <c r="AP57" s="12">
         <v>691</v>
       </c>
-      <c r="AQ57" s="20">
+      <c r="AQ57" s="13">
         <v>541</v>
       </c>
       <c r="AR57" s="1">
         <f t="shared" si="28"/>
         <v>44</v>
       </c>
-      <c r="AS57" s="20">
+      <c r="AS57" s="13">
         <v>126</v>
       </c>
-      <c r="AT57" s="20">
+      <c r="AT57" s="13">
         <v>82</v>
       </c>
       <c r="AU57" s="1">
         <f t="shared" si="29"/>
         <v>17</v>
       </c>
-      <c r="AV57" s="20">
+      <c r="AV57" s="13">
         <v>92</v>
       </c>
-      <c r="AW57" s="20">
+      <c r="AW57" s="13">
         <v>75</v>
       </c>
       <c r="AX57" s="1">
         <f t="shared" si="30"/>
         <v>-6</v>
       </c>
-      <c r="AY57" s="20">
+      <c r="AY57" s="13">
         <v>7</v>
       </c>
-      <c r="AZ57" s="20">
+      <c r="AZ57" s="13">
         <v>13</v>
       </c>
       <c r="BA57" s="1">
@@ -4210,7 +4193,7 @@
       </c>
     </row>
     <row r="58" spans="1:84" x14ac:dyDescent="0.55000000000000004">
-      <c r="A58" s="19">
+      <c r="A58" s="9">
         <f t="shared" si="13"/>
         <v>1887</v>
       </c>
@@ -4218,170 +4201,170 @@
         <f t="shared" si="14"/>
         <v>2475</v>
       </c>
-      <c r="C58" s="17">
+      <c r="C58" s="11">
         <v>65234</v>
       </c>
-      <c r="D58" s="17">
+      <c r="D58" s="11">
         <v>62759</v>
       </c>
       <c r="E58" s="1">
         <f t="shared" si="15"/>
         <v>10626</v>
       </c>
-      <c r="F58" s="17">
+      <c r="F58" s="11">
         <v>119769</v>
       </c>
-      <c r="G58" s="17">
+      <c r="G58" s="11">
         <v>109143</v>
       </c>
       <c r="H58" s="1">
         <f t="shared" si="16"/>
         <v>-898</v>
       </c>
-      <c r="I58" s="17">
+      <c r="I58" s="11">
         <v>2625</v>
       </c>
-      <c r="J58" s="17">
+      <c r="J58" s="11">
         <v>3523</v>
       </c>
       <c r="K58" s="1">
         <f t="shared" si="17"/>
         <v>-429</v>
       </c>
-      <c r="L58" s="17">
+      <c r="L58" s="11">
         <v>2182</v>
       </c>
-      <c r="M58" s="17">
+      <c r="M58" s="11">
         <v>2611</v>
       </c>
       <c r="N58" s="1">
         <f t="shared" si="18"/>
         <v>-76</v>
       </c>
-      <c r="O58" s="17">
+      <c r="O58" s="11">
         <v>453</v>
       </c>
-      <c r="P58" s="17">
+      <c r="P58" s="11">
         <v>529</v>
       </c>
       <c r="Q58" s="1">
         <f t="shared" si="19"/>
         <v>-294</v>
       </c>
-      <c r="R58" s="17">
+      <c r="R58" s="11">
         <v>825</v>
       </c>
-      <c r="S58" s="17">
+      <c r="S58" s="11">
         <v>1119</v>
       </c>
       <c r="T58" s="1">
         <f t="shared" si="20"/>
         <v>-121</v>
       </c>
-      <c r="U58" s="17">
+      <c r="U58" s="11">
         <v>340</v>
       </c>
-      <c r="V58" s="17">
+      <c r="V58" s="11">
         <v>461</v>
       </c>
       <c r="W58" s="1">
         <f t="shared" si="21"/>
         <v>-27</v>
       </c>
-      <c r="X58" s="17">
+      <c r="X58" s="11">
         <v>88</v>
       </c>
-      <c r="Y58" s="17">
+      <c r="Y58" s="11">
         <v>115</v>
       </c>
       <c r="Z58" s="1">
         <f t="shared" si="22"/>
         <v>93</v>
       </c>
-      <c r="AA58" s="21">
+      <c r="AA58" s="14">
         <v>1174</v>
       </c>
-      <c r="AB58" s="21">
+      <c r="AB58" s="14">
         <v>1081</v>
       </c>
       <c r="AC58" s="1">
         <f t="shared" si="23"/>
         <v>-6</v>
       </c>
-      <c r="AD58" s="20">
+      <c r="AD58" s="13">
         <v>949</v>
       </c>
-      <c r="AE58" s="18">
+      <c r="AE58" s="12">
         <v>955</v>
       </c>
       <c r="AF58" s="1">
         <f t="shared" si="24"/>
         <v>-14</v>
       </c>
-      <c r="AG58" s="21">
+      <c r="AG58" s="14">
         <v>3841</v>
       </c>
-      <c r="AH58" s="21">
+      <c r="AH58" s="14">
         <v>3855</v>
       </c>
       <c r="AI58" s="1">
         <f t="shared" si="25"/>
         <v>312</v>
       </c>
-      <c r="AJ58" s="21">
+      <c r="AJ58" s="14">
         <v>4062</v>
       </c>
-      <c r="AK58" s="21">
+      <c r="AK58" s="14">
         <v>3750</v>
       </c>
       <c r="AL58" s="1">
         <f t="shared" si="26"/>
         <v>-20</v>
       </c>
-      <c r="AM58" s="18">
+      <c r="AM58" s="12">
         <v>213</v>
       </c>
-      <c r="AN58" s="20">
+      <c r="AN58" s="13">
         <v>233</v>
       </c>
       <c r="AO58" s="1">
         <f t="shared" si="27"/>
         <v>-37</v>
       </c>
-      <c r="AP58" s="18">
+      <c r="AP58" s="12">
         <v>613</v>
       </c>
-      <c r="AQ58" s="20">
+      <c r="AQ58" s="13">
         <v>650</v>
       </c>
       <c r="AR58" s="1">
         <f t="shared" si="28"/>
         <v>13</v>
       </c>
-      <c r="AS58" s="20">
+      <c r="AS58" s="13">
         <v>160</v>
       </c>
-      <c r="AT58" s="20">
+      <c r="AT58" s="13">
         <v>147</v>
       </c>
       <c r="AU58" s="1">
         <f t="shared" si="29"/>
         <v>-5</v>
       </c>
-      <c r="AV58" s="20">
+      <c r="AV58" s="13">
         <v>63</v>
       </c>
-      <c r="AW58" s="20">
+      <c r="AW58" s="13">
         <v>68</v>
       </c>
       <c r="AX58" s="1">
         <f t="shared" si="30"/>
         <v>-17</v>
       </c>
-      <c r="AY58" s="20">
+      <c r="AY58" s="13">
         <v>8</v>
       </c>
-      <c r="AZ58" s="20">
+      <c r="AZ58" s="13">
         <v>25</v>
       </c>
       <c r="BA58" s="1">
@@ -4491,7 +4474,7 @@
       </c>
     </row>
     <row r="59" spans="1:84" x14ac:dyDescent="0.55000000000000004">
-      <c r="A59" s="19">
+      <c r="A59" s="9">
         <f t="shared" si="13"/>
         <v>1888</v>
       </c>
@@ -4499,170 +4482,170 @@
         <f t="shared" si="14"/>
         <v>4550</v>
       </c>
-      <c r="C59" s="17">
+      <c r="C59" s="11">
         <v>94503</v>
       </c>
-      <c r="D59" s="17">
+      <c r="D59" s="11">
         <v>89953</v>
       </c>
       <c r="E59" s="1">
         <f t="shared" si="15"/>
         <v>4271</v>
       </c>
-      <c r="F59" s="17">
+      <c r="F59" s="11">
         <v>109278</v>
       </c>
-      <c r="G59" s="17">
+      <c r="G59" s="11">
         <v>105007</v>
       </c>
       <c r="H59" s="1">
         <f t="shared" si="16"/>
         <v>-112</v>
       </c>
-      <c r="I59" s="17">
+      <c r="I59" s="11">
         <v>3018</v>
       </c>
-      <c r="J59" s="17">
+      <c r="J59" s="11">
         <v>3130</v>
       </c>
       <c r="K59" s="1">
         <f t="shared" si="17"/>
         <v>243</v>
       </c>
-      <c r="L59" s="17">
+      <c r="L59" s="11">
         <v>3099</v>
       </c>
-      <c r="M59" s="17">
+      <c r="M59" s="11">
         <v>2856</v>
       </c>
       <c r="N59" s="1">
         <f t="shared" si="18"/>
         <v>-75</v>
       </c>
-      <c r="O59" s="17">
+      <c r="O59" s="11">
         <v>706</v>
       </c>
-      <c r="P59" s="17">
+      <c r="P59" s="11">
         <v>781</v>
       </c>
       <c r="Q59" s="1">
         <f t="shared" si="19"/>
         <v>5</v>
       </c>
-      <c r="R59" s="17">
+      <c r="R59" s="11">
         <v>1182</v>
       </c>
-      <c r="S59" s="17">
+      <c r="S59" s="11">
         <v>1177</v>
       </c>
       <c r="T59" s="1">
         <f t="shared" si="20"/>
         <v>74</v>
       </c>
-      <c r="U59" s="17">
+      <c r="U59" s="11">
         <v>768</v>
       </c>
-      <c r="V59" s="17">
+      <c r="V59" s="11">
         <v>694</v>
       </c>
       <c r="W59" s="1">
         <f t="shared" si="21"/>
         <v>8</v>
       </c>
-      <c r="X59" s="17">
+      <c r="X59" s="11">
         <v>103</v>
       </c>
-      <c r="Y59" s="17">
+      <c r="Y59" s="11">
         <v>95</v>
       </c>
       <c r="Z59" s="1">
         <f t="shared" si="22"/>
         <v>174</v>
       </c>
-      <c r="AA59" s="21">
+      <c r="AA59" s="14">
         <v>1129</v>
       </c>
-      <c r="AB59" s="20">
+      <c r="AB59" s="13">
         <v>955</v>
       </c>
       <c r="AC59" s="1">
         <f t="shared" si="23"/>
         <v>79</v>
       </c>
-      <c r="AD59" s="20">
+      <c r="AD59" s="13">
         <v>875</v>
       </c>
-      <c r="AE59" s="18">
+      <c r="AE59" s="12">
         <v>796</v>
       </c>
       <c r="AF59" s="1">
         <f t="shared" si="24"/>
         <v>-27</v>
       </c>
-      <c r="AG59" s="21">
+      <c r="AG59" s="14">
         <v>4800</v>
       </c>
-      <c r="AH59" s="21">
+      <c r="AH59" s="14">
         <v>4827</v>
       </c>
       <c r="AI59" s="1">
         <f t="shared" si="25"/>
         <v>661</v>
       </c>
-      <c r="AJ59" s="21">
+      <c r="AJ59" s="14">
         <v>3619</v>
       </c>
-      <c r="AK59" s="21">
+      <c r="AK59" s="14">
         <v>2958</v>
       </c>
       <c r="AL59" s="1">
         <f t="shared" si="26"/>
         <v>44</v>
       </c>
-      <c r="AM59" s="18">
+      <c r="AM59" s="12">
         <v>274</v>
       </c>
-      <c r="AN59" s="20">
+      <c r="AN59" s="13">
         <v>230</v>
       </c>
       <c r="AO59" s="1">
         <f t="shared" si="27"/>
         <v>30</v>
       </c>
-      <c r="AP59" s="18">
+      <c r="AP59" s="12">
         <v>675</v>
       </c>
-      <c r="AQ59" s="20">
+      <c r="AQ59" s="13">
         <v>645</v>
       </c>
       <c r="AR59" s="1">
         <f t="shared" si="28"/>
         <v>11</v>
       </c>
-      <c r="AS59" s="20">
+      <c r="AS59" s="13">
         <v>158</v>
       </c>
-      <c r="AT59" s="20">
+      <c r="AT59" s="13">
         <v>147</v>
       </c>
       <c r="AU59" s="1">
         <f t="shared" si="29"/>
         <v>-6</v>
       </c>
-      <c r="AV59" s="20">
+      <c r="AV59" s="13">
         <v>65</v>
       </c>
-      <c r="AW59" s="20">
+      <c r="AW59" s="13">
         <v>71</v>
       </c>
       <c r="AX59" s="1">
         <f t="shared" si="30"/>
         <v>-12</v>
       </c>
-      <c r="AY59" s="20">
+      <c r="AY59" s="13">
         <v>10</v>
       </c>
-      <c r="AZ59" s="20">
+      <c r="AZ59" s="13">
         <v>22</v>
       </c>
       <c r="BA59" s="1">
@@ -4772,7 +4755,7 @@
       </c>
     </row>
     <row r="60" spans="1:84" x14ac:dyDescent="0.55000000000000004">
-      <c r="A60" s="19">
+      <c r="A60" s="9">
         <f t="shared" si="13"/>
         <v>1889</v>
       </c>
@@ -4780,170 +4763,170 @@
         <f t="shared" si="14"/>
         <v>17395</v>
       </c>
-      <c r="C60" s="17">
+      <c r="C60" s="11">
         <v>923112</v>
       </c>
-      <c r="D60" s="17">
+      <c r="D60" s="11">
         <v>905717</v>
       </c>
       <c r="E60" s="1">
         <f t="shared" si="15"/>
         <v>16643</v>
       </c>
-      <c r="F60" s="17">
+      <c r="F60" s="11">
         <v>324485</v>
       </c>
-      <c r="G60" s="17">
+      <c r="G60" s="11">
         <v>307842</v>
       </c>
       <c r="H60" s="1">
         <f t="shared" si="16"/>
         <v>400</v>
       </c>
-      <c r="I60" s="17">
+      <c r="I60" s="11">
         <v>4554</v>
       </c>
-      <c r="J60" s="17">
+      <c r="J60" s="11">
         <v>4154</v>
       </c>
       <c r="K60" s="1">
         <f t="shared" si="17"/>
         <v>1075</v>
       </c>
-      <c r="L60" s="17">
+      <c r="L60" s="11">
         <v>4781</v>
       </c>
-      <c r="M60" s="17">
+      <c r="M60" s="11">
         <v>3706</v>
       </c>
       <c r="N60" s="1">
         <f t="shared" si="18"/>
         <v>920</v>
       </c>
-      <c r="O60" s="17">
+      <c r="O60" s="11">
         <v>2503</v>
       </c>
-      <c r="P60" s="17">
+      <c r="P60" s="11">
         <v>1583</v>
       </c>
       <c r="Q60" s="1">
         <f t="shared" si="19"/>
         <v>252</v>
       </c>
-      <c r="R60" s="17">
+      <c r="R60" s="11">
         <v>1836</v>
       </c>
-      <c r="S60" s="17">
+      <c r="S60" s="11">
         <v>1584</v>
       </c>
       <c r="T60" s="1">
         <f t="shared" si="20"/>
         <v>-52</v>
       </c>
-      <c r="U60" s="17">
+      <c r="U60" s="11">
         <v>1219</v>
       </c>
-      <c r="V60" s="17">
+      <c r="V60" s="11">
         <v>1271</v>
       </c>
       <c r="W60" s="1">
         <f t="shared" si="21"/>
         <v>30</v>
       </c>
-      <c r="X60" s="17">
+      <c r="X60" s="11">
         <v>310</v>
       </c>
-      <c r="Y60" s="17">
+      <c r="Y60" s="11">
         <v>280</v>
       </c>
       <c r="Z60" s="1">
         <f t="shared" si="22"/>
         <v>-25</v>
       </c>
-      <c r="AA60" s="21">
+      <c r="AA60" s="14">
         <v>1849</v>
       </c>
-      <c r="AB60" s="21">
+      <c r="AB60" s="14">
         <v>1874</v>
       </c>
       <c r="AC60" s="1">
         <f t="shared" si="23"/>
         <v>4</v>
       </c>
-      <c r="AD60" s="20">
+      <c r="AD60" s="13">
         <v>948</v>
       </c>
-      <c r="AE60" s="18">
+      <c r="AE60" s="12">
         <v>944</v>
       </c>
       <c r="AF60" s="1">
         <f t="shared" si="24"/>
         <v>335</v>
       </c>
-      <c r="AG60" s="21">
+      <c r="AG60" s="14">
         <v>7620</v>
       </c>
-      <c r="AH60" s="21">
+      <c r="AH60" s="14">
         <v>7285</v>
       </c>
       <c r="AI60" s="1">
         <f t="shared" si="25"/>
         <v>296</v>
       </c>
-      <c r="AJ60" s="21">
+      <c r="AJ60" s="14">
         <v>3620</v>
       </c>
-      <c r="AK60" s="21">
+      <c r="AK60" s="14">
         <v>3324</v>
       </c>
       <c r="AL60" s="1">
         <f t="shared" si="26"/>
         <v>-9</v>
       </c>
-      <c r="AM60" s="18">
+      <c r="AM60" s="12">
         <v>607</v>
       </c>
-      <c r="AN60" s="20">
+      <c r="AN60" s="13">
         <v>616</v>
       </c>
       <c r="AO60" s="1">
         <f t="shared" si="27"/>
         <v>162</v>
       </c>
-      <c r="AP60" s="17">
+      <c r="AP60" s="11">
         <v>1292</v>
       </c>
-      <c r="AQ60" s="21">
+      <c r="AQ60" s="14">
         <v>1130</v>
       </c>
       <c r="AR60" s="1">
         <f t="shared" si="28"/>
         <v>-11</v>
       </c>
-      <c r="AS60" s="20">
+      <c r="AS60" s="13">
         <v>228</v>
       </c>
-      <c r="AT60" s="20">
+      <c r="AT60" s="13">
         <v>239</v>
       </c>
       <c r="AU60" s="1">
         <f t="shared" si="29"/>
         <v>36</v>
       </c>
-      <c r="AV60" s="20">
+      <c r="AV60" s="13">
         <v>115</v>
       </c>
-      <c r="AW60" s="20">
+      <c r="AW60" s="13">
         <v>79</v>
       </c>
       <c r="AX60" s="1">
         <f t="shared" si="30"/>
         <v>12</v>
       </c>
-      <c r="AY60" s="20">
+      <c r="AY60" s="13">
         <v>41</v>
       </c>
-      <c r="AZ60" s="20">
+      <c r="AZ60" s="13">
         <v>29</v>
       </c>
       <c r="BA60" s="1">
@@ -5053,7 +5036,7 @@
       </c>
     </row>
     <row r="61" spans="1:84" x14ac:dyDescent="0.55000000000000004">
-      <c r="A61" s="19">
+      <c r="A61" s="9">
         <f t="shared" si="13"/>
         <v>1890</v>
       </c>
@@ -5061,170 +5044,170 @@
         <f t="shared" si="14"/>
         <v>32800</v>
       </c>
-      <c r="C61" s="17">
+      <c r="C61" s="11">
         <v>1265126</v>
       </c>
-      <c r="D61" s="17">
+      <c r="D61" s="11">
         <v>1232326</v>
       </c>
       <c r="E61" s="1">
         <f t="shared" si="15"/>
         <v>15833</v>
       </c>
-      <c r="F61" s="17">
+      <c r="F61" s="11">
         <v>329920</v>
       </c>
-      <c r="G61" s="17">
+      <c r="G61" s="11">
         <v>314087</v>
       </c>
       <c r="H61" s="1">
         <f t="shared" si="16"/>
         <v>1581</v>
       </c>
-      <c r="I61" s="17">
+      <c r="I61" s="11">
         <v>7043</v>
       </c>
-      <c r="J61" s="17">
+      <c r="J61" s="11">
         <v>5462</v>
       </c>
       <c r="K61" s="1">
         <f t="shared" si="17"/>
         <v>868</v>
       </c>
-      <c r="L61" s="17">
+      <c r="L61" s="11">
         <v>5555</v>
       </c>
-      <c r="M61" s="17">
+      <c r="M61" s="11">
         <v>4687</v>
       </c>
       <c r="N61" s="1">
         <f t="shared" si="18"/>
         <v>290</v>
       </c>
-      <c r="O61" s="17">
+      <c r="O61" s="11">
         <v>3131</v>
       </c>
-      <c r="P61" s="17">
+      <c r="P61" s="11">
         <v>2841</v>
       </c>
       <c r="Q61" s="1">
         <f t="shared" si="19"/>
         <v>446</v>
       </c>
-      <c r="R61" s="17">
+      <c r="R61" s="11">
         <v>2462</v>
       </c>
-      <c r="S61" s="17">
+      <c r="S61" s="11">
         <v>2016</v>
       </c>
       <c r="T61" s="1">
         <f t="shared" si="20"/>
         <v>113</v>
       </c>
-      <c r="U61" s="17">
+      <c r="U61" s="11">
         <v>2876</v>
       </c>
-      <c r="V61" s="17">
+      <c r="V61" s="11">
         <v>2763</v>
       </c>
       <c r="W61" s="1">
         <f t="shared" si="21"/>
         <v>12</v>
       </c>
-      <c r="X61" s="17">
+      <c r="X61" s="11">
         <v>404</v>
       </c>
-      <c r="Y61" s="17">
+      <c r="Y61" s="11">
         <v>392</v>
       </c>
       <c r="Z61" s="1">
         <f t="shared" si="22"/>
         <v>1378</v>
       </c>
-      <c r="AA61" s="21">
+      <c r="AA61" s="14">
         <v>3505</v>
       </c>
-      <c r="AB61" s="21">
+      <c r="AB61" s="14">
         <v>2127</v>
       </c>
       <c r="AC61" s="1">
         <f t="shared" si="23"/>
         <v>9</v>
       </c>
-      <c r="AD61" s="20">
+      <c r="AD61" s="13">
         <v>813</v>
       </c>
-      <c r="AE61" s="18">
+      <c r="AE61" s="12">
         <v>804</v>
       </c>
       <c r="AF61" s="1">
         <f t="shared" si="24"/>
         <v>612</v>
       </c>
-      <c r="AG61" s="21">
+      <c r="AG61" s="14">
         <v>6387</v>
       </c>
-      <c r="AH61" s="21">
+      <c r="AH61" s="14">
         <v>5775</v>
       </c>
       <c r="AI61" s="1">
         <f t="shared" si="25"/>
         <v>426</v>
       </c>
-      <c r="AJ61" s="21">
+      <c r="AJ61" s="14">
         <v>4038</v>
       </c>
-      <c r="AK61" s="21">
+      <c r="AK61" s="14">
         <v>3612</v>
       </c>
       <c r="AL61" s="1">
         <f t="shared" si="26"/>
         <v>21</v>
       </c>
-      <c r="AM61" s="18">
+      <c r="AM61" s="12">
         <v>659</v>
       </c>
-      <c r="AN61" s="20">
+      <c r="AN61" s="13">
         <v>638</v>
       </c>
       <c r="AO61" s="1">
         <f t="shared" si="27"/>
         <v>291</v>
       </c>
-      <c r="AP61" s="17">
+      <c r="AP61" s="11">
         <v>1413</v>
       </c>
-      <c r="AQ61" s="21">
+      <c r="AQ61" s="14">
         <v>1122</v>
       </c>
       <c r="AR61" s="1">
         <f t="shared" si="28"/>
         <v>-34</v>
       </c>
-      <c r="AS61" s="20">
+      <c r="AS61" s="13">
         <v>297</v>
       </c>
-      <c r="AT61" s="20">
+      <c r="AT61" s="13">
         <v>331</v>
       </c>
       <c r="AU61" s="1">
         <f t="shared" si="29"/>
         <v>25</v>
       </c>
-      <c r="AV61" s="20">
+      <c r="AV61" s="13">
         <v>147</v>
       </c>
-      <c r="AW61" s="20">
+      <c r="AW61" s="13">
         <v>122</v>
       </c>
       <c r="AX61" s="1">
         <f t="shared" si="30"/>
         <v>-24</v>
       </c>
-      <c r="AY61" s="20">
+      <c r="AY61" s="13">
         <v>268</v>
       </c>
-      <c r="AZ61" s="20">
+      <c r="AZ61" s="13">
         <v>292</v>
       </c>
       <c r="BA61" s="1">
@@ -5334,7 +5317,7 @@
       </c>
     </row>
     <row r="62" spans="1:84" x14ac:dyDescent="0.55000000000000004">
-      <c r="A62" s="19">
+      <c r="A62" s="9">
         <f t="shared" si="13"/>
         <v>1891</v>
       </c>
@@ -5342,170 +5325,170 @@
         <f t="shared" si="14"/>
         <v>-11339</v>
       </c>
-      <c r="C62" s="17">
+      <c r="C62" s="11">
         <v>1484237</v>
       </c>
-      <c r="D62" s="17">
+      <c r="D62" s="11">
         <v>1495576</v>
       </c>
       <c r="E62" s="1">
         <f t="shared" si="15"/>
         <v>19882</v>
       </c>
-      <c r="F62" s="17">
+      <c r="F62" s="11">
         <v>292278</v>
       </c>
-      <c r="G62" s="17">
+      <c r="G62" s="11">
         <v>272396</v>
       </c>
       <c r="H62" s="1">
         <f t="shared" si="16"/>
         <v>-526</v>
       </c>
-      <c r="I62" s="17">
+      <c r="I62" s="11">
         <v>5983</v>
       </c>
-      <c r="J62" s="17">
+      <c r="J62" s="11">
         <v>6509</v>
       </c>
       <c r="K62" s="1">
         <f t="shared" si="17"/>
         <v>851</v>
       </c>
-      <c r="L62" s="17">
+      <c r="L62" s="11">
         <v>4909</v>
       </c>
-      <c r="M62" s="17">
+      <c r="M62" s="11">
         <v>4058</v>
       </c>
       <c r="N62" s="1">
         <f t="shared" si="18"/>
         <v>581</v>
       </c>
-      <c r="O62" s="17">
+      <c r="O62" s="11">
         <v>3011</v>
       </c>
-      <c r="P62" s="17">
+      <c r="P62" s="11">
         <v>2430</v>
       </c>
       <c r="Q62" s="1">
         <f t="shared" si="19"/>
         <v>39</v>
       </c>
-      <c r="R62" s="17">
+      <c r="R62" s="11">
         <v>2027</v>
       </c>
-      <c r="S62" s="17">
+      <c r="S62" s="11">
         <v>1988</v>
       </c>
       <c r="T62" s="1">
         <f t="shared" si="20"/>
         <v>-98</v>
       </c>
-      <c r="U62" s="17">
+      <c r="U62" s="11">
         <v>1802</v>
       </c>
-      <c r="V62" s="17">
+      <c r="V62" s="11">
         <v>1900</v>
       </c>
       <c r="W62" s="1">
         <f t="shared" si="21"/>
         <v>-2</v>
       </c>
-      <c r="X62" s="17">
+      <c r="X62" s="11">
         <v>318</v>
       </c>
-      <c r="Y62" s="17">
+      <c r="Y62" s="11">
         <v>320</v>
       </c>
       <c r="Z62" s="1">
         <f t="shared" si="22"/>
         <v>879</v>
       </c>
-      <c r="AA62" s="21">
+      <c r="AA62" s="14">
         <v>2937</v>
       </c>
-      <c r="AB62" s="21">
+      <c r="AB62" s="14">
         <v>2058</v>
       </c>
       <c r="AC62" s="1">
         <f t="shared" si="23"/>
         <v>100</v>
       </c>
-      <c r="AD62" s="20">
+      <c r="AD62" s="13">
         <v>885</v>
       </c>
-      <c r="AE62" s="18">
+      <c r="AE62" s="12">
         <v>785</v>
       </c>
       <c r="AF62" s="1">
         <f t="shared" si="24"/>
         <v>-275</v>
       </c>
-      <c r="AG62" s="20">
+      <c r="AG62" s="13">
         <v>5609</v>
       </c>
-      <c r="AH62" s="21">
+      <c r="AH62" s="14">
         <v>5884</v>
       </c>
       <c r="AI62" s="1">
         <f t="shared" si="25"/>
         <v>201</v>
       </c>
-      <c r="AJ62" s="21">
+      <c r="AJ62" s="14">
         <v>4052</v>
       </c>
-      <c r="AK62" s="21">
+      <c r="AK62" s="14">
         <v>3851</v>
       </c>
       <c r="AL62" s="1">
         <f t="shared" si="26"/>
         <v>85</v>
       </c>
-      <c r="AM62" s="18">
+      <c r="AM62" s="12">
         <v>695</v>
       </c>
-      <c r="AN62" s="20">
+      <c r="AN62" s="13">
         <v>610</v>
       </c>
       <c r="AO62" s="1">
         <f t="shared" si="27"/>
         <v>240</v>
       </c>
-      <c r="AP62" s="17">
+      <c r="AP62" s="11">
         <v>1454</v>
       </c>
-      <c r="AQ62" s="21">
+      <c r="AQ62" s="14">
         <v>1214</v>
       </c>
       <c r="AR62" s="1">
         <f t="shared" si="28"/>
         <v>31</v>
       </c>
-      <c r="AS62" s="20">
+      <c r="AS62" s="13">
         <v>232</v>
       </c>
-      <c r="AT62" s="20">
+      <c r="AT62" s="13">
         <v>201</v>
       </c>
       <c r="AU62" s="1">
         <f t="shared" si="29"/>
         <v>-2</v>
       </c>
-      <c r="AV62" s="20">
+      <c r="AV62" s="13">
         <v>160</v>
       </c>
-      <c r="AW62" s="20">
+      <c r="AW62" s="13">
         <v>162</v>
       </c>
       <c r="AX62" s="1">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="AY62" s="20">
+      <c r="AY62" s="13">
         <v>17</v>
       </c>
-      <c r="AZ62" s="20">
+      <c r="AZ62" s="13">
         <v>17</v>
       </c>
       <c r="BA62" s="1">
@@ -5615,7 +5598,7 @@
       </c>
     </row>
     <row r="63" spans="1:84" x14ac:dyDescent="0.55000000000000004">
-      <c r="A63" s="19">
+      <c r="A63" s="9">
         <f t="shared" si="13"/>
         <v>1892</v>
       </c>
@@ -5623,170 +5606,170 @@
         <f t="shared" si="14"/>
         <v>3616</v>
       </c>
-      <c r="C63" s="17">
+      <c r="C63" s="11">
         <v>875237</v>
       </c>
-      <c r="D63" s="17">
+      <c r="D63" s="11">
         <v>871621</v>
       </c>
       <c r="E63" s="1">
         <f t="shared" si="15"/>
         <v>9892</v>
       </c>
-      <c r="F63" s="17">
+      <c r="F63" s="11">
         <v>210869</v>
       </c>
-      <c r="G63" s="17">
+      <c r="G63" s="11">
         <v>200977</v>
       </c>
       <c r="H63" s="1">
         <f t="shared" si="16"/>
         <v>-999</v>
       </c>
-      <c r="I63" s="17">
+      <c r="I63" s="11">
         <v>5420</v>
       </c>
-      <c r="J63" s="17">
+      <c r="J63" s="11">
         <v>6419</v>
       </c>
       <c r="K63" s="1">
         <f t="shared" si="17"/>
         <v>416</v>
       </c>
-      <c r="L63" s="17">
+      <c r="L63" s="11">
         <v>4185</v>
       </c>
-      <c r="M63" s="17">
+      <c r="M63" s="11">
         <v>3769</v>
       </c>
       <c r="N63" s="1">
         <f t="shared" si="18"/>
         <v>224</v>
       </c>
-      <c r="O63" s="17">
+      <c r="O63" s="11">
         <v>2714</v>
       </c>
-      <c r="P63" s="17">
+      <c r="P63" s="11">
         <v>2490</v>
       </c>
       <c r="Q63" s="1">
         <f t="shared" si="19"/>
         <v>-391</v>
       </c>
-      <c r="R63" s="17">
+      <c r="R63" s="11">
         <v>1699</v>
       </c>
-      <c r="S63" s="17">
+      <c r="S63" s="11">
         <v>2090</v>
       </c>
       <c r="T63" s="1">
         <f t="shared" si="20"/>
         <v>-9</v>
       </c>
-      <c r="U63" s="17">
+      <c r="U63" s="11">
         <v>1883</v>
       </c>
-      <c r="V63" s="17">
+      <c r="V63" s="11">
         <v>1892</v>
       </c>
       <c r="W63" s="1">
         <f t="shared" si="21"/>
         <v>17</v>
       </c>
-      <c r="X63" s="17">
+      <c r="X63" s="11">
         <v>308</v>
       </c>
-      <c r="Y63" s="17">
+      <c r="Y63" s="11">
         <v>291</v>
       </c>
       <c r="Z63" s="1">
         <f t="shared" si="22"/>
         <v>899</v>
       </c>
-      <c r="AA63" s="21">
+      <c r="AA63" s="14">
         <v>2723</v>
       </c>
-      <c r="AB63" s="21">
+      <c r="AB63" s="14">
         <v>1824</v>
       </c>
       <c r="AC63" s="1">
         <f t="shared" si="23"/>
         <v>101</v>
       </c>
-      <c r="AD63" s="20">
+      <c r="AD63" s="13">
         <v>949</v>
       </c>
-      <c r="AE63" s="18">
+      <c r="AE63" s="12">
         <v>848</v>
       </c>
       <c r="AF63" s="1">
         <f t="shared" si="24"/>
         <v>-287</v>
       </c>
-      <c r="AG63" s="20">
+      <c r="AG63" s="13">
         <v>3294</v>
       </c>
-      <c r="AH63" s="21">
+      <c r="AH63" s="14">
         <v>3581</v>
       </c>
       <c r="AI63" s="1">
         <f t="shared" si="25"/>
         <v>214</v>
       </c>
-      <c r="AJ63" s="21">
+      <c r="AJ63" s="14">
         <v>2934</v>
       </c>
-      <c r="AK63" s="21">
+      <c r="AK63" s="14">
         <v>2720</v>
       </c>
       <c r="AL63" s="1">
         <f t="shared" si="26"/>
         <v>118</v>
       </c>
-      <c r="AM63" s="18">
+      <c r="AM63" s="12">
         <v>495</v>
       </c>
-      <c r="AN63" s="20">
+      <c r="AN63" s="13">
         <v>377</v>
       </c>
       <c r="AO63" s="1">
         <f t="shared" si="27"/>
         <v>199</v>
       </c>
-      <c r="AP63" s="17">
+      <c r="AP63" s="11">
         <v>1449</v>
       </c>
-      <c r="AQ63" s="21">
+      <c r="AQ63" s="14">
         <v>1250</v>
       </c>
       <c r="AR63" s="1">
         <f t="shared" si="28"/>
         <v>10</v>
       </c>
-      <c r="AS63" s="20">
+      <c r="AS63" s="13">
         <v>218</v>
       </c>
-      <c r="AT63" s="20">
+      <c r="AT63" s="13">
         <v>208</v>
       </c>
       <c r="AU63" s="1">
         <f t="shared" si="29"/>
         <v>14</v>
       </c>
-      <c r="AV63" s="20">
+      <c r="AV63" s="13">
         <v>160</v>
       </c>
-      <c r="AW63" s="20">
+      <c r="AW63" s="13">
         <v>146</v>
       </c>
       <c r="AX63" s="1">
         <f t="shared" si="30"/>
         <v>34</v>
       </c>
-      <c r="AY63" s="20">
+      <c r="AY63" s="13">
         <v>47</v>
       </c>
-      <c r="AZ63" s="20">
+      <c r="AZ63" s="13">
         <v>13</v>
       </c>
       <c r="BA63" s="1">
@@ -5896,7 +5879,7 @@
       </c>
     </row>
     <row r="64" spans="1:84" x14ac:dyDescent="0.55000000000000004">
-      <c r="A64" s="19">
+      <c r="A64" s="9">
         <f t="shared" si="13"/>
         <v>1893</v>
       </c>
@@ -5904,170 +5887,170 @@
         <f t="shared" si="14"/>
         <v>26811</v>
       </c>
-      <c r="C64" s="17">
+      <c r="C64" s="11">
         <v>1018183</v>
       </c>
-      <c r="D64" s="17">
+      <c r="D64" s="11">
         <v>991372</v>
       </c>
       <c r="E64" s="1">
         <f t="shared" si="15"/>
         <v>3749</v>
       </c>
-      <c r="F64" s="17">
+      <c r="F64" s="11">
         <v>222653</v>
       </c>
-      <c r="G64" s="17">
+      <c r="G64" s="11">
         <v>218904</v>
       </c>
       <c r="H64" s="1">
         <f t="shared" si="16"/>
         <v>-127</v>
       </c>
-      <c r="I64" s="17">
+      <c r="I64" s="11">
         <v>5300</v>
       </c>
-      <c r="J64" s="17">
+      <c r="J64" s="11">
         <v>5427</v>
       </c>
       <c r="K64" s="1">
         <f t="shared" si="17"/>
         <v>1811</v>
       </c>
-      <c r="L64" s="17">
+      <c r="L64" s="11">
         <v>5301</v>
       </c>
-      <c r="M64" s="17">
+      <c r="M64" s="11">
         <v>3490</v>
       </c>
       <c r="N64" s="1">
         <f t="shared" si="18"/>
         <v>284</v>
       </c>
-      <c r="O64" s="17">
+      <c r="O64" s="11">
         <v>2209</v>
       </c>
-      <c r="P64" s="17">
+      <c r="P64" s="11">
         <v>1925</v>
       </c>
       <c r="Q64" s="1">
         <f t="shared" si="19"/>
         <v>76</v>
       </c>
-      <c r="R64" s="17">
+      <c r="R64" s="11">
         <v>1714</v>
       </c>
-      <c r="S64" s="17">
+      <c r="S64" s="11">
         <v>1638</v>
       </c>
       <c r="T64" s="1">
         <f t="shared" si="20"/>
         <v>699</v>
       </c>
-      <c r="U64" s="17">
+      <c r="U64" s="11">
         <v>2705</v>
       </c>
-      <c r="V64" s="17">
+      <c r="V64" s="11">
         <v>2006</v>
       </c>
       <c r="W64" s="1">
         <f t="shared" si="21"/>
         <v>69</v>
       </c>
-      <c r="X64" s="17">
+      <c r="X64" s="11">
         <v>285</v>
       </c>
-      <c r="Y64" s="17">
+      <c r="Y64" s="11">
         <v>216</v>
       </c>
       <c r="Z64" s="1">
         <f t="shared" si="22"/>
         <v>351</v>
       </c>
-      <c r="AA64" s="21">
+      <c r="AA64" s="14">
         <v>2210</v>
       </c>
-      <c r="AB64" s="21">
+      <c r="AB64" s="14">
         <v>1859</v>
       </c>
       <c r="AC64" s="1">
         <f t="shared" si="23"/>
         <v>178</v>
       </c>
-      <c r="AD64" s="21">
+      <c r="AD64" s="14">
         <v>1039</v>
       </c>
-      <c r="AE64" s="18">
+      <c r="AE64" s="12">
         <v>861</v>
       </c>
       <c r="AF64" s="1">
         <f t="shared" si="24"/>
         <v>69</v>
       </c>
-      <c r="AG64" s="21">
+      <c r="AG64" s="14">
         <v>3159</v>
       </c>
-      <c r="AH64" s="21">
+      <c r="AH64" s="14">
         <v>3090</v>
       </c>
       <c r="AI64" s="1">
         <f t="shared" si="25"/>
         <v>4</v>
       </c>
-      <c r="AJ64" s="21">
+      <c r="AJ64" s="14">
         <v>3210</v>
       </c>
-      <c r="AK64" s="21">
+      <c r="AK64" s="14">
         <v>3206</v>
       </c>
       <c r="AL64" s="1">
         <f t="shared" si="26"/>
         <v>-31</v>
       </c>
-      <c r="AM64" s="18">
+      <c r="AM64" s="12">
         <v>514</v>
       </c>
-      <c r="AN64" s="20">
+      <c r="AN64" s="13">
         <v>545</v>
       </c>
       <c r="AO64" s="1">
         <f t="shared" si="27"/>
         <v>275</v>
       </c>
-      <c r="AP64" s="17">
+      <c r="AP64" s="11">
         <v>1199</v>
       </c>
-      <c r="AQ64" s="20">
+      <c r="AQ64" s="13">
         <v>924</v>
       </c>
       <c r="AR64" s="1">
         <f t="shared" si="28"/>
         <v>29</v>
       </c>
-      <c r="AS64" s="20">
+      <c r="AS64" s="13">
         <v>245</v>
       </c>
-      <c r="AT64" s="20">
+      <c r="AT64" s="13">
         <v>216</v>
       </c>
       <c r="AU64" s="1">
         <f t="shared" si="29"/>
         <v>-32</v>
       </c>
-      <c r="AV64" s="20">
+      <c r="AV64" s="13">
         <v>144</v>
       </c>
-      <c r="AW64" s="20">
+      <c r="AW64" s="13">
         <v>176</v>
       </c>
       <c r="AX64" s="1">
         <f t="shared" si="30"/>
         <v>-3</v>
       </c>
-      <c r="AY64" s="20">
+      <c r="AY64" s="13">
         <v>33</v>
       </c>
-      <c r="AZ64" s="20">
+      <c r="AZ64" s="13">
         <v>36</v>
       </c>
       <c r="BA64" s="1">
@@ -6177,7 +6160,7 @@
       </c>
     </row>
     <row r="65" spans="1:84" x14ac:dyDescent="0.55000000000000004">
-      <c r="A65" s="19">
+      <c r="A65" s="9">
         <f t="shared" si="13"/>
         <v>1894</v>
       </c>
@@ -6185,170 +6168,170 @@
         <f t="shared" si="14"/>
         <v>5875</v>
       </c>
-      <c r="C65" s="17">
+      <c r="C65" s="11">
         <v>922021</v>
       </c>
-      <c r="D65" s="17">
+      <c r="D65" s="11">
         <v>916146</v>
       </c>
       <c r="E65" s="1">
         <f t="shared" si="15"/>
         <v>5078</v>
       </c>
-      <c r="F65" s="17">
+      <c r="F65" s="11">
         <v>231955</v>
       </c>
-      <c r="G65" s="17">
+      <c r="G65" s="11">
         <v>226877</v>
       </c>
       <c r="H65" s="1">
         <f t="shared" si="16"/>
         <v>-1092</v>
       </c>
-      <c r="I65" s="17">
+      <c r="I65" s="11">
         <v>6794</v>
       </c>
-      <c r="J65" s="17">
+      <c r="J65" s="11">
         <v>7886</v>
       </c>
       <c r="K65" s="1">
         <f t="shared" si="17"/>
         <v>871</v>
       </c>
-      <c r="L65" s="17">
+      <c r="L65" s="11">
         <v>4533</v>
       </c>
-      <c r="M65" s="17">
+      <c r="M65" s="11">
         <v>3662</v>
       </c>
       <c r="N65" s="1">
         <f t="shared" si="18"/>
         <v>430</v>
       </c>
-      <c r="O65" s="17">
+      <c r="O65" s="11">
         <v>3067</v>
       </c>
-      <c r="P65" s="17">
+      <c r="P65" s="11">
         <v>2637</v>
       </c>
       <c r="Q65" s="1">
         <f t="shared" si="19"/>
         <v>-10</v>
       </c>
-      <c r="R65" s="17">
+      <c r="R65" s="11">
         <v>2332</v>
       </c>
-      <c r="S65" s="17">
+      <c r="S65" s="11">
         <v>2342</v>
       </c>
       <c r="T65" s="1">
         <f t="shared" si="20"/>
         <v>-314</v>
       </c>
-      <c r="U65" s="17">
+      <c r="U65" s="11">
         <v>2000</v>
       </c>
-      <c r="V65" s="17">
+      <c r="V65" s="11">
         <v>2314</v>
       </c>
       <c r="W65" s="1">
         <f t="shared" si="21"/>
         <v>40</v>
       </c>
-      <c r="X65" s="17">
+      <c r="X65" s="11">
         <v>437</v>
       </c>
-      <c r="Y65" s="17">
+      <c r="Y65" s="11">
         <v>397</v>
       </c>
       <c r="Z65" s="1">
         <f t="shared" si="22"/>
         <v>1153</v>
       </c>
-      <c r="AA65" s="21">
+      <c r="AA65" s="14">
         <v>3309</v>
       </c>
-      <c r="AB65" s="21">
+      <c r="AB65" s="14">
         <v>2156</v>
       </c>
       <c r="AC65" s="1">
         <f t="shared" si="23"/>
         <v>103</v>
       </c>
-      <c r="AD65" s="21">
+      <c r="AD65" s="14">
         <v>1219</v>
       </c>
-      <c r="AE65" s="17">
+      <c r="AE65" s="11">
         <v>1116</v>
       </c>
       <c r="AF65" s="1">
         <f t="shared" si="24"/>
         <v>385</v>
       </c>
-      <c r="AG65" s="21">
+      <c r="AG65" s="14">
         <v>6048</v>
       </c>
-      <c r="AH65" s="21">
+      <c r="AH65" s="14">
         <v>5663</v>
       </c>
       <c r="AI65" s="1">
         <f t="shared" si="25"/>
         <v>398</v>
       </c>
-      <c r="AJ65" s="21">
+      <c r="AJ65" s="14">
         <v>3319</v>
       </c>
-      <c r="AK65" s="21">
+      <c r="AK65" s="14">
         <v>2921</v>
       </c>
       <c r="AL65" s="1">
         <f t="shared" si="26"/>
         <v>99</v>
       </c>
-      <c r="AM65" s="18">
+      <c r="AM65" s="12">
         <v>498</v>
       </c>
-      <c r="AN65" s="20">
+      <c r="AN65" s="13">
         <v>399</v>
       </c>
       <c r="AO65" s="1">
         <f t="shared" si="27"/>
         <v>390</v>
       </c>
-      <c r="AP65" s="17">
+      <c r="AP65" s="11">
         <v>1708</v>
       </c>
-      <c r="AQ65" s="21">
+      <c r="AQ65" s="14">
         <v>1318</v>
       </c>
       <c r="AR65" s="1">
         <f t="shared" si="28"/>
         <v>-4</v>
       </c>
-      <c r="AS65" s="20">
+      <c r="AS65" s="13">
         <v>168</v>
       </c>
-      <c r="AT65" s="20">
+      <c r="AT65" s="13">
         <v>172</v>
       </c>
       <c r="AU65" s="1">
         <f t="shared" si="29"/>
         <v>52</v>
       </c>
-      <c r="AV65" s="20">
+      <c r="AV65" s="13">
         <v>225</v>
       </c>
-      <c r="AW65" s="20">
+      <c r="AW65" s="13">
         <v>173</v>
       </c>
       <c r="AX65" s="1">
         <f t="shared" si="30"/>
         <v>25</v>
       </c>
-      <c r="AY65" s="20">
+      <c r="AY65" s="13">
         <v>54</v>
       </c>
-      <c r="AZ65" s="20">
+      <c r="AZ65" s="13">
         <v>29</v>
       </c>
       <c r="BA65" s="1">
@@ -6458,7 +6441,7 @@
       </c>
     </row>
     <row r="66" spans="1:84" x14ac:dyDescent="0.55000000000000004">
-      <c r="A66" s="19">
+      <c r="A66" s="9">
         <f>A67-1</f>
         <v>1895</v>
       </c>
@@ -6466,170 +6449,170 @@
         <f t="shared" si="14"/>
         <v>-85110</v>
       </c>
-      <c r="C66" s="17">
+      <c r="C66" s="11">
         <v>1298867</v>
       </c>
-      <c r="D66" s="17">
+      <c r="D66" s="11">
         <v>1383977</v>
       </c>
       <c r="E66" s="1">
         <f t="shared" si="15"/>
         <v>15846</v>
       </c>
-      <c r="F66" s="17">
+      <c r="F66" s="11">
         <v>262943</v>
       </c>
-      <c r="G66" s="17">
+      <c r="G66" s="11">
         <v>247097</v>
       </c>
       <c r="H66" s="1">
         <f t="shared" si="16"/>
         <v>-144</v>
       </c>
-      <c r="I66" s="17">
+      <c r="I66" s="11">
         <v>6847</v>
       </c>
-      <c r="J66" s="17">
+      <c r="J66" s="11">
         <v>6991</v>
       </c>
       <c r="K66" s="1">
         <f t="shared" si="17"/>
         <v>1033</v>
       </c>
-      <c r="L66" s="17">
+      <c r="L66" s="11">
         <v>5411</v>
       </c>
-      <c r="M66" s="17">
+      <c r="M66" s="11">
         <v>4378</v>
       </c>
       <c r="N66" s="1">
         <f t="shared" si="18"/>
         <v>1080</v>
       </c>
-      <c r="O66" s="17">
+      <c r="O66" s="11">
         <v>2399</v>
       </c>
-      <c r="P66" s="17">
+      <c r="P66" s="11">
         <v>1319</v>
       </c>
       <c r="Q66" s="1">
         <f t="shared" si="19"/>
         <v>347</v>
       </c>
-      <c r="R66" s="17">
+      <c r="R66" s="11">
         <v>3273</v>
       </c>
-      <c r="S66" s="17">
+      <c r="S66" s="11">
         <v>2926</v>
       </c>
       <c r="T66" s="1">
         <f t="shared" si="20"/>
         <v>25</v>
       </c>
-      <c r="U66" s="17">
+      <c r="U66" s="11">
         <v>2327</v>
       </c>
-      <c r="V66" s="17">
+      <c r="V66" s="11">
         <v>2302</v>
       </c>
       <c r="W66" s="1">
         <f t="shared" si="21"/>
         <v>-57</v>
       </c>
-      <c r="X66" s="17">
+      <c r="X66" s="11">
         <v>434</v>
       </c>
-      <c r="Y66" s="17">
+      <c r="Y66" s="11">
         <v>491</v>
       </c>
       <c r="Z66" s="1">
         <f t="shared" si="22"/>
         <v>597</v>
       </c>
-      <c r="AA66" s="21">
+      <c r="AA66" s="14">
         <v>2201</v>
       </c>
-      <c r="AB66" s="21">
+      <c r="AB66" s="14">
         <v>1604</v>
       </c>
       <c r="AC66" s="1">
         <f t="shared" si="23"/>
         <v>8</v>
       </c>
-      <c r="AD66" s="21">
+      <c r="AD66" s="14">
         <v>1282</v>
       </c>
-      <c r="AE66" s="17">
+      <c r="AE66" s="11">
         <v>1274</v>
       </c>
       <c r="AF66" s="1">
         <f t="shared" si="24"/>
         <v>356</v>
       </c>
-      <c r="AG66" s="21">
+      <c r="AG66" s="14">
         <v>5761</v>
       </c>
-      <c r="AH66" s="20">
+      <c r="AH66" s="13">
         <v>5405</v>
       </c>
       <c r="AI66" s="1">
         <f t="shared" si="25"/>
         <v>107</v>
       </c>
-      <c r="AJ66" s="21">
+      <c r="AJ66" s="14">
         <v>3259</v>
       </c>
-      <c r="AK66" s="21">
+      <c r="AK66" s="14">
         <v>3152</v>
       </c>
       <c r="AL66" s="1">
         <f t="shared" si="26"/>
         <v>36</v>
       </c>
-      <c r="AM66" s="18">
+      <c r="AM66" s="12">
         <v>416</v>
       </c>
-      <c r="AN66" s="20">
+      <c r="AN66" s="13">
         <v>380</v>
       </c>
       <c r="AO66" s="1">
         <f t="shared" si="27"/>
         <v>204</v>
       </c>
-      <c r="AP66" s="17">
+      <c r="AP66" s="11">
         <v>1365</v>
       </c>
-      <c r="AQ66" s="21">
+      <c r="AQ66" s="14">
         <v>1161</v>
       </c>
       <c r="AR66" s="1">
         <f t="shared" si="28"/>
         <v>15</v>
       </c>
-      <c r="AS66" s="20">
+      <c r="AS66" s="13">
         <v>519</v>
       </c>
-      <c r="AT66" s="20">
+      <c r="AT66" s="13">
         <v>504</v>
       </c>
       <c r="AU66" s="1">
         <f t="shared" si="29"/>
         <v>22</v>
       </c>
-      <c r="AV66" s="20">
+      <c r="AV66" s="13">
         <v>150</v>
       </c>
-      <c r="AW66" s="20">
+      <c r="AW66" s="13">
         <v>128</v>
       </c>
       <c r="AX66" s="1">
         <f t="shared" si="30"/>
         <v>-4</v>
       </c>
-      <c r="AY66" s="20">
+      <c r="AY66" s="13">
         <v>50</v>
       </c>
-      <c r="AZ66" s="20">
+      <c r="AZ66" s="13">
         <v>54</v>
       </c>
       <c r="BA66" s="1">
@@ -6739,7 +6722,7 @@
       </c>
     </row>
     <row r="67" spans="1:84" x14ac:dyDescent="0.55000000000000004">
-      <c r="A67" s="11">
+      <c r="A67" s="9">
         <v>1896</v>
       </c>
       <c r="B67" s="1">
@@ -6986,10 +6969,10 @@
         <f t="shared" si="38"/>
         <v>12174</v>
       </c>
-      <c r="BW67" s="22">
+      <c r="BW67" s="1">
         <v>268727</v>
       </c>
-      <c r="BX67" s="22">
+      <c r="BX67" s="1">
         <v>256553</v>
       </c>
       <c r="BZ67" s="1">
@@ -7019,7 +7002,7 @@
       </c>
     </row>
     <row r="68" spans="1:84" x14ac:dyDescent="0.55000000000000004">
-      <c r="A68" s="11">
+      <c r="A68" s="9">
         <f>A67+1</f>
         <v>1897</v>
       </c>
@@ -7300,7 +7283,7 @@
       </c>
     </row>
     <row r="69" spans="1:84" x14ac:dyDescent="0.55000000000000004">
-      <c r="A69" s="11">
+      <c r="A69" s="9">
         <f t="shared" ref="A69:A86" si="67">A68+1</f>
         <v>1898</v>
       </c>
@@ -7581,7 +7564,7 @@
       </c>
     </row>
     <row r="70" spans="1:84" x14ac:dyDescent="0.55000000000000004">
-      <c r="A70" s="11">
+      <c r="A70" s="9">
         <f t="shared" si="67"/>
         <v>1899</v>
       </c>
@@ -7862,7 +7845,7 @@
       </c>
     </row>
     <row r="71" spans="1:84" x14ac:dyDescent="0.55000000000000004">
-      <c r="A71" s="11">
+      <c r="A71" s="9">
         <f t="shared" si="67"/>
         <v>1900</v>
       </c>
@@ -8143,7 +8126,7 @@
       </c>
     </row>
     <row r="72" spans="1:84" x14ac:dyDescent="0.55000000000000004">
-      <c r="A72" s="11">
+      <c r="A72" s="9">
         <f t="shared" si="67"/>
         <v>1901</v>
       </c>
@@ -8424,7 +8407,7 @@
       </c>
     </row>
     <row r="73" spans="1:84" x14ac:dyDescent="0.55000000000000004">
-      <c r="A73" s="11">
+      <c r="A73" s="9">
         <f t="shared" si="67"/>
         <v>1902</v>
       </c>
@@ -8705,7 +8688,7 @@
       </c>
     </row>
     <row r="74" spans="1:84" x14ac:dyDescent="0.55000000000000004">
-      <c r="A74" s="11">
+      <c r="A74" s="9">
         <f t="shared" si="67"/>
         <v>1903</v>
       </c>
@@ -8986,7 +8969,7 @@
       </c>
     </row>
     <row r="75" spans="1:84" x14ac:dyDescent="0.55000000000000004">
-      <c r="A75" s="11">
+      <c r="A75" s="9">
         <f t="shared" si="67"/>
         <v>1904</v>
       </c>
@@ -9267,7 +9250,7 @@
       </c>
     </row>
     <row r="76" spans="1:84" x14ac:dyDescent="0.55000000000000004">
-      <c r="A76" s="11">
+      <c r="A76" s="9">
         <f t="shared" si="67"/>
         <v>1905</v>
       </c>
@@ -9548,7 +9531,7 @@
       </c>
     </row>
     <row r="77" spans="1:84" x14ac:dyDescent="0.55000000000000004">
-      <c r="A77" s="11">
+      <c r="A77" s="9">
         <f t="shared" si="67"/>
         <v>1906</v>
       </c>
@@ -9829,7 +9812,7 @@
       </c>
     </row>
     <row r="78" spans="1:84" x14ac:dyDescent="0.55000000000000004">
-      <c r="A78" s="11">
+      <c r="A78" s="9">
         <f t="shared" si="67"/>
         <v>1907</v>
       </c>
@@ -10110,7 +10093,7 @@
       </c>
     </row>
     <row r="79" spans="1:84" x14ac:dyDescent="0.55000000000000004">
-      <c r="A79" s="11">
+      <c r="A79" s="9">
         <f t="shared" si="67"/>
         <v>1908</v>
       </c>
@@ -10391,7 +10374,7 @@
       </c>
     </row>
     <row r="80" spans="1:84" x14ac:dyDescent="0.55000000000000004">
-      <c r="A80" s="11">
+      <c r="A80" s="9">
         <f t="shared" si="67"/>
         <v>1909</v>
       </c>
@@ -10672,7 +10655,7 @@
       </c>
     </row>
     <row r="81" spans="1:84" x14ac:dyDescent="0.55000000000000004">
-      <c r="A81" s="11">
+      <c r="A81" s="9">
         <f t="shared" si="67"/>
         <v>1910</v>
       </c>
@@ -10953,7 +10936,7 @@
       </c>
     </row>
     <row r="82" spans="1:84" x14ac:dyDescent="0.55000000000000004">
-      <c r="A82" s="11">
+      <c r="A82" s="9">
         <f t="shared" si="67"/>
         <v>1911</v>
       </c>
@@ -11234,7 +11217,7 @@
       </c>
     </row>
     <row r="83" spans="1:84" x14ac:dyDescent="0.55000000000000004">
-      <c r="A83" s="11">
+      <c r="A83" s="9">
         <f t="shared" si="67"/>
         <v>1912</v>
       </c>
@@ -11515,7 +11498,7 @@
       </c>
     </row>
     <row r="84" spans="1:84" x14ac:dyDescent="0.55000000000000004">
-      <c r="A84" s="11">
+      <c r="A84" s="9">
         <f t="shared" si="67"/>
         <v>1913</v>
       </c>
@@ -11796,7 +11779,7 @@
       </c>
     </row>
     <row r="85" spans="1:84" x14ac:dyDescent="0.55000000000000004">
-      <c r="A85" s="11">
+      <c r="A85" s="9">
         <f t="shared" si="67"/>
         <v>1914</v>
       </c>
@@ -12077,7 +12060,7 @@
       </c>
     </row>
     <row r="86" spans="1:84" x14ac:dyDescent="0.55000000000000004">
-      <c r="A86" s="11">
+      <c r="A86" s="9">
         <f t="shared" si="67"/>
         <v>1915</v>
       </c>
@@ -12358,7 +12341,7 @@
       </c>
     </row>
     <row r="87" spans="1:84" x14ac:dyDescent="0.55000000000000004">
-      <c r="A87" s="12" t="s">
+      <c r="A87" s="10" t="s">
         <v>4</v>
       </c>
       <c r="B87" s="1">
@@ -12514,7 +12497,7 @@
     </row>
     <row r="89" spans="1:84" x14ac:dyDescent="0.55000000000000004">
       <c r="A89" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="AS89" s="1"/>
       <c r="AT89" s="1"/>
@@ -12523,7 +12506,7 @@
     </row>
     <row r="90" spans="1:84" x14ac:dyDescent="0.55000000000000004">
       <c r="B90" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="BK90" s="1"/>
       <c r="BL90" s="1"/>
@@ -12540,7 +12523,7 @@
     </row>
     <row r="92" spans="1:84" x14ac:dyDescent="0.55000000000000004">
       <c r="A92" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B92" s="1">
         <v>205805</v>
@@ -12580,7 +12563,7 @@
     </row>
     <row r="96" spans="1:84" x14ac:dyDescent="0.55000000000000004">
       <c r="A96" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B96" s="1">
         <v>20477</v>
@@ -12590,7 +12573,7 @@
     </row>
     <row r="97" spans="1:64" x14ac:dyDescent="0.55000000000000004">
       <c r="A97" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B97" s="1">
         <v>16981</v>
@@ -12600,7 +12583,7 @@
     </row>
     <row r="98" spans="1:64" x14ac:dyDescent="0.55000000000000004">
       <c r="A98" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B98" s="1">
         <v>12542</v>
@@ -12610,7 +12593,7 @@
     </row>
     <row r="99" spans="1:64" x14ac:dyDescent="0.55000000000000004">
       <c r="A99" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B99" s="1">
         <v>10431</v>
@@ -12620,7 +12603,7 @@
     </row>
     <row r="100" spans="1:64" x14ac:dyDescent="0.55000000000000004">
       <c r="A100" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B100" s="1">
         <v>9020</v>
@@ -12630,7 +12613,7 @@
     </row>
     <row r="101" spans="1:64" x14ac:dyDescent="0.55000000000000004">
       <c r="A101" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B101" s="1">
         <v>8369</v>
@@ -12640,7 +12623,7 @@
     </row>
     <row r="102" spans="1:64" x14ac:dyDescent="0.55000000000000004">
       <c r="A102" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B102" s="1">
         <v>8006</v>
@@ -12650,7 +12633,7 @@
     </row>
     <row r="103" spans="1:64" x14ac:dyDescent="0.55000000000000004">
       <c r="A103" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B103" s="1">
         <v>6426</v>
@@ -12660,7 +12643,7 @@
     </row>
     <row r="104" spans="1:64" x14ac:dyDescent="0.55000000000000004">
       <c r="A104" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B104" s="1">
         <v>5897</v>
@@ -12670,7 +12653,7 @@
     </row>
     <row r="105" spans="1:64" x14ac:dyDescent="0.55000000000000004">
       <c r="A105" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B105" s="1">
         <v>5622</v>
@@ -12690,7 +12673,7 @@
     </row>
     <row r="107" spans="1:64" x14ac:dyDescent="0.55000000000000004">
       <c r="A107" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B107" s="1">
         <v>4068</v>
@@ -12700,7 +12683,7 @@
     </row>
     <row r="108" spans="1:64" x14ac:dyDescent="0.55000000000000004">
       <c r="A108" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B108" s="1">
         <v>3063</v>
@@ -12710,7 +12693,7 @@
     </row>
     <row r="109" spans="1:64" x14ac:dyDescent="0.55000000000000004">
       <c r="A109" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B109" s="1">
         <v>1009</v>
@@ -12720,7 +12703,7 @@
     </row>
     <row r="110" spans="1:64" x14ac:dyDescent="0.55000000000000004">
       <c r="A110" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B110">
         <v>542</v>
@@ -12730,7 +12713,7 @@
     </row>
     <row r="111" spans="1:64" x14ac:dyDescent="0.55000000000000004">
       <c r="A111" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B111">
         <v>309</v>
@@ -12740,7 +12723,7 @@
     </row>
     <row r="112" spans="1:64" x14ac:dyDescent="0.55000000000000004">
       <c r="A112" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B112">
         <v>78</v>
@@ -12750,7 +12733,7 @@
     </row>
     <row r="113" spans="1:64" x14ac:dyDescent="0.55000000000000004">
       <c r="A113" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B113" s="1">
         <v>-5491</v>
@@ -12760,7 +12743,7 @@
     </row>
     <row r="114" spans="1:64" x14ac:dyDescent="0.55000000000000004">
       <c r="A114" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B114" s="1">
         <v>24087</v>
@@ -12770,7 +12753,7 @@
     </row>
     <row r="115" spans="1:64" x14ac:dyDescent="0.55000000000000004">
       <c r="A115" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B115" s="1">
         <f>SUM(B91:B113)</f>
@@ -12862,7 +12845,7 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.55000000000000004">
@@ -12877,21 +12860,21 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="2"/>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9" t="s">
+      <c r="C7" s="16"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9" t="s">
+      <c r="F7" s="16"/>
+      <c r="G7" s="16"/>
+      <c r="H7" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="I7" s="9"/>
-      <c r="J7" s="9"/>
+      <c r="I7" s="16"/>
+      <c r="J7" s="16"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="3" t="s">
@@ -13743,36 +13726,36 @@
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="2"/>
-      <c r="B33" s="9" t="s">
+      <c r="B33" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="C33" s="9"/>
-      <c r="D33" s="9"/>
-      <c r="E33" s="9" t="s">
+      <c r="C33" s="16"/>
+      <c r="D33" s="16"/>
+      <c r="E33" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="F33" s="9"/>
-      <c r="G33" s="9"/>
-      <c r="H33" s="9" t="s">
+      <c r="F33" s="16"/>
+      <c r="G33" s="16"/>
+      <c r="H33" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="I33" s="9"/>
-      <c r="J33" s="9"/>
-      <c r="K33" s="9" t="s">
+      <c r="I33" s="16"/>
+      <c r="J33" s="16"/>
+      <c r="K33" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="L33" s="9"/>
-      <c r="M33" s="9"/>
-      <c r="N33" s="9" t="s">
+      <c r="L33" s="16"/>
+      <c r="M33" s="16"/>
+      <c r="N33" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="O33" s="9"/>
-      <c r="P33" s="9"/>
-      <c r="Q33" s="9" t="s">
+      <c r="O33" s="16"/>
+      <c r="P33" s="16"/>
+      <c r="Q33" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="R33" s="9"/>
-      <c r="S33" s="9"/>
+      <c r="R33" s="16"/>
+      <c r="S33" s="16"/>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="3" t="s">
@@ -15252,22 +15235,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="D1" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="C1" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="D1" s="8" t="s">
+      <c r="E1" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="F1" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="F1" s="8" t="s">
-        <v>47</v>
-      </c>
       <c r="G1" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H1" s="8" t="s">
         <v>7</v>
@@ -15276,52 +15259,52 @@
         <v>8</v>
       </c>
       <c r="J1" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K1" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="L1" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="M1" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="M1" s="8" t="s">
+      <c r="N1" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="N1" s="8" t="s">
+      <c r="O1" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="O1" s="8" t="s">
+      <c r="P1" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="P1" s="8" t="s">
+      <c r="Q1" s="8" t="s">
         <v>28</v>
-      </c>
-      <c r="Q1" s="8" t="s">
-        <v>29</v>
       </c>
       <c r="R1" s="8" t="s">
         <v>9</v>
       </c>
       <c r="S1" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="T1" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="T1" s="8" t="s">
+      <c r="U1" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="U1" s="8" t="s">
+      <c r="V1" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="V1" s="8" t="s">
+      <c r="W1" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="W1" s="8" t="s">
+      <c r="X1" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="X1" s="8" t="s">
+      <c r="Y1" s="8" t="s">
         <v>35</v>
-      </c>
-      <c r="Y1" s="8" t="s">
-        <v>36</v>
       </c>
       <c r="Z1" s="8" t="s">
         <v>12</v>
@@ -15330,16 +15313,16 @@
         <v>10</v>
       </c>
       <c r="AB1" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC1" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="AC1" s="8" t="s">
+      <c r="AD1" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="AD1" s="8" t="s">
-        <v>39</v>
-      </c>
       <c r="AE1" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.55000000000000004">
@@ -17263,23 +17246,23 @@
     </row>
     <row r="23" spans="1:31" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="P23" s="1"/>
     </row>
     <row r="25" spans="1:31" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="27" spans="1:31" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="28" spans="1:31" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/rtss-pre1917/src/main/resources/immigration.xlsx
+++ b/rtss-pre1917/src/main/resources/immigration.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\WINAPPS\SLOVO\UKR\github\RTSS\rtss-pre1917\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99BCCDA4-09F5-4BD8-AB8C-8B3AF2C02E8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE1CDB19-CB4D-44B3-999D-0FBE8A26DACD}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{F5C0FC2C-9C7B-4145-981E-7BD1765E4EE3}"/>
+    <workbookView xWindow="1380" yWindow="2115" windowWidth="29775" windowHeight="21255" xr2:uid="{F5C0FC2C-9C7B-4145-981E-7BD1765E4EE3}"/>
   </bookViews>
   <sheets>
     <sheet name="note-1" sheetId="2" r:id="rId1"/>
     <sheet name="note-2" sheetId="1" r:id="rId2"/>
     <sheet name="data" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,12 +25,7 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -38,14 +33,14 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
   <futureMetadata name="XLDAPR" count="1">
     <bk>
       <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+        <ext xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray" uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
           <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
         </ext>
       </extLst>
@@ -369,9 +364,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -409,7 +404,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -515,7 +510,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -657,7 +652,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -666,22 +661,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AE7EB44-DA37-426E-8733-CEB32776A88C}">
   <dimension ref="A1:CF129"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.83984375" customWidth="1"/>
+    <col min="1" max="1" width="11.85546875" customWidth="1"/>
+    <col min="23" max="23" width="10.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
       <c r="B5" s="16" t="s">
         <v>5</v>
@@ -699,7 +695,7 @@
       <c r="I5" s="16"/>
       <c r="J5" s="16"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>0</v>
       </c>
@@ -731,7 +727,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="9">
         <f t="shared" ref="A7:A20" si="0">A8-1</f>
         <v>1881</v>
@@ -769,7 +765,7 @@
         <v>48689</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="9">
         <f t="shared" si="0"/>
         <v>1882</v>
@@ -807,7 +803,7 @@
         <v>26006</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="9">
         <f t="shared" si="0"/>
         <v>1883</v>
@@ -845,7 +841,7 @@
         <v>25477</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="9">
         <f t="shared" si="0"/>
         <v>1884</v>
@@ -883,7 +879,7 @@
         <v>26503</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="9">
         <f t="shared" si="0"/>
         <v>1885</v>
@@ -921,7 +917,7 @@
         <v>29497</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="9">
         <f t="shared" si="0"/>
         <v>1886</v>
@@ -959,7 +955,7 @@
         <v>23547</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="9">
         <f t="shared" si="0"/>
         <v>1887</v>
@@ -997,7 +993,7 @@
         <v>33837</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="9">
         <f t="shared" si="0"/>
         <v>1888</v>
@@ -1035,7 +1031,7 @@
         <v>33036</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="9">
         <f t="shared" si="0"/>
         <v>1889</v>
@@ -1073,7 +1069,7 @@
         <v>38891</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="9">
         <f t="shared" si="0"/>
         <v>1890</v>
@@ -1111,7 +1107,7 @@
         <v>37780</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="9">
         <f t="shared" si="0"/>
         <v>1891</v>
@@ -1149,7 +1145,7 @@
         <v>41539</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="9">
         <f t="shared" si="0"/>
         <v>1892</v>
@@ -1187,7 +1183,7 @@
         <v>38125</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="9">
         <f t="shared" si="0"/>
         <v>1893</v>
@@ -1225,7 +1221,7 @@
         <v>43936</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="9">
         <f t="shared" si="0"/>
         <v>1894</v>
@@ -1263,7 +1259,7 @@
         <v>49688</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="9">
         <f>A22-1</f>
         <v>1895</v>
@@ -1301,7 +1297,7 @@
         <v>54197</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="9">
         <v>1896</v>
       </c>
@@ -1339,7 +1335,7 @@
       </c>
       <c r="O22" s="1"/>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="9">
         <f>A22+1</f>
         <v>1897</v>
@@ -1378,7 +1374,7 @@
       </c>
       <c r="O23" s="1"/>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="9">
         <f t="shared" ref="A24:A41" si="12">A23+1</f>
         <v>1898</v>
@@ -1417,7 +1413,7 @@
       </c>
       <c r="O24" s="1"/>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="9">
         <f t="shared" si="12"/>
         <v>1899</v>
@@ -1456,7 +1452,7 @@
       </c>
       <c r="O25" s="1"/>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="9">
         <f t="shared" si="12"/>
         <v>1900</v>
@@ -1495,7 +1491,7 @@
       </c>
       <c r="O26" s="1"/>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="9">
         <f t="shared" si="12"/>
         <v>1901</v>
@@ -1534,7 +1530,7 @@
       </c>
       <c r="O27" s="1"/>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="9">
         <f t="shared" si="12"/>
         <v>1902</v>
@@ -1573,7 +1569,7 @@
       </c>
       <c r="O28" s="1"/>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="9">
         <f t="shared" si="12"/>
         <v>1903</v>
@@ -1612,7 +1608,7 @@
       </c>
       <c r="O29" s="1"/>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="9">
         <f t="shared" si="12"/>
         <v>1904</v>
@@ -1651,7 +1647,7 @@
       </c>
       <c r="O30" s="1"/>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="9">
         <f t="shared" si="12"/>
         <v>1905</v>
@@ -1690,7 +1686,7 @@
       </c>
       <c r="O31" s="1"/>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="9">
         <f t="shared" si="12"/>
         <v>1906</v>
@@ -1729,7 +1725,7 @@
       </c>
       <c r="O32" s="1"/>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="9">
         <f t="shared" si="12"/>
         <v>1907</v>
@@ -1768,7 +1764,7 @@
       </c>
       <c r="O33" s="1"/>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="9">
         <f t="shared" si="12"/>
         <v>1908</v>
@@ -1807,7 +1803,7 @@
       </c>
       <c r="O34" s="1"/>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="9">
         <f t="shared" si="12"/>
         <v>1909</v>
@@ -1846,7 +1842,7 @@
       </c>
       <c r="O35" s="1"/>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="9">
         <f t="shared" si="12"/>
         <v>1910</v>
@@ -1885,7 +1881,7 @@
       </c>
       <c r="O36" s="1"/>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="9">
         <f t="shared" si="12"/>
         <v>1911</v>
@@ -1924,7 +1920,7 @@
       </c>
       <c r="O37" s="1"/>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="9">
         <f t="shared" si="12"/>
         <v>1912</v>
@@ -1963,7 +1959,7 @@
       </c>
       <c r="O38" s="1"/>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="9">
         <f t="shared" si="12"/>
         <v>1913</v>
@@ -2002,7 +1998,7 @@
       </c>
       <c r="O39" s="1"/>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="9">
         <f t="shared" si="12"/>
         <v>1914</v>
@@ -2041,7 +2037,7 @@
       </c>
       <c r="O40" s="1"/>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="9">
         <f t="shared" si="12"/>
         <v>1915</v>
@@ -2080,7 +2076,7 @@
       </c>
       <c r="O41" s="1"/>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="10" t="s">
         <v>4</v>
       </c>
@@ -2104,7 +2100,7 @@
       <c r="J42" s="4"/>
       <c r="O42" s="1"/>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="10" t="s">
         <v>52</v>
       </c>
@@ -2128,7 +2124,7 @@
       <c r="J43" s="4"/>
       <c r="O43" s="1"/>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="10" t="s">
         <v>53</v>
       </c>
@@ -2152,103 +2148,108 @@
       <c r="J44" s="4"/>
       <c r="O44" s="1"/>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="O45" s="1"/>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>41</v>
       </c>
       <c r="O46" s="1"/>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="O47" s="1"/>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>18</v>
       </c>
       <c r="M48" s="6"/>
       <c r="O48" s="1"/>
     </row>
-    <row r="49" spans="1:84" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:84" x14ac:dyDescent="0.25">
       <c r="O49" s="1"/>
     </row>
-    <row r="50" spans="1:84" x14ac:dyDescent="0.55000000000000004">
-      <c r="B50" t="s">
+    <row r="50" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="B50" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E50" t="s">
+      <c r="E50" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="H50" t="s">
+      <c r="H50" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="K50" t="s">
+      <c r="K50" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="N50" t="s">
+      <c r="N50" s="2" t="s">
         <v>23</v>
       </c>
       <c r="O50" s="1"/>
-      <c r="Q50" t="s">
+      <c r="Q50" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="T50" t="s">
+      <c r="T50" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="W50" t="s">
+      <c r="W50" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="Z50" t="s">
+      <c r="Z50" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="AC50" t="s">
+      <c r="AC50" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="AF50" t="s">
+      <c r="AF50" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="AI50" t="s">
+      <c r="AI50" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="AL50" t="s">
+      <c r="AL50" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="AO50" t="s">
+      <c r="AO50" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="AR50" t="s">
+      <c r="AP50" s="2"/>
+      <c r="AR50" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="AU50" t="s">
+      <c r="AU50" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="AX50" t="s">
+      <c r="AX50" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="BA50" t="s">
+      <c r="AY50" s="2"/>
+      <c r="BA50" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="BD50" t="s">
+      <c r="BB50" s="2"/>
+      <c r="BD50" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="BG50" t="s">
+      <c r="BG50" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="BJ50" t="s">
+      <c r="BJ50" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="BM50" t="s">
+      <c r="BM50" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="BP50" t="s">
+      <c r="BP50" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="BS50" t="s">
+      <c r="BQ50" s="2"/>
+      <c r="BS50" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="BV50" t="s">
+      <c r="BT50" s="2"/>
+      <c r="BV50" s="2" t="s">
         <v>58</v>
       </c>
       <c r="BZ50" t="s">
@@ -2258,7 +2259,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="51" spans="1:84" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
         <v>0</v>
       </c>
@@ -2506,7 +2507,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="52" spans="1:84" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A52" s="9">
         <f t="shared" ref="A52:A65" si="13">A53-1</f>
         <v>1881</v>
@@ -2787,7 +2788,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:84" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A53" s="9">
         <f t="shared" si="13"/>
         <v>1882</v>
@@ -3068,7 +3069,7 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="54" spans="1:84" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A54" s="9">
         <f t="shared" si="13"/>
         <v>1883</v>
@@ -3349,7 +3350,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:84" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A55" s="9">
         <f t="shared" si="13"/>
         <v>1884</v>
@@ -3630,7 +3631,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:84" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A56" s="9">
         <f t="shared" si="13"/>
         <v>1885</v>
@@ -3911,7 +3912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:84" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A57" s="9">
         <f t="shared" si="13"/>
         <v>1886</v>
@@ -4192,7 +4193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:84" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A58" s="9">
         <f t="shared" si="13"/>
         <v>1887</v>
@@ -4473,7 +4474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:84" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A59" s="9">
         <f t="shared" si="13"/>
         <v>1888</v>
@@ -4754,7 +4755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:84" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A60" s="9">
         <f t="shared" si="13"/>
         <v>1889</v>
@@ -5035,7 +5036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:84" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A61" s="9">
         <f t="shared" si="13"/>
         <v>1890</v>
@@ -5316,7 +5317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:84" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A62" s="9">
         <f t="shared" si="13"/>
         <v>1891</v>
@@ -5597,7 +5598,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="63" spans="1:84" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A63" s="9">
         <f t="shared" si="13"/>
         <v>1892</v>
@@ -5878,7 +5879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:84" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A64" s="9">
         <f t="shared" si="13"/>
         <v>1893</v>
@@ -6159,7 +6160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:84" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A65" s="9">
         <f t="shared" si="13"/>
         <v>1894</v>
@@ -6440,7 +6441,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:84" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A66" s="9">
         <f>A67-1</f>
         <v>1895</v>
@@ -6721,7 +6722,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:84" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A67" s="9">
         <v>1896</v>
       </c>
@@ -6857,13 +6858,13 @@
       </c>
       <c r="AO67" s="1">
         <f>AP67-AQ67</f>
-        <v>-23</v>
+        <v>526</v>
       </c>
       <c r="AP67" s="1">
         <v>1486</v>
       </c>
       <c r="AQ67" s="1">
-        <v>1509</v>
+        <v>960</v>
       </c>
       <c r="AR67" s="1">
         <f>AS67-AT67</f>
@@ -6977,7 +6978,7 @@
       </c>
       <c r="BZ67" s="1">
         <f t="shared" si="39"/>
-        <v>11625</v>
+        <v>12174</v>
       </c>
       <c r="CA67" s="1" cm="1">
         <f t="array" ref="CA67">SUMPRODUCT(C67:BT67*(MOD(COLUMN(C67:BT67)-COLUMN(C67),3)=0))</f>
@@ -6985,12 +6986,12 @@
       </c>
       <c r="CB67" s="1" cm="1">
         <f t="array" ref="CB67">SUMPRODUCT(D67:BU67*(MOD(COLUMN(D67:BU67)-COLUMN(D67),3)=0))</f>
-        <v>257102</v>
+        <v>256553</v>
       </c>
       <c r="CC67" s="1"/>
       <c r="CD67" s="1">
         <f t="shared" si="40"/>
-        <v>549</v>
+        <v>0</v>
       </c>
       <c r="CE67" s="1">
         <f t="shared" si="41"/>
@@ -6998,10 +6999,10 @@
       </c>
       <c r="CF67" s="1">
         <f t="shared" si="42"/>
-        <v>-549</v>
-      </c>
-    </row>
-    <row r="68" spans="1:84" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A68" s="9">
         <f>A67+1</f>
         <v>1897</v>
@@ -7138,13 +7139,13 @@
       </c>
       <c r="AO68" s="1">
         <f t="shared" ref="AO68:AO86" si="56">AP68-AQ68</f>
-        <v>137</v>
+        <v>414</v>
       </c>
       <c r="AP68" s="1">
         <v>1923</v>
       </c>
       <c r="AQ68" s="1">
-        <v>1786</v>
+        <v>1509</v>
       </c>
       <c r="AR68" s="1">
         <f t="shared" ref="AR68:AR86" si="57">AS68-AT68</f>
@@ -7258,7 +7259,7 @@
       </c>
       <c r="BZ68" s="1">
         <f t="shared" si="39"/>
-        <v>45875</v>
+        <v>46152</v>
       </c>
       <c r="CA68" s="1" cm="1">
         <f t="array" ref="CA68">SUMPRODUCT(C68:BT68*(MOD(COLUMN(C68:BT68)-COLUMN(C68),3)=0))</f>
@@ -7266,12 +7267,12 @@
       </c>
       <c r="CB68" s="1" cm="1">
         <f t="array" ref="CB68">SUMPRODUCT(D68:BU68*(MOD(COLUMN(D68:BU68)-COLUMN(D68),3)=0))</f>
-        <v>240415</v>
+        <v>240138</v>
       </c>
       <c r="CC68" s="1"/>
       <c r="CD68" s="1">
         <f t="shared" si="40"/>
-        <v>223</v>
+        <v>-54</v>
       </c>
       <c r="CE68" s="1">
         <f t="shared" si="41"/>
@@ -7279,10 +7280,10 @@
       </c>
       <c r="CF68" s="1">
         <f t="shared" si="42"/>
-        <v>-223</v>
-      </c>
-    </row>
-    <row r="69" spans="1:84" x14ac:dyDescent="0.55000000000000004">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="69" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A69" s="9">
         <f t="shared" ref="A69:A86" si="67">A68+1</f>
         <v>1898</v>
@@ -7419,13 +7420,13 @@
       </c>
       <c r="AO69" s="1">
         <f t="shared" si="56"/>
-        <v>1175</v>
+        <v>582</v>
       </c>
       <c r="AP69" s="1">
         <v>2368</v>
       </c>
       <c r="AQ69" s="1">
-        <v>1193</v>
+        <v>1786</v>
       </c>
       <c r="AR69" s="1">
         <f t="shared" si="57"/>
@@ -7539,7 +7540,7 @@
       </c>
       <c r="BZ69" s="1">
         <f t="shared" si="39"/>
-        <v>54493</v>
+        <v>53900</v>
       </c>
       <c r="CA69" s="1" cm="1">
         <f t="array" ref="CA69">SUMPRODUCT(C69:BT69*(MOD(COLUMN(C69:BT69)-COLUMN(C69),3)=0))</f>
@@ -7547,12 +7548,12 @@
       </c>
       <c r="CB69" s="1" cm="1">
         <f t="array" ref="CB69">SUMPRODUCT(D69:BU69*(MOD(COLUMN(D69:BU69)-COLUMN(D69),3)=0))</f>
-        <v>225639</v>
+        <v>226232</v>
       </c>
       <c r="CC69" s="1"/>
       <c r="CD69" s="1">
         <f t="shared" si="40"/>
-        <v>-593</v>
+        <v>0</v>
       </c>
       <c r="CE69" s="1">
         <f t="shared" si="41"/>
@@ -7560,10 +7561,10 @@
       </c>
       <c r="CF69" s="1">
         <f t="shared" si="42"/>
-        <v>593</v>
-      </c>
-    </row>
-    <row r="70" spans="1:84" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A70" s="9">
         <f t="shared" si="67"/>
         <v>1899</v>
@@ -7700,13 +7701,13 @@
       </c>
       <c r="AO70" s="1">
         <f t="shared" si="56"/>
-        <v>791</v>
+        <v>695</v>
       </c>
       <c r="AP70" s="1">
         <v>1888</v>
       </c>
       <c r="AQ70" s="1">
-        <v>1097</v>
+        <v>1193</v>
       </c>
       <c r="AR70" s="1">
         <f t="shared" si="57"/>
@@ -7820,7 +7821,7 @@
       </c>
       <c r="BZ70" s="1">
         <f t="shared" si="39"/>
-        <v>46057</v>
+        <v>45961</v>
       </c>
       <c r="CA70" s="1" cm="1">
         <f t="array" ref="CA70">SUMPRODUCT(C70:BT70*(MOD(COLUMN(C70:BT70)-COLUMN(C70),3)=0))</f>
@@ -7828,12 +7829,12 @@
       </c>
       <c r="CB70" s="1" cm="1">
         <f t="array" ref="CB70">SUMPRODUCT(D70:BU70*(MOD(COLUMN(D70:BU70)-COLUMN(D70),3)=0))</f>
-        <v>219541</v>
+        <v>219637</v>
       </c>
       <c r="CC70" s="1"/>
       <c r="CD70" s="1">
         <f t="shared" si="40"/>
-        <v>-96</v>
+        <v>0</v>
       </c>
       <c r="CE70" s="1">
         <f t="shared" si="41"/>
@@ -7841,10 +7842,10 @@
       </c>
       <c r="CF70" s="1">
         <f t="shared" si="42"/>
-        <v>96</v>
-      </c>
-    </row>
-    <row r="71" spans="1:84" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A71" s="9">
         <f t="shared" si="67"/>
         <v>1900</v>
@@ -7981,13 +7982,13 @@
       </c>
       <c r="AO71" s="1">
         <f t="shared" si="56"/>
-        <v>342</v>
+        <v>233</v>
       </c>
       <c r="AP71" s="1">
         <v>1330</v>
       </c>
       <c r="AQ71" s="1">
-        <v>988</v>
+        <v>1097</v>
       </c>
       <c r="AR71" s="1">
         <f t="shared" si="57"/>
@@ -8101,7 +8102,7 @@
       </c>
       <c r="BZ71" s="1">
         <f t="shared" si="39"/>
-        <v>27144</v>
+        <v>27035</v>
       </c>
       <c r="CA71" s="1" cm="1">
         <f t="array" ref="CA71">SUMPRODUCT(C71:BT71*(MOD(COLUMN(C71:BT71)-COLUMN(C71),3)=0))</f>
@@ -8109,12 +8110,12 @@
       </c>
       <c r="CB71" s="1" cm="1">
         <f t="array" ref="CB71">SUMPRODUCT(D71:BU71*(MOD(COLUMN(D71:BU71)-COLUMN(D71),3)=0))</f>
-        <v>221095</v>
+        <v>221204</v>
       </c>
       <c r="CC71" s="1"/>
       <c r="CD71" s="1">
         <f t="shared" si="40"/>
-        <v>-109</v>
+        <v>0</v>
       </c>
       <c r="CE71" s="1">
         <f t="shared" si="41"/>
@@ -8122,10 +8123,10 @@
       </c>
       <c r="CF71" s="1">
         <f t="shared" si="42"/>
-        <v>109</v>
-      </c>
-    </row>
-    <row r="72" spans="1:84" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A72" s="9">
         <f t="shared" si="67"/>
         <v>1901</v>
@@ -8262,13 +8263,13 @@
       </c>
       <c r="AO72" s="1">
         <f t="shared" si="56"/>
-        <v>164</v>
+        <v>322</v>
       </c>
       <c r="AP72" s="1">
         <v>1310</v>
       </c>
       <c r="AQ72" s="1">
-        <v>1146</v>
+        <v>988</v>
       </c>
       <c r="AR72" s="1">
         <f t="shared" si="57"/>
@@ -8382,7 +8383,7 @@
       </c>
       <c r="BZ72" s="1">
         <f t="shared" si="39"/>
-        <v>54718</v>
+        <v>54876</v>
       </c>
       <c r="CA72" s="1" cm="1">
         <f t="array" ref="CA72">SUMPRODUCT(C72:BT72*(MOD(COLUMN(C72:BT72)-COLUMN(C72),3)=0))</f>
@@ -8390,12 +8391,12 @@
       </c>
       <c r="CB72" s="1" cm="1">
         <f t="array" ref="CB72">SUMPRODUCT(D72:BU72*(MOD(COLUMN(D72:BU72)-COLUMN(D72),3)=0))</f>
-        <v>236926</v>
+        <v>236768</v>
       </c>
       <c r="CC72" s="1"/>
       <c r="CD72" s="1">
         <f t="shared" si="40"/>
-        <v>-842</v>
+        <v>-1000</v>
       </c>
       <c r="CE72" s="1">
         <f t="shared" si="41"/>
@@ -8403,10 +8404,10 @@
       </c>
       <c r="CF72" s="1">
         <f t="shared" si="42"/>
-        <v>842</v>
-      </c>
-    </row>
-    <row r="73" spans="1:84" x14ac:dyDescent="0.55000000000000004">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="73" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A73" s="9">
         <f t="shared" si="67"/>
         <v>1902</v>
@@ -8543,13 +8544,13 @@
       </c>
       <c r="AO73" s="1">
         <f t="shared" si="56"/>
-        <v>131</v>
+        <v>198</v>
       </c>
       <c r="AP73" s="1">
         <v>1344</v>
       </c>
       <c r="AQ73" s="1">
-        <v>1213</v>
+        <v>1146</v>
       </c>
       <c r="AR73" s="1">
         <f t="shared" si="57"/>
@@ -8663,7 +8664,7 @@
       </c>
       <c r="BZ73" s="1">
         <f t="shared" si="39"/>
-        <v>62978</v>
+        <v>63045</v>
       </c>
       <c r="CA73" s="1" cm="1">
         <f t="array" ref="CA73">SUMPRODUCT(C73:BT73*(MOD(COLUMN(C73:BT73)-COLUMN(C73),3)=0))</f>
@@ -8671,12 +8672,12 @@
       </c>
       <c r="CB73" s="1" cm="1">
         <f t="array" ref="CB73">SUMPRODUCT(D73:BU73*(MOD(COLUMN(D73:BU73)-COLUMN(D73),3)=0))</f>
-        <v>236788</v>
+        <v>236721</v>
       </c>
       <c r="CC73" s="1"/>
       <c r="CD73" s="1">
         <f t="shared" si="40"/>
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="CE73" s="1">
         <f t="shared" si="41"/>
@@ -8684,10 +8685,10 @@
       </c>
       <c r="CF73" s="1">
         <f t="shared" si="42"/>
-        <v>-67</v>
-      </c>
-    </row>
-    <row r="74" spans="1:84" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A74" s="9">
         <f t="shared" si="67"/>
         <v>1903</v>
@@ -8824,13 +8825,13 @@
       </c>
       <c r="AO74" s="1">
         <f t="shared" si="56"/>
-        <v>432</v>
+        <v>377</v>
       </c>
       <c r="AP74" s="1">
         <v>1590</v>
       </c>
       <c r="AQ74" s="1">
-        <v>1158</v>
+        <v>1213</v>
       </c>
       <c r="AR74" s="1">
         <f t="shared" si="57"/>
@@ -8944,7 +8945,7 @@
       </c>
       <c r="BZ74" s="1">
         <f t="shared" si="39"/>
-        <v>48775</v>
+        <v>48720</v>
       </c>
       <c r="CA74" s="1" cm="1">
         <f t="array" ref="CA74">SUMPRODUCT(C74:BT74*(MOD(COLUMN(C74:BT74)-COLUMN(C74),3)=0))</f>
@@ -8952,12 +8953,12 @@
       </c>
       <c r="CB74" s="1" cm="1">
         <f t="array" ref="CB74">SUMPRODUCT(D74:BU74*(MOD(COLUMN(D74:BU74)-COLUMN(D74),3)=0))</f>
-        <v>266446</v>
+        <v>266501</v>
       </c>
       <c r="CC74" s="1"/>
       <c r="CD74" s="1">
         <f t="shared" si="40"/>
-        <v>-55</v>
+        <v>0</v>
       </c>
       <c r="CE74" s="1">
         <f t="shared" si="41"/>
@@ -8965,10 +8966,10 @@
       </c>
       <c r="CF74" s="1">
         <f t="shared" si="42"/>
-        <v>55</v>
-      </c>
-    </row>
-    <row r="75" spans="1:84" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A75" s="9">
         <f t="shared" si="67"/>
         <v>1904</v>
@@ -9105,13 +9106,13 @@
       </c>
       <c r="AO75" s="1">
         <f t="shared" si="56"/>
-        <v>370</v>
+        <v>83</v>
       </c>
       <c r="AP75" s="1">
         <v>1241</v>
       </c>
       <c r="AQ75" s="1">
-        <v>871</v>
+        <v>1158</v>
       </c>
       <c r="AR75" s="1">
         <f t="shared" si="57"/>
@@ -9225,7 +9226,7 @@
       </c>
       <c r="BZ75" s="1">
         <f t="shared" si="39"/>
-        <v>25580</v>
+        <v>25293</v>
       </c>
       <c r="CA75" s="1" cm="1">
         <f t="array" ref="CA75">SUMPRODUCT(C75:BT75*(MOD(COLUMN(C75:BT75)-COLUMN(C75),3)=0))</f>
@@ -9233,12 +9234,12 @@
       </c>
       <c r="CB75" s="1" cm="1">
         <f t="array" ref="CB75">SUMPRODUCT(D75:BU75*(MOD(COLUMN(D75:BU75)-COLUMN(D75),3)=0))</f>
-        <v>251436</v>
+        <v>251723</v>
       </c>
       <c r="CC75" s="1"/>
       <c r="CD75" s="1">
         <f t="shared" si="40"/>
-        <v>-293</v>
+        <v>-6</v>
       </c>
       <c r="CE75" s="1">
         <f t="shared" si="41"/>
@@ -9246,10 +9247,10 @@
       </c>
       <c r="CF75" s="1">
         <f t="shared" si="42"/>
-        <v>287</v>
-      </c>
-    </row>
-    <row r="76" spans="1:84" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A76" s="9">
         <f t="shared" si="67"/>
         <v>1905</v>
@@ -9386,13 +9387,13 @@
       </c>
       <c r="AO76" s="1">
         <f t="shared" si="56"/>
-        <v>240</v>
+        <v>208</v>
       </c>
       <c r="AP76" s="1">
         <v>1079</v>
       </c>
       <c r="AQ76" s="1">
-        <v>839</v>
+        <v>871</v>
       </c>
       <c r="AR76" s="1">
         <f t="shared" si="57"/>
@@ -9506,7 +9507,7 @@
       </c>
       <c r="BZ76" s="1">
         <f t="shared" si="39"/>
-        <v>8043</v>
+        <v>8011</v>
       </c>
       <c r="CA76" s="1" cm="1">
         <f t="array" ref="CA76">SUMPRODUCT(C76:BT76*(MOD(COLUMN(C76:BT76)-COLUMN(C76),3)=0))</f>
@@ -9514,12 +9515,12 @@
       </c>
       <c r="CB76" s="1" cm="1">
         <f t="array" ref="CB76">SUMPRODUCT(D76:BU76*(MOD(COLUMN(D76:BU76)-COLUMN(D76),3)=0))</f>
-        <v>239377</v>
+        <v>239409</v>
       </c>
       <c r="CC76" s="1"/>
       <c r="CD76" s="1">
         <f t="shared" si="40"/>
-        <v>-32</v>
+        <v>0</v>
       </c>
       <c r="CE76" s="1">
         <f t="shared" si="41"/>
@@ -9527,10 +9528,10 @@
       </c>
       <c r="CF76" s="1">
         <f t="shared" si="42"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="77" spans="1:84" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A77" s="9">
         <f t="shared" si="67"/>
         <v>1906</v>
@@ -9667,13 +9668,13 @@
       </c>
       <c r="AO77" s="1">
         <f t="shared" si="56"/>
-        <v>38</v>
+        <v>108</v>
       </c>
       <c r="AP77" s="1">
         <v>947</v>
       </c>
       <c r="AQ77" s="1">
-        <v>909</v>
+        <v>839</v>
       </c>
       <c r="AR77" s="1">
         <f t="shared" si="57"/>
@@ -9787,7 +9788,7 @@
       </c>
       <c r="BZ77" s="1">
         <f t="shared" si="39"/>
-        <v>49402</v>
+        <v>49472</v>
       </c>
       <c r="CA77" s="1" cm="1">
         <f t="array" ref="CA77">SUMPRODUCT(C77:BT77*(MOD(COLUMN(C77:BT77)-COLUMN(C77),3)=0))</f>
@@ -9795,12 +9796,12 @@
       </c>
       <c r="CB77" s="1" cm="1">
         <f t="array" ref="CB77">SUMPRODUCT(D77:BU77*(MOD(COLUMN(D77:BU77)-COLUMN(D77),3)=0))</f>
-        <v>266500</v>
+        <v>266430</v>
       </c>
       <c r="CC77" s="1"/>
       <c r="CD77" s="1">
         <f t="shared" si="40"/>
-        <v>18070</v>
+        <v>18000</v>
       </c>
       <c r="CE77" s="1">
         <f t="shared" si="41"/>
@@ -9808,10 +9809,10 @@
       </c>
       <c r="CF77" s="1">
         <f t="shared" si="42"/>
-        <v>-70</v>
-      </c>
-    </row>
-    <row r="78" spans="1:84" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A78" s="9">
         <f t="shared" si="67"/>
         <v>1907</v>
@@ -9948,13 +9949,13 @@
       </c>
       <c r="AO78" s="1">
         <f t="shared" si="56"/>
-        <v>289</v>
+        <v>445</v>
       </c>
       <c r="AP78" s="1">
         <v>1354</v>
       </c>
       <c r="AQ78" s="1">
-        <v>1065</v>
+        <v>909</v>
       </c>
       <c r="AR78" s="1">
         <f t="shared" si="57"/>
@@ -10068,7 +10069,7 @@
       </c>
       <c r="BZ78" s="1">
         <f t="shared" si="39"/>
-        <v>80387</v>
+        <v>80543</v>
       </c>
       <c r="CA78" s="1" cm="1">
         <f t="array" ref="CA78">SUMPRODUCT(C78:BT78*(MOD(COLUMN(C78:BT78)-COLUMN(C78),3)=0))</f>
@@ -10076,12 +10077,12 @@
       </c>
       <c r="CB78" s="1" cm="1">
         <f t="array" ref="CB78">SUMPRODUCT(D78:BU78*(MOD(COLUMN(D78:BU78)-COLUMN(D78),3)=0))</f>
-        <v>277544</v>
+        <v>277388</v>
       </c>
       <c r="CC78" s="1"/>
       <c r="CD78" s="1">
         <f t="shared" si="40"/>
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="CE78" s="1">
         <f t="shared" si="41"/>
@@ -10089,10 +10090,10 @@
       </c>
       <c r="CF78" s="1">
         <f t="shared" si="42"/>
-        <v>-156</v>
-      </c>
-    </row>
-    <row r="79" spans="1:84" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A79" s="9">
         <f t="shared" si="67"/>
         <v>1908</v>
@@ -10229,13 +10230,13 @@
       </c>
       <c r="AO79" s="1">
         <f t="shared" si="56"/>
-        <v>-47</v>
+        <v>343</v>
       </c>
       <c r="AP79" s="1">
         <v>1408</v>
       </c>
       <c r="AQ79" s="1">
-        <v>1455</v>
+        <v>1065</v>
       </c>
       <c r="AR79" s="1">
         <f t="shared" si="57"/>
@@ -10349,7 +10350,7 @@
       </c>
       <c r="BZ79" s="1">
         <f t="shared" si="39"/>
-        <v>55430</v>
+        <v>55820</v>
       </c>
       <c r="CA79" s="1" cm="1">
         <f t="array" ref="CA79">SUMPRODUCT(C79:BT79*(MOD(COLUMN(C79:BT79)-COLUMN(C79),3)=0))</f>
@@ -10357,12 +10358,12 @@
       </c>
       <c r="CB79" s="1" cm="1">
         <f t="array" ref="CB79">SUMPRODUCT(D79:BU79*(MOD(COLUMN(D79:BU79)-COLUMN(D79),3)=0))</f>
-        <v>285430</v>
+        <v>285040</v>
       </c>
       <c r="CC79" s="1"/>
       <c r="CD79" s="1">
         <f t="shared" si="40"/>
-        <v>390</v>
+        <v>0</v>
       </c>
       <c r="CE79" s="1">
         <f t="shared" si="41"/>
@@ -10370,10 +10371,10 @@
       </c>
       <c r="CF79" s="1">
         <f t="shared" si="42"/>
-        <v>-390</v>
-      </c>
-    </row>
-    <row r="80" spans="1:84" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A80" s="9">
         <f t="shared" si="67"/>
         <v>1909</v>
@@ -10510,13 +10511,13 @@
       </c>
       <c r="AO80" s="1">
         <f t="shared" si="56"/>
-        <v>327</v>
+        <v>474</v>
       </c>
       <c r="AP80" s="1">
         <v>1929</v>
       </c>
       <c r="AQ80" s="1">
-        <v>1602</v>
+        <v>1455</v>
       </c>
       <c r="AR80" s="1">
         <f t="shared" si="57"/>
@@ -10630,7 +10631,7 @@
       </c>
       <c r="BZ80" s="1">
         <f t="shared" si="39"/>
-        <v>73838</v>
+        <v>73985</v>
       </c>
       <c r="CA80" s="1" cm="1">
         <f t="array" ref="CA80">SUMPRODUCT(C80:BT80*(MOD(COLUMN(C80:BT80)-COLUMN(C80),3)=0))</f>
@@ -10638,12 +10639,12 @@
       </c>
       <c r="CB80" s="1" cm="1">
         <f t="array" ref="CB80">SUMPRODUCT(D80:BU80*(MOD(COLUMN(D80:BU80)-COLUMN(D80),3)=0))</f>
-        <v>297172</v>
+        <v>297025</v>
       </c>
       <c r="CC80" s="1"/>
       <c r="CD80" s="1">
         <f t="shared" si="40"/>
-        <v>147</v>
+        <v>0</v>
       </c>
       <c r="CE80" s="1">
         <f t="shared" si="41"/>
@@ -10651,10 +10652,10 @@
       </c>
       <c r="CF80" s="1">
         <f t="shared" si="42"/>
-        <v>-147</v>
-      </c>
-    </row>
-    <row r="81" spans="1:84" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A81" s="9">
         <f t="shared" si="67"/>
         <v>1910</v>
@@ -10791,13 +10792,13 @@
       </c>
       <c r="AO81" s="1">
         <f t="shared" si="56"/>
-        <v>680</v>
+        <v>725</v>
       </c>
       <c r="AP81" s="1">
         <v>2327</v>
       </c>
       <c r="AQ81" s="1">
-        <v>1647</v>
+        <v>1602</v>
       </c>
       <c r="AR81" s="1">
         <f t="shared" si="57"/>
@@ -10911,7 +10912,7 @@
       </c>
       <c r="BZ81" s="1">
         <f t="shared" si="39"/>
-        <v>73596</v>
+        <v>73641</v>
       </c>
       <c r="CA81" s="1" cm="1">
         <f t="array" ref="CA81">SUMPRODUCT(C81:BT81*(MOD(COLUMN(C81:BT81)-COLUMN(C81),3)=0))</f>
@@ -10919,12 +10920,12 @@
       </c>
       <c r="CB81" s="1" cm="1">
         <f t="array" ref="CB81">SUMPRODUCT(D81:BU81*(MOD(COLUMN(D81:BU81)-COLUMN(D81),3)=0))</f>
-        <v>353724</v>
+        <v>353679</v>
       </c>
       <c r="CC81" s="1"/>
       <c r="CD81" s="1">
         <f t="shared" si="40"/>
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="CE81" s="1">
         <f t="shared" si="41"/>
@@ -10932,10 +10933,10 @@
       </c>
       <c r="CF81" s="1">
         <f t="shared" si="42"/>
-        <v>-45</v>
-      </c>
-    </row>
-    <row r="82" spans="1:84" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A82" s="9">
         <f t="shared" si="67"/>
         <v>1911</v>
@@ -11072,13 +11073,13 @@
       </c>
       <c r="AO82" s="1">
         <f t="shared" si="56"/>
-        <v>577</v>
+        <v>652</v>
       </c>
       <c r="AP82" s="1">
         <v>2299</v>
       </c>
       <c r="AQ82" s="1">
-        <v>1722</v>
+        <v>1647</v>
       </c>
       <c r="AR82" s="1">
         <f t="shared" si="57"/>
@@ -11192,7 +11193,7 @@
       </c>
       <c r="BZ82" s="1">
         <f t="shared" si="39"/>
-        <v>58380</v>
+        <v>58455</v>
       </c>
       <c r="CA82" s="1" cm="1">
         <f t="array" ref="CA82">SUMPRODUCT(C82:BT82*(MOD(COLUMN(C82:BT82)-COLUMN(C82),3)=0))</f>
@@ -11200,12 +11201,12 @@
       </c>
       <c r="CB82" s="1" cm="1">
         <f t="array" ref="CB82">SUMPRODUCT(D82:BU82*(MOD(COLUMN(D82:BU82)-COLUMN(D82),3)=0))</f>
-        <v>383935</v>
+        <v>383860</v>
       </c>
       <c r="CC82" s="1"/>
       <c r="CD82" s="1">
         <f t="shared" si="40"/>
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="CE82" s="1">
         <f t="shared" si="41"/>
@@ -11213,10 +11214,10 @@
       </c>
       <c r="CF82" s="1">
         <f t="shared" si="42"/>
-        <v>-75</v>
-      </c>
-    </row>
-    <row r="83" spans="1:84" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A83" s="9">
         <f t="shared" si="67"/>
         <v>1912</v>
@@ -11353,13 +11354,13 @@
       </c>
       <c r="AO83" s="1">
         <f t="shared" si="56"/>
-        <v>521</v>
+        <v>845</v>
       </c>
       <c r="AP83" s="1">
         <v>2567</v>
       </c>
       <c r="AQ83" s="1">
-        <v>2046</v>
+        <v>1722</v>
       </c>
       <c r="AR83" s="1">
         <f t="shared" si="57"/>
@@ -11473,7 +11474,7 @@
       </c>
       <c r="BZ83" s="1">
         <f t="shared" si="39"/>
-        <v>69986</v>
+        <v>70310</v>
       </c>
       <c r="CA83" s="1" cm="1">
         <f t="array" ref="CA83">SUMPRODUCT(C83:BT83*(MOD(COLUMN(C83:BT83)-COLUMN(C83),3)=0))</f>
@@ -11481,12 +11482,12 @@
       </c>
       <c r="CB83" s="1" cm="1">
         <f t="array" ref="CB83">SUMPRODUCT(D83:BU83*(MOD(COLUMN(D83:BU83)-COLUMN(D83),3)=0))</f>
-        <v>422484</v>
+        <v>422160</v>
       </c>
       <c r="CC83" s="1"/>
       <c r="CD83" s="1">
         <f t="shared" si="40"/>
-        <v>306</v>
+        <v>-18</v>
       </c>
       <c r="CE83" s="1">
         <f t="shared" si="41"/>
@@ -11494,10 +11495,10 @@
       </c>
       <c r="CF83" s="1">
         <f t="shared" si="42"/>
-        <v>-324</v>
-      </c>
-    </row>
-    <row r="84" spans="1:84" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A84" s="9">
         <f t="shared" si="67"/>
         <v>1913</v>
@@ -11634,13 +11635,13 @@
       </c>
       <c r="AO84" s="1">
         <f t="shared" si="56"/>
-        <v>1094</v>
+        <v>478</v>
       </c>
       <c r="AP84" s="1">
         <v>2524</v>
       </c>
       <c r="AQ84" s="1">
-        <v>1430</v>
+        <v>2046</v>
       </c>
       <c r="AR84" s="1">
         <f t="shared" si="57"/>
@@ -11754,7 +11755,7 @@
       </c>
       <c r="BZ84" s="1">
         <f t="shared" si="39"/>
-        <v>95449</v>
+        <v>94833</v>
       </c>
       <c r="CA84" s="1" cm="1">
         <f t="array" ref="CA84">SUMPRODUCT(C84:BT84*(MOD(COLUMN(C84:BT84)-COLUMN(C84),3)=0))</f>
@@ -11762,12 +11763,12 @@
       </c>
       <c r="CB84" s="1" cm="1">
         <f t="array" ref="CB84">SUMPRODUCT(D84:BU84*(MOD(COLUMN(D84:BU84)-COLUMN(D84),3)=0))</f>
-        <v>420565</v>
+        <v>421181</v>
       </c>
       <c r="CC84" s="1"/>
       <c r="CD84" s="1">
         <f t="shared" si="40"/>
-        <v>-616</v>
+        <v>0</v>
       </c>
       <c r="CE84" s="1">
         <f t="shared" si="41"/>
@@ -11775,10 +11776,10 @@
       </c>
       <c r="CF84" s="1">
         <f t="shared" si="42"/>
-        <v>616</v>
-      </c>
-    </row>
-    <row r="85" spans="1:84" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A85" s="9">
         <f t="shared" si="67"/>
         <v>1914</v>
@@ -11915,13 +11916,13 @@
       </c>
       <c r="AO85" s="1">
         <f t="shared" si="56"/>
-        <v>791</v>
+        <v>12</v>
       </c>
       <c r="AP85" s="1">
         <v>1442</v>
       </c>
       <c r="AQ85" s="1">
-        <v>651</v>
+        <v>1430</v>
       </c>
       <c r="AR85" s="1">
         <f t="shared" si="57"/>
@@ -12035,7 +12036,7 @@
       </c>
       <c r="BZ85" s="1">
         <f t="shared" si="39"/>
-        <v>71618</v>
+        <v>70839</v>
       </c>
       <c r="CA85" s="1" cm="1">
         <f t="array" ref="CA85">SUMPRODUCT(C85:BT85*(MOD(COLUMN(C85:BT85)-COLUMN(C85),3)=0))</f>
@@ -12043,12 +12044,12 @@
       </c>
       <c r="CB85" s="1" cm="1">
         <f t="array" ref="CB85">SUMPRODUCT(D85:BU85*(MOD(COLUMN(D85:BU85)-COLUMN(D85),3)=0))</f>
-        <v>299371</v>
+        <v>300150</v>
       </c>
       <c r="CC85" s="1"/>
       <c r="CD85" s="1">
         <f t="shared" si="40"/>
-        <v>-781</v>
+        <v>-2</v>
       </c>
       <c r="CE85" s="1">
         <f t="shared" si="41"/>
@@ -12056,10 +12057,10 @@
       </c>
       <c r="CF85" s="1">
         <f t="shared" si="42"/>
-        <v>779</v>
-      </c>
-    </row>
-    <row r="86" spans="1:84" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A86" s="9">
         <f t="shared" si="67"/>
         <v>1915</v>
@@ -12196,13 +12197,13 @@
       </c>
       <c r="AO86" s="1">
         <f t="shared" si="56"/>
-        <v>340</v>
+        <v>67</v>
       </c>
       <c r="AP86" s="1">
         <v>718</v>
       </c>
       <c r="AQ86" s="1">
-        <v>378</v>
+        <v>651</v>
       </c>
       <c r="AR86" s="1">
         <f t="shared" si="57"/>
@@ -12316,7 +12317,7 @@
       </c>
       <c r="BZ86" s="1">
         <f t="shared" si="39"/>
-        <v>26928</v>
+        <v>26655</v>
       </c>
       <c r="CA86" s="1" cm="1">
         <f t="array" ref="CA86">SUMPRODUCT(C86:BT86*(MOD(COLUMN(C86:BT86)-COLUMN(C86),3)=0))</f>
@@ -12324,12 +12325,12 @@
       </c>
       <c r="CB86" s="1" cm="1">
         <f t="array" ref="CB86">SUMPRODUCT(D86:BU86*(MOD(COLUMN(D86:BU86)-COLUMN(D86),3)=0))</f>
-        <v>125936</v>
+        <v>126209</v>
       </c>
       <c r="CC86" s="1"/>
       <c r="CD86" s="1">
         <f t="shared" si="40"/>
-        <v>-293</v>
+        <v>-20</v>
       </c>
       <c r="CE86" s="1">
         <f t="shared" si="41"/>
@@ -12337,10 +12338,10 @@
       </c>
       <c r="CF86" s="1">
         <f t="shared" si="42"/>
-        <v>293</v>
-      </c>
-    </row>
-    <row r="87" spans="1:84" x14ac:dyDescent="0.55000000000000004">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="87" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A87" s="10" t="s">
         <v>4</v>
       </c>
@@ -12424,7 +12425,7 @@
       <c r="AN87" s="1"/>
       <c r="AO87" s="1">
         <f>SUM(AO67:AO86)</f>
-        <v>8369</v>
+        <v>7787</v>
       </c>
       <c r="AP87" s="1"/>
       <c r="AQ87" s="1"/>
@@ -12489,13 +12490,13 @@
       <c r="BT87" s="1"/>
       <c r="BU87" s="1"/>
     </row>
-    <row r="88" spans="1:84" x14ac:dyDescent="0.55000000000000004">
+    <row r="88" spans="1:84" x14ac:dyDescent="0.25">
       <c r="AS88" s="1"/>
       <c r="AT88" s="1"/>
       <c r="BK88" s="1"/>
       <c r="BL88" s="1"/>
     </row>
-    <row r="89" spans="1:84" x14ac:dyDescent="0.55000000000000004">
+    <row r="89" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>55</v>
       </c>
@@ -12504,14 +12505,14 @@
       <c r="BK89" s="1"/>
       <c r="BL89" s="1"/>
     </row>
-    <row r="90" spans="1:84" x14ac:dyDescent="0.55000000000000004">
+    <row r="90" spans="1:84" x14ac:dyDescent="0.25">
       <c r="B90" s="8" t="s">
         <v>54</v>
       </c>
       <c r="BK90" s="1"/>
       <c r="BL90" s="1"/>
     </row>
-    <row r="91" spans="1:84" x14ac:dyDescent="0.55000000000000004">
+    <row r="91" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>12</v>
       </c>
@@ -12521,7 +12522,7 @@
       <c r="BK91" s="1"/>
       <c r="BL91" s="1"/>
     </row>
-    <row r="92" spans="1:84" x14ac:dyDescent="0.55000000000000004">
+    <row r="92" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>36</v>
       </c>
@@ -12531,7 +12532,7 @@
       <c r="BK92" s="1"/>
       <c r="BL92" s="1"/>
     </row>
-    <row r="93" spans="1:84" x14ac:dyDescent="0.55000000000000004">
+    <row r="93" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>10</v>
       </c>
@@ -12541,7 +12542,7 @@
       <c r="BK93" s="1"/>
       <c r="BL93" s="1"/>
     </row>
-    <row r="94" spans="1:84" x14ac:dyDescent="0.55000000000000004">
+    <row r="94" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>8</v>
       </c>
@@ -12551,7 +12552,7 @@
       <c r="BK94" s="1"/>
       <c r="BL94" s="1"/>
     </row>
-    <row r="95" spans="1:84" x14ac:dyDescent="0.55000000000000004">
+    <row r="95" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>7</v>
       </c>
@@ -12561,7 +12562,7 @@
       <c r="BK95" s="1"/>
       <c r="BL95" s="1"/>
     </row>
-    <row r="96" spans="1:84" x14ac:dyDescent="0.55000000000000004">
+    <row r="96" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>22</v>
       </c>
@@ -12571,7 +12572,7 @@
       <c r="BK96" s="1"/>
       <c r="BL96" s="1"/>
     </row>
-    <row r="97" spans="1:64" x14ac:dyDescent="0.55000000000000004">
+    <row r="97" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>37</v>
       </c>
@@ -12581,7 +12582,7 @@
       <c r="BK97" s="1"/>
       <c r="BL97" s="1"/>
     </row>
-    <row r="98" spans="1:64" x14ac:dyDescent="0.55000000000000004">
+    <row r="98" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>21</v>
       </c>
@@ -12591,7 +12592,7 @@
       <c r="BK98" s="1"/>
       <c r="BL98" s="1"/>
     </row>
-    <row r="99" spans="1:64" x14ac:dyDescent="0.55000000000000004">
+    <row r="99" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>25</v>
       </c>
@@ -12601,7 +12602,7 @@
       <c r="BK99" s="1"/>
       <c r="BL99" s="1"/>
     </row>
-    <row r="100" spans="1:64" x14ac:dyDescent="0.55000000000000004">
+    <row r="100" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>28</v>
       </c>
@@ -12611,7 +12612,7 @@
       <c r="BK100" s="1"/>
       <c r="BL100" s="1"/>
     </row>
-    <row r="101" spans="1:64" x14ac:dyDescent="0.55000000000000004">
+    <row r="101" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>31</v>
       </c>
@@ -12621,7 +12622,7 @@
       <c r="BK101" s="1"/>
       <c r="BL101" s="1"/>
     </row>
-    <row r="102" spans="1:64" x14ac:dyDescent="0.55000000000000004">
+    <row r="102" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>23</v>
       </c>
@@ -12631,7 +12632,7 @@
       <c r="BK102" s="1"/>
       <c r="BL102" s="1"/>
     </row>
-    <row r="103" spans="1:64" x14ac:dyDescent="0.55000000000000004">
+    <row r="103" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>30</v>
       </c>
@@ -12641,7 +12642,7 @@
       <c r="BK103" s="1"/>
       <c r="BL103" s="1"/>
     </row>
-    <row r="104" spans="1:64" x14ac:dyDescent="0.55000000000000004">
+    <row r="104" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>26</v>
       </c>
@@ -12651,7 +12652,7 @@
       <c r="BK104" s="1"/>
       <c r="BL104" s="1"/>
     </row>
-    <row r="105" spans="1:64" x14ac:dyDescent="0.55000000000000004">
+    <row r="105" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>29</v>
       </c>
@@ -12661,7 +12662,7 @@
       <c r="BK105" s="1"/>
       <c r="BL105" s="1"/>
     </row>
-    <row r="106" spans="1:64" x14ac:dyDescent="0.55000000000000004">
+    <row r="106" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>9</v>
       </c>
@@ -12671,7 +12672,7 @@
       <c r="BK106" s="1"/>
       <c r="BL106" s="1"/>
     </row>
-    <row r="107" spans="1:64" x14ac:dyDescent="0.55000000000000004">
+    <row r="107" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>27</v>
       </c>
@@ -12681,7 +12682,7 @@
       <c r="BK107" s="1"/>
       <c r="BL107" s="1"/>
     </row>
-    <row r="108" spans="1:64" x14ac:dyDescent="0.55000000000000004">
+    <row r="108" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>24</v>
       </c>
@@ -12691,7 +12692,7 @@
       <c r="BK108" s="1"/>
       <c r="BL108" s="1"/>
     </row>
-    <row r="109" spans="1:64" x14ac:dyDescent="0.55000000000000004">
+    <row r="109" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>33</v>
       </c>
@@ -12701,7 +12702,7 @@
       <c r="BK109" s="1"/>
       <c r="BL109" s="1"/>
     </row>
-    <row r="110" spans="1:64" x14ac:dyDescent="0.55000000000000004">
+    <row r="110" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>32</v>
       </c>
@@ -12711,7 +12712,7 @@
       <c r="BK110" s="1"/>
       <c r="BL110" s="1"/>
     </row>
-    <row r="111" spans="1:64" x14ac:dyDescent="0.55000000000000004">
+    <row r="111" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>35</v>
       </c>
@@ -12721,7 +12722,7 @@
       <c r="BK111" s="1"/>
       <c r="BL111" s="1"/>
     </row>
-    <row r="112" spans="1:64" x14ac:dyDescent="0.55000000000000004">
+    <row r="112" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>34</v>
       </c>
@@ -12731,7 +12732,7 @@
       <c r="BK112" s="1"/>
       <c r="BL112" s="1"/>
     </row>
-    <row r="113" spans="1:64" x14ac:dyDescent="0.55000000000000004">
+    <row r="113" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>38</v>
       </c>
@@ -12741,7 +12742,7 @@
       <c r="BK113" s="1"/>
       <c r="BL113" s="1"/>
     </row>
-    <row r="114" spans="1:64" x14ac:dyDescent="0.55000000000000004">
+    <row r="114" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>39</v>
       </c>
@@ -12751,7 +12752,7 @@
       <c r="BK114" s="1"/>
       <c r="BL114" s="1"/>
     </row>
-    <row r="115" spans="1:64" x14ac:dyDescent="0.55000000000000004">
+    <row r="115" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>40</v>
       </c>
@@ -12762,59 +12763,59 @@
       <c r="BK115" s="1"/>
       <c r="BL115" s="1"/>
     </row>
-    <row r="116" spans="1:64" x14ac:dyDescent="0.55000000000000004">
+    <row r="116" spans="1:64" x14ac:dyDescent="0.25">
       <c r="BK116" s="1"/>
       <c r="BL116" s="1"/>
     </row>
-    <row r="117" spans="1:64" x14ac:dyDescent="0.55000000000000004">
+    <row r="117" spans="1:64" x14ac:dyDescent="0.25">
       <c r="BK117" s="1"/>
       <c r="BL117" s="1"/>
     </row>
-    <row r="118" spans="1:64" x14ac:dyDescent="0.55000000000000004">
+    <row r="118" spans="1:64" x14ac:dyDescent="0.25">
       <c r="BK118" s="1"/>
       <c r="BL118" s="1"/>
     </row>
-    <row r="119" spans="1:64" x14ac:dyDescent="0.55000000000000004">
+    <row r="119" spans="1:64" x14ac:dyDescent="0.25">
       <c r="BK119" s="1"/>
       <c r="BL119" s="1"/>
     </row>
-    <row r="120" spans="1:64" x14ac:dyDescent="0.55000000000000004">
+    <row r="120" spans="1:64" x14ac:dyDescent="0.25">
       <c r="BK120" s="1"/>
       <c r="BL120" s="1"/>
     </row>
-    <row r="121" spans="1:64" x14ac:dyDescent="0.55000000000000004">
+    <row r="121" spans="1:64" x14ac:dyDescent="0.25">
       <c r="BK121" s="1"/>
       <c r="BL121" s="1"/>
     </row>
-    <row r="122" spans="1:64" x14ac:dyDescent="0.55000000000000004">
+    <row r="122" spans="1:64" x14ac:dyDescent="0.25">
       <c r="BK122" s="1"/>
       <c r="BL122" s="1"/>
     </row>
-    <row r="123" spans="1:64" x14ac:dyDescent="0.55000000000000004">
+    <row r="123" spans="1:64" x14ac:dyDescent="0.25">
       <c r="BK123" s="1"/>
       <c r="BL123" s="1"/>
     </row>
-    <row r="124" spans="1:64" x14ac:dyDescent="0.55000000000000004">
+    <row r="124" spans="1:64" x14ac:dyDescent="0.25">
       <c r="BK124" s="1"/>
       <c r="BL124" s="1"/>
     </row>
-    <row r="125" spans="1:64" x14ac:dyDescent="0.55000000000000004">
+    <row r="125" spans="1:64" x14ac:dyDescent="0.25">
       <c r="BK125" s="1"/>
       <c r="BL125" s="1"/>
     </row>
-    <row r="126" spans="1:64" x14ac:dyDescent="0.55000000000000004">
+    <row r="126" spans="1:64" x14ac:dyDescent="0.25">
       <c r="BK126" s="1"/>
       <c r="BL126" s="1"/>
     </row>
-    <row r="127" spans="1:64" x14ac:dyDescent="0.55000000000000004">
+    <row r="127" spans="1:64" x14ac:dyDescent="0.25">
       <c r="BK127" s="1"/>
       <c r="BL127" s="1"/>
     </row>
-    <row r="128" spans="1:64" x14ac:dyDescent="0.55000000000000004">
+    <row r="128" spans="1:64" x14ac:dyDescent="0.25">
       <c r="BK128" s="1"/>
       <c r="BL128" s="1"/>
     </row>
-    <row r="129" spans="63:64" x14ac:dyDescent="0.55000000000000004">
+    <row r="129" spans="63:64" x14ac:dyDescent="0.25">
       <c r="BK129" s="1"/>
       <c r="BL129" s="1"/>
     </row>
@@ -12832,33 +12833,33 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C7873D5-0E5D-4C85-A503-F7801E4CF69A}">
   <dimension ref="A1:U55"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="11.68359375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
       <c r="B7" s="16" t="s">
         <v>5</v>
@@ -12876,7 +12877,7 @@
       <c r="I7" s="16"/>
       <c r="J7" s="16"/>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>0</v>
       </c>
@@ -12909,7 +12910,7 @@
       </c>
       <c r="O8" s="1"/>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>1896</v>
       </c>
@@ -12947,7 +12948,7 @@
       </c>
       <c r="O9" s="1"/>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10">
         <f>A9+1</f>
         <v>1897</v>
@@ -12986,7 +12987,7 @@
       </c>
       <c r="O10" s="1"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11">
         <f t="shared" ref="A11:A28" si="6">A10+1</f>
         <v>1898</v>
@@ -13025,7 +13026,7 @@
       </c>
       <c r="O11" s="1"/>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12">
         <f t="shared" si="6"/>
         <v>1899</v>
@@ -13064,7 +13065,7 @@
       </c>
       <c r="O12" s="1"/>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13">
         <f t="shared" si="6"/>
         <v>1900</v>
@@ -13103,7 +13104,7 @@
       </c>
       <c r="O13" s="1"/>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14">
         <f t="shared" si="6"/>
         <v>1901</v>
@@ -13142,7 +13143,7 @@
       </c>
       <c r="O14" s="1"/>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15">
         <f t="shared" si="6"/>
         <v>1902</v>
@@ -13181,7 +13182,7 @@
       </c>
       <c r="O15" s="1"/>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16">
         <f t="shared" si="6"/>
         <v>1903</v>
@@ -13220,7 +13221,7 @@
       </c>
       <c r="O16" s="1"/>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17">
         <f t="shared" si="6"/>
         <v>1904</v>
@@ -13259,7 +13260,7 @@
       </c>
       <c r="O17" s="1"/>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18">
         <f t="shared" si="6"/>
         <v>1905</v>
@@ -13298,7 +13299,7 @@
       </c>
       <c r="O18" s="1"/>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19">
         <f t="shared" si="6"/>
         <v>1906</v>
@@ -13337,7 +13338,7 @@
       </c>
       <c r="O19" s="1"/>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20">
         <f t="shared" si="6"/>
         <v>1907</v>
@@ -13376,7 +13377,7 @@
       </c>
       <c r="O20" s="1"/>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21">
         <f t="shared" si="6"/>
         <v>1908</v>
@@ -13415,7 +13416,7 @@
       </c>
       <c r="O21" s="1"/>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22">
         <f t="shared" si="6"/>
         <v>1909</v>
@@ -13454,7 +13455,7 @@
       </c>
       <c r="O22" s="1"/>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23">
         <f t="shared" si="6"/>
         <v>1910</v>
@@ -13493,7 +13494,7 @@
       </c>
       <c r="O23" s="1"/>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24">
         <f t="shared" si="6"/>
         <v>1911</v>
@@ -13532,7 +13533,7 @@
       </c>
       <c r="O24" s="1"/>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25">
         <f t="shared" si="6"/>
         <v>1912</v>
@@ -13571,7 +13572,7 @@
       </c>
       <c r="O25" s="1"/>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26">
         <f t="shared" si="6"/>
         <v>1913</v>
@@ -13610,7 +13611,7 @@
       </c>
       <c r="O26" s="1"/>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27">
         <f t="shared" si="6"/>
         <v>1914</v>
@@ -13649,7 +13650,7 @@
       </c>
       <c r="O27" s="1"/>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28">
         <f t="shared" si="6"/>
         <v>1915</v>
@@ -13688,7 +13689,7 @@
       </c>
       <c r="O28" s="1"/>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>4</v>
       </c>
@@ -13712,19 +13713,19 @@
       <c r="J29" s="4"/>
       <c r="O29" s="1"/>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="O30" s="1"/>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>6</v>
       </c>
       <c r="O31" s="1"/>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="O32" s="1"/>
     </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A33" s="2"/>
       <c r="B33" s="16" t="s">
         <v>7</v>
@@ -13757,7 +13758,7 @@
       <c r="R33" s="16"/>
       <c r="S33" s="16"/>
     </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>0</v>
       </c>
@@ -13816,7 +13817,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>1896</v>
       </c>
@@ -13881,7 +13882,7 @@
         <v>2685</v>
       </c>
     </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A36">
         <f>A35+1</f>
         <v>1897</v>
@@ -13947,7 +13948,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A37">
         <f t="shared" ref="A37:A54" si="13">A36+1</f>
         <v>1898</v>
@@ -14013,7 +14014,7 @@
         <v>1222</v>
       </c>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A38">
         <f t="shared" si="13"/>
         <v>1899</v>
@@ -14079,7 +14080,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A39">
         <f t="shared" si="13"/>
         <v>1900</v>
@@ -14145,7 +14146,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A40">
         <f t="shared" si="13"/>
         <v>1901</v>
@@ -14211,7 +14212,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A41">
         <f t="shared" si="13"/>
         <v>1902</v>
@@ -14277,7 +14278,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A42">
         <f t="shared" si="13"/>
         <v>1903</v>
@@ -14343,7 +14344,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A43">
         <f t="shared" si="13"/>
         <v>1904</v>
@@ -14409,7 +14410,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A44">
         <f t="shared" si="13"/>
         <v>1905</v>
@@ -14475,7 +14476,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A45">
         <f t="shared" si="13"/>
         <v>1906</v>
@@ -14541,7 +14542,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A46">
         <f t="shared" si="13"/>
         <v>1907</v>
@@ -14607,7 +14608,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A47">
         <f t="shared" si="13"/>
         <v>1908</v>
@@ -14673,7 +14674,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A48">
         <f t="shared" si="13"/>
         <v>1909</v>
@@ -14739,7 +14740,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="49" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49">
         <f t="shared" si="13"/>
         <v>1910</v>
@@ -14805,7 +14806,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="50" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50">
         <f t="shared" si="13"/>
         <v>1911</v>
@@ -14871,7 +14872,7 @@
         <v>2584</v>
       </c>
     </row>
-    <row r="51" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51">
         <f t="shared" si="13"/>
         <v>1912</v>
@@ -14937,7 +14938,7 @@
         <v>11687</v>
       </c>
     </row>
-    <row r="52" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52">
         <f t="shared" si="13"/>
         <v>1913</v>
@@ -15003,7 +15004,7 @@
         <v>27718</v>
       </c>
     </row>
-    <row r="53" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53">
         <f t="shared" si="13"/>
         <v>1914</v>
@@ -15069,7 +15070,7 @@
         <v>6799</v>
       </c>
     </row>
-    <row r="54" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54">
         <f t="shared" si="13"/>
         <v>1915</v>
@@ -15133,7 +15134,7 @@
         <v>4456</v>
       </c>
     </row>
-    <row r="55" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
         <v>4</v>
       </c>
@@ -15195,42 +15196,42 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7B60D45-40A7-4AEF-8152-6E6E2D19E14F}">
   <dimension ref="A1:AE28"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.26171875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.83984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.83984375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.26171875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.28515625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="5.26171875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.26171875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.68359375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="7.578125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="9.41796875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9.26171875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="7.41796875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="6.68359375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="19.15625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="7.68359375" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="8.68359375" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="11.41796875" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="11.83984375" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="7.578125" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="7.26171875" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="7.41796875" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="7.68359375" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="6.26171875" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="10.15625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="10.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -15325,7 +15326,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1896</v>
       </c>
@@ -15420,7 +15421,7 @@
         <v>4102</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3">
         <f>A2+1</f>
         <v>1897</v>
@@ -15516,7 +15517,7 @@
         <v>3222</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4">
         <f t="shared" ref="A4:A21" si="0">A3+1</f>
         <v>1898</v>
@@ -15612,7 +15613,7 @@
         <v>3325</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5">
         <f t="shared" si="0"/>
         <v>1899</v>
@@ -15708,7 +15709,7 @@
         <v>1734</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6">
         <f t="shared" si="0"/>
         <v>1900</v>
@@ -15804,7 +15805,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7">
         <f t="shared" si="0"/>
         <v>1901</v>
@@ -15900,7 +15901,7 @@
         <v>-1288</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8">
         <f t="shared" si="0"/>
         <v>1902</v>
@@ -15996,7 +15997,7 @@
         <v>-1670</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A9">
         <f t="shared" si="0"/>
         <v>1903</v>
@@ -16092,7 +16093,7 @@
         <v>1204</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A10">
         <f t="shared" si="0"/>
         <v>1904</v>
@@ -16188,7 +16189,7 @@
         <v>-2998</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A11">
         <f t="shared" si="0"/>
         <v>1905</v>
@@ -16284,7 +16285,7 @@
         <v>-97</v>
       </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A12">
         <f t="shared" si="0"/>
         <v>1906</v>
@@ -16380,7 +16381,7 @@
         <v>3499</v>
       </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A13">
         <f t="shared" si="0"/>
         <v>1907</v>
@@ -16476,7 +16477,7 @@
         <v>9747</v>
       </c>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A14">
         <f t="shared" si="0"/>
         <v>1908</v>
@@ -16572,7 +16573,7 @@
         <v>938</v>
       </c>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A15">
         <f t="shared" si="0"/>
         <v>1909</v>
@@ -16668,7 +16669,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A16">
         <f t="shared" si="0"/>
         <v>1910</v>
@@ -16764,7 +16765,7 @@
         <v>-46</v>
       </c>
     </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A17">
         <f t="shared" si="0"/>
         <v>1911</v>
@@ -16860,7 +16861,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A18">
         <f t="shared" si="0"/>
         <v>1912</v>
@@ -16956,7 +16957,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A19">
         <f t="shared" si="0"/>
         <v>1913</v>
@@ -17052,7 +17053,7 @@
         <v>-239</v>
       </c>
     </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A20">
         <f t="shared" si="0"/>
         <v>1914</v>
@@ -17148,7 +17149,7 @@
         <v>-1287</v>
       </c>
     </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A21">
         <f t="shared" si="0"/>
         <v>1915</v>
@@ -17244,23 +17245,23 @@
         <v>-2496</v>
       </c>
     </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
         <v>49</v>
       </c>
       <c r="P23" s="1"/>
     </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="27" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="28" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>51</v>
       </c>

--- a/rtss-pre1917/src/main/resources/immigration.xlsx
+++ b/rtss-pre1917/src/main/resources/immigration.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\WINAPPS\SLOVO\UKR\github\RTSS\rtss-pre1917\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A1358FA-C15F-4072-9945-BE132F86C8A3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15D49887-193B-470F-93CF-B78432D3FAB5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-60" yWindow="-60" windowWidth="38520" windowHeight="23700" xr2:uid="{F5C0FC2C-9C7B-4145-981E-7BD1765E4EE3}"/>
+    <workbookView xWindow="8235" yWindow="1500" windowWidth="24945" windowHeight="21255" activeTab="2" xr2:uid="{F5C0FC2C-9C7B-4145-981E-7BD1765E4EE3}"/>
   </bookViews>
   <sheets>
     <sheet name="note-1" sheetId="2" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="61">
   <si>
     <t>год</t>
   </si>
@@ -169,9 +169,6 @@
   </si>
   <si>
     <t>Япония</t>
-  </si>
-  <si>
-    <t>Хива</t>
   </si>
   <si>
     <t>Другие страны</t>
@@ -359,9 +356,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -380,6 +374,9 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -706,7 +703,7 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -716,21 +713,21 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17" t="s">
+      <c r="C5" s="27"/>
+      <c r="D5" s="27"/>
+      <c r="E5" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="17"/>
-      <c r="G5" s="17"/>
-      <c r="H5" s="17" t="s">
+      <c r="F5" s="27"/>
+      <c r="G5" s="27"/>
+      <c r="H5" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="I5" s="17"/>
-      <c r="J5" s="17"/>
+      <c r="I5" s="27"/>
+      <c r="J5" s="27"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
@@ -2139,7 +2136,7 @@
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B43" s="5">
         <f>SUM(B7:B21)</f>
@@ -2163,7 +2160,7 @@
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B44" s="5">
         <f>B42+B43</f>
@@ -2190,7 +2187,7 @@
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="O46" s="1"/>
     </row>
@@ -2205,8 +2202,8 @@
       <c r="O48" s="1"/>
     </row>
     <row r="49" spans="1:84" x14ac:dyDescent="0.25">
-      <c r="A49" s="23" t="s">
-        <v>61</v>
+      <c r="A49" s="22" t="s">
+        <v>60</v>
       </c>
       <c r="M49" s="6"/>
       <c r="O49" s="1"/>
@@ -2286,21 +2283,21 @@
         <v>37</v>
       </c>
       <c r="BP51" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="BQ51" s="2"/>
       <c r="BS51" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="BT51" s="2"/>
       <c r="BV51" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="BZ51" t="s">
         <v>55</v>
       </c>
-      <c r="BZ51" t="s">
-        <v>56</v>
-      </c>
       <c r="CD51" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="52" spans="1:84" x14ac:dyDescent="0.25">
@@ -9594,7 +9591,7 @@
         <f t="shared" si="44"/>
         <v>1882</v>
       </c>
-      <c r="F78" s="20">
+      <c r="F78" s="19">
         <v>86749</v>
       </c>
       <c r="G78" s="1">
@@ -12387,7 +12384,7 @@
     </row>
     <row r="88" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A88" s="10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B88" s="1">
         <f>SUM(B53:B67)</f>
@@ -12396,145 +12393,145 @@
       <c r="C88" s="1"/>
       <c r="D88" s="1"/>
       <c r="E88" s="1">
-        <f t="shared" ref="E88:AJ88" si="68">SUM(E53:E67)</f>
+        <f t="shared" ref="E88" si="68">SUM(E53:E67)</f>
         <v>270548</v>
       </c>
       <c r="F88" s="1"/>
       <c r="G88" s="1"/>
       <c r="H88" s="1">
-        <f t="shared" ref="H88:AM88" si="69">SUM(H53:H67)</f>
+        <f t="shared" ref="H88" si="69">SUM(H53:H67)</f>
         <v>1194</v>
       </c>
       <c r="I88" s="1"/>
       <c r="J88" s="1"/>
       <c r="K88" s="1">
-        <f t="shared" ref="K88:AP88" si="70">SUM(K53:K67)</f>
+        <f t="shared" ref="K88" si="70">SUM(K53:K67)</f>
         <v>7593</v>
       </c>
       <c r="L88" s="1"/>
       <c r="M88" s="1"/>
       <c r="N88" s="1">
-        <f t="shared" ref="N88:AS88" si="71">SUM(N53:N67)</f>
+        <f t="shared" ref="N88" si="71">SUM(N53:N67)</f>
         <v>4360</v>
       </c>
       <c r="O88" s="1"/>
       <c r="P88" s="1"/>
       <c r="Q88" s="1">
-        <f t="shared" ref="Q88:AV88" si="72">SUM(Q53:Q67)</f>
+        <f t="shared" ref="Q88" si="72">SUM(Q53:Q67)</f>
         <v>93</v>
       </c>
       <c r="R88" s="1"/>
       <c r="S88" s="1"/>
       <c r="T88" s="1">
-        <f t="shared" ref="T88:AY88" si="73">SUM(T53:T67)</f>
+        <f t="shared" ref="T88" si="73">SUM(T53:T67)</f>
         <v>407</v>
       </c>
       <c r="U88" s="1"/>
       <c r="V88" s="1"/>
       <c r="W88" s="1">
-        <f t="shared" ref="W88:BB88" si="74">SUM(W53:W67)</f>
+        <f t="shared" ref="W88" si="74">SUM(W53:W67)</f>
         <v>-47</v>
       </c>
       <c r="X88" s="1"/>
       <c r="Y88" s="1"/>
       <c r="Z88" s="1">
-        <f t="shared" ref="Z88:BE88" si="75">SUM(Z53:Z67)</f>
+        <f t="shared" ref="Z88" si="75">SUM(Z53:Z67)</f>
         <v>6276</v>
       </c>
       <c r="AA88" s="1"/>
       <c r="AB88" s="1"/>
       <c r="AC88" s="1">
-        <f t="shared" ref="AC88:BX88" si="76">SUM(AC53:AC67)</f>
+        <f t="shared" ref="AC88" si="76">SUM(AC53:AC67)</f>
         <v>573</v>
       </c>
       <c r="AD88" s="1"/>
       <c r="AE88" s="1"/>
       <c r="AF88" s="1">
-        <f t="shared" ref="AF88:BX88" si="77">SUM(AF53:AF67)</f>
+        <f t="shared" ref="AF88" si="77">SUM(AF53:AF67)</f>
         <v>1510</v>
       </c>
       <c r="AG88" s="1"/>
       <c r="AH88" s="1"/>
       <c r="AI88" s="1">
-        <f t="shared" ref="AI88:BX88" si="78">SUM(AI53:AI67)</f>
+        <f t="shared" ref="AI88" si="78">SUM(AI53:AI67)</f>
         <v>5131</v>
       </c>
       <c r="AJ88" s="1"/>
       <c r="AK88" s="1"/>
       <c r="AL88" s="1">
-        <f t="shared" ref="AL88:BX88" si="79">SUM(AL53:AL67)</f>
+        <f t="shared" ref="AL88" si="79">SUM(AL53:AL67)</f>
         <v>477</v>
       </c>
       <c r="AM88" s="1"/>
       <c r="AN88" s="1"/>
       <c r="AO88" s="1">
-        <f t="shared" ref="AO88:BX88" si="80">SUM(AO53:AO67)</f>
+        <f t="shared" ref="AO88" si="80">SUM(AO53:AO67)</f>
         <v>2396</v>
       </c>
       <c r="AP88" s="1"/>
       <c r="AQ88" s="1"/>
       <c r="AR88" s="1">
-        <f t="shared" ref="AR88:BX88" si="81">SUM(AR53:AR67)</f>
+        <f t="shared" ref="AR88" si="81">SUM(AR53:AR67)</f>
         <v>197</v>
       </c>
       <c r="AS88" s="1"/>
       <c r="AT88" s="1"/>
       <c r="AU88" s="1">
-        <f t="shared" ref="AU88:BX88" si="82">SUM(AU53:AU67)</f>
+        <f t="shared" ref="AU88" si="82">SUM(AU53:AU67)</f>
         <v>90</v>
       </c>
       <c r="AV88" s="1"/>
       <c r="AW88" s="1"/>
       <c r="AX88" s="1">
-        <f t="shared" ref="AX88:BX88" si="83">SUM(AX53:AX67)</f>
+        <f t="shared" ref="AX88" si="83">SUM(AX53:AX67)</f>
         <v>7</v>
       </c>
       <c r="AY88" s="1"/>
       <c r="AZ88" s="1"/>
       <c r="BA88" s="1">
-        <f t="shared" ref="BA88:BX88" si="84">SUM(BA53:BA67)</f>
+        <f t="shared" ref="BA88" si="84">SUM(BA53:BA67)</f>
         <v>205</v>
       </c>
       <c r="BB88" s="1"/>
       <c r="BC88" s="1"/>
       <c r="BD88" s="1">
-        <f t="shared" ref="BD88:BX88" si="85">SUM(BD53:BD67)</f>
+        <f t="shared" ref="BD88" si="85">SUM(BD53:BD67)</f>
         <v>137996</v>
       </c>
       <c r="BE88" s="1"/>
       <c r="BF88" s="1"/>
       <c r="BG88" s="1">
-        <f t="shared" ref="BG88:BX88" si="86">SUM(BG53:BG67)</f>
+        <f t="shared" ref="BG88" si="86">SUM(BG53:BG67)</f>
         <v>296</v>
       </c>
       <c r="BH88" s="1"/>
       <c r="BI88" s="1"/>
       <c r="BJ88" s="1">
-        <f t="shared" ref="BJ88:BX88" si="87">SUM(BJ53:BJ67)</f>
+        <f t="shared" ref="BJ88" si="87">SUM(BJ53:BJ67)</f>
         <v>48840</v>
       </c>
       <c r="BK88" s="1"/>
       <c r="BL88" s="1"/>
       <c r="BM88" s="1">
-        <f t="shared" ref="BM88:BX88" si="88">SUM(BM53:BM67)</f>
+        <f t="shared" ref="BM88" si="88">SUM(BM53:BM67)</f>
         <v>50</v>
       </c>
       <c r="BN88" s="1"/>
       <c r="BO88" s="1"/>
       <c r="BP88" s="1">
-        <f t="shared" ref="BP88:BX88" si="89">SUM(BP53:BP67)</f>
+        <f t="shared" ref="BP88" si="89">SUM(BP53:BP67)</f>
         <v>-1825</v>
       </c>
       <c r="BQ88" s="1"/>
       <c r="BR88" s="1"/>
       <c r="BS88" s="1">
-        <f t="shared" ref="BS88:BX88" si="90">SUM(BS53:BS67)</f>
+        <f t="shared" ref="BS88" si="90">SUM(BS53:BS67)</f>
         <v>7529</v>
       </c>
       <c r="BT88" s="1"/>
       <c r="BU88" s="1"/>
       <c r="BV88" s="1">
-        <f t="shared" ref="BV88:BX88" si="91">SUM(BV53:BV67)</f>
+        <f t="shared" ref="BV88" si="91">SUM(BV53:BV67)</f>
         <v>591572</v>
       </c>
       <c r="BW88" s="1"/>
@@ -12558,145 +12555,145 @@
       <c r="C89" s="1"/>
       <c r="D89" s="1"/>
       <c r="E89" s="1">
-        <f t="shared" ref="E89:AJ89" si="92">SUM(E68:E87)</f>
+        <f t="shared" ref="E89" si="92">SUM(E68:E87)</f>
         <v>88815</v>
       </c>
       <c r="F89" s="1"/>
       <c r="G89" s="1"/>
       <c r="H89" s="1">
-        <f t="shared" ref="H89:AM89" si="93">SUM(H68:H87)</f>
+        <f t="shared" ref="H89" si="93">SUM(H68:H87)</f>
         <v>12542</v>
       </c>
       <c r="I89" s="1"/>
       <c r="J89" s="1"/>
       <c r="K89" s="1">
-        <f t="shared" ref="K89:AP89" si="94">SUM(K68:K87)</f>
+        <f t="shared" ref="K89" si="94">SUM(K68:K87)</f>
         <v>20477</v>
       </c>
       <c r="L89" s="1"/>
       <c r="M89" s="1"/>
       <c r="N89" s="1">
-        <f t="shared" ref="N89:AS89" si="95">SUM(N68:N87)</f>
+        <f t="shared" ref="N89" si="95">SUM(N68:N87)</f>
         <v>8006</v>
       </c>
       <c r="O89" s="1"/>
       <c r="P89" s="1"/>
       <c r="Q89" s="1">
-        <f t="shared" ref="Q89:AV89" si="96">SUM(Q68:Q87)</f>
+        <f t="shared" ref="Q89" si="96">SUM(Q68:Q87)</f>
         <v>3063</v>
       </c>
       <c r="R89" s="1"/>
       <c r="S89" s="1"/>
       <c r="T89" s="1">
-        <f t="shared" ref="T89:AY89" si="97">SUM(T68:T87)</f>
+        <f t="shared" ref="T89" si="97">SUM(T68:T87)</f>
         <v>10431</v>
       </c>
       <c r="U89" s="1"/>
       <c r="V89" s="1"/>
       <c r="W89" s="1">
-        <f t="shared" ref="W89:BB89" si="98">SUM(W68:W87)</f>
+        <f t="shared" ref="W89" si="98">SUM(W68:W87)</f>
         <v>5897</v>
       </c>
       <c r="X89" s="1"/>
       <c r="Y89" s="1"/>
       <c r="Z89" s="1">
-        <f t="shared" ref="Z89:BE89" si="99">SUM(Z68:Z87)</f>
+        <f t="shared" ref="Z89" si="99">SUM(Z68:Z87)</f>
         <v>4068</v>
       </c>
       <c r="AA89" s="1"/>
       <c r="AB89" s="1"/>
       <c r="AC89" s="1">
-        <f t="shared" ref="AC89:BX89" si="100">SUM(AC68:AC87)</f>
+        <f t="shared" ref="AC89" si="100">SUM(AC68:AC87)</f>
         <v>9020</v>
       </c>
       <c r="AD89" s="1"/>
       <c r="AE89" s="1"/>
       <c r="AF89" s="1">
-        <f t="shared" ref="AF89:BX89" si="101">SUM(AF68:AF87)</f>
+        <f t="shared" ref="AF89" si="101">SUM(AF68:AF87)</f>
         <v>4862</v>
       </c>
       <c r="AG89" s="1"/>
       <c r="AH89" s="1"/>
       <c r="AI89" s="1">
-        <f t="shared" ref="AI89:BX89" si="102">SUM(AI68:AI87)</f>
+        <f t="shared" ref="AI89" si="102">SUM(AI68:AI87)</f>
         <v>5622</v>
       </c>
       <c r="AJ89" s="1"/>
       <c r="AK89" s="1"/>
       <c r="AL89" s="1">
-        <f t="shared" ref="AL89:BX89" si="103">SUM(AL68:AL87)</f>
+        <f t="shared" ref="AL89" si="103">SUM(AL68:AL87)</f>
         <v>6426</v>
       </c>
       <c r="AM89" s="1"/>
       <c r="AN89" s="1"/>
       <c r="AO89" s="1">
-        <f t="shared" ref="AO89:BX89" si="104">SUM(AO68:AO87)</f>
+        <f t="shared" ref="AO89" si="104">SUM(AO68:AO87)</f>
         <v>7787</v>
       </c>
       <c r="AP89" s="1"/>
       <c r="AQ89" s="1"/>
       <c r="AR89" s="1">
-        <f t="shared" ref="AR89:BX89" si="105">SUM(AR68:AR87)</f>
+        <f t="shared" ref="AR89" si="105">SUM(AR68:AR87)</f>
         <v>542</v>
       </c>
       <c r="AS89" s="1"/>
       <c r="AT89" s="1"/>
       <c r="AU89" s="1">
-        <f t="shared" ref="AU89:BX89" si="106">SUM(AU68:AU87)</f>
+        <f t="shared" ref="AU89" si="106">SUM(AU68:AU87)</f>
         <v>1009</v>
       </c>
       <c r="AV89" s="1"/>
       <c r="AW89" s="1"/>
       <c r="AX89" s="1">
-        <f t="shared" ref="AX89:BX89" si="107">SUM(AX68:AX87)</f>
+        <f t="shared" ref="AX89" si="107">SUM(AX68:AX87)</f>
         <v>78</v>
       </c>
       <c r="AY89" s="1"/>
       <c r="AZ89" s="1"/>
       <c r="BA89" s="1">
-        <f t="shared" ref="BA89:BX89" si="108">SUM(BA68:BA87)</f>
+        <f t="shared" ref="BA89" si="108">SUM(BA68:BA87)</f>
         <v>309</v>
       </c>
       <c r="BB89" s="1"/>
       <c r="BC89" s="1"/>
       <c r="BD89" s="1">
-        <f t="shared" ref="BD89:BX89" si="109">SUM(BD68:BD87)</f>
+        <f t="shared" ref="BD89" si="109">SUM(BD68:BD87)</f>
         <v>363961</v>
       </c>
       <c r="BE89" s="1"/>
       <c r="BF89" s="1"/>
       <c r="BG89" s="1">
-        <f t="shared" ref="BG89:BX89" si="110">SUM(BG68:BG87)</f>
+        <f t="shared" ref="BG89" si="110">SUM(BG68:BG87)</f>
         <v>202921</v>
       </c>
       <c r="BH89" s="1"/>
       <c r="BI89" s="1"/>
       <c r="BJ89" s="1">
-        <f t="shared" ref="BJ89:BX89" si="111">SUM(BJ68:BJ87)</f>
+        <f t="shared" ref="BJ89" si="111">SUM(BJ68:BJ87)</f>
         <v>205805</v>
       </c>
       <c r="BK89" s="1"/>
       <c r="BL89" s="1"/>
       <c r="BM89" s="1">
-        <f t="shared" ref="BM89:BX89" si="112">SUM(BM68:BM87)</f>
+        <f t="shared" ref="BM89" si="112">SUM(BM68:BM87)</f>
         <v>16981</v>
       </c>
       <c r="BN89" s="1"/>
       <c r="BO89" s="1"/>
       <c r="BP89" s="1">
-        <f t="shared" ref="BP89:BX89" si="113">SUM(BP68:BP87)</f>
+        <f t="shared" ref="BP89" si="113">SUM(BP68:BP87)</f>
         <v>-5491</v>
       </c>
       <c r="BQ89" s="1"/>
       <c r="BR89" s="1"/>
       <c r="BS89" s="1">
-        <f t="shared" ref="BS89:BX89" si="114">SUM(BS68:BS87)</f>
+        <f t="shared" ref="BS89" si="114">SUM(BS68:BS87)</f>
         <v>19956</v>
       </c>
       <c r="BT89" s="1"/>
       <c r="BU89" s="1"/>
       <c r="BV89" s="1">
-        <f t="shared" ref="BV89:BX89" si="115">SUM(BV68:BV87)</f>
+        <f t="shared" ref="BV89" si="115">SUM(BV68:BV87)</f>
         <v>1056620</v>
       </c>
       <c r="BW89" s="1"/>
@@ -12704,7 +12701,7 @@
     </row>
     <row r="90" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A90" s="10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B90" s="1">
         <f>B88+B89</f>
@@ -12865,7 +12862,7 @@
     </row>
     <row r="92" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="AS92" s="1"/>
       <c r="AT92" s="1"/>
@@ -12880,7 +12877,7 @@
     </row>
     <row r="94" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AS94" s="1"/>
       <c r="AT94" s="1"/>
@@ -12892,14 +12889,14 @@
       <c r="BL95" s="1"/>
     </row>
     <row r="96" spans="1:84" x14ac:dyDescent="0.25">
-      <c r="B96" s="21" t="s">
+      <c r="B96" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="C96" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D96" s="20" t="s">
         <v>51</v>
-      </c>
-      <c r="C96" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="D96" s="21" t="s">
-        <v>52</v>
       </c>
       <c r="BK96" s="1"/>
       <c r="BL96" s="1"/>
@@ -13238,7 +13235,7 @@
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B119" s="1">
         <v>-1825</v>
@@ -13252,7 +13249,7 @@
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B120" s="1">
         <v>7529</v>
@@ -13266,7 +13263,7 @@
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B121" s="1">
         <v>591572</v>
@@ -13320,21 +13317,21 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="17"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="17" t="s">
+      <c r="C7" s="27"/>
+      <c r="D7" s="27"/>
+      <c r="E7" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="F7" s="17"/>
-      <c r="G7" s="17"/>
-      <c r="H7" s="17" t="s">
+      <c r="F7" s="27"/>
+      <c r="G7" s="27"/>
+      <c r="H7" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="I7" s="17"/>
-      <c r="J7" s="17"/>
+      <c r="I7" s="27"/>
+      <c r="J7" s="27"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
@@ -13370,7 +13367,7 @@
       <c r="O8" s="1"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="19">
+      <c r="A9" s="18">
         <f t="shared" ref="A9:A22" si="0">A10-1</f>
         <v>1881</v>
       </c>
@@ -13409,7 +13406,7 @@
       <c r="O9" s="1"/>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="19">
+      <c r="A10" s="18">
         <f t="shared" si="0"/>
         <v>1882</v>
       </c>
@@ -13448,7 +13445,7 @@
       <c r="O10" s="1"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="19">
+      <c r="A11" s="18">
         <f t="shared" si="0"/>
         <v>1883</v>
       </c>
@@ -13487,7 +13484,7 @@
       <c r="O11" s="1"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="19">
+      <c r="A12" s="18">
         <f t="shared" si="0"/>
         <v>1884</v>
       </c>
@@ -13526,7 +13523,7 @@
       <c r="O12" s="1"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="19">
+      <c r="A13" s="18">
         <f t="shared" si="0"/>
         <v>1885</v>
       </c>
@@ -13565,7 +13562,7 @@
       <c r="O13" s="1"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="19">
+      <c r="A14" s="18">
         <f t="shared" si="0"/>
         <v>1886</v>
       </c>
@@ -13604,7 +13601,7 @@
       <c r="O14" s="1"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" s="19">
+      <c r="A15" s="18">
         <f t="shared" si="0"/>
         <v>1887</v>
       </c>
@@ -13643,7 +13640,7 @@
       <c r="O15" s="1"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="19">
+      <c r="A16" s="18">
         <f t="shared" si="0"/>
         <v>1888</v>
       </c>
@@ -13682,7 +13679,7 @@
       <c r="O16" s="1"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17" s="19">
+      <c r="A17" s="18">
         <f t="shared" si="0"/>
         <v>1889</v>
       </c>
@@ -13721,7 +13718,7 @@
       <c r="O17" s="1"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A18" s="19">
+      <c r="A18" s="18">
         <f t="shared" si="0"/>
         <v>1890</v>
       </c>
@@ -13760,7 +13757,7 @@
       <c r="O18" s="1"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" s="19">
+      <c r="A19" s="18">
         <f t="shared" si="0"/>
         <v>1891</v>
       </c>
@@ -13799,7 +13796,7 @@
       <c r="O19" s="1"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A20" s="19">
+      <c r="A20" s="18">
         <f t="shared" si="0"/>
         <v>1892</v>
       </c>
@@ -13838,7 +13835,7 @@
       <c r="O20" s="1"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A21" s="19">
+      <c r="A21" s="18">
         <f t="shared" si="0"/>
         <v>1893</v>
       </c>
@@ -13877,7 +13874,7 @@
       <c r="O21" s="1"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A22" s="19">
+      <c r="A22" s="18">
         <f t="shared" si="0"/>
         <v>1894</v>
       </c>
@@ -13916,11 +13913,11 @@
       <c r="O22" s="1"/>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A23" s="19">
+      <c r="A23" s="18">
         <f>A24-1</f>
         <v>1895</v>
       </c>
-      <c r="B23" s="22">
+      <c r="B23" s="21">
         <f t="shared" si="1"/>
         <v>-78419</v>
       </c>
@@ -14735,7 +14732,7 @@
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B44" s="5">
         <f>SUM(B9:B23)</f>
@@ -14783,7 +14780,7 @@
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B46" s="5">
         <f>B45+B44</f>
@@ -14815,8 +14812,8 @@
       <c r="O48" s="1"/>
     </row>
     <row r="49" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A49" s="23" t="s">
-        <v>61</v>
+      <c r="A49" s="22" t="s">
+        <v>60</v>
       </c>
       <c r="O49" s="1"/>
     </row>
@@ -14825,44 +14822,44 @@
     </row>
     <row r="51" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A51" s="2"/>
-      <c r="B51" s="17" t="s">
+      <c r="B51" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="C51" s="17"/>
-      <c r="D51" s="17"/>
-      <c r="E51" s="17" t="s">
+      <c r="C51" s="27"/>
+      <c r="D51" s="27"/>
+      <c r="E51" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="F51" s="17"/>
-      <c r="G51" s="17"/>
-      <c r="H51" s="17" t="s">
+      <c r="F51" s="27"/>
+      <c r="G51" s="27"/>
+      <c r="H51" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="I51" s="17"/>
-      <c r="J51" s="17"/>
-      <c r="K51" s="17" t="s">
+      <c r="I51" s="27"/>
+      <c r="J51" s="27"/>
+      <c r="K51" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="L51" s="17"/>
-      <c r="M51" s="17"/>
-      <c r="N51" s="17" t="s">
+      <c r="L51" s="27"/>
+      <c r="M51" s="27"/>
+      <c r="N51" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="O51" s="17"/>
-      <c r="P51" s="17"/>
-      <c r="Q51" s="17" t="s">
+      <c r="O51" s="27"/>
+      <c r="P51" s="27"/>
+      <c r="Q51" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="R51" s="17"/>
-      <c r="S51" s="17"/>
-      <c r="U51" s="24" t="s">
+      <c r="R51" s="27"/>
+      <c r="S51" s="27"/>
+      <c r="U51" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="Y51" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="AC51" s="25" t="s">
-        <v>58</v>
+      <c r="Y51" s="25" t="s">
+        <v>55</v>
+      </c>
+      <c r="AC51" s="24" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="52" spans="1:31" x14ac:dyDescent="0.25">
@@ -14952,7 +14949,7 @@
       </c>
     </row>
     <row r="53" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A53" s="19">
+      <c r="A53" s="18">
         <f t="shared" ref="A53:A66" si="13">A54-1</f>
         <v>1881</v>
       </c>
@@ -14986,9 +14983,9 @@
       <c r="J53" s="1">
         <v>7392</v>
       </c>
-      <c r="K53" s="18"/>
-      <c r="L53" s="18"/>
-      <c r="M53" s="18"/>
+      <c r="K53" s="17"/>
+      <c r="L53" s="17"/>
+      <c r="M53" s="17"/>
       <c r="N53" s="1">
         <v>2099</v>
       </c>
@@ -15019,15 +15016,15 @@
         <v>231516</v>
       </c>
       <c r="Y53" s="1">
-        <f t="shared" ref="Y52:Y60" si="18">B53+E53+H53+K53+N53+Q53</f>
+        <f t="shared" ref="Y53:Y60" si="18">B53+E53+H53+K53+N53+Q53</f>
         <v>32313</v>
       </c>
       <c r="Z53" s="1">
-        <f t="shared" ref="Z52:Z60" si="19">C53+F53+I53+L53+O53+R53</f>
+        <f t="shared" ref="Z53:Z60" si="19">C53+F53+I53+L53+O53+R53</f>
         <v>263849</v>
       </c>
       <c r="AA53" s="1">
-        <f t="shared" ref="AA52:AA60" si="20">D53+G53+J53+M53+P53+S53</f>
+        <f t="shared" ref="AA53:AA60" si="20">D53+G53+J53+M53+P53+S53</f>
         <v>231536</v>
       </c>
       <c r="AC53" s="1">
@@ -15044,7 +15041,7 @@
       </c>
     </row>
     <row r="54" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A54" s="19">
+      <c r="A54" s="18">
         <f t="shared" si="13"/>
         <v>1882</v>
       </c>
@@ -15078,12 +15075,12 @@
       <c r="J54" s="1">
         <v>8538</v>
       </c>
-      <c r="K54" s="18"/>
-      <c r="L54" s="18"/>
-      <c r="M54" s="18"/>
-      <c r="N54" s="18"/>
-      <c r="O54" s="18"/>
-      <c r="P54" s="18"/>
+      <c r="K54" s="17"/>
+      <c r="L54" s="17"/>
+      <c r="M54" s="17"/>
+      <c r="N54" s="17"/>
+      <c r="O54" s="17"/>
+      <c r="P54" s="17"/>
       <c r="Q54" s="1">
         <f t="shared" si="17"/>
         <v>-10</v>
@@ -15130,7 +15127,7 @@
       </c>
     </row>
     <row r="55" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A55" s="19">
+      <c r="A55" s="18">
         <f t="shared" si="13"/>
         <v>1883</v>
       </c>
@@ -15164,12 +15161,12 @@
       <c r="J55" s="1">
         <v>7215</v>
       </c>
-      <c r="K55" s="18"/>
-      <c r="L55" s="18"/>
-      <c r="M55" s="18"/>
-      <c r="N55" s="18"/>
-      <c r="O55" s="18"/>
-      <c r="P55" s="18"/>
+      <c r="K55" s="17"/>
+      <c r="L55" s="17"/>
+      <c r="M55" s="17"/>
+      <c r="N55" s="17"/>
+      <c r="O55" s="17"/>
+      <c r="P55" s="17"/>
       <c r="Q55" s="1">
         <f t="shared" si="17"/>
         <v>0</v>
@@ -15210,7 +15207,7 @@
       </c>
     </row>
     <row r="56" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A56" s="19">
+      <c r="A56" s="18">
         <f t="shared" si="13"/>
         <v>1884</v>
       </c>
@@ -15244,12 +15241,12 @@
       <c r="J56" s="1">
         <v>7388</v>
       </c>
-      <c r="K56" s="18"/>
-      <c r="L56" s="18"/>
-      <c r="M56" s="18"/>
-      <c r="N56" s="18"/>
-      <c r="O56" s="18"/>
-      <c r="P56" s="18"/>
+      <c r="K56" s="17"/>
+      <c r="L56" s="17"/>
+      <c r="M56" s="17"/>
+      <c r="N56" s="17"/>
+      <c r="O56" s="17"/>
+      <c r="P56" s="17"/>
       <c r="Q56" s="1">
         <f t="shared" si="17"/>
         <v>1</v>
@@ -15296,7 +15293,7 @@
       </c>
     </row>
     <row r="57" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A57" s="19">
+      <c r="A57" s="18">
         <f t="shared" si="13"/>
         <v>1885</v>
       </c>
@@ -15330,12 +15327,12 @@
       <c r="J57" s="1">
         <v>9803</v>
       </c>
-      <c r="K57" s="18"/>
-      <c r="L57" s="18"/>
-      <c r="M57" s="18"/>
-      <c r="N57" s="18"/>
-      <c r="O57" s="18"/>
-      <c r="P57" s="18"/>
+      <c r="K57" s="17"/>
+      <c r="L57" s="17"/>
+      <c r="M57" s="17"/>
+      <c r="N57" s="17"/>
+      <c r="O57" s="17"/>
+      <c r="P57" s="17"/>
       <c r="Q57" s="1">
         <f t="shared" si="17"/>
         <v>0</v>
@@ -15376,7 +15373,7 @@
       </c>
     </row>
     <row r="58" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A58" s="19">
+      <c r="A58" s="18">
         <f t="shared" si="13"/>
         <v>1886</v>
       </c>
@@ -15410,12 +15407,12 @@
       <c r="J58" s="1">
         <v>8814</v>
       </c>
-      <c r="K58" s="18"/>
-      <c r="L58" s="18"/>
-      <c r="M58" s="18"/>
-      <c r="N58" s="18"/>
-      <c r="O58" s="18"/>
-      <c r="P58" s="18"/>
+      <c r="K58" s="17"/>
+      <c r="L58" s="17"/>
+      <c r="M58" s="17"/>
+      <c r="N58" s="17"/>
+      <c r="O58" s="17"/>
+      <c r="P58" s="17"/>
       <c r="Q58" s="1">
         <f t="shared" si="17"/>
         <v>-12</v>
@@ -15462,7 +15459,7 @@
       </c>
     </row>
     <row r="59" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A59" s="19">
+      <c r="A59" s="18">
         <f t="shared" si="13"/>
         <v>1887</v>
       </c>
@@ -15496,15 +15493,15 @@
       <c r="J59" s="1">
         <v>2014</v>
       </c>
-      <c r="K59" s="18"/>
-      <c r="L59" s="18"/>
-      <c r="M59" s="18"/>
-      <c r="N59" s="18"/>
-      <c r="O59" s="18"/>
-      <c r="P59" s="18"/>
-      <c r="Q59" s="18"/>
-      <c r="R59" s="18"/>
-      <c r="S59" s="18"/>
+      <c r="K59" s="17"/>
+      <c r="L59" s="17"/>
+      <c r="M59" s="17"/>
+      <c r="N59" s="17"/>
+      <c r="O59" s="17"/>
+      <c r="P59" s="17"/>
+      <c r="Q59" s="17"/>
+      <c r="R59" s="17"/>
+      <c r="S59" s="17"/>
       <c r="U59" s="1">
         <f t="shared" si="21"/>
         <v>44769</v>
@@ -15541,7 +15538,7 @@
       </c>
     </row>
     <row r="60" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A60" s="19">
+      <c r="A60" s="18">
         <f t="shared" si="13"/>
         <v>1888</v>
       </c>
@@ -15575,15 +15572,15 @@
       <c r="J60">
         <v>213</v>
       </c>
-      <c r="K60" s="18"/>
-      <c r="L60" s="18"/>
-      <c r="M60" s="18"/>
-      <c r="N60" s="18"/>
-      <c r="O60" s="18"/>
-      <c r="P60" s="18"/>
-      <c r="Q60" s="18"/>
-      <c r="R60" s="18"/>
-      <c r="S60" s="18"/>
+      <c r="K60" s="17"/>
+      <c r="L60" s="17"/>
+      <c r="M60" s="17"/>
+      <c r="N60" s="17"/>
+      <c r="O60" s="17"/>
+      <c r="P60" s="17"/>
+      <c r="Q60" s="17"/>
+      <c r="R60" s="17"/>
+      <c r="S60" s="17"/>
       <c r="U60" s="1">
         <f t="shared" si="21"/>
         <v>75001</v>
@@ -15620,28 +15617,28 @@
       </c>
     </row>
     <row r="61" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A61" s="19">
+      <c r="A61" s="18">
         <f t="shared" si="13"/>
         <v>1889</v>
       </c>
-      <c r="B61" s="18"/>
-      <c r="C61" s="18"/>
-      <c r="D61" s="18"/>
-      <c r="E61" s="18"/>
-      <c r="F61" s="18"/>
-      <c r="G61" s="18"/>
-      <c r="H61" s="18"/>
-      <c r="I61" s="18"/>
-      <c r="J61" s="18"/>
-      <c r="K61" s="18"/>
-      <c r="L61" s="18"/>
-      <c r="M61" s="18"/>
-      <c r="N61" s="18"/>
-      <c r="O61" s="18"/>
-      <c r="P61" s="18"/>
-      <c r="Q61" s="18"/>
-      <c r="R61" s="18"/>
-      <c r="S61" s="18"/>
+      <c r="B61" s="17"/>
+      <c r="C61" s="17"/>
+      <c r="D61" s="17"/>
+      <c r="E61" s="17"/>
+      <c r="F61" s="17"/>
+      <c r="G61" s="17"/>
+      <c r="H61" s="17"/>
+      <c r="I61" s="17"/>
+      <c r="J61" s="17"/>
+      <c r="K61" s="17"/>
+      <c r="L61" s="17"/>
+      <c r="M61" s="17"/>
+      <c r="N61" s="17"/>
+      <c r="O61" s="17"/>
+      <c r="P61" s="17"/>
+      <c r="Q61" s="17"/>
+      <c r="R61" s="17"/>
+      <c r="S61" s="17"/>
       <c r="U61" s="1">
         <f t="shared" si="21"/>
         <v>30882</v>
@@ -15654,28 +15651,28 @@
       </c>
     </row>
     <row r="62" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A62" s="19">
+      <c r="A62" s="18">
         <f t="shared" si="13"/>
         <v>1890</v>
       </c>
-      <c r="B62" s="18"/>
-      <c r="C62" s="18"/>
-      <c r="D62" s="18"/>
-      <c r="E62" s="18"/>
-      <c r="F62" s="18"/>
-      <c r="G62" s="18"/>
-      <c r="H62" s="18"/>
-      <c r="I62" s="18"/>
-      <c r="J62" s="18"/>
-      <c r="K62" s="18"/>
-      <c r="L62" s="18"/>
-      <c r="M62" s="18"/>
-      <c r="N62" s="18"/>
-      <c r="O62" s="18"/>
-      <c r="P62" s="18"/>
-      <c r="Q62" s="18"/>
-      <c r="R62" s="18"/>
-      <c r="S62" s="18"/>
+      <c r="B62" s="17"/>
+      <c r="C62" s="17"/>
+      <c r="D62" s="17"/>
+      <c r="E62" s="17"/>
+      <c r="F62" s="17"/>
+      <c r="G62" s="17"/>
+      <c r="H62" s="17"/>
+      <c r="I62" s="17"/>
+      <c r="J62" s="17"/>
+      <c r="K62" s="17"/>
+      <c r="L62" s="17"/>
+      <c r="M62" s="17"/>
+      <c r="N62" s="17"/>
+      <c r="O62" s="17"/>
+      <c r="P62" s="17"/>
+      <c r="Q62" s="17"/>
+      <c r="R62" s="17"/>
+      <c r="S62" s="17"/>
       <c r="U62" s="1">
         <f t="shared" si="21"/>
         <v>50014</v>
@@ -15688,28 +15685,28 @@
       </c>
     </row>
     <row r="63" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A63" s="19">
+      <c r="A63" s="18">
         <f t="shared" si="13"/>
         <v>1891</v>
       </c>
-      <c r="B63" s="18"/>
-      <c r="C63" s="18"/>
-      <c r="D63" s="18"/>
-      <c r="E63" s="18"/>
-      <c r="F63" s="18"/>
-      <c r="G63" s="18"/>
-      <c r="H63" s="18"/>
-      <c r="I63" s="18"/>
-      <c r="J63" s="18"/>
-      <c r="K63" s="18"/>
-      <c r="L63" s="18"/>
-      <c r="M63" s="18"/>
-      <c r="N63" s="18"/>
-      <c r="O63" s="18"/>
-      <c r="P63" s="18"/>
-      <c r="Q63" s="18"/>
-      <c r="R63" s="18"/>
-      <c r="S63" s="18"/>
+      <c r="B63" s="17"/>
+      <c r="C63" s="17"/>
+      <c r="D63" s="17"/>
+      <c r="E63" s="17"/>
+      <c r="F63" s="17"/>
+      <c r="G63" s="17"/>
+      <c r="H63" s="17"/>
+      <c r="I63" s="17"/>
+      <c r="J63" s="17"/>
+      <c r="K63" s="17"/>
+      <c r="L63" s="17"/>
+      <c r="M63" s="17"/>
+      <c r="N63" s="17"/>
+      <c r="O63" s="17"/>
+      <c r="P63" s="17"/>
+      <c r="Q63" s="17"/>
+      <c r="R63" s="17"/>
+      <c r="S63" s="17"/>
       <c r="U63" s="1">
         <f t="shared" si="21"/>
         <v>15917</v>
@@ -15722,28 +15719,28 @@
       </c>
     </row>
     <row r="64" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A64" s="19">
+      <c r="A64" s="18">
         <f t="shared" si="13"/>
         <v>1892</v>
       </c>
-      <c r="B64" s="18"/>
-      <c r="C64" s="18"/>
-      <c r="D64" s="18"/>
-      <c r="E64" s="18"/>
-      <c r="F64" s="18"/>
-      <c r="G64" s="18"/>
-      <c r="H64" s="18"/>
-      <c r="I64" s="18"/>
-      <c r="J64" s="18"/>
-      <c r="K64" s="18"/>
-      <c r="L64" s="18"/>
-      <c r="M64" s="18"/>
-      <c r="N64" s="18"/>
-      <c r="O64" s="18"/>
-      <c r="P64" s="18"/>
-      <c r="Q64" s="18"/>
-      <c r="R64" s="18"/>
-      <c r="S64" s="18"/>
+      <c r="B64" s="17"/>
+      <c r="C64" s="17"/>
+      <c r="D64" s="17"/>
+      <c r="E64" s="17"/>
+      <c r="F64" s="17"/>
+      <c r="G64" s="17"/>
+      <c r="H64" s="17"/>
+      <c r="I64" s="17"/>
+      <c r="J64" s="17"/>
+      <c r="K64" s="17"/>
+      <c r="L64" s="17"/>
+      <c r="M64" s="17"/>
+      <c r="N64" s="17"/>
+      <c r="O64" s="17"/>
+      <c r="P64" s="17"/>
+      <c r="Q64" s="17"/>
+      <c r="R64" s="17"/>
+      <c r="S64" s="17"/>
       <c r="U64" s="1">
         <f t="shared" si="21"/>
         <v>12069</v>
@@ -15756,28 +15753,28 @@
       </c>
     </row>
     <row r="65" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A65" s="19">
+      <c r="A65" s="18">
         <f t="shared" si="13"/>
         <v>1893</v>
       </c>
-      <c r="B65" s="18"/>
-      <c r="C65" s="18"/>
-      <c r="D65" s="18"/>
-      <c r="E65" s="18"/>
-      <c r="F65" s="18"/>
-      <c r="G65" s="18"/>
-      <c r="H65" s="18"/>
-      <c r="I65" s="18"/>
-      <c r="J65" s="18"/>
-      <c r="K65" s="18"/>
-      <c r="L65" s="18"/>
-      <c r="M65" s="18"/>
-      <c r="N65" s="18"/>
-      <c r="O65" s="18"/>
-      <c r="P65" s="18"/>
-      <c r="Q65" s="18"/>
-      <c r="R65" s="18"/>
-      <c r="S65" s="18"/>
+      <c r="B65" s="17"/>
+      <c r="C65" s="17"/>
+      <c r="D65" s="17"/>
+      <c r="E65" s="17"/>
+      <c r="F65" s="17"/>
+      <c r="G65" s="17"/>
+      <c r="H65" s="17"/>
+      <c r="I65" s="17"/>
+      <c r="J65" s="17"/>
+      <c r="K65" s="17"/>
+      <c r="L65" s="17"/>
+      <c r="M65" s="17"/>
+      <c r="N65" s="17"/>
+      <c r="O65" s="17"/>
+      <c r="P65" s="17"/>
+      <c r="Q65" s="17"/>
+      <c r="R65" s="17"/>
+      <c r="S65" s="17"/>
       <c r="U65" s="1">
         <f t="shared" si="21"/>
         <v>31556</v>
@@ -15790,28 +15787,28 @@
       </c>
     </row>
     <row r="66" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A66" s="19">
+      <c r="A66" s="18">
         <f t="shared" si="13"/>
         <v>1894</v>
       </c>
-      <c r="B66" s="18"/>
-      <c r="C66" s="18"/>
-      <c r="D66" s="18"/>
-      <c r="E66" s="18"/>
-      <c r="F66" s="18"/>
-      <c r="G66" s="18"/>
-      <c r="H66" s="18"/>
-      <c r="I66" s="18"/>
-      <c r="J66" s="18"/>
-      <c r="K66" s="18"/>
-      <c r="L66" s="18"/>
-      <c r="M66" s="18"/>
-      <c r="N66" s="18"/>
-      <c r="O66" s="18"/>
-      <c r="P66" s="18"/>
-      <c r="Q66" s="18"/>
-      <c r="R66" s="18"/>
-      <c r="S66" s="18"/>
+      <c r="B66" s="17"/>
+      <c r="C66" s="17"/>
+      <c r="D66" s="17"/>
+      <c r="E66" s="17"/>
+      <c r="F66" s="17"/>
+      <c r="G66" s="17"/>
+      <c r="H66" s="17"/>
+      <c r="I66" s="17"/>
+      <c r="J66" s="17"/>
+      <c r="K66" s="17"/>
+      <c r="L66" s="17"/>
+      <c r="M66" s="17"/>
+      <c r="N66" s="17"/>
+      <c r="O66" s="17"/>
+      <c r="P66" s="17"/>
+      <c r="Q66" s="17"/>
+      <c r="R66" s="17"/>
+      <c r="S66" s="17"/>
       <c r="U66" s="1">
         <f t="shared" si="21"/>
         <v>72247</v>
@@ -15824,28 +15821,28 @@
       </c>
     </row>
     <row r="67" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A67" s="19">
+      <c r="A67" s="18">
         <f>A68-1</f>
         <v>1895</v>
       </c>
-      <c r="B67" s="18"/>
-      <c r="C67" s="18"/>
-      <c r="D67" s="18"/>
-      <c r="E67" s="18"/>
-      <c r="F67" s="18"/>
-      <c r="G67" s="18"/>
-      <c r="H67" s="18"/>
-      <c r="I67" s="18"/>
-      <c r="J67" s="18"/>
-      <c r="K67" s="18"/>
-      <c r="L67" s="18"/>
-      <c r="M67" s="18"/>
-      <c r="N67" s="18"/>
-      <c r="O67" s="18"/>
-      <c r="P67" s="18"/>
-      <c r="Q67" s="18"/>
-      <c r="R67" s="18"/>
-      <c r="S67" s="18"/>
+      <c r="B67" s="17"/>
+      <c r="C67" s="17"/>
+      <c r="D67" s="17"/>
+      <c r="E67" s="17"/>
+      <c r="F67" s="17"/>
+      <c r="G67" s="17"/>
+      <c r="H67" s="17"/>
+      <c r="I67" s="17"/>
+      <c r="J67" s="17"/>
+      <c r="K67" s="17"/>
+      <c r="L67" s="17"/>
+      <c r="M67" s="17"/>
+      <c r="N67" s="17"/>
+      <c r="O67" s="17"/>
+      <c r="P67" s="17"/>
+      <c r="Q67" s="17"/>
+      <c r="R67" s="17"/>
+      <c r="S67" s="17"/>
       <c r="U67" s="1">
         <f t="shared" si="21"/>
         <v>-78419</v>
@@ -17856,7 +17853,7 @@
     </row>
     <row r="88" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A88" s="10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B88" s="5">
         <f>SUM(B53:B67)</f>
@@ -17865,31 +17862,31 @@
       <c r="C88" s="5"/>
       <c r="D88" s="5"/>
       <c r="E88" s="5">
-        <f t="shared" ref="E88:S88" si="38">SUM(E53:E67)</f>
+        <f t="shared" ref="E88" si="38">SUM(E53:E67)</f>
         <v>71263</v>
       </c>
       <c r="F88" s="5"/>
       <c r="G88" s="5"/>
       <c r="H88" s="5">
-        <f t="shared" ref="H88:S88" si="39">SUM(H53:H67)</f>
+        <f t="shared" ref="H88" si="39">SUM(H53:H67)</f>
         <v>5980</v>
       </c>
       <c r="I88" s="5"/>
       <c r="J88" s="5"/>
       <c r="K88" s="5">
-        <f t="shared" ref="K88:S88" si="40">SUM(K53:K67)</f>
+        <f t="shared" ref="K88" si="40">SUM(K53:K67)</f>
         <v>0</v>
       </c>
       <c r="L88" s="5"/>
       <c r="M88" s="5"/>
       <c r="N88" s="5">
-        <f t="shared" ref="N88:S88" si="41">SUM(N53:N67)</f>
+        <f t="shared" ref="N88" si="41">SUM(N53:N67)</f>
         <v>2099</v>
       </c>
       <c r="O88" s="5"/>
       <c r="P88" s="5"/>
       <c r="Q88" s="5">
-        <f t="shared" ref="Q88:S88" si="42">SUM(Q53:Q67)</f>
+        <f t="shared" ref="Q88" si="42">SUM(Q53:Q67)</f>
         <v>-4</v>
       </c>
       <c r="R88" s="5"/>
@@ -17950,7 +17947,7 @@
     </row>
     <row r="90" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B90" s="5">
         <f>B89+B88</f>
@@ -18046,7 +18043,7 @@
     <col min="27" max="27" width="7.28515625" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="7.42578125" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.28515625" customWidth="1"/>
     <col min="31" max="31" width="10.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -18055,22 +18052,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D1" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="D1" s="8" t="s">
+      <c r="E1" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="F1" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="F1" s="8" t="s">
-        <v>45</v>
-      </c>
       <c r="G1" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H1" s="8" t="s">
         <v>7</v>
@@ -18139,550 +18136,1273 @@
         <v>37</v>
       </c>
       <c r="AD1" s="8" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="AE1" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A2" s="27">
+      <c r="A2" s="26">
         <v>1881</v>
       </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="8"/>
-      <c r="L2" s="8"/>
-      <c r="M2" s="8"/>
-      <c r="N2" s="8"/>
-      <c r="O2" s="8"/>
-      <c r="P2" s="8"/>
-      <c r="Q2" s="8"/>
-      <c r="R2" s="8"/>
-      <c r="S2" s="8"/>
-      <c r="T2" s="8"/>
-      <c r="U2" s="8"/>
-      <c r="V2" s="8"/>
-      <c r="W2" s="8"/>
-      <c r="X2" s="8"/>
-      <c r="Y2" s="8"/>
-      <c r="Z2" s="8"/>
-      <c r="AA2" s="8"/>
-      <c r="AB2" s="8"/>
-      <c r="AC2" s="8"/>
-      <c r="AD2" s="8"/>
-      <c r="AE2" s="8"/>
+      <c r="B2" s="1">
+        <v>23580</v>
+      </c>
+      <c r="C2" s="1">
+        <v>5725</v>
+      </c>
+      <c r="D2" s="1">
+        <v>892</v>
+      </c>
+      <c r="F2" s="1">
+        <v>2099</v>
+      </c>
+      <c r="G2" s="1">
+        <v>17</v>
+      </c>
+      <c r="H2" s="1">
+        <v>31266</v>
+      </c>
+      <c r="I2" s="1">
+        <v>15527</v>
+      </c>
+      <c r="J2" s="1">
+        <v>-366</v>
+      </c>
+      <c r="K2" s="1">
+        <v>-294</v>
+      </c>
+      <c r="L2" s="1">
+        <v>7</v>
+      </c>
+      <c r="M2" s="1">
+        <v>-159</v>
+      </c>
+      <c r="N2" s="1">
+        <v>-3</v>
+      </c>
+      <c r="O2" s="1">
+        <v>-55</v>
+      </c>
+      <c r="P2" s="1">
+        <v>58</v>
+      </c>
+      <c r="Q2" s="1">
+        <v>-76</v>
+      </c>
+      <c r="R2" s="1">
+        <v>119</v>
+      </c>
+      <c r="S2" s="1">
+        <v>598</v>
+      </c>
+      <c r="T2" s="1">
+        <v>-18</v>
+      </c>
+      <c r="U2" s="1">
+        <v>122</v>
+      </c>
+      <c r="V2" s="1">
+        <v>-27</v>
+      </c>
+      <c r="W2" s="1">
+        <v>6</v>
+      </c>
+      <c r="X2" s="1">
+        <v>-2</v>
+      </c>
+      <c r="Y2" s="1">
+        <v>26</v>
+      </c>
+      <c r="Z2" s="1">
+        <v>-942</v>
+      </c>
+      <c r="AA2" s="1">
+        <v>5</v>
+      </c>
+      <c r="AB2" s="1">
+        <v>890</v>
+      </c>
+      <c r="AC2" s="1">
+        <v>-2</v>
+      </c>
+      <c r="AD2" s="1">
+        <v>20</v>
+      </c>
+      <c r="AE2" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="3" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A3" s="27">
+      <c r="A3" s="26">
         <f t="shared" ref="A3:A15" si="0">A4-1</f>
         <v>1882</v>
       </c>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="8"/>
-      <c r="J3" s="8"/>
-      <c r="K3" s="8"/>
-      <c r="L3" s="8"/>
-      <c r="M3" s="8"/>
-      <c r="N3" s="8"/>
-      <c r="O3" s="8"/>
-      <c r="P3" s="8"/>
-      <c r="Q3" s="8"/>
-      <c r="R3" s="8"/>
-      <c r="S3" s="8"/>
-      <c r="T3" s="8"/>
-      <c r="U3" s="8"/>
-      <c r="V3" s="8"/>
-      <c r="W3" s="8"/>
-      <c r="X3" s="8"/>
-      <c r="Y3" s="8"/>
-      <c r="Z3" s="8"/>
-      <c r="AA3" s="8"/>
-      <c r="AB3" s="8"/>
-      <c r="AC3" s="8"/>
-      <c r="AD3" s="8"/>
-      <c r="AE3" s="8"/>
+      <c r="B3" s="1">
+        <v>31320</v>
+      </c>
+      <c r="C3" s="1">
+        <v>4379</v>
+      </c>
+      <c r="D3" s="1">
+        <v>902</v>
+      </c>
+      <c r="G3" s="1">
+        <v>-10</v>
+      </c>
+      <c r="H3" s="1">
+        <v>19184</v>
+      </c>
+      <c r="I3" s="1">
+        <v>37463</v>
+      </c>
+      <c r="J3" s="1">
+        <v>-493</v>
+      </c>
+      <c r="K3" s="1">
+        <v>599</v>
+      </c>
+      <c r="L3" s="1">
+        <v>-11</v>
+      </c>
+      <c r="M3" s="1">
+        <v>-781</v>
+      </c>
+      <c r="N3" s="1">
+        <v>79</v>
+      </c>
+      <c r="O3" s="1">
+        <v>-56</v>
+      </c>
+      <c r="P3" s="1">
+        <v>387</v>
+      </c>
+      <c r="Q3" s="1">
+        <v>-2</v>
+      </c>
+      <c r="R3" s="1">
+        <v>526</v>
+      </c>
+      <c r="S3" s="1">
+        <v>419</v>
+      </c>
+      <c r="T3" s="1">
+        <v>-21</v>
+      </c>
+      <c r="U3" s="1">
+        <v>17</v>
+      </c>
+      <c r="V3" s="1">
+        <v>5</v>
+      </c>
+      <c r="W3" s="1">
+        <v>4</v>
+      </c>
+      <c r="X3" s="1">
+        <v>-2</v>
+      </c>
+      <c r="Y3" s="1">
+        <v>-3</v>
+      </c>
+      <c r="Z3" s="1">
+        <v>7068</v>
+      </c>
+      <c r="AA3" s="1">
+        <v>10</v>
+      </c>
+      <c r="AB3" s="1">
+        <v>3081</v>
+      </c>
+      <c r="AC3" s="1">
+        <v>35</v>
+      </c>
+      <c r="AD3" s="1">
+        <v>2</v>
+      </c>
+      <c r="AE3" s="1">
+        <v>77</v>
+      </c>
     </row>
     <row r="4" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A4" s="27">
+      <c r="A4" s="26">
         <f t="shared" si="0"/>
         <v>1883</v>
       </c>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="8"/>
-      <c r="K4" s="8"/>
-      <c r="L4" s="8"/>
-      <c r="M4" s="8"/>
-      <c r="N4" s="8"/>
-      <c r="O4" s="8"/>
-      <c r="P4" s="8"/>
-      <c r="Q4" s="8"/>
-      <c r="R4" s="8"/>
-      <c r="S4" s="8"/>
-      <c r="T4" s="8"/>
-      <c r="U4" s="8"/>
-      <c r="V4" s="8"/>
-      <c r="W4" s="8"/>
-      <c r="X4" s="8"/>
-      <c r="Y4" s="8"/>
-      <c r="Z4" s="8"/>
-      <c r="AA4" s="8"/>
-      <c r="AB4" s="8"/>
-      <c r="AC4" s="8"/>
-      <c r="AD4" s="8"/>
-      <c r="AE4" s="8"/>
+      <c r="B4" s="1">
+        <v>15017</v>
+      </c>
+      <c r="C4" s="1">
+        <v>6371</v>
+      </c>
+      <c r="D4" s="1">
+        <v>662</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0</v>
+      </c>
+      <c r="H4" s="1">
+        <v>15565</v>
+      </c>
+      <c r="I4" s="1">
+        <v>28795</v>
+      </c>
+      <c r="J4" s="1">
+        <v>1223</v>
+      </c>
+      <c r="K4" s="1">
+        <v>154</v>
+      </c>
+      <c r="L4" s="1">
+        <v>88</v>
+      </c>
+      <c r="M4" s="1">
+        <v>93</v>
+      </c>
+      <c r="N4" s="1">
+        <v>-1</v>
+      </c>
+      <c r="O4" s="1">
+        <v>-6</v>
+      </c>
+      <c r="P4" s="1">
+        <v>34</v>
+      </c>
+      <c r="Q4" s="1">
+        <v>90</v>
+      </c>
+      <c r="R4" s="1">
+        <v>-489</v>
+      </c>
+      <c r="S4" s="1">
+        <v>279</v>
+      </c>
+      <c r="T4" s="1">
+        <v>46</v>
+      </c>
+      <c r="U4" s="1">
+        <v>78</v>
+      </c>
+      <c r="V4" s="1">
+        <v>85</v>
+      </c>
+      <c r="W4" s="1">
+        <v>2</v>
+      </c>
+      <c r="X4" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="1">
+        <v>10</v>
+      </c>
+      <c r="Z4" s="1">
+        <v>4546</v>
+      </c>
+      <c r="AA4" s="1">
+        <v>-3</v>
+      </c>
+      <c r="AB4" s="1">
+        <v>4826</v>
+      </c>
+      <c r="AC4" s="1">
+        <v>-6</v>
+      </c>
+      <c r="AD4" s="1">
+        <v>-7</v>
+      </c>
+      <c r="AE4" s="1">
+        <v>49</v>
+      </c>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A5" s="27">
+      <c r="A5" s="26">
         <f t="shared" si="0"/>
         <v>1884</v>
       </c>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="8"/>
-      <c r="I5" s="8"/>
-      <c r="J5" s="8"/>
-      <c r="K5" s="8"/>
-      <c r="L5" s="8"/>
-      <c r="M5" s="8"/>
-      <c r="N5" s="8"/>
-      <c r="O5" s="8"/>
-      <c r="P5" s="8"/>
-      <c r="Q5" s="8"/>
-      <c r="R5" s="8"/>
-      <c r="S5" s="8"/>
-      <c r="T5" s="8"/>
-      <c r="U5" s="8"/>
-      <c r="V5" s="8"/>
-      <c r="W5" s="8"/>
-      <c r="X5" s="8"/>
-      <c r="Y5" s="8"/>
-      <c r="Z5" s="8"/>
-      <c r="AA5" s="8"/>
-      <c r="AB5" s="8"/>
-      <c r="AC5" s="8"/>
-      <c r="AD5" s="8"/>
-      <c r="AE5" s="8"/>
+      <c r="B5" s="1">
+        <v>23871</v>
+      </c>
+      <c r="C5" s="1">
+        <v>11873</v>
+      </c>
+      <c r="D5" s="1">
+        <v>2206</v>
+      </c>
+      <c r="G5" s="1">
+        <v>1</v>
+      </c>
+      <c r="H5" s="1">
+        <v>9047</v>
+      </c>
+      <c r="I5" s="1">
+        <v>26116</v>
+      </c>
+      <c r="J5" s="1">
+        <v>281</v>
+      </c>
+      <c r="K5" s="1">
+        <v>-371</v>
+      </c>
+      <c r="L5" s="1">
+        <v>59</v>
+      </c>
+      <c r="M5" s="1">
+        <v>29</v>
+      </c>
+      <c r="N5" s="1">
+        <v>45</v>
+      </c>
+      <c r="O5" s="1">
+        <v>12</v>
+      </c>
+      <c r="P5" s="1">
+        <v>102</v>
+      </c>
+      <c r="Q5" s="1">
+        <v>83</v>
+      </c>
+      <c r="R5" s="1">
+        <v>237</v>
+      </c>
+      <c r="S5" s="1">
+        <v>298</v>
+      </c>
+      <c r="T5" s="1">
+        <v>67</v>
+      </c>
+      <c r="U5" s="1">
+        <v>-83</v>
+      </c>
+      <c r="V5" s="1">
+        <v>17</v>
+      </c>
+      <c r="W5" s="1">
+        <v>-24</v>
+      </c>
+      <c r="X5" s="1">
+        <v>9</v>
+      </c>
+      <c r="Y5" s="1">
+        <v>26</v>
+      </c>
+      <c r="Z5" s="1">
+        <v>6357</v>
+      </c>
+      <c r="AA5" s="1">
+        <v>-8</v>
+      </c>
+      <c r="AB5" s="1">
+        <v>2773</v>
+      </c>
+      <c r="AC5" s="1">
+        <v>-7</v>
+      </c>
+      <c r="AD5" s="1">
+        <v>-85</v>
+      </c>
+      <c r="AE5" s="1">
+        <v>104</v>
+      </c>
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A6" s="27">
+      <c r="A6" s="26">
         <f t="shared" si="0"/>
         <v>1885</v>
       </c>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
-      <c r="J6" s="8"/>
-      <c r="K6" s="8"/>
-      <c r="L6" s="8"/>
-      <c r="M6" s="8"/>
-      <c r="N6" s="8"/>
-      <c r="O6" s="8"/>
-      <c r="P6" s="8"/>
-      <c r="Q6" s="8"/>
-      <c r="R6" s="8"/>
-      <c r="S6" s="8"/>
-      <c r="T6" s="8"/>
-      <c r="U6" s="8"/>
-      <c r="V6" s="8"/>
-      <c r="W6" s="8"/>
-      <c r="X6" s="8"/>
-      <c r="Y6" s="8"/>
-      <c r="Z6" s="8"/>
-      <c r="AA6" s="8"/>
-      <c r="AB6" s="8"/>
-      <c r="AC6" s="8"/>
-      <c r="AD6" s="8"/>
-      <c r="AE6" s="8"/>
+      <c r="B6" s="1">
+        <v>49904</v>
+      </c>
+      <c r="C6" s="1">
+        <v>13393</v>
+      </c>
+      <c r="D6" s="1">
+        <v>420</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0</v>
+      </c>
+      <c r="H6" s="1">
+        <v>15529</v>
+      </c>
+      <c r="I6" s="1">
+        <v>31366</v>
+      </c>
+      <c r="J6" s="1">
+        <v>2181</v>
+      </c>
+      <c r="K6" s="1">
+        <v>537</v>
+      </c>
+      <c r="L6" s="1">
+        <v>145</v>
+      </c>
+      <c r="M6" s="1">
+        <v>218</v>
+      </c>
+      <c r="N6" s="1">
+        <v>63</v>
+      </c>
+      <c r="O6" s="1">
+        <v>-43</v>
+      </c>
+      <c r="P6" s="1">
+        <v>-121</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>-90</v>
+      </c>
+      <c r="R6" s="1">
+        <v>33</v>
+      </c>
+      <c r="S6" s="1">
+        <v>39</v>
+      </c>
+      <c r="T6" s="1">
+        <v>17</v>
+      </c>
+      <c r="U6" s="1">
+        <v>358</v>
+      </c>
+      <c r="V6" s="1">
+        <v>13</v>
+      </c>
+      <c r="W6" s="1">
+        <v>-19</v>
+      </c>
+      <c r="X6" s="1">
+        <v>-3</v>
+      </c>
+      <c r="Y6" s="1">
+        <v>31</v>
+      </c>
+      <c r="Z6" s="1">
+        <v>4602</v>
+      </c>
+      <c r="AA6" s="1">
+        <v>-20</v>
+      </c>
+      <c r="AB6" s="1">
+        <v>3934</v>
+      </c>
+      <c r="AC6" s="1">
+        <v>4</v>
+      </c>
+      <c r="AD6" s="1">
+        <v>-34</v>
+      </c>
+      <c r="AE6" s="1">
+        <v>64</v>
+      </c>
     </row>
     <row r="7" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A7" s="27">
+      <c r="A7" s="26">
         <f t="shared" si="0"/>
         <v>1886</v>
       </c>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="8"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="8"/>
-      <c r="N7" s="8"/>
-      <c r="O7" s="8"/>
-      <c r="P7" s="8"/>
-      <c r="Q7" s="8"/>
-      <c r="R7" s="8"/>
-      <c r="S7" s="8"/>
-      <c r="T7" s="8"/>
-      <c r="U7" s="8"/>
-      <c r="V7" s="8"/>
-      <c r="W7" s="8"/>
-      <c r="X7" s="8"/>
-      <c r="Y7" s="8"/>
-      <c r="Z7" s="8"/>
-      <c r="AA7" s="8"/>
-      <c r="AB7" s="8"/>
-      <c r="AC7" s="8"/>
-      <c r="AD7" s="8"/>
-      <c r="AE7" s="8"/>
+      <c r="B7" s="1">
+        <v>44346</v>
+      </c>
+      <c r="C7" s="1">
+        <v>11146</v>
+      </c>
+      <c r="D7" s="1">
+        <v>716</v>
+      </c>
+      <c r="G7" s="1">
+        <v>-12</v>
+      </c>
+      <c r="H7" s="1">
+        <v>10819</v>
+      </c>
+      <c r="I7" s="1">
+        <v>29461</v>
+      </c>
+      <c r="J7" s="1">
+        <v>285</v>
+      </c>
+      <c r="K7" s="1">
+        <v>229</v>
+      </c>
+      <c r="L7" s="1">
+        <v>414</v>
+      </c>
+      <c r="M7" s="1">
+        <v>223</v>
+      </c>
+      <c r="N7" s="1">
+        <v>-93</v>
+      </c>
+      <c r="O7" s="1">
+        <v>11</v>
+      </c>
+      <c r="P7" s="1">
+        <v>317</v>
+      </c>
+      <c r="Q7" s="1">
+        <v>-8</v>
+      </c>
+      <c r="R7" s="1">
+        <v>-70</v>
+      </c>
+      <c r="S7" s="1">
+        <v>879</v>
+      </c>
+      <c r="T7" s="1">
+        <v>43</v>
+      </c>
+      <c r="U7" s="1">
+        <v>150</v>
+      </c>
+      <c r="V7" s="1">
+        <v>44</v>
+      </c>
+      <c r="W7" s="1">
+        <v>17</v>
+      </c>
+      <c r="X7" s="1">
+        <v>-6</v>
+      </c>
+      <c r="Y7" s="1">
+        <v>4</v>
+      </c>
+      <c r="Z7" s="1">
+        <v>14035</v>
+      </c>
+      <c r="AA7" s="1">
+        <v>-24</v>
+      </c>
+      <c r="AB7" s="1">
+        <v>3094</v>
+      </c>
+      <c r="AC7" s="1">
+        <v>-8</v>
+      </c>
+      <c r="AD7" s="1">
+        <v>17</v>
+      </c>
+      <c r="AE7" s="1">
+        <v>-297</v>
+      </c>
     </row>
     <row r="8" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A8" s="27">
+      <c r="A8" s="26">
         <f t="shared" si="0"/>
         <v>1887</v>
       </c>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
-      <c r="K8" s="8"/>
-      <c r="L8" s="8"/>
-      <c r="M8" s="8"/>
-      <c r="N8" s="8"/>
-      <c r="O8" s="8"/>
-      <c r="P8" s="8"/>
-      <c r="Q8" s="8"/>
-      <c r="R8" s="8"/>
-      <c r="S8" s="8"/>
-      <c r="T8" s="8"/>
-      <c r="U8" s="8"/>
-      <c r="V8" s="8"/>
-      <c r="W8" s="8"/>
-      <c r="X8" s="8"/>
-      <c r="Y8" s="8"/>
-      <c r="Z8" s="8"/>
-      <c r="AA8" s="8"/>
-      <c r="AB8" s="8"/>
-      <c r="AC8" s="8"/>
-      <c r="AD8" s="8"/>
-      <c r="AE8" s="8"/>
+      <c r="B8" s="1">
+        <v>37602</v>
+      </c>
+      <c r="C8" s="1">
+        <v>7028</v>
+      </c>
+      <c r="D8" s="1">
+        <v>139</v>
+      </c>
+      <c r="H8" s="1">
+        <v>2475</v>
+      </c>
+      <c r="I8" s="1">
+        <v>10626</v>
+      </c>
+      <c r="J8" s="1">
+        <v>-898</v>
+      </c>
+      <c r="K8" s="1">
+        <v>-429</v>
+      </c>
+      <c r="L8" s="1">
+        <v>-76</v>
+      </c>
+      <c r="M8" s="1">
+        <v>-294</v>
+      </c>
+      <c r="N8" s="1">
+        <v>-121</v>
+      </c>
+      <c r="O8" s="1">
+        <v>-27</v>
+      </c>
+      <c r="P8" s="1">
+        <v>93</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>-6</v>
+      </c>
+      <c r="R8" s="1">
+        <v>-14</v>
+      </c>
+      <c r="S8" s="1">
+        <v>312</v>
+      </c>
+      <c r="T8" s="1">
+        <v>-20</v>
+      </c>
+      <c r="U8" s="1">
+        <v>-37</v>
+      </c>
+      <c r="V8" s="1">
+        <v>13</v>
+      </c>
+      <c r="W8" s="1">
+        <v>-5</v>
+      </c>
+      <c r="X8" s="1">
+        <v>-17</v>
+      </c>
+      <c r="Y8" s="1">
+        <v>22</v>
+      </c>
+      <c r="Z8" s="1">
+        <v>8123</v>
+      </c>
+      <c r="AA8" s="1">
+        <v>-99</v>
+      </c>
+      <c r="AB8" s="1">
+        <v>2183</v>
+      </c>
+      <c r="AC8" s="1">
+        <v>-5</v>
+      </c>
+      <c r="AD8" s="1">
+        <v>-38</v>
+      </c>
+      <c r="AE8" s="1">
+        <v>-215</v>
+      </c>
     </row>
     <row r="9" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A9" s="27">
+      <c r="A9" s="26">
         <f t="shared" si="0"/>
         <v>1888</v>
       </c>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="8"/>
-      <c r="K9" s="8"/>
-      <c r="L9" s="8"/>
-      <c r="M9" s="8"/>
-      <c r="N9" s="8"/>
-      <c r="O9" s="8"/>
-      <c r="P9" s="8"/>
-      <c r="Q9" s="8"/>
-      <c r="R9" s="8"/>
-      <c r="S9" s="8"/>
-      <c r="T9" s="8"/>
-      <c r="U9" s="8"/>
-      <c r="V9" s="8"/>
-      <c r="W9" s="8"/>
-      <c r="X9" s="8"/>
-      <c r="Y9" s="8"/>
-      <c r="Z9" s="8"/>
-      <c r="AA9" s="8"/>
-      <c r="AB9" s="8"/>
-      <c r="AC9" s="8"/>
-      <c r="AD9" s="8"/>
-      <c r="AE9" s="8"/>
+      <c r="B9" s="1">
+        <v>63610</v>
+      </c>
+      <c r="C9" s="1">
+        <v>11348</v>
+      </c>
+      <c r="D9" s="1">
+        <v>43</v>
+      </c>
+      <c r="H9" s="1">
+        <v>4550</v>
+      </c>
+      <c r="I9" s="1">
+        <v>4271</v>
+      </c>
+      <c r="J9" s="1">
+        <v>-112</v>
+      </c>
+      <c r="K9" s="1">
+        <v>243</v>
+      </c>
+      <c r="L9" s="1">
+        <v>-75</v>
+      </c>
+      <c r="M9" s="1">
+        <v>5</v>
+      </c>
+      <c r="N9" s="1">
+        <v>74</v>
+      </c>
+      <c r="O9" s="1">
+        <v>8</v>
+      </c>
+      <c r="P9" s="1">
+        <v>174</v>
+      </c>
+      <c r="Q9" s="1">
+        <v>79</v>
+      </c>
+      <c r="R9" s="1">
+        <v>-27</v>
+      </c>
+      <c r="S9" s="1">
+        <v>661</v>
+      </c>
+      <c r="T9" s="1">
+        <v>44</v>
+      </c>
+      <c r="U9" s="1">
+        <v>30</v>
+      </c>
+      <c r="V9" s="1">
+        <v>11</v>
+      </c>
+      <c r="W9" s="1">
+        <v>-6</v>
+      </c>
+      <c r="X9" s="1">
+        <v>-12</v>
+      </c>
+      <c r="Y9" s="1">
+        <v>-9</v>
+      </c>
+      <c r="Z9" s="1">
+        <v>6129</v>
+      </c>
+      <c r="AA9" s="1">
+        <v>-34</v>
+      </c>
+      <c r="AB9" s="1">
+        <v>5927</v>
+      </c>
+      <c r="AC9" s="1">
+        <v>-3</v>
+      </c>
+      <c r="AD9" s="1">
+        <v>-71</v>
+      </c>
+      <c r="AE9" s="1">
+        <v>42</v>
+      </c>
     </row>
     <row r="10" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A10" s="27">
+      <c r="A10" s="26">
         <f t="shared" si="0"/>
         <v>1889</v>
       </c>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
-      <c r="J10" s="8"/>
-      <c r="K10" s="8"/>
-      <c r="L10" s="8"/>
-      <c r="M10" s="8"/>
-      <c r="N10" s="8"/>
-      <c r="O10" s="8"/>
-      <c r="P10" s="8"/>
-      <c r="Q10" s="8"/>
-      <c r="R10" s="8"/>
-      <c r="S10" s="8"/>
-      <c r="T10" s="8"/>
-      <c r="U10" s="8"/>
-      <c r="V10" s="8"/>
-      <c r="W10" s="8"/>
-      <c r="X10" s="8"/>
-      <c r="Y10" s="8"/>
-      <c r="Z10" s="8"/>
-      <c r="AA10" s="8"/>
-      <c r="AB10" s="8"/>
-      <c r="AC10" s="8"/>
-      <c r="AD10" s="8"/>
-      <c r="AE10" s="8"/>
+      <c r="H10" s="1">
+        <v>17395</v>
+      </c>
+      <c r="I10" s="1">
+        <v>16643</v>
+      </c>
+      <c r="J10" s="1">
+        <v>400</v>
+      </c>
+      <c r="K10" s="1">
+        <v>1075</v>
+      </c>
+      <c r="L10" s="1">
+        <v>920</v>
+      </c>
+      <c r="M10" s="1">
+        <v>252</v>
+      </c>
+      <c r="N10" s="1">
+        <v>-52</v>
+      </c>
+      <c r="O10" s="1">
+        <v>30</v>
+      </c>
+      <c r="P10" s="1">
+        <v>-25</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>4</v>
+      </c>
+      <c r="R10" s="1">
+        <v>335</v>
+      </c>
+      <c r="S10" s="1">
+        <v>296</v>
+      </c>
+      <c r="T10" s="1">
+        <v>-9</v>
+      </c>
+      <c r="U10" s="1">
+        <v>162</v>
+      </c>
+      <c r="V10" s="1">
+        <v>-11</v>
+      </c>
+      <c r="W10" s="1">
+        <v>36</v>
+      </c>
+      <c r="X10" s="1">
+        <v>12</v>
+      </c>
+      <c r="Y10" s="1">
+        <v>-2</v>
+      </c>
+      <c r="Z10" s="1">
+        <v>8526</v>
+      </c>
+      <c r="AA10" s="1">
+        <v>-100</v>
+      </c>
+      <c r="AB10" s="1">
+        <v>2995</v>
+      </c>
+      <c r="AC10" s="1">
+        <v>5</v>
+      </c>
+      <c r="AD10" s="1">
+        <v>23</v>
+      </c>
+      <c r="AE10" s="1">
+        <v>-19</v>
+      </c>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A11" s="27">
+      <c r="A11" s="26">
         <f t="shared" si="0"/>
         <v>1890</v>
       </c>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
-      <c r="J11" s="8"/>
-      <c r="K11" s="8"/>
-      <c r="L11" s="8"/>
-      <c r="M11" s="8"/>
-      <c r="N11" s="8"/>
-      <c r="O11" s="8"/>
-      <c r="P11" s="8"/>
-      <c r="Q11" s="8"/>
-      <c r="R11" s="8"/>
-      <c r="S11" s="8"/>
-      <c r="T11" s="8"/>
-      <c r="U11" s="8"/>
-      <c r="V11" s="8"/>
-      <c r="W11" s="8"/>
-      <c r="X11" s="8"/>
-      <c r="Y11" s="8"/>
-      <c r="Z11" s="8"/>
-      <c r="AA11" s="8"/>
-      <c r="AB11" s="8"/>
-      <c r="AC11" s="8"/>
-      <c r="AD11" s="8"/>
-      <c r="AE11" s="8"/>
+      <c r="H11" s="1">
+        <v>32800</v>
+      </c>
+      <c r="I11" s="1">
+        <v>15833</v>
+      </c>
+      <c r="J11" s="1">
+        <v>1581</v>
+      </c>
+      <c r="K11" s="1">
+        <v>868</v>
+      </c>
+      <c r="L11" s="1">
+        <v>290</v>
+      </c>
+      <c r="M11" s="1">
+        <v>446</v>
+      </c>
+      <c r="N11" s="1">
+        <v>113</v>
+      </c>
+      <c r="O11" s="1">
+        <v>12</v>
+      </c>
+      <c r="P11" s="1">
+        <v>1378</v>
+      </c>
+      <c r="Q11" s="1">
+        <v>9</v>
+      </c>
+      <c r="R11" s="1">
+        <v>612</v>
+      </c>
+      <c r="S11" s="1">
+        <v>426</v>
+      </c>
+      <c r="T11" s="1">
+        <v>21</v>
+      </c>
+      <c r="U11" s="1">
+        <v>291</v>
+      </c>
+      <c r="V11" s="1">
+        <v>-34</v>
+      </c>
+      <c r="W11" s="1">
+        <v>25</v>
+      </c>
+      <c r="X11" s="1">
+        <v>-24</v>
+      </c>
+      <c r="Y11" s="1">
+        <v>41</v>
+      </c>
+      <c r="Z11" s="1">
+        <v>12580</v>
+      </c>
+      <c r="AA11" s="1">
+        <v>-89</v>
+      </c>
+      <c r="AB11" s="1">
+        <v>3372</v>
+      </c>
+      <c r="AC11" s="1">
+        <v>-2</v>
+      </c>
+      <c r="AD11" s="1">
+        <v>-295</v>
+      </c>
+      <c r="AE11" s="1">
+        <v>-706</v>
+      </c>
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A12" s="27">
+      <c r="A12" s="26">
         <f t="shared" si="0"/>
         <v>1891</v>
       </c>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="8"/>
-      <c r="K12" s="8"/>
-      <c r="L12" s="8"/>
-      <c r="M12" s="8"/>
-      <c r="N12" s="8"/>
-      <c r="O12" s="8"/>
-      <c r="P12" s="8"/>
-      <c r="Q12" s="8"/>
-      <c r="R12" s="8"/>
-      <c r="S12" s="8"/>
-      <c r="T12" s="8"/>
-      <c r="U12" s="8"/>
-      <c r="V12" s="8"/>
-      <c r="W12" s="8"/>
-      <c r="X12" s="8"/>
-      <c r="Y12" s="8"/>
-      <c r="Z12" s="8"/>
-      <c r="AA12" s="8"/>
-      <c r="AB12" s="8"/>
-      <c r="AC12" s="8"/>
-      <c r="AD12" s="8"/>
-      <c r="AE12" s="8"/>
+      <c r="H12" s="1">
+        <v>-11339</v>
+      </c>
+      <c r="I12" s="1">
+        <v>19882</v>
+      </c>
+      <c r="J12" s="1">
+        <v>-526</v>
+      </c>
+      <c r="K12" s="1">
+        <v>851</v>
+      </c>
+      <c r="L12" s="1">
+        <v>581</v>
+      </c>
+      <c r="M12" s="1">
+        <v>39</v>
+      </c>
+      <c r="N12" s="1">
+        <v>-98</v>
+      </c>
+      <c r="O12" s="1">
+        <v>-2</v>
+      </c>
+      <c r="P12" s="1">
+        <v>879</v>
+      </c>
+      <c r="Q12" s="1">
+        <v>100</v>
+      </c>
+      <c r="R12" s="1">
+        <v>-275</v>
+      </c>
+      <c r="S12" s="1">
+        <v>201</v>
+      </c>
+      <c r="T12" s="1">
+        <v>85</v>
+      </c>
+      <c r="U12" s="1">
+        <v>240</v>
+      </c>
+      <c r="V12" s="1">
+        <v>31</v>
+      </c>
+      <c r="W12" s="1">
+        <v>-2</v>
+      </c>
+      <c r="X12" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="1">
+        <v>4</v>
+      </c>
+      <c r="Z12" s="1">
+        <v>7662</v>
+      </c>
+      <c r="AA12" s="1">
+        <v>-122</v>
+      </c>
+      <c r="AB12" s="1">
+        <v>3159</v>
+      </c>
+      <c r="AC12" s="1">
+        <v>3</v>
+      </c>
+      <c r="AD12" s="1">
+        <v>-343</v>
+      </c>
+      <c r="AE12" s="1">
+        <v>-470</v>
+      </c>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A13" s="27">
+      <c r="A13" s="26">
         <f t="shared" si="0"/>
         <v>1892</v>
       </c>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
-      <c r="I13" s="8"/>
-      <c r="J13" s="8"/>
-      <c r="K13" s="8"/>
-      <c r="L13" s="8"/>
-      <c r="M13" s="8"/>
-      <c r="N13" s="8"/>
-      <c r="O13" s="8"/>
-      <c r="P13" s="8"/>
-      <c r="Q13" s="8"/>
-      <c r="R13" s="8"/>
-      <c r="S13" s="8"/>
-      <c r="T13" s="8"/>
-      <c r="U13" s="8"/>
-      <c r="V13" s="8"/>
-      <c r="W13" s="8"/>
-      <c r="X13" s="8"/>
-      <c r="Y13" s="8"/>
-      <c r="Z13" s="8"/>
-      <c r="AA13" s="8"/>
-      <c r="AB13" s="8"/>
-      <c r="AC13" s="8"/>
-      <c r="AD13" s="8"/>
-      <c r="AE13" s="8"/>
+      <c r="H13" s="1">
+        <v>3616</v>
+      </c>
+      <c r="I13" s="1">
+        <v>9892</v>
+      </c>
+      <c r="J13" s="1">
+        <v>-999</v>
+      </c>
+      <c r="K13" s="1">
+        <v>416</v>
+      </c>
+      <c r="L13" s="1">
+        <v>224</v>
+      </c>
+      <c r="M13" s="1">
+        <v>-391</v>
+      </c>
+      <c r="N13" s="1">
+        <v>-9</v>
+      </c>
+      <c r="O13" s="1">
+        <v>17</v>
+      </c>
+      <c r="P13" s="1">
+        <v>899</v>
+      </c>
+      <c r="Q13" s="1">
+        <v>101</v>
+      </c>
+      <c r="R13" s="1">
+        <v>-287</v>
+      </c>
+      <c r="S13" s="1">
+        <v>214</v>
+      </c>
+      <c r="T13" s="1">
+        <v>118</v>
+      </c>
+      <c r="U13" s="1">
+        <v>199</v>
+      </c>
+      <c r="V13" s="1">
+        <v>10</v>
+      </c>
+      <c r="W13" s="1">
+        <v>14</v>
+      </c>
+      <c r="X13" s="1">
+        <v>34</v>
+      </c>
+      <c r="Y13" s="1">
+        <v>2</v>
+      </c>
+      <c r="Z13" s="1">
+        <v>16360</v>
+      </c>
+      <c r="AA13" s="1">
+        <v>-201</v>
+      </c>
+      <c r="AB13" s="1">
+        <v>-164</v>
+      </c>
+      <c r="AC13" s="1">
+        <v>5</v>
+      </c>
+      <c r="AD13" s="1">
+        <v>-250</v>
+      </c>
+      <c r="AE13" s="1">
+        <v>-16</v>
+      </c>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A14" s="27">
+      <c r="A14" s="26">
         <f t="shared" si="0"/>
         <v>1893</v>
       </c>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="8"/>
-      <c r="H14" s="8"/>
-      <c r="I14" s="8"/>
-      <c r="J14" s="8"/>
-      <c r="K14" s="8"/>
-      <c r="L14" s="8"/>
-      <c r="M14" s="8"/>
-      <c r="N14" s="8"/>
-      <c r="O14" s="8"/>
-      <c r="P14" s="8"/>
-      <c r="Q14" s="8"/>
-      <c r="R14" s="8"/>
-      <c r="S14" s="8"/>
-      <c r="T14" s="8"/>
-      <c r="U14" s="8"/>
-      <c r="V14" s="8"/>
-      <c r="W14" s="8"/>
-      <c r="X14" s="8"/>
-      <c r="Y14" s="8"/>
-      <c r="Z14" s="8"/>
-      <c r="AA14" s="8"/>
-      <c r="AB14" s="8"/>
-      <c r="AC14" s="8"/>
-      <c r="AD14" s="8"/>
-      <c r="AE14" s="8"/>
+      <c r="H14" s="1">
+        <v>26811</v>
+      </c>
+      <c r="I14" s="1">
+        <v>3749</v>
+      </c>
+      <c r="J14" s="1">
+        <v>-127</v>
+      </c>
+      <c r="K14" s="1">
+        <v>1811</v>
+      </c>
+      <c r="L14" s="1">
+        <v>284</v>
+      </c>
+      <c r="M14" s="1">
+        <v>76</v>
+      </c>
+      <c r="N14" s="1">
+        <v>699</v>
+      </c>
+      <c r="O14" s="1">
+        <v>69</v>
+      </c>
+      <c r="P14" s="1">
+        <v>351</v>
+      </c>
+      <c r="Q14" s="1">
+        <v>178</v>
+      </c>
+      <c r="R14" s="1">
+        <v>69</v>
+      </c>
+      <c r="S14" s="1">
+        <v>4</v>
+      </c>
+      <c r="T14" s="1">
+        <v>-31</v>
+      </c>
+      <c r="U14" s="1">
+        <v>275</v>
+      </c>
+      <c r="V14" s="1">
+        <v>29</v>
+      </c>
+      <c r="W14" s="1">
+        <v>-32</v>
+      </c>
+      <c r="X14" s="1">
+        <v>-3</v>
+      </c>
+      <c r="Y14" s="1">
+        <v>15</v>
+      </c>
+      <c r="Z14" s="1">
+        <v>12664</v>
+      </c>
+      <c r="AA14" s="1">
+        <v>385</v>
+      </c>
+      <c r="AB14" s="1">
+        <v>5813</v>
+      </c>
+      <c r="AC14" s="1">
+        <v>13</v>
+      </c>
+      <c r="AD14" s="1">
+        <v>-393</v>
+      </c>
+      <c r="AE14" s="1">
+        <v>44</v>
+      </c>
     </row>
     <row r="15" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A15" s="27">
+      <c r="A15" s="26">
         <f t="shared" si="0"/>
         <v>1894</v>
       </c>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8"/>
-      <c r="I15" s="8"/>
-      <c r="J15" s="8"/>
-      <c r="K15" s="8"/>
-      <c r="L15" s="8"/>
-      <c r="M15" s="8"/>
-      <c r="N15" s="8"/>
-      <c r="O15" s="8"/>
-      <c r="P15" s="8"/>
-      <c r="Q15" s="8"/>
-      <c r="R15" s="8"/>
-      <c r="S15" s="8"/>
-      <c r="T15" s="8"/>
-      <c r="U15" s="8"/>
-      <c r="V15" s="8"/>
-      <c r="W15" s="8"/>
-      <c r="X15" s="8"/>
-      <c r="Y15" s="8"/>
-      <c r="Z15" s="8"/>
-      <c r="AA15" s="8"/>
-      <c r="AB15" s="8"/>
-      <c r="AC15" s="8"/>
-      <c r="AD15" s="8"/>
-      <c r="AE15" s="8"/>
+      <c r="H15" s="1">
+        <v>5875</v>
+      </c>
+      <c r="I15" s="1">
+        <v>5078</v>
+      </c>
+      <c r="J15" s="1">
+        <v>-1092</v>
+      </c>
+      <c r="K15" s="1">
+        <v>871</v>
+      </c>
+      <c r="L15" s="1">
+        <v>430</v>
+      </c>
+      <c r="M15" s="1">
+        <v>-10</v>
+      </c>
+      <c r="N15" s="1">
+        <v>-314</v>
+      </c>
+      <c r="O15" s="1">
+        <v>40</v>
+      </c>
+      <c r="P15" s="1">
+        <v>1153</v>
+      </c>
+      <c r="Q15" s="1">
+        <v>103</v>
+      </c>
+      <c r="R15" s="1">
+        <v>385</v>
+      </c>
+      <c r="S15" s="1">
+        <v>398</v>
+      </c>
+      <c r="T15" s="1">
+        <v>99</v>
+      </c>
+      <c r="U15" s="1">
+        <v>390</v>
+      </c>
+      <c r="V15" s="1">
+        <v>-4</v>
+      </c>
+      <c r="W15" s="1">
+        <v>52</v>
+      </c>
+      <c r="X15" s="1">
+        <v>25</v>
+      </c>
+      <c r="Y15" s="1">
+        <v>16</v>
+      </c>
+      <c r="Z15" s="1">
+        <v>14190</v>
+      </c>
+      <c r="AA15" s="1">
+        <v>537</v>
+      </c>
+      <c r="AB15" s="1">
+        <v>2051</v>
+      </c>
+      <c r="AC15" s="1">
+        <v>6</v>
+      </c>
+      <c r="AD15" s="1">
+        <v>-143</v>
+      </c>
+      <c r="AE15" s="1">
+        <v>4552</v>
+      </c>
     </row>
     <row r="16" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A16" s="27">
+      <c r="A16" s="26">
         <f>A17-1</f>
         <v>1895</v>
       </c>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="8"/>
-      <c r="H16" s="8"/>
-      <c r="I16" s="8"/>
-      <c r="J16" s="8"/>
-      <c r="K16" s="8"/>
-      <c r="L16" s="8"/>
-      <c r="M16" s="8"/>
-      <c r="N16" s="8"/>
-      <c r="O16" s="8"/>
-      <c r="P16" s="8"/>
-      <c r="Q16" s="8"/>
-      <c r="R16" s="8"/>
-      <c r="S16" s="8"/>
-      <c r="T16" s="8"/>
-      <c r="U16" s="8"/>
-      <c r="V16" s="8"/>
-      <c r="W16" s="8"/>
-      <c r="X16" s="8"/>
-      <c r="Y16" s="8"/>
-      <c r="Z16" s="8"/>
-      <c r="AA16" s="8"/>
-      <c r="AB16" s="8"/>
-      <c r="AC16" s="8"/>
-      <c r="AD16" s="8"/>
-      <c r="AE16" s="8"/>
+      <c r="H16" s="1">
+        <v>-85110</v>
+      </c>
+      <c r="I16" s="1">
+        <v>15846</v>
+      </c>
+      <c r="J16" s="1">
+        <v>-144</v>
+      </c>
+      <c r="K16" s="1">
+        <v>1033</v>
+      </c>
+      <c r="L16" s="1">
+        <v>1080</v>
+      </c>
+      <c r="M16" s="1">
+        <v>347</v>
+      </c>
+      <c r="N16" s="1">
+        <v>25</v>
+      </c>
+      <c r="O16" s="1">
+        <v>-57</v>
+      </c>
+      <c r="P16" s="1">
+        <v>597</v>
+      </c>
+      <c r="Q16" s="1">
+        <v>8</v>
+      </c>
+      <c r="R16" s="1">
+        <v>356</v>
+      </c>
+      <c r="S16" s="1">
+        <v>107</v>
+      </c>
+      <c r="T16" s="1">
+        <v>36</v>
+      </c>
+      <c r="U16" s="1">
+        <v>204</v>
+      </c>
+      <c r="V16" s="1">
+        <v>15</v>
+      </c>
+      <c r="W16" s="1">
+        <v>22</v>
+      </c>
+      <c r="X16" s="1">
+        <v>-4</v>
+      </c>
+      <c r="Y16" s="1">
+        <v>22</v>
+      </c>
+      <c r="Z16" s="1">
+        <v>16096</v>
+      </c>
+      <c r="AA16" s="1">
+        <v>59</v>
+      </c>
+      <c r="AB16" s="1">
+        <v>4906</v>
+      </c>
+      <c r="AC16" s="1">
+        <v>12</v>
+      </c>
+      <c r="AD16" s="1">
+        <v>-228</v>
+      </c>
+      <c r="AE16" s="1">
+        <v>4320</v>
+      </c>
     </row>
     <row r="17" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A17">
@@ -18746,7 +19466,7 @@
         <v>51</v>
       </c>
       <c r="U17" s="1">
-        <v>-23</v>
+        <v>526</v>
       </c>
       <c r="V17" s="1">
         <v>129</v>
@@ -18842,7 +19562,7 @@
         <v>290</v>
       </c>
       <c r="U18" s="1">
-        <v>137</v>
+        <v>414</v>
       </c>
       <c r="V18" s="1">
         <v>75</v>
@@ -18938,7 +19658,7 @@
         <v>-171</v>
       </c>
       <c r="U19" s="1">
-        <v>1175</v>
+        <v>582</v>
       </c>
       <c r="V19" s="1">
         <v>223</v>
@@ -19034,7 +19754,7 @@
         <v>159</v>
       </c>
       <c r="U20" s="1">
-        <v>791</v>
+        <v>695</v>
       </c>
       <c r="V20" s="1">
         <v>62</v>
@@ -19130,7 +19850,7 @@
         <v>204</v>
       </c>
       <c r="U21" s="1">
-        <v>342</v>
+        <v>233</v>
       </c>
       <c r="V21" s="1">
         <v>0</v>
@@ -19226,7 +19946,7 @@
         <v>183</v>
       </c>
       <c r="U22" s="1">
-        <v>164</v>
+        <v>322</v>
       </c>
       <c r="V22" s="1">
         <v>-11</v>
@@ -19322,7 +20042,7 @@
         <v>166</v>
       </c>
       <c r="U23" s="1">
-        <v>131</v>
+        <v>198</v>
       </c>
       <c r="V23" s="1">
         <v>-19</v>
@@ -19418,7 +20138,7 @@
         <v>249</v>
       </c>
       <c r="U24" s="1">
-        <v>432</v>
+        <v>377</v>
       </c>
       <c r="V24" s="1">
         <v>30</v>
@@ -19514,7 +20234,7 @@
         <v>53</v>
       </c>
       <c r="U25" s="1">
-        <v>370</v>
+        <v>83</v>
       </c>
       <c r="V25" s="1">
         <v>-85</v>
@@ -19610,7 +20330,7 @@
         <v>-289</v>
       </c>
       <c r="U26" s="1">
-        <v>240</v>
+        <v>208</v>
       </c>
       <c r="V26" s="1">
         <v>48</v>
@@ -19670,7 +20390,7 @@
         <v>1400</v>
       </c>
       <c r="I27" s="1">
-        <v>-16118</v>
+        <v>1882</v>
       </c>
       <c r="J27" s="1">
         <v>184</v>
@@ -19706,7 +20426,7 @@
         <v>146</v>
       </c>
       <c r="U27" s="1">
-        <v>38</v>
+        <v>108</v>
       </c>
       <c r="V27" s="1">
         <v>58</v>
@@ -19802,7 +20522,7 @@
         <v>140</v>
       </c>
       <c r="U28" s="1">
-        <v>289</v>
+        <v>445</v>
       </c>
       <c r="V28" s="1">
         <v>83</v>
@@ -19898,7 +20618,7 @@
         <v>459</v>
       </c>
       <c r="U29" s="1">
-        <v>-47</v>
+        <v>343</v>
       </c>
       <c r="V29" s="1">
         <v>-70</v>
@@ -19994,7 +20714,7 @@
         <v>580</v>
       </c>
       <c r="U30" s="1">
-        <v>327</v>
+        <v>474</v>
       </c>
       <c r="V30" s="1">
         <v>33</v>
@@ -20090,7 +20810,7 @@
         <v>455</v>
       </c>
       <c r="U31" s="1">
-        <v>680</v>
+        <v>725</v>
       </c>
       <c r="V31" s="1">
         <v>121</v>
@@ -20186,7 +20906,7 @@
         <v>831</v>
       </c>
       <c r="U32" s="1">
-        <v>577</v>
+        <v>652</v>
       </c>
       <c r="V32" s="1">
         <v>-1</v>
@@ -20282,7 +21002,7 @@
         <v>1010</v>
       </c>
       <c r="U33" s="1">
-        <v>521</v>
+        <v>845</v>
       </c>
       <c r="V33" s="1">
         <v>-171</v>
@@ -20378,7 +21098,7 @@
         <v>1330</v>
       </c>
       <c r="U34" s="1">
-        <v>1094</v>
+        <v>478</v>
       </c>
       <c r="V34" s="1">
         <v>17</v>
@@ -20474,7 +21194,7 @@
         <v>557</v>
       </c>
       <c r="U35" s="1">
-        <v>791</v>
+        <v>12</v>
       </c>
       <c r="V35" s="1">
         <v>-14</v>
@@ -20570,7 +21290,7 @@
         <v>23</v>
       </c>
       <c r="U36" s="1">
-        <v>340</v>
+        <v>67</v>
       </c>
       <c r="V36" s="1">
         <v>34</v>
@@ -20605,23 +21325,23 @@
     </row>
     <row r="38" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A38" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P38" s="1"/>
     </row>
     <row r="40" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="42" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="43" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/rtss-pre1917/src/main/resources/immigration.xlsx
+++ b/rtss-pre1917/src/main/resources/immigration.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\WINAPPS\SLOVO\UKR\github\RTSS\rtss-pre1917\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15D49887-193B-470F-93CF-B78432D3FAB5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E1F5FCC-10DC-470A-9737-3CFE4E3CD846}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8235" yWindow="1500" windowWidth="24945" windowHeight="21255" activeTab="2" xr2:uid="{F5C0FC2C-9C7B-4145-981E-7BD1765E4EE3}"/>
+    <workbookView xWindow="10860" yWindow="2055" windowWidth="24945" windowHeight="21255" xr2:uid="{F5C0FC2C-9C7B-4145-981E-7BD1765E4EE3}"/>
   </bookViews>
   <sheets>
     <sheet name="note-1" sheetId="2" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="63">
   <si>
     <t>год</t>
   </si>
@@ -238,6 +238,12 @@
   </si>
   <si>
     <t>Для 1889-1895 гг. число иностранцев пересекших границы России по легитимационным билетам включено в таблицу пересекших по паспортам</t>
+  </si>
+  <si>
+    <t>Баланс по странам, движение по паспортам и легитимационным билетам:</t>
+  </si>
+  <si>
+    <t>Баланс по странам, движение по легитимационным билетам кроме 1889-1895 (см. страницу note-2):</t>
   </si>
 </sst>
 </file>
@@ -691,7 +697,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AE7EB44-DA37-426E-8733-CEB32776A88C}">
-  <dimension ref="A1:CF121"/>
+  <dimension ref="A1:CF162"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.28515625" customWidth="1"/>
@@ -13273,6 +13279,569 @@
       </c>
       <c r="D121" s="1">
         <v>1648192</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B125" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="C125" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D125" s="20" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>7</v>
+      </c>
+      <c r="B126" s="1">
+        <v>289250</v>
+      </c>
+      <c r="C126" s="1">
+        <v>608681</v>
+      </c>
+      <c r="D126" s="1">
+        <v>897931</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>8</v>
+      </c>
+      <c r="B127" s="1">
+        <v>71263</v>
+      </c>
+      <c r="C127" s="1">
+        <v>59385</v>
+      </c>
+      <c r="D127" s="1">
+        <v>130648</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>9</v>
+      </c>
+      <c r="B128" s="1">
+        <v>5980</v>
+      </c>
+      <c r="C128" s="1">
+        <v>12946</v>
+      </c>
+      <c r="D128" s="1">
+        <v>18926</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>12</v>
+      </c>
+      <c r="B129" s="1">
+        <v>0</v>
+      </c>
+      <c r="C129" s="1">
+        <v>151250</v>
+      </c>
+      <c r="D129" s="1">
+        <v>151250</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>10</v>
+      </c>
+      <c r="B130" s="1">
+        <v>2099</v>
+      </c>
+      <c r="C130" s="1">
+        <v>89510</v>
+      </c>
+      <c r="D130" s="1">
+        <v>91609</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>11</v>
+      </c>
+      <c r="B131" s="1">
+        <v>-4</v>
+      </c>
+      <c r="C131" s="1">
+        <v>11120</v>
+      </c>
+      <c r="D131" s="1">
+        <v>11116</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>54</v>
+      </c>
+      <c r="B132" s="1">
+        <f>SUM(B126:B131)</f>
+        <v>368588</v>
+      </c>
+      <c r="C132" s="1">
+        <f>SUM(C126:C131)</f>
+        <v>932892</v>
+      </c>
+      <c r="D132" s="1">
+        <f>SUM(D126:D131)</f>
+        <v>1301480</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B133" s="1"/>
+      <c r="C133" s="1"/>
+      <c r="D133" s="1"/>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B137" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="C137" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D137" s="20" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>7</v>
+      </c>
+      <c r="B138" s="1">
+        <f t="shared" ref="B138:D139" si="140">B97+B126</f>
+        <v>387733</v>
+      </c>
+      <c r="C138" s="1">
+        <f t="shared" si="140"/>
+        <v>673314</v>
+      </c>
+      <c r="D138" s="1">
+        <f t="shared" si="140"/>
+        <v>1061047</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>8</v>
+      </c>
+      <c r="B139" s="1">
+        <f t="shared" si="140"/>
+        <v>341811</v>
+      </c>
+      <c r="C139" s="1">
+        <f t="shared" si="140"/>
+        <v>148200</v>
+      </c>
+      <c r="D139" s="1">
+        <f t="shared" si="140"/>
+        <v>490011</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>21</v>
+      </c>
+      <c r="B140" s="1">
+        <f t="shared" ref="B140:D140" si="141">B99</f>
+        <v>1194</v>
+      </c>
+      <c r="C140" s="1">
+        <f t="shared" si="141"/>
+        <v>12542</v>
+      </c>
+      <c r="D140" s="1">
+        <f t="shared" si="141"/>
+        <v>13736</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>22</v>
+      </c>
+      <c r="B141" s="1">
+        <f t="shared" ref="B141:D141" si="142">B100</f>
+        <v>7593</v>
+      </c>
+      <c r="C141" s="1">
+        <f t="shared" si="142"/>
+        <v>20477</v>
+      </c>
+      <c r="D141" s="1">
+        <f t="shared" si="142"/>
+        <v>28070</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>23</v>
+      </c>
+      <c r="B142" s="1">
+        <f t="shared" ref="B142:D142" si="143">B101</f>
+        <v>4360</v>
+      </c>
+      <c r="C142" s="1">
+        <f t="shared" si="143"/>
+        <v>8006</v>
+      </c>
+      <c r="D142" s="1">
+        <f t="shared" si="143"/>
+        <v>12366</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>24</v>
+      </c>
+      <c r="B143" s="1">
+        <f t="shared" ref="B143:D143" si="144">B102</f>
+        <v>93</v>
+      </c>
+      <c r="C143" s="1">
+        <f t="shared" si="144"/>
+        <v>3063</v>
+      </c>
+      <c r="D143" s="1">
+        <f t="shared" si="144"/>
+        <v>3156</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>25</v>
+      </c>
+      <c r="B144" s="1">
+        <f t="shared" ref="B144:D144" si="145">B103</f>
+        <v>407</v>
+      </c>
+      <c r="C144" s="1">
+        <f t="shared" si="145"/>
+        <v>10431</v>
+      </c>
+      <c r="D144" s="1">
+        <f t="shared" si="145"/>
+        <v>10838</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>26</v>
+      </c>
+      <c r="B145" s="1">
+        <f t="shared" ref="B145:D145" si="146">B104</f>
+        <v>-47</v>
+      </c>
+      <c r="C145" s="1">
+        <f t="shared" si="146"/>
+        <v>5897</v>
+      </c>
+      <c r="D145" s="1">
+        <f t="shared" si="146"/>
+        <v>5850</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>27</v>
+      </c>
+      <c r="B146" s="1">
+        <f t="shared" ref="B146:D146" si="147">B105</f>
+        <v>6276</v>
+      </c>
+      <c r="C146" s="1">
+        <f t="shared" si="147"/>
+        <v>4068</v>
+      </c>
+      <c r="D146" s="1">
+        <f t="shared" si="147"/>
+        <v>10344</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>28</v>
+      </c>
+      <c r="B147" s="1">
+        <f t="shared" ref="B147:D147" si="148">B106</f>
+        <v>573</v>
+      </c>
+      <c r="C147" s="1">
+        <f t="shared" si="148"/>
+        <v>9020</v>
+      </c>
+      <c r="D147" s="1">
+        <f t="shared" si="148"/>
+        <v>9593</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>9</v>
+      </c>
+      <c r="B148" s="1">
+        <f>B107+B128</f>
+        <v>7490</v>
+      </c>
+      <c r="C148" s="1">
+        <f>C107+C128</f>
+        <v>17808</v>
+      </c>
+      <c r="D148" s="1">
+        <f>D107+D128</f>
+        <v>25298</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>29</v>
+      </c>
+      <c r="B149" s="1">
+        <f t="shared" ref="B149:D149" si="149">B108</f>
+        <v>5131</v>
+      </c>
+      <c r="C149" s="1">
+        <f t="shared" si="149"/>
+        <v>5622</v>
+      </c>
+      <c r="D149" s="1">
+        <f t="shared" si="149"/>
+        <v>10753</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>30</v>
+      </c>
+      <c r="B150" s="1">
+        <f t="shared" ref="B150:D150" si="150">B109</f>
+        <v>477</v>
+      </c>
+      <c r="C150" s="1">
+        <f t="shared" si="150"/>
+        <v>6426</v>
+      </c>
+      <c r="D150" s="1">
+        <f t="shared" si="150"/>
+        <v>6903</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>31</v>
+      </c>
+      <c r="B151" s="1">
+        <f t="shared" ref="B151:D151" si="151">B110</f>
+        <v>2396</v>
+      </c>
+      <c r="C151" s="1">
+        <f t="shared" si="151"/>
+        <v>7787</v>
+      </c>
+      <c r="D151" s="1">
+        <f t="shared" si="151"/>
+        <v>10183</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>32</v>
+      </c>
+      <c r="B152" s="1">
+        <f t="shared" ref="B152:D152" si="152">B111</f>
+        <v>197</v>
+      </c>
+      <c r="C152" s="1">
+        <f t="shared" si="152"/>
+        <v>542</v>
+      </c>
+      <c r="D152" s="1">
+        <f t="shared" si="152"/>
+        <v>739</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>33</v>
+      </c>
+      <c r="B153" s="1">
+        <f t="shared" ref="B153:D153" si="153">B112</f>
+        <v>90</v>
+      </c>
+      <c r="C153" s="1">
+        <f t="shared" si="153"/>
+        <v>1009</v>
+      </c>
+      <c r="D153" s="1">
+        <f t="shared" si="153"/>
+        <v>1099</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>34</v>
+      </c>
+      <c r="B154" s="1">
+        <f t="shared" ref="B154:D154" si="154">B113</f>
+        <v>7</v>
+      </c>
+      <c r="C154" s="1">
+        <f t="shared" si="154"/>
+        <v>78</v>
+      </c>
+      <c r="D154" s="1">
+        <f t="shared" si="154"/>
+        <v>85</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>35</v>
+      </c>
+      <c r="B155" s="1">
+        <f t="shared" ref="B155:D155" si="155">B114</f>
+        <v>205</v>
+      </c>
+      <c r="C155" s="1">
+        <f t="shared" si="155"/>
+        <v>309</v>
+      </c>
+      <c r="D155" s="1">
+        <f t="shared" si="155"/>
+        <v>514</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>12</v>
+      </c>
+      <c r="B156" s="1">
+        <f t="shared" ref="B156:D157" si="156">B115+B129</f>
+        <v>137996</v>
+      </c>
+      <c r="C156" s="1">
+        <f t="shared" si="156"/>
+        <v>515211</v>
+      </c>
+      <c r="D156" s="1">
+        <f t="shared" si="156"/>
+        <v>653207</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>10</v>
+      </c>
+      <c r="B157" s="1">
+        <f t="shared" si="156"/>
+        <v>2395</v>
+      </c>
+      <c r="C157" s="1">
+        <f t="shared" si="156"/>
+        <v>292431</v>
+      </c>
+      <c r="D157" s="1">
+        <f t="shared" si="156"/>
+        <v>294826</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>36</v>
+      </c>
+      <c r="B158" s="1">
+        <f t="shared" ref="B158:D158" si="157">B117</f>
+        <v>48840</v>
+      </c>
+      <c r="C158" s="1">
+        <f t="shared" si="157"/>
+        <v>205805</v>
+      </c>
+      <c r="D158" s="1">
+        <f t="shared" si="157"/>
+        <v>254645</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>37</v>
+      </c>
+      <c r="B159" s="1">
+        <f t="shared" ref="B159:D159" si="158">B118</f>
+        <v>50</v>
+      </c>
+      <c r="C159" s="1">
+        <f t="shared" si="158"/>
+        <v>16981</v>
+      </c>
+      <c r="D159" s="1">
+        <f t="shared" si="158"/>
+        <v>17031</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>53</v>
+      </c>
+      <c r="B160" s="1">
+        <f t="shared" ref="B160:D160" si="159">B119</f>
+        <v>-1825</v>
+      </c>
+      <c r="C160" s="1">
+        <f t="shared" si="159"/>
+        <v>-5491</v>
+      </c>
+      <c r="D160" s="1">
+        <f t="shared" si="159"/>
+        <v>-7316</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>38</v>
+      </c>
+      <c r="B161" s="1">
+        <f>B120+B131</f>
+        <v>7525</v>
+      </c>
+      <c r="C161" s="1">
+        <f>C120+C131</f>
+        <v>31076</v>
+      </c>
+      <c r="D161" s="1">
+        <f>D120+D131</f>
+        <v>38601</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>54</v>
+      </c>
+      <c r="B162" s="1">
+        <f>SUM(B138:B161)</f>
+        <v>960967</v>
+      </c>
+      <c r="C162" s="1">
+        <f>SUM(C138:C161)</f>
+        <v>1990612</v>
+      </c>
+      <c r="D162" s="1">
+        <f>SUM(D138:D161)</f>
+        <v>2951579</v>
       </c>
     </row>
   </sheetData>
@@ -13715,6 +14284,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
+      <c r="M17" s="1"/>
       <c r="O17" s="1"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">

--- a/rtss-pre1917/src/main/resources/immigration.xlsx
+++ b/rtss-pre1917/src/main/resources/immigration.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\WINAPPS\SLOVO\UKR\github\RTSS\rtss-pre1917\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E1F5FCC-10DC-470A-9737-3CFE4E3CD846}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A99E6AF-F077-4BEB-9D71-618CCB32E839}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10860" yWindow="2055" windowWidth="24945" windowHeight="21255" xr2:uid="{F5C0FC2C-9C7B-4145-981E-7BD1765E4EE3}"/>
+    <workbookView xWindow="-60" yWindow="-60" windowWidth="38520" windowHeight="23700" activeTab="2" xr2:uid="{F5C0FC2C-9C7B-4145-981E-7BD1765E4EE3}"/>
   </bookViews>
   <sheets>
     <sheet name="note-1" sheetId="2" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="65">
   <si>
     <t>год</t>
   </si>
@@ -244,6 +244,12 @@
   </si>
   <si>
     <t>Баланс по странам, движение по легитимационным билетам кроме 1889-1895 (см. страницу note-2):</t>
+  </si>
+  <si>
+    <t>всего (п + лб)</t>
+  </si>
+  <si>
+    <t>всего (п)</t>
   </si>
 </sst>
 </file>
@@ -18581,10 +18587,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7B60D45-40A7-4AEF-8152-6E6E2D19E14F}">
-  <dimension ref="A1:AE43"/>
+  <dimension ref="A1:AI52"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11" customWidth="1"/>
     <col min="2" max="2" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
@@ -18595,7 +18601,7 @@
     <col min="9" max="9" width="8.28515625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.28515625" customWidth="1"/>
     <col min="13" max="13" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="8.28515625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -21509,7 +21515,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="33" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A33">
         <f t="shared" si="1"/>
         <v>1912</v>
@@ -21605,7 +21611,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="34" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A34">
         <f t="shared" si="1"/>
         <v>1913</v>
@@ -21701,7 +21707,7 @@
         <v>-239</v>
       </c>
     </row>
-    <row r="35" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A35">
         <f t="shared" si="1"/>
         <v>1914</v>
@@ -21797,7 +21803,7 @@
         <v>-1287</v>
       </c>
     </row>
-    <row r="36" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A36">
         <f t="shared" si="1"/>
         <v>1915</v>
@@ -21893,25 +21899,825 @@
         <v>-2496</v>
       </c>
     </row>
-    <row r="38" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A38" s="8" t="s">
         <v>47</v>
       </c>
       <c r="P38" s="1"/>
     </row>
-    <row r="40" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="42" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="43" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>49</v>
+      </c>
+    </row>
+    <row r="45" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="B45" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C45" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F45" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="G45" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="H45" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="I45" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J45" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K45" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="L45" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="M45" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="N45" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="O45" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P45" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q45" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="R45" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="S45" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="T45" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="U45" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="V45" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="W45" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="X45" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y45" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z45" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="AA45" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB45" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC45" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="AD45" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="AE45" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="AG45" t="s">
+        <v>63</v>
+      </c>
+      <c r="AI45" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="46" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>50</v>
+      </c>
+      <c r="B46" s="1">
+        <f>SUM(B2:B16)</f>
+        <v>289250</v>
+      </c>
+      <c r="C46" s="1">
+        <f t="shared" ref="C46:AE46" si="2">SUM(C2:C16)</f>
+        <v>71263</v>
+      </c>
+      <c r="D46" s="1">
+        <f t="shared" si="2"/>
+        <v>5980</v>
+      </c>
+      <c r="E46" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F46" s="1">
+        <f t="shared" si="2"/>
+        <v>2099</v>
+      </c>
+      <c r="G46" s="1">
+        <f t="shared" si="2"/>
+        <v>-4</v>
+      </c>
+      <c r="H46" s="1">
+        <f t="shared" si="2"/>
+        <v>98483</v>
+      </c>
+      <c r="I46" s="1">
+        <f t="shared" si="2"/>
+        <v>270548</v>
+      </c>
+      <c r="J46" s="1">
+        <f t="shared" si="2"/>
+        <v>1194</v>
+      </c>
+      <c r="K46" s="1">
+        <f t="shared" si="2"/>
+        <v>7593</v>
+      </c>
+      <c r="L46" s="1">
+        <f t="shared" si="2"/>
+        <v>4360</v>
+      </c>
+      <c r="M46" s="1">
+        <f t="shared" si="2"/>
+        <v>93</v>
+      </c>
+      <c r="N46" s="1">
+        <f t="shared" si="2"/>
+        <v>407</v>
+      </c>
+      <c r="O46" s="1">
+        <f t="shared" si="2"/>
+        <v>-47</v>
+      </c>
+      <c r="P46" s="1">
+        <f t="shared" si="2"/>
+        <v>6276</v>
+      </c>
+      <c r="Q46" s="1">
+        <f t="shared" si="2"/>
+        <v>573</v>
+      </c>
+      <c r="R46" s="1">
+        <f t="shared" si="2"/>
+        <v>1510</v>
+      </c>
+      <c r="S46" s="1">
+        <f t="shared" si="2"/>
+        <v>5131</v>
+      </c>
+      <c r="T46" s="1">
+        <f t="shared" si="2"/>
+        <v>477</v>
+      </c>
+      <c r="U46" s="1">
+        <f t="shared" si="2"/>
+        <v>2396</v>
+      </c>
+      <c r="V46" s="1">
+        <f t="shared" si="2"/>
+        <v>197</v>
+      </c>
+      <c r="W46" s="1">
+        <f t="shared" si="2"/>
+        <v>90</v>
+      </c>
+      <c r="X46" s="1">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+      <c r="Y46" s="1">
+        <f t="shared" si="2"/>
+        <v>205</v>
+      </c>
+      <c r="Z46" s="1">
+        <f t="shared" si="2"/>
+        <v>137996</v>
+      </c>
+      <c r="AA46" s="1">
+        <f t="shared" si="2"/>
+        <v>296</v>
+      </c>
+      <c r="AB46" s="1">
+        <f t="shared" si="2"/>
+        <v>48840</v>
+      </c>
+      <c r="AC46" s="1">
+        <f t="shared" si="2"/>
+        <v>50</v>
+      </c>
+      <c r="AD46" s="1">
+        <f t="shared" si="2"/>
+        <v>-1825</v>
+      </c>
+      <c r="AE46" s="1">
+        <f t="shared" si="2"/>
+        <v>7529</v>
+      </c>
+      <c r="AG46" s="1">
+        <f>SUM(B46:AE46)</f>
+        <v>960967</v>
+      </c>
+    </row>
+    <row r="47" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>4</v>
+      </c>
+      <c r="B47" s="1">
+        <f>SUM(B17:B36)</f>
+        <v>319431</v>
+      </c>
+      <c r="C47" s="1">
+        <f t="shared" ref="C47:AE47" si="3">SUM(C17:C36)</f>
+        <v>-11878</v>
+      </c>
+      <c r="D47" s="1">
+        <f t="shared" si="3"/>
+        <v>6966</v>
+      </c>
+      <c r="E47" s="1">
+        <f t="shared" si="3"/>
+        <v>151250</v>
+      </c>
+      <c r="F47" s="1">
+        <f t="shared" si="3"/>
+        <v>87411</v>
+      </c>
+      <c r="G47" s="1">
+        <f t="shared" si="3"/>
+        <v>11124</v>
+      </c>
+      <c r="H47" s="1">
+        <f t="shared" si="3"/>
+        <v>64633</v>
+      </c>
+      <c r="I47" s="1">
+        <f t="shared" si="3"/>
+        <v>88815</v>
+      </c>
+      <c r="J47" s="1">
+        <f t="shared" si="3"/>
+        <v>12542</v>
+      </c>
+      <c r="K47" s="1">
+        <f t="shared" si="3"/>
+        <v>20477</v>
+      </c>
+      <c r="L47" s="1">
+        <f t="shared" si="3"/>
+        <v>8006</v>
+      </c>
+      <c r="M47" s="1">
+        <f t="shared" si="3"/>
+        <v>3063</v>
+      </c>
+      <c r="N47" s="1">
+        <f t="shared" si="3"/>
+        <v>10431</v>
+      </c>
+      <c r="O47" s="1">
+        <f t="shared" si="3"/>
+        <v>5897</v>
+      </c>
+      <c r="P47" s="1">
+        <f t="shared" si="3"/>
+        <v>4068</v>
+      </c>
+      <c r="Q47" s="1">
+        <f t="shared" si="3"/>
+        <v>9020</v>
+      </c>
+      <c r="R47" s="1">
+        <f t="shared" si="3"/>
+        <v>4862</v>
+      </c>
+      <c r="S47" s="1">
+        <f t="shared" si="3"/>
+        <v>5622</v>
+      </c>
+      <c r="T47" s="1">
+        <f t="shared" si="3"/>
+        <v>6426</v>
+      </c>
+      <c r="U47" s="1">
+        <f t="shared" si="3"/>
+        <v>7787</v>
+      </c>
+      <c r="V47" s="1">
+        <f t="shared" si="3"/>
+        <v>542</v>
+      </c>
+      <c r="W47" s="1">
+        <f t="shared" si="3"/>
+        <v>1009</v>
+      </c>
+      <c r="X47" s="1">
+        <f t="shared" si="3"/>
+        <v>78</v>
+      </c>
+      <c r="Y47" s="1">
+        <f t="shared" si="3"/>
+        <v>309</v>
+      </c>
+      <c r="Z47" s="1">
+        <f t="shared" si="3"/>
+        <v>363961</v>
+      </c>
+      <c r="AA47" s="1">
+        <f t="shared" si="3"/>
+        <v>202921</v>
+      </c>
+      <c r="AB47" s="1">
+        <f t="shared" si="3"/>
+        <v>205805</v>
+      </c>
+      <c r="AC47" s="1">
+        <f t="shared" si="3"/>
+        <v>16981</v>
+      </c>
+      <c r="AD47" s="1">
+        <f t="shared" si="3"/>
+        <v>-5491</v>
+      </c>
+      <c r="AE47" s="1">
+        <f t="shared" si="3"/>
+        <v>19956</v>
+      </c>
+      <c r="AG47" s="1">
+        <f>SUM(B47:AE47)</f>
+        <v>1622024</v>
+      </c>
+    </row>
+    <row r="48" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>51</v>
+      </c>
+      <c r="B48" s="1">
+        <f>B47+B46</f>
+        <v>608681</v>
+      </c>
+      <c r="C48" s="1">
+        <f t="shared" ref="C48:AE48" si="4">C47+C46</f>
+        <v>59385</v>
+      </c>
+      <c r="D48" s="1">
+        <f t="shared" si="4"/>
+        <v>12946</v>
+      </c>
+      <c r="E48" s="1">
+        <f t="shared" si="4"/>
+        <v>151250</v>
+      </c>
+      <c r="F48" s="1">
+        <f t="shared" si="4"/>
+        <v>89510</v>
+      </c>
+      <c r="G48" s="1">
+        <f t="shared" si="4"/>
+        <v>11120</v>
+      </c>
+      <c r="H48" s="1">
+        <f t="shared" si="4"/>
+        <v>163116</v>
+      </c>
+      <c r="I48" s="1">
+        <f t="shared" si="4"/>
+        <v>359363</v>
+      </c>
+      <c r="J48" s="1">
+        <f t="shared" si="4"/>
+        <v>13736</v>
+      </c>
+      <c r="K48" s="1">
+        <f t="shared" si="4"/>
+        <v>28070</v>
+      </c>
+      <c r="L48" s="1">
+        <f t="shared" si="4"/>
+        <v>12366</v>
+      </c>
+      <c r="M48" s="1">
+        <f t="shared" si="4"/>
+        <v>3156</v>
+      </c>
+      <c r="N48" s="1">
+        <f t="shared" si="4"/>
+        <v>10838</v>
+      </c>
+      <c r="O48" s="1">
+        <f t="shared" si="4"/>
+        <v>5850</v>
+      </c>
+      <c r="P48" s="1">
+        <f t="shared" si="4"/>
+        <v>10344</v>
+      </c>
+      <c r="Q48" s="1">
+        <f t="shared" si="4"/>
+        <v>9593</v>
+      </c>
+      <c r="R48" s="1">
+        <f t="shared" si="4"/>
+        <v>6372</v>
+      </c>
+      <c r="S48" s="1">
+        <f t="shared" si="4"/>
+        <v>10753</v>
+      </c>
+      <c r="T48" s="1">
+        <f t="shared" si="4"/>
+        <v>6903</v>
+      </c>
+      <c r="U48" s="1">
+        <f t="shared" si="4"/>
+        <v>10183</v>
+      </c>
+      <c r="V48" s="1">
+        <f t="shared" si="4"/>
+        <v>739</v>
+      </c>
+      <c r="W48" s="1">
+        <f t="shared" si="4"/>
+        <v>1099</v>
+      </c>
+      <c r="X48" s="1">
+        <f t="shared" si="4"/>
+        <v>85</v>
+      </c>
+      <c r="Y48" s="1">
+        <f t="shared" si="4"/>
+        <v>514</v>
+      </c>
+      <c r="Z48" s="1">
+        <f t="shared" si="4"/>
+        <v>501957</v>
+      </c>
+      <c r="AA48" s="1">
+        <f t="shared" si="4"/>
+        <v>203217</v>
+      </c>
+      <c r="AB48" s="1">
+        <f t="shared" si="4"/>
+        <v>254645</v>
+      </c>
+      <c r="AC48" s="1">
+        <f t="shared" si="4"/>
+        <v>17031</v>
+      </c>
+      <c r="AD48" s="1">
+        <f t="shared" si="4"/>
+        <v>-7316</v>
+      </c>
+      <c r="AE48" s="1">
+        <f t="shared" si="4"/>
+        <v>27485</v>
+      </c>
+      <c r="AG48" s="1">
+        <f>SUM(B48:AE48)</f>
+        <v>2582991</v>
+      </c>
+    </row>
+    <row r="50" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>50</v>
+      </c>
+      <c r="H50" s="1">
+        <f>H46+B46</f>
+        <v>387733</v>
+      </c>
+      <c r="I50" s="1">
+        <f>I46+C46</f>
+        <v>341811</v>
+      </c>
+      <c r="J50" s="1">
+        <f t="shared" ref="I50:AE52" si="5">J46</f>
+        <v>1194</v>
+      </c>
+      <c r="K50" s="1">
+        <f t="shared" si="5"/>
+        <v>7593</v>
+      </c>
+      <c r="L50" s="1">
+        <f t="shared" si="5"/>
+        <v>4360</v>
+      </c>
+      <c r="M50" s="1">
+        <f t="shared" si="5"/>
+        <v>93</v>
+      </c>
+      <c r="N50" s="1">
+        <f t="shared" si="5"/>
+        <v>407</v>
+      </c>
+      <c r="O50" s="1">
+        <f t="shared" si="5"/>
+        <v>-47</v>
+      </c>
+      <c r="P50" s="1">
+        <f t="shared" si="5"/>
+        <v>6276</v>
+      </c>
+      <c r="Q50" s="1">
+        <f t="shared" si="5"/>
+        <v>573</v>
+      </c>
+      <c r="R50" s="1">
+        <f>R46+D46</f>
+        <v>7490</v>
+      </c>
+      <c r="S50" s="1">
+        <f t="shared" si="5"/>
+        <v>5131</v>
+      </c>
+      <c r="T50" s="1">
+        <f t="shared" si="5"/>
+        <v>477</v>
+      </c>
+      <c r="U50" s="1">
+        <f t="shared" si="5"/>
+        <v>2396</v>
+      </c>
+      <c r="V50" s="1">
+        <f t="shared" si="5"/>
+        <v>197</v>
+      </c>
+      <c r="W50" s="1">
+        <f t="shared" si="5"/>
+        <v>90</v>
+      </c>
+      <c r="X50" s="1">
+        <f t="shared" si="5"/>
+        <v>7</v>
+      </c>
+      <c r="Y50" s="1">
+        <f t="shared" si="5"/>
+        <v>205</v>
+      </c>
+      <c r="Z50" s="1">
+        <f>Z46+E46</f>
+        <v>137996</v>
+      </c>
+      <c r="AA50" s="1">
+        <f>AA46+F46</f>
+        <v>2395</v>
+      </c>
+      <c r="AB50" s="1">
+        <f t="shared" si="5"/>
+        <v>48840</v>
+      </c>
+      <c r="AC50" s="1">
+        <f t="shared" si="5"/>
+        <v>50</v>
+      </c>
+      <c r="AD50" s="1">
+        <f t="shared" si="5"/>
+        <v>-1825</v>
+      </c>
+      <c r="AE50" s="1">
+        <f>AE46+G46</f>
+        <v>7525</v>
+      </c>
+      <c r="AG50" s="1">
+        <f>SUM(B50:AE50)</f>
+        <v>960967</v>
+      </c>
+    </row>
+    <row r="51" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>4</v>
+      </c>
+      <c r="H51" s="1">
+        <f t="shared" ref="H51:I52" si="6">H47+B47</f>
+        <v>384064</v>
+      </c>
+      <c r="I51" s="1">
+        <f t="shared" si="6"/>
+        <v>76937</v>
+      </c>
+      <c r="J51" s="1">
+        <f t="shared" ref="H51:W52" si="7">J47</f>
+        <v>12542</v>
+      </c>
+      <c r="K51" s="1">
+        <f t="shared" si="7"/>
+        <v>20477</v>
+      </c>
+      <c r="L51" s="1">
+        <f t="shared" si="7"/>
+        <v>8006</v>
+      </c>
+      <c r="M51" s="1">
+        <f t="shared" si="7"/>
+        <v>3063</v>
+      </c>
+      <c r="N51" s="1">
+        <f t="shared" si="7"/>
+        <v>10431</v>
+      </c>
+      <c r="O51" s="1">
+        <f t="shared" si="7"/>
+        <v>5897</v>
+      </c>
+      <c r="P51" s="1">
+        <f t="shared" si="7"/>
+        <v>4068</v>
+      </c>
+      <c r="Q51" s="1">
+        <f t="shared" si="7"/>
+        <v>9020</v>
+      </c>
+      <c r="R51" s="1">
+        <f t="shared" ref="R51:R52" si="8">R47+D47</f>
+        <v>11828</v>
+      </c>
+      <c r="S51" s="1">
+        <f t="shared" si="7"/>
+        <v>5622</v>
+      </c>
+      <c r="T51" s="1">
+        <f t="shared" si="7"/>
+        <v>6426</v>
+      </c>
+      <c r="U51" s="1">
+        <f t="shared" si="7"/>
+        <v>7787</v>
+      </c>
+      <c r="V51" s="1">
+        <f t="shared" si="7"/>
+        <v>542</v>
+      </c>
+      <c r="W51" s="1">
+        <f t="shared" si="7"/>
+        <v>1009</v>
+      </c>
+      <c r="X51" s="1">
+        <f t="shared" si="5"/>
+        <v>78</v>
+      </c>
+      <c r="Y51" s="1">
+        <f t="shared" si="5"/>
+        <v>309</v>
+      </c>
+      <c r="Z51" s="1">
+        <f t="shared" ref="Z51:Z52" si="9">Z47+E47</f>
+        <v>515211</v>
+      </c>
+      <c r="AA51" s="1">
+        <f t="shared" ref="AA51:AA52" si="10">AA47+F47</f>
+        <v>290332</v>
+      </c>
+      <c r="AB51" s="1">
+        <f t="shared" si="5"/>
+        <v>205805</v>
+      </c>
+      <c r="AC51" s="1">
+        <f t="shared" si="5"/>
+        <v>16981</v>
+      </c>
+      <c r="AD51" s="1">
+        <f t="shared" si="5"/>
+        <v>-5491</v>
+      </c>
+      <c r="AE51" s="1">
+        <f t="shared" ref="AE51:AE52" si="11">AE47+G47</f>
+        <v>31080</v>
+      </c>
+      <c r="AG51" s="1">
+        <f>SUM(B51:AE51)</f>
+        <v>1622024</v>
+      </c>
+    </row>
+    <row r="52" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>51</v>
+      </c>
+      <c r="H52" s="1">
+        <f t="shared" si="6"/>
+        <v>771797</v>
+      </c>
+      <c r="I52" s="1">
+        <f t="shared" si="6"/>
+        <v>418748</v>
+      </c>
+      <c r="J52" s="1">
+        <f t="shared" si="5"/>
+        <v>13736</v>
+      </c>
+      <c r="K52" s="1">
+        <f t="shared" si="5"/>
+        <v>28070</v>
+      </c>
+      <c r="L52" s="1">
+        <f t="shared" si="5"/>
+        <v>12366</v>
+      </c>
+      <c r="M52" s="1">
+        <f t="shared" si="5"/>
+        <v>3156</v>
+      </c>
+      <c r="N52" s="1">
+        <f t="shared" si="5"/>
+        <v>10838</v>
+      </c>
+      <c r="O52" s="1">
+        <f t="shared" si="5"/>
+        <v>5850</v>
+      </c>
+      <c r="P52" s="1">
+        <f t="shared" si="5"/>
+        <v>10344</v>
+      </c>
+      <c r="Q52" s="1">
+        <f t="shared" si="5"/>
+        <v>9593</v>
+      </c>
+      <c r="R52" s="1">
+        <f t="shared" si="8"/>
+        <v>19318</v>
+      </c>
+      <c r="S52" s="1">
+        <f t="shared" si="5"/>
+        <v>10753</v>
+      </c>
+      <c r="T52" s="1">
+        <f t="shared" si="5"/>
+        <v>6903</v>
+      </c>
+      <c r="U52" s="1">
+        <f t="shared" si="5"/>
+        <v>10183</v>
+      </c>
+      <c r="V52" s="1">
+        <f t="shared" si="5"/>
+        <v>739</v>
+      </c>
+      <c r="W52" s="1">
+        <f t="shared" si="5"/>
+        <v>1099</v>
+      </c>
+      <c r="X52" s="1">
+        <f t="shared" si="5"/>
+        <v>85</v>
+      </c>
+      <c r="Y52" s="1">
+        <f t="shared" si="5"/>
+        <v>514</v>
+      </c>
+      <c r="Z52" s="1">
+        <f t="shared" si="9"/>
+        <v>653207</v>
+      </c>
+      <c r="AA52" s="1">
+        <f t="shared" si="10"/>
+        <v>292727</v>
+      </c>
+      <c r="AB52" s="1">
+        <f t="shared" si="5"/>
+        <v>254645</v>
+      </c>
+      <c r="AC52" s="1">
+        <f t="shared" si="5"/>
+        <v>17031</v>
+      </c>
+      <c r="AD52" s="1">
+        <f t="shared" si="5"/>
+        <v>-7316</v>
+      </c>
+      <c r="AE52" s="1">
+        <f t="shared" si="11"/>
+        <v>38605</v>
+      </c>
+      <c r="AG52" s="1">
+        <f>SUM(B52:AE52)</f>
+        <v>2582991</v>
       </c>
     </row>
   </sheetData>

--- a/rtss-pre1917/src/main/resources/immigration.xlsx
+++ b/rtss-pre1917/src/main/resources/immigration.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\WINAPPS\SLOVO\UKR\github\RTSS\rtss-pre1917\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A99E6AF-F077-4BEB-9D71-618CCB32E839}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C9E4ADC-8588-4A6B-BBF8-F4E4EE3D7543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-60" yWindow="-60" windowWidth="38520" windowHeight="23700" activeTab="2" xr2:uid="{F5C0FC2C-9C7B-4145-981E-7BD1765E4EE3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="23520" activeTab="2" xr2:uid="{F5C0FC2C-9C7B-4145-981E-7BD1765E4EE3}"/>
   </bookViews>
   <sheets>
     <sheet name="note-1" sheetId="2" r:id="rId1"/>
     <sheet name="note-2" sheetId="1" r:id="rId2"/>
     <sheet name="data" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +25,12 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -33,14 +38,14 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
   <futureMetadata name="XLDAPR" count="1">
     <bk>
       <extLst>
-        <ext xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray" uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
           <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
         </ext>
       </extLst>
@@ -55,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="66">
   <si>
     <t>год</t>
   </si>
@@ -251,6 +256,9 @@
   <si>
     <t>всего (п)</t>
   </si>
+  <si>
+    <t>всего (лб)</t>
+  </si>
 </sst>
 </file>
 
@@ -336,7 +344,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -365,27 +373,17 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -407,9 +405,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -447,7 +445,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -553,7 +551,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -695,7 +693,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -725,21 +723,21 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
-      <c r="B5" s="27" t="s">
+      <c r="B5" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="27"/>
-      <c r="D5" s="27"/>
-      <c r="E5" s="27" t="s">
+      <c r="C5" s="23"/>
+      <c r="D5" s="23"/>
+      <c r="E5" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="27"/>
-      <c r="G5" s="27"/>
-      <c r="H5" s="27" t="s">
+      <c r="F5" s="23"/>
+      <c r="G5" s="23"/>
+      <c r="H5" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="I5" s="27"/>
-      <c r="J5" s="27"/>
+      <c r="I5" s="23"/>
+      <c r="J5" s="23"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
@@ -2214,7 +2212,7 @@
       <c r="O48" s="1"/>
     </row>
     <row r="49" spans="1:84" x14ac:dyDescent="0.25">
-      <c r="A49" s="22" t="s">
+      <c r="A49" s="19" t="s">
         <v>60</v>
       </c>
       <c r="M49" s="6"/>
@@ -9603,7 +9601,7 @@
         <f t="shared" si="44"/>
         <v>1882</v>
       </c>
-      <c r="F78" s="19">
+      <c r="F78" s="17">
         <v>86749</v>
       </c>
       <c r="G78" s="1">
@@ -12901,13 +12899,13 @@
       <c r="BL95" s="1"/>
     </row>
     <row r="96" spans="1:84" x14ac:dyDescent="0.25">
-      <c r="B96" s="20" t="s">
+      <c r="B96" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="C96" s="20" t="s">
+      <c r="C96" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="D96" s="20" t="s">
+      <c r="D96" s="16" t="s">
         <v>51</v>
       </c>
       <c r="BK96" s="1"/>
@@ -13161,7 +13159,7 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>34</v>
       </c>
@@ -13175,7 +13173,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>35</v>
       </c>
@@ -13189,7 +13187,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>12</v>
       </c>
@@ -13203,7 +13201,7 @@
         <v>501957</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>10</v>
       </c>
@@ -13217,7 +13215,7 @@
         <v>203217</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>36</v>
       </c>
@@ -13231,7 +13229,7 @@
         <v>254645</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>37</v>
       </c>
@@ -13245,7 +13243,7 @@
         <v>17031</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>53</v>
       </c>
@@ -13259,7 +13257,7 @@
         <v>-7316</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>38</v>
       </c>
@@ -13273,7 +13271,7 @@
         <v>27485</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>54</v>
       </c>
@@ -13287,107 +13285,135 @@
         <v>1648192</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B125" s="20" t="s">
+    <row r="125" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B125" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="C125" s="20" t="s">
+      <c r="C125" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="D125" s="20" t="s">
+      <c r="D125" s="16" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K125" s="12"/>
+      <c r="L125" s="12"/>
+      <c r="M125" s="12"/>
+      <c r="N125" s="12"/>
+    </row>
+    <row r="126" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>7</v>
       </c>
-      <c r="B126" s="1">
+      <c r="B126" s="11">
         <v>289250</v>
       </c>
-      <c r="C126" s="1">
+      <c r="C126" s="11">
+        <v>319431</v>
+      </c>
+      <c r="D126" s="11">
         <v>608681</v>
       </c>
-      <c r="D126" s="1">
-        <v>897931</v>
-      </c>
-    </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K126" s="12"/>
+      <c r="L126" s="11"/>
+      <c r="M126" s="11"/>
+      <c r="N126" s="11"/>
+    </row>
+    <row r="127" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>8</v>
       </c>
-      <c r="B127" s="1">
+      <c r="B127" s="11">
         <v>71263</v>
       </c>
-      <c r="C127" s="1">
+      <c r="C127" s="11">
+        <v>-11878</v>
+      </c>
+      <c r="D127" s="11">
         <v>59385</v>
       </c>
-      <c r="D127" s="1">
-        <v>130648</v>
-      </c>
-    </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K127" s="12"/>
+      <c r="L127" s="11"/>
+      <c r="M127" s="11"/>
+      <c r="N127" s="11"/>
+    </row>
+    <row r="128" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>9</v>
       </c>
-      <c r="B128" s="1">
+      <c r="B128" s="11">
         <v>5980</v>
       </c>
-      <c r="C128" s="1">
+      <c r="C128" s="11">
+        <v>6966</v>
+      </c>
+      <c r="D128" s="11">
         <v>12946</v>
       </c>
-      <c r="D128" s="1">
-        <v>18926</v>
-      </c>
-    </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K128" s="12"/>
+      <c r="L128" s="11"/>
+      <c r="M128" s="11"/>
+      <c r="N128" s="11"/>
+    </row>
+    <row r="129" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>12</v>
       </c>
-      <c r="B129" s="1">
-        <v>0</v>
-      </c>
-      <c r="C129" s="1">
+      <c r="B129" s="11">
+        <v>0</v>
+      </c>
+      <c r="C129" s="11">
         <v>151250</v>
       </c>
-      <c r="D129" s="1">
+      <c r="D129" s="11">
         <v>151250</v>
       </c>
-    </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K129" s="12"/>
+      <c r="L129" s="11"/>
+      <c r="M129" s="11"/>
+      <c r="N129" s="11"/>
+    </row>
+    <row r="130" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>10</v>
       </c>
-      <c r="B130" s="1">
+      <c r="B130" s="11">
         <v>2099</v>
       </c>
-      <c r="C130" s="1">
+      <c r="C130" s="11">
+        <v>87411</v>
+      </c>
+      <c r="D130" s="11">
         <v>89510</v>
       </c>
-      <c r="D130" s="1">
-        <v>91609</v>
-      </c>
-    </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K130" s="12"/>
+      <c r="L130" s="11"/>
+      <c r="M130" s="11"/>
+      <c r="N130" s="11"/>
+    </row>
+    <row r="131" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>11</v>
       </c>
-      <c r="B131" s="1">
+      <c r="B131" s="11">
         <v>-4</v>
       </c>
-      <c r="C131" s="1">
+      <c r="C131" s="11">
+        <v>11124</v>
+      </c>
+      <c r="D131" s="11">
         <v>11120</v>
       </c>
-      <c r="D131" s="1">
-        <v>11116</v>
-      </c>
-    </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K131" s="12"/>
+      <c r="L131" s="11"/>
+      <c r="M131" s="11"/>
+      <c r="N131" s="11"/>
+    </row>
+    <row r="132" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>54</v>
       </c>
@@ -13397,35 +13423,35 @@
       </c>
       <c r="C132" s="1">
         <f>SUM(C126:C131)</f>
-        <v>932892</v>
+        <v>564304</v>
       </c>
       <c r="D132" s="1">
         <f>SUM(D126:D131)</f>
-        <v>1301480</v>
-      </c>
-    </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
+        <v>932892</v>
+      </c>
+    </row>
+    <row r="133" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B133" s="1"/>
       <c r="C133" s="1"/>
       <c r="D133" s="1"/>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B137" s="20" t="s">
+    <row r="137" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B137" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="C137" s="20" t="s">
+      <c r="C137" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="D137" s="20" t="s">
+      <c r="D137" s="16" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>7</v>
       </c>
@@ -13435,14 +13461,14 @@
       </c>
       <c r="C138" s="1">
         <f t="shared" si="140"/>
-        <v>673314</v>
+        <v>384064</v>
       </c>
       <c r="D138" s="1">
         <f t="shared" si="140"/>
-        <v>1061047</v>
-      </c>
-    </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
+        <v>771797</v>
+      </c>
+    </row>
+    <row r="139" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>8</v>
       </c>
@@ -13452,14 +13478,14 @@
       </c>
       <c r="C139" s="1">
         <f t="shared" si="140"/>
-        <v>148200</v>
+        <v>76937</v>
       </c>
       <c r="D139" s="1">
         <f t="shared" si="140"/>
-        <v>490011</v>
-      </c>
-    </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
+        <v>418748</v>
+      </c>
+    </row>
+    <row r="140" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>21</v>
       </c>
@@ -13476,7 +13502,7 @@
         <v>13736</v>
       </c>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>22</v>
       </c>
@@ -13493,7 +13519,7 @@
         <v>28070</v>
       </c>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>23</v>
       </c>
@@ -13510,7 +13536,7 @@
         <v>12366</v>
       </c>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>24</v>
       </c>
@@ -13527,7 +13553,7 @@
         <v>3156</v>
       </c>
     </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>25</v>
       </c>
@@ -13605,11 +13631,11 @@
       </c>
       <c r="C148" s="1">
         <f>C107+C128</f>
-        <v>17808</v>
+        <v>11828</v>
       </c>
       <c r="D148" s="1">
         <f>D107+D128</f>
-        <v>25298</v>
+        <v>19318</v>
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.25">
@@ -13758,11 +13784,11 @@
       </c>
       <c r="C157" s="1">
         <f t="shared" si="156"/>
-        <v>292431</v>
+        <v>290332</v>
       </c>
       <c r="D157" s="1">
         <f t="shared" si="156"/>
-        <v>294826</v>
+        <v>292727</v>
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.25">
@@ -13826,11 +13852,11 @@
       </c>
       <c r="C161" s="1">
         <f>C120+C131</f>
-        <v>31076</v>
+        <v>31080</v>
       </c>
       <c r="D161" s="1">
         <f>D120+D131</f>
-        <v>38601</v>
+        <v>38605</v>
       </c>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.25">
@@ -13843,11 +13869,11 @@
       </c>
       <c r="C162" s="1">
         <f>SUM(C138:C161)</f>
-        <v>1990612</v>
+        <v>1622024</v>
       </c>
       <c r="D162" s="1">
         <f>SUM(D138:D161)</f>
-        <v>2951579</v>
+        <v>2582991</v>
       </c>
     </row>
   </sheetData>
@@ -13892,21 +13918,21 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
-      <c r="B7" s="27" t="s">
+      <c r="B7" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="27"/>
-      <c r="D7" s="27"/>
-      <c r="E7" s="27" t="s">
+      <c r="C7" s="23"/>
+      <c r="D7" s="23"/>
+      <c r="E7" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="F7" s="27"/>
-      <c r="G7" s="27"/>
-      <c r="H7" s="27" t="s">
+      <c r="F7" s="23"/>
+      <c r="G7" s="23"/>
+      <c r="H7" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="I7" s="27"/>
-      <c r="J7" s="27"/>
+      <c r="I7" s="23"/>
+      <c r="J7" s="23"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
@@ -13942,7 +13968,7 @@
       <c r="O8" s="1"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="18">
+      <c r="A9" s="9">
         <f t="shared" ref="A9:A22" si="0">A10-1</f>
         <v>1881</v>
       </c>
@@ -13981,7 +14007,7 @@
       <c r="O9" s="1"/>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="18">
+      <c r="A10" s="9">
         <f t="shared" si="0"/>
         <v>1882</v>
       </c>
@@ -14020,7 +14046,7 @@
       <c r="O10" s="1"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="18">
+      <c r="A11" s="9">
         <f t="shared" si="0"/>
         <v>1883</v>
       </c>
@@ -14059,7 +14085,7 @@
       <c r="O11" s="1"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="18">
+      <c r="A12" s="9">
         <f t="shared" si="0"/>
         <v>1884</v>
       </c>
@@ -14098,7 +14124,7 @@
       <c r="O12" s="1"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="18">
+      <c r="A13" s="9">
         <f t="shared" si="0"/>
         <v>1885</v>
       </c>
@@ -14137,7 +14163,7 @@
       <c r="O13" s="1"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="18">
+      <c r="A14" s="9">
         <f t="shared" si="0"/>
         <v>1886</v>
       </c>
@@ -14176,7 +14202,7 @@
       <c r="O14" s="1"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" s="18">
+      <c r="A15" s="9">
         <f t="shared" si="0"/>
         <v>1887</v>
       </c>
@@ -14215,7 +14241,7 @@
       <c r="O15" s="1"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="18">
+      <c r="A16" s="9">
         <f t="shared" si="0"/>
         <v>1888</v>
       </c>
@@ -14254,7 +14280,7 @@
       <c r="O16" s="1"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17" s="18">
+      <c r="A17" s="9">
         <f t="shared" si="0"/>
         <v>1889</v>
       </c>
@@ -14294,7 +14320,7 @@
       <c r="O17" s="1"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A18" s="18">
+      <c r="A18" s="9">
         <f t="shared" si="0"/>
         <v>1890</v>
       </c>
@@ -14333,7 +14359,7 @@
       <c r="O18" s="1"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" s="18">
+      <c r="A19" s="9">
         <f t="shared" si="0"/>
         <v>1891</v>
       </c>
@@ -14372,7 +14398,7 @@
       <c r="O19" s="1"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A20" s="18">
+      <c r="A20" s="9">
         <f t="shared" si="0"/>
         <v>1892</v>
       </c>
@@ -14411,7 +14437,7 @@
       <c r="O20" s="1"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A21" s="18">
+      <c r="A21" s="9">
         <f t="shared" si="0"/>
         <v>1893</v>
       </c>
@@ -14450,7 +14476,7 @@
       <c r="O21" s="1"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A22" s="18">
+      <c r="A22" s="9">
         <f t="shared" si="0"/>
         <v>1894</v>
       </c>
@@ -14489,11 +14515,11 @@
       <c r="O22" s="1"/>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A23" s="18">
+      <c r="A23" s="9">
         <f>A24-1</f>
         <v>1895</v>
       </c>
-      <c r="B23" s="21">
+      <c r="B23" s="18">
         <f t="shared" si="1"/>
         <v>-78419</v>
       </c>
@@ -15388,7 +15414,7 @@
       <c r="O48" s="1"/>
     </row>
     <row r="49" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A49" s="22" t="s">
+      <c r="A49" s="19" t="s">
         <v>60</v>
       </c>
       <c r="O49" s="1"/>
@@ -15398,43 +15424,43 @@
     </row>
     <row r="51" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A51" s="2"/>
-      <c r="B51" s="27" t="s">
+      <c r="B51" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="C51" s="27"/>
-      <c r="D51" s="27"/>
-      <c r="E51" s="27" t="s">
+      <c r="C51" s="23"/>
+      <c r="D51" s="23"/>
+      <c r="E51" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="F51" s="27"/>
-      <c r="G51" s="27"/>
-      <c r="H51" s="27" t="s">
+      <c r="F51" s="23"/>
+      <c r="G51" s="23"/>
+      <c r="H51" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="I51" s="27"/>
-      <c r="J51" s="27"/>
-      <c r="K51" s="27" t="s">
+      <c r="I51" s="23"/>
+      <c r="J51" s="23"/>
+      <c r="K51" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="L51" s="27"/>
-      <c r="M51" s="27"/>
-      <c r="N51" s="27" t="s">
+      <c r="L51" s="23"/>
+      <c r="M51" s="23"/>
+      <c r="N51" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="O51" s="27"/>
-      <c r="P51" s="27"/>
-      <c r="Q51" s="27" t="s">
+      <c r="O51" s="23"/>
+      <c r="P51" s="23"/>
+      <c r="Q51" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="R51" s="27"/>
-      <c r="S51" s="27"/>
-      <c r="U51" s="23" t="s">
+      <c r="R51" s="23"/>
+      <c r="S51" s="23"/>
+      <c r="U51" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="Y51" s="25" t="s">
+      <c r="Y51" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="AC51" s="24" t="s">
+      <c r="AC51" s="21" t="s">
         <v>57</v>
       </c>
     </row>
@@ -15496,13 +15522,13 @@
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U52" s="16" t="s">
+      <c r="U52" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="V52" s="16" t="s">
+      <c r="V52" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="W52" s="16" t="s">
+      <c r="W52" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y52" s="15" t="s">
@@ -15525,7 +15551,7 @@
       </c>
     </row>
     <row r="53" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A53" s="18">
+      <c r="A53" s="9">
         <f t="shared" ref="A53:A66" si="13">A54-1</f>
         <v>1881</v>
       </c>
@@ -15559,9 +15585,9 @@
       <c r="J53" s="1">
         <v>7392</v>
       </c>
-      <c r="K53" s="17"/>
-      <c r="L53" s="17"/>
-      <c r="M53" s="17"/>
+      <c r="K53" s="16"/>
+      <c r="L53" s="16"/>
+      <c r="M53" s="16"/>
       <c r="N53" s="1">
         <v>2099</v>
       </c>
@@ -15617,7 +15643,7 @@
       </c>
     </row>
     <row r="54" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A54" s="18">
+      <c r="A54" s="9">
         <f t="shared" si="13"/>
         <v>1882</v>
       </c>
@@ -15651,12 +15677,12 @@
       <c r="J54" s="1">
         <v>8538</v>
       </c>
-      <c r="K54" s="17"/>
-      <c r="L54" s="17"/>
-      <c r="M54" s="17"/>
-      <c r="N54" s="17"/>
-      <c r="O54" s="17"/>
-      <c r="P54" s="17"/>
+      <c r="K54" s="16"/>
+      <c r="L54" s="16"/>
+      <c r="M54" s="16"/>
+      <c r="N54" s="16"/>
+      <c r="O54" s="16"/>
+      <c r="P54" s="16"/>
       <c r="Q54" s="1">
         <f t="shared" si="17"/>
         <v>-10</v>
@@ -15703,7 +15729,7 @@
       </c>
     </row>
     <row r="55" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A55" s="18">
+      <c r="A55" s="9">
         <f t="shared" si="13"/>
         <v>1883</v>
       </c>
@@ -15737,12 +15763,12 @@
       <c r="J55" s="1">
         <v>7215</v>
       </c>
-      <c r="K55" s="17"/>
-      <c r="L55" s="17"/>
-      <c r="M55" s="17"/>
-      <c r="N55" s="17"/>
-      <c r="O55" s="17"/>
-      <c r="P55" s="17"/>
+      <c r="K55" s="16"/>
+      <c r="L55" s="16"/>
+      <c r="M55" s="16"/>
+      <c r="N55" s="16"/>
+      <c r="O55" s="16"/>
+      <c r="P55" s="16"/>
       <c r="Q55" s="1">
         <f t="shared" si="17"/>
         <v>0</v>
@@ -15783,7 +15809,7 @@
       </c>
     </row>
     <row r="56" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A56" s="18">
+      <c r="A56" s="9">
         <f t="shared" si="13"/>
         <v>1884</v>
       </c>
@@ -15817,12 +15843,12 @@
       <c r="J56" s="1">
         <v>7388</v>
       </c>
-      <c r="K56" s="17"/>
-      <c r="L56" s="17"/>
-      <c r="M56" s="17"/>
-      <c r="N56" s="17"/>
-      <c r="O56" s="17"/>
-      <c r="P56" s="17"/>
+      <c r="K56" s="16"/>
+      <c r="L56" s="16"/>
+      <c r="M56" s="16"/>
+      <c r="N56" s="16"/>
+      <c r="O56" s="16"/>
+      <c r="P56" s="16"/>
       <c r="Q56" s="1">
         <f t="shared" si="17"/>
         <v>1</v>
@@ -15869,7 +15895,7 @@
       </c>
     </row>
     <row r="57" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A57" s="18">
+      <c r="A57" s="9">
         <f t="shared" si="13"/>
         <v>1885</v>
       </c>
@@ -15903,12 +15929,12 @@
       <c r="J57" s="1">
         <v>9803</v>
       </c>
-      <c r="K57" s="17"/>
-      <c r="L57" s="17"/>
-      <c r="M57" s="17"/>
-      <c r="N57" s="17"/>
-      <c r="O57" s="17"/>
-      <c r="P57" s="17"/>
+      <c r="K57" s="16"/>
+      <c r="L57" s="16"/>
+      <c r="M57" s="16"/>
+      <c r="N57" s="16"/>
+      <c r="O57" s="16"/>
+      <c r="P57" s="16"/>
       <c r="Q57" s="1">
         <f t="shared" si="17"/>
         <v>0</v>
@@ -15949,7 +15975,7 @@
       </c>
     </row>
     <row r="58" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A58" s="18">
+      <c r="A58" s="9">
         <f t="shared" si="13"/>
         <v>1886</v>
       </c>
@@ -15983,12 +16009,12 @@
       <c r="J58" s="1">
         <v>8814</v>
       </c>
-      <c r="K58" s="17"/>
-      <c r="L58" s="17"/>
-      <c r="M58" s="17"/>
-      <c r="N58" s="17"/>
-      <c r="O58" s="17"/>
-      <c r="P58" s="17"/>
+      <c r="K58" s="16"/>
+      <c r="L58" s="16"/>
+      <c r="M58" s="16"/>
+      <c r="N58" s="16"/>
+      <c r="O58" s="16"/>
+      <c r="P58" s="16"/>
       <c r="Q58" s="1">
         <f t="shared" si="17"/>
         <v>-12</v>
@@ -16035,7 +16061,7 @@
       </c>
     </row>
     <row r="59" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A59" s="18">
+      <c r="A59" s="9">
         <f t="shared" si="13"/>
         <v>1887</v>
       </c>
@@ -16069,15 +16095,15 @@
       <c r="J59" s="1">
         <v>2014</v>
       </c>
-      <c r="K59" s="17"/>
-      <c r="L59" s="17"/>
-      <c r="M59" s="17"/>
-      <c r="N59" s="17"/>
-      <c r="O59" s="17"/>
-      <c r="P59" s="17"/>
-      <c r="Q59" s="17"/>
-      <c r="R59" s="17"/>
-      <c r="S59" s="17"/>
+      <c r="K59" s="16"/>
+      <c r="L59" s="16"/>
+      <c r="M59" s="16"/>
+      <c r="N59" s="16"/>
+      <c r="O59" s="16"/>
+      <c r="P59" s="16"/>
+      <c r="Q59" s="16"/>
+      <c r="R59" s="16"/>
+      <c r="S59" s="16"/>
       <c r="U59" s="1">
         <f t="shared" si="21"/>
         <v>44769</v>
@@ -16114,7 +16140,7 @@
       </c>
     </row>
     <row r="60" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A60" s="18">
+      <c r="A60" s="9">
         <f t="shared" si="13"/>
         <v>1888</v>
       </c>
@@ -16148,15 +16174,15 @@
       <c r="J60">
         <v>213</v>
       </c>
-      <c r="K60" s="17"/>
-      <c r="L60" s="17"/>
-      <c r="M60" s="17"/>
-      <c r="N60" s="17"/>
-      <c r="O60" s="17"/>
-      <c r="P60" s="17"/>
-      <c r="Q60" s="17"/>
-      <c r="R60" s="17"/>
-      <c r="S60" s="17"/>
+      <c r="K60" s="16"/>
+      <c r="L60" s="16"/>
+      <c r="M60" s="16"/>
+      <c r="N60" s="16"/>
+      <c r="O60" s="16"/>
+      <c r="P60" s="16"/>
+      <c r="Q60" s="16"/>
+      <c r="R60" s="16"/>
+      <c r="S60" s="16"/>
       <c r="U60" s="1">
         <f t="shared" si="21"/>
         <v>75001</v>
@@ -16193,28 +16219,28 @@
       </c>
     </row>
     <row r="61" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A61" s="18">
+      <c r="A61" s="9">
         <f t="shared" si="13"/>
         <v>1889</v>
       </c>
-      <c r="B61" s="17"/>
-      <c r="C61" s="17"/>
-      <c r="D61" s="17"/>
-      <c r="E61" s="17"/>
-      <c r="F61" s="17"/>
-      <c r="G61" s="17"/>
-      <c r="H61" s="17"/>
-      <c r="I61" s="17"/>
-      <c r="J61" s="17"/>
-      <c r="K61" s="17"/>
-      <c r="L61" s="17"/>
-      <c r="M61" s="17"/>
-      <c r="N61" s="17"/>
-      <c r="O61" s="17"/>
-      <c r="P61" s="17"/>
-      <c r="Q61" s="17"/>
-      <c r="R61" s="17"/>
-      <c r="S61" s="17"/>
+      <c r="B61" s="16"/>
+      <c r="C61" s="16"/>
+      <c r="D61" s="16"/>
+      <c r="E61" s="16"/>
+      <c r="F61" s="16"/>
+      <c r="G61" s="16"/>
+      <c r="H61" s="16"/>
+      <c r="I61" s="16"/>
+      <c r="J61" s="16"/>
+      <c r="K61" s="16"/>
+      <c r="L61" s="16"/>
+      <c r="M61" s="16"/>
+      <c r="N61" s="16"/>
+      <c r="O61" s="16"/>
+      <c r="P61" s="16"/>
+      <c r="Q61" s="16"/>
+      <c r="R61" s="16"/>
+      <c r="S61" s="16"/>
       <c r="U61" s="1">
         <f t="shared" si="21"/>
         <v>30882</v>
@@ -16227,28 +16253,28 @@
       </c>
     </row>
     <row r="62" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A62" s="18">
+      <c r="A62" s="9">
         <f t="shared" si="13"/>
         <v>1890</v>
       </c>
-      <c r="B62" s="17"/>
-      <c r="C62" s="17"/>
-      <c r="D62" s="17"/>
-      <c r="E62" s="17"/>
-      <c r="F62" s="17"/>
-      <c r="G62" s="17"/>
-      <c r="H62" s="17"/>
-      <c r="I62" s="17"/>
-      <c r="J62" s="17"/>
-      <c r="K62" s="17"/>
-      <c r="L62" s="17"/>
-      <c r="M62" s="17"/>
-      <c r="N62" s="17"/>
-      <c r="O62" s="17"/>
-      <c r="P62" s="17"/>
-      <c r="Q62" s="17"/>
-      <c r="R62" s="17"/>
-      <c r="S62" s="17"/>
+      <c r="B62" s="16"/>
+      <c r="C62" s="16"/>
+      <c r="D62" s="16"/>
+      <c r="E62" s="16"/>
+      <c r="F62" s="16"/>
+      <c r="G62" s="16"/>
+      <c r="H62" s="16"/>
+      <c r="I62" s="16"/>
+      <c r="J62" s="16"/>
+      <c r="K62" s="16"/>
+      <c r="L62" s="16"/>
+      <c r="M62" s="16"/>
+      <c r="N62" s="16"/>
+      <c r="O62" s="16"/>
+      <c r="P62" s="16"/>
+      <c r="Q62" s="16"/>
+      <c r="R62" s="16"/>
+      <c r="S62" s="16"/>
       <c r="U62" s="1">
         <f t="shared" si="21"/>
         <v>50014</v>
@@ -16261,28 +16287,28 @@
       </c>
     </row>
     <row r="63" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A63" s="18">
+      <c r="A63" s="9">
         <f t="shared" si="13"/>
         <v>1891</v>
       </c>
-      <c r="B63" s="17"/>
-      <c r="C63" s="17"/>
-      <c r="D63" s="17"/>
-      <c r="E63" s="17"/>
-      <c r="F63" s="17"/>
-      <c r="G63" s="17"/>
-      <c r="H63" s="17"/>
-      <c r="I63" s="17"/>
-      <c r="J63" s="17"/>
-      <c r="K63" s="17"/>
-      <c r="L63" s="17"/>
-      <c r="M63" s="17"/>
-      <c r="N63" s="17"/>
-      <c r="O63" s="17"/>
-      <c r="P63" s="17"/>
-      <c r="Q63" s="17"/>
-      <c r="R63" s="17"/>
-      <c r="S63" s="17"/>
+      <c r="B63" s="16"/>
+      <c r="C63" s="16"/>
+      <c r="D63" s="16"/>
+      <c r="E63" s="16"/>
+      <c r="F63" s="16"/>
+      <c r="G63" s="16"/>
+      <c r="H63" s="16"/>
+      <c r="I63" s="16"/>
+      <c r="J63" s="16"/>
+      <c r="K63" s="16"/>
+      <c r="L63" s="16"/>
+      <c r="M63" s="16"/>
+      <c r="N63" s="16"/>
+      <c r="O63" s="16"/>
+      <c r="P63" s="16"/>
+      <c r="Q63" s="16"/>
+      <c r="R63" s="16"/>
+      <c r="S63" s="16"/>
       <c r="U63" s="1">
         <f t="shared" si="21"/>
         <v>15917</v>
@@ -16295,28 +16321,28 @@
       </c>
     </row>
     <row r="64" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A64" s="18">
+      <c r="A64" s="9">
         <f t="shared" si="13"/>
         <v>1892</v>
       </c>
-      <c r="B64" s="17"/>
-      <c r="C64" s="17"/>
-      <c r="D64" s="17"/>
-      <c r="E64" s="17"/>
-      <c r="F64" s="17"/>
-      <c r="G64" s="17"/>
-      <c r="H64" s="17"/>
-      <c r="I64" s="17"/>
-      <c r="J64" s="17"/>
-      <c r="K64" s="17"/>
-      <c r="L64" s="17"/>
-      <c r="M64" s="17"/>
-      <c r="N64" s="17"/>
-      <c r="O64" s="17"/>
-      <c r="P64" s="17"/>
-      <c r="Q64" s="17"/>
-      <c r="R64" s="17"/>
-      <c r="S64" s="17"/>
+      <c r="B64" s="16"/>
+      <c r="C64" s="16"/>
+      <c r="D64" s="16"/>
+      <c r="E64" s="16"/>
+      <c r="F64" s="16"/>
+      <c r="G64" s="16"/>
+      <c r="H64" s="16"/>
+      <c r="I64" s="16"/>
+      <c r="J64" s="16"/>
+      <c r="K64" s="16"/>
+      <c r="L64" s="16"/>
+      <c r="M64" s="16"/>
+      <c r="N64" s="16"/>
+      <c r="O64" s="16"/>
+      <c r="P64" s="16"/>
+      <c r="Q64" s="16"/>
+      <c r="R64" s="16"/>
+      <c r="S64" s="16"/>
       <c r="U64" s="1">
         <f t="shared" si="21"/>
         <v>12069</v>
@@ -16329,28 +16355,28 @@
       </c>
     </row>
     <row r="65" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A65" s="18">
+      <c r="A65" s="9">
         <f t="shared" si="13"/>
         <v>1893</v>
       </c>
-      <c r="B65" s="17"/>
-      <c r="C65" s="17"/>
-      <c r="D65" s="17"/>
-      <c r="E65" s="17"/>
-      <c r="F65" s="17"/>
-      <c r="G65" s="17"/>
-      <c r="H65" s="17"/>
-      <c r="I65" s="17"/>
-      <c r="J65" s="17"/>
-      <c r="K65" s="17"/>
-      <c r="L65" s="17"/>
-      <c r="M65" s="17"/>
-      <c r="N65" s="17"/>
-      <c r="O65" s="17"/>
-      <c r="P65" s="17"/>
-      <c r="Q65" s="17"/>
-      <c r="R65" s="17"/>
-      <c r="S65" s="17"/>
+      <c r="B65" s="16"/>
+      <c r="C65" s="16"/>
+      <c r="D65" s="16"/>
+      <c r="E65" s="16"/>
+      <c r="F65" s="16"/>
+      <c r="G65" s="16"/>
+      <c r="H65" s="16"/>
+      <c r="I65" s="16"/>
+      <c r="J65" s="16"/>
+      <c r="K65" s="16"/>
+      <c r="L65" s="16"/>
+      <c r="M65" s="16"/>
+      <c r="N65" s="16"/>
+      <c r="O65" s="16"/>
+      <c r="P65" s="16"/>
+      <c r="Q65" s="16"/>
+      <c r="R65" s="16"/>
+      <c r="S65" s="16"/>
       <c r="U65" s="1">
         <f t="shared" si="21"/>
         <v>31556</v>
@@ -16363,28 +16389,28 @@
       </c>
     </row>
     <row r="66" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A66" s="18">
+      <c r="A66" s="9">
         <f t="shared" si="13"/>
         <v>1894</v>
       </c>
-      <c r="B66" s="17"/>
-      <c r="C66" s="17"/>
-      <c r="D66" s="17"/>
-      <c r="E66" s="17"/>
-      <c r="F66" s="17"/>
-      <c r="G66" s="17"/>
-      <c r="H66" s="17"/>
-      <c r="I66" s="17"/>
-      <c r="J66" s="17"/>
-      <c r="K66" s="17"/>
-      <c r="L66" s="17"/>
-      <c r="M66" s="17"/>
-      <c r="N66" s="17"/>
-      <c r="O66" s="17"/>
-      <c r="P66" s="17"/>
-      <c r="Q66" s="17"/>
-      <c r="R66" s="17"/>
-      <c r="S66" s="17"/>
+      <c r="B66" s="16"/>
+      <c r="C66" s="16"/>
+      <c r="D66" s="16"/>
+      <c r="E66" s="16"/>
+      <c r="F66" s="16"/>
+      <c r="G66" s="16"/>
+      <c r="H66" s="16"/>
+      <c r="I66" s="16"/>
+      <c r="J66" s="16"/>
+      <c r="K66" s="16"/>
+      <c r="L66" s="16"/>
+      <c r="M66" s="16"/>
+      <c r="N66" s="16"/>
+      <c r="O66" s="16"/>
+      <c r="P66" s="16"/>
+      <c r="Q66" s="16"/>
+      <c r="R66" s="16"/>
+      <c r="S66" s="16"/>
       <c r="U66" s="1">
         <f t="shared" si="21"/>
         <v>72247</v>
@@ -16397,28 +16423,28 @@
       </c>
     </row>
     <row r="67" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A67" s="18">
+      <c r="A67" s="9">
         <f>A68-1</f>
         <v>1895</v>
       </c>
-      <c r="B67" s="17"/>
-      <c r="C67" s="17"/>
-      <c r="D67" s="17"/>
-      <c r="E67" s="17"/>
-      <c r="F67" s="17"/>
-      <c r="G67" s="17"/>
-      <c r="H67" s="17"/>
-      <c r="I67" s="17"/>
-      <c r="J67" s="17"/>
-      <c r="K67" s="17"/>
-      <c r="L67" s="17"/>
-      <c r="M67" s="17"/>
-      <c r="N67" s="17"/>
-      <c r="O67" s="17"/>
-      <c r="P67" s="17"/>
-      <c r="Q67" s="17"/>
-      <c r="R67" s="17"/>
-      <c r="S67" s="17"/>
+      <c r="B67" s="16"/>
+      <c r="C67" s="16"/>
+      <c r="D67" s="16"/>
+      <c r="E67" s="16"/>
+      <c r="F67" s="16"/>
+      <c r="G67" s="16"/>
+      <c r="H67" s="16"/>
+      <c r="I67" s="16"/>
+      <c r="J67" s="16"/>
+      <c r="K67" s="16"/>
+      <c r="L67" s="16"/>
+      <c r="M67" s="16"/>
+      <c r="N67" s="16"/>
+      <c r="O67" s="16"/>
+      <c r="P67" s="16"/>
+      <c r="Q67" s="16"/>
+      <c r="R67" s="16"/>
+      <c r="S67" s="16"/>
       <c r="U67" s="1">
         <f t="shared" si="21"/>
         <v>-78419</v>
@@ -18479,44 +18505,44 @@
         <v>4</v>
       </c>
       <c r="B89" s="5">
-        <f>SUM(B68:B88)</f>
-        <v>608681</v>
+        <f>SUM(B68:B87)</f>
+        <v>319431</v>
       </c>
       <c r="C89" s="5"/>
       <c r="D89" s="5"/>
       <c r="E89" s="5">
-        <f t="shared" ref="E89" si="43">SUM(E68:E88)</f>
-        <v>59385</v>
+        <f t="shared" ref="E89:S89" si="43">SUM(E68:E87)</f>
+        <v>-11878</v>
       </c>
       <c r="F89" s="5"/>
       <c r="G89" s="5"/>
       <c r="H89" s="5">
-        <f t="shared" ref="H89" si="44">SUM(H68:H88)</f>
-        <v>12946</v>
+        <f t="shared" ref="H89:S89" si="44">SUM(H68:H87)</f>
+        <v>6966</v>
       </c>
       <c r="I89" s="5"/>
       <c r="J89" s="5"/>
       <c r="K89" s="5">
-        <f t="shared" ref="K89" si="45">SUM(K68:K88)</f>
+        <f t="shared" ref="K89:S89" si="45">SUM(K68:K87)</f>
         <v>151250</v>
       </c>
       <c r="L89" s="5"/>
       <c r="M89" s="5"/>
       <c r="N89" s="5">
-        <f t="shared" ref="N89" si="46">SUM(N68:N88)</f>
-        <v>89510</v>
+        <f t="shared" ref="N89:S89" si="46">SUM(N68:N87)</f>
+        <v>87411</v>
       </c>
       <c r="O89" s="5"/>
       <c r="P89" s="5"/>
       <c r="Q89" s="5">
-        <f t="shared" ref="Q89" si="47">SUM(Q68:Q88)</f>
-        <v>11120</v>
+        <f t="shared" ref="Q89:U89" si="47">SUM(Q68:Q87)</f>
+        <v>11124</v>
       </c>
       <c r="R89" s="5"/>
       <c r="S89" s="5"/>
       <c r="U89" s="5">
-        <f>SUM(U68:U88)</f>
-        <v>1066141</v>
+        <f t="shared" si="47"/>
+        <v>563304</v>
       </c>
       <c r="V89" s="4"/>
       <c r="W89" s="4"/>
@@ -18527,19 +18553,19 @@
       </c>
       <c r="B90" s="5">
         <f>B89+B88</f>
-        <v>897931</v>
+        <v>608681</v>
       </c>
       <c r="C90" s="4"/>
       <c r="D90" s="4"/>
       <c r="E90" s="5">
         <f t="shared" ref="E90" si="48">E89+E88</f>
-        <v>130648</v>
+        <v>59385</v>
       </c>
       <c r="F90" s="4"/>
       <c r="G90" s="4"/>
       <c r="H90" s="5">
         <f t="shared" ref="H90" si="49">H89+H88</f>
-        <v>18926</v>
+        <v>12946</v>
       </c>
       <c r="I90" s="4"/>
       <c r="J90" s="4"/>
@@ -18551,19 +18577,19 @@
       <c r="M90" s="4"/>
       <c r="N90" s="5">
         <f t="shared" ref="N90" si="51">N89+N88</f>
-        <v>91609</v>
+        <v>89510</v>
       </c>
       <c r="O90" s="4"/>
       <c r="P90" s="4"/>
       <c r="Q90" s="5">
         <f t="shared" ref="Q90" si="52">Q89+Q88</f>
-        <v>11116</v>
+        <v>11120</v>
       </c>
       <c r="R90" s="4"/>
       <c r="S90" s="4"/>
       <c r="U90" s="5">
         <f>U89+U88</f>
-        <v>1568978</v>
+        <v>1066141</v>
       </c>
       <c r="V90" s="4"/>
       <c r="W90" s="4"/>
@@ -18587,7 +18613,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7B60D45-40A7-4AEF-8152-6E6E2D19E14F}">
-  <dimension ref="A1:AI52"/>
+  <dimension ref="A1:AI75"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -18621,6 +18647,7 @@
     <col min="29" max="29" width="7.7109375" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="14.28515625" customWidth="1"/>
     <col min="31" max="31" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="12.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:31" x14ac:dyDescent="0.25">
@@ -18719,7 +18746,7 @@
       </c>
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A2" s="26">
+      <c r="A2">
         <v>1881</v>
       </c>
       <c r="B2" s="1">
@@ -18811,7 +18838,7 @@
       </c>
     </row>
     <row r="3" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A3" s="26">
+      <c r="A3">
         <f t="shared" ref="A3:A15" si="0">A4-1</f>
         <v>1882</v>
       </c>
@@ -18901,7 +18928,7 @@
       </c>
     </row>
     <row r="4" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A4" s="26">
+      <c r="A4">
         <f t="shared" si="0"/>
         <v>1883</v>
       </c>
@@ -18991,7 +19018,7 @@
       </c>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A5" s="26">
+      <c r="A5">
         <f t="shared" si="0"/>
         <v>1884</v>
       </c>
@@ -19081,7 +19108,7 @@
       </c>
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A6" s="26">
+      <c r="A6">
         <f t="shared" si="0"/>
         <v>1885</v>
       </c>
@@ -19171,7 +19198,7 @@
       </c>
     </row>
     <row r="7" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A7" s="26">
+      <c r="A7">
         <f t="shared" si="0"/>
         <v>1886</v>
       </c>
@@ -19261,7 +19288,7 @@
       </c>
     </row>
     <row r="8" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A8" s="26">
+      <c r="A8">
         <f t="shared" si="0"/>
         <v>1887</v>
       </c>
@@ -19348,7 +19375,7 @@
       </c>
     </row>
     <row r="9" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A9" s="26">
+      <c r="A9">
         <f t="shared" si="0"/>
         <v>1888</v>
       </c>
@@ -19435,7 +19462,7 @@
       </c>
     </row>
     <row r="10" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A10" s="26">
+      <c r="A10">
         <f t="shared" si="0"/>
         <v>1889</v>
       </c>
@@ -19513,7 +19540,7 @@
       </c>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A11" s="26">
+      <c r="A11">
         <f t="shared" si="0"/>
         <v>1890</v>
       </c>
@@ -19591,7 +19618,7 @@
       </c>
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A12" s="26">
+      <c r="A12">
         <f t="shared" si="0"/>
         <v>1891</v>
       </c>
@@ -19669,7 +19696,7 @@
       </c>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A13" s="26">
+      <c r="A13">
         <f t="shared" si="0"/>
         <v>1892</v>
       </c>
@@ -19747,7 +19774,7 @@
       </c>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A14" s="26">
+      <c r="A14">
         <f t="shared" si="0"/>
         <v>1893</v>
       </c>
@@ -19825,7 +19852,7 @@
       </c>
     </row>
     <row r="15" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A15" s="26">
+      <c r="A15">
         <f t="shared" si="0"/>
         <v>1894</v>
       </c>
@@ -19903,7 +19930,7 @@
       </c>
     </row>
     <row r="16" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A16" s="26">
+      <c r="A16">
         <f>A17-1</f>
         <v>1895</v>
       </c>
@@ -22011,11 +22038,14 @@
       <c r="AE45" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="AG45" t="s">
+      <c r="AG45" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="AI45" t="s">
+      <c r="AH45" s="8" t="s">
         <v>64</v>
+      </c>
+      <c r="AI45" s="8" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="46" spans="1:35" x14ac:dyDescent="0.25">
@@ -22146,6 +22176,14 @@
         <f>SUM(B46:AE46)</f>
         <v>960967</v>
       </c>
+      <c r="AH46" s="1">
+        <f>SUM(H46:AE46)</f>
+        <v>592379</v>
+      </c>
+      <c r="AI46" s="1">
+        <f>SUM(B46:G46)</f>
+        <v>368588</v>
+      </c>
     </row>
     <row r="47" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
@@ -22275,6 +22313,14 @@
         <f>SUM(B47:AE47)</f>
         <v>1622024</v>
       </c>
+      <c r="AH47" s="1">
+        <f>SUM(H47:AE47)</f>
+        <v>1057720</v>
+      </c>
+      <c r="AI47" s="1">
+        <f>SUM(B47:G47)</f>
+        <v>564304</v>
+      </c>
     </row>
     <row r="48" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
@@ -22404,6 +22450,14 @@
         <f>SUM(B48:AE48)</f>
         <v>2582991</v>
       </c>
+      <c r="AH48" s="1">
+        <f>SUM(H48:AE48)</f>
+        <v>1650099</v>
+      </c>
+      <c r="AI48" s="1">
+        <f>SUM(B48:G48)</f>
+        <v>932892</v>
+      </c>
     </row>
     <row r="50" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
@@ -22418,7 +22472,7 @@
         <v>341811</v>
       </c>
       <c r="J50" s="1">
-        <f t="shared" ref="I50:AE52" si="5">J46</f>
+        <f t="shared" ref="J50:AD52" si="5">J46</f>
         <v>1194</v>
       </c>
       <c r="K50" s="1">
@@ -22523,7 +22577,7 @@
         <v>76937</v>
       </c>
       <c r="J51" s="1">
-        <f t="shared" ref="H51:W52" si="7">J47</f>
+        <f t="shared" ref="J51:W51" si="7">J47</f>
         <v>12542</v>
       </c>
       <c r="K51" s="1">
@@ -22719,6 +22773,69 @@
         <f>SUM(B52:AE52)</f>
         <v>2582991</v>
       </c>
+    </row>
+    <row r="54" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="B54" s="1"/>
+    </row>
+    <row r="55" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="B55" s="1"/>
+    </row>
+    <row r="56" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="B56" s="1"/>
+    </row>
+    <row r="57" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="B57" s="1"/>
+    </row>
+    <row r="58" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="B58" s="1"/>
+    </row>
+    <row r="59" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="B59" s="1"/>
+    </row>
+    <row r="60" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="B60" s="1"/>
+    </row>
+    <row r="61" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="B61" s="1"/>
+    </row>
+    <row r="62" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="B62" s="1"/>
+    </row>
+    <row r="63" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="B63" s="1"/>
+    </row>
+    <row r="64" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="B64" s="1"/>
+    </row>
+    <row r="65" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B65" s="1"/>
+    </row>
+    <row r="66" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B66" s="1"/>
+    </row>
+    <row r="67" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B67" s="1"/>
+    </row>
+    <row r="68" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B68" s="1"/>
+    </row>
+    <row r="69" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B69" s="1"/>
+    </row>
+    <row r="70" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B70" s="1"/>
+    </row>
+    <row r="71" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B71" s="1"/>
+    </row>
+    <row r="72" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B72" s="1"/>
+    </row>
+    <row r="73" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B73" s="1"/>
+    </row>
+    <row r="75" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B75" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/rtss-pre1917/src/main/resources/immigration.xlsx
+++ b/rtss-pre1917/src/main/resources/immigration.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\WINAPPS\SLOVO\UKR\github\RTSS\rtss-pre1917\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C9E4ADC-8588-4A6B-BBF8-F4E4EE3D7543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{846E8832-0F25-47D6-B582-D4D9720D8AD9}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="23520" activeTab="2" xr2:uid="{F5C0FC2C-9C7B-4145-981E-7BD1765E4EE3}"/>
+    <workbookView xWindow="-60" yWindow="-60" windowWidth="38520" windowHeight="23700" activeTab="2" xr2:uid="{F5C0FC2C-9C7B-4145-981E-7BD1765E4EE3}"/>
   </bookViews>
   <sheets>
     <sheet name="note-1" sheetId="2" r:id="rId1"/>
     <sheet name="note-2" sheetId="1" r:id="rId2"/>
     <sheet name="data" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,12 +25,7 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -38,14 +33,14 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
   <futureMetadata name="XLDAPR" count="1">
     <bk>
       <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+        <ext xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray" uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
           <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
         </ext>
       </extLst>
@@ -405,9 +400,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -445,7 +440,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -551,7 +546,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -693,7 +688,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -18511,25 +18506,25 @@
       <c r="C89" s="5"/>
       <c r="D89" s="5"/>
       <c r="E89" s="5">
-        <f t="shared" ref="E89:S89" si="43">SUM(E68:E87)</f>
+        <f t="shared" ref="E89" si="43">SUM(E68:E87)</f>
         <v>-11878</v>
       </c>
       <c r="F89" s="5"/>
       <c r="G89" s="5"/>
       <c r="H89" s="5">
-        <f t="shared" ref="H89:S89" si="44">SUM(H68:H87)</f>
+        <f t="shared" ref="H89" si="44">SUM(H68:H87)</f>
         <v>6966</v>
       </c>
       <c r="I89" s="5"/>
       <c r="J89" s="5"/>
       <c r="K89" s="5">
-        <f t="shared" ref="K89:S89" si="45">SUM(K68:K87)</f>
+        <f t="shared" ref="K89" si="45">SUM(K68:K87)</f>
         <v>151250</v>
       </c>
       <c r="L89" s="5"/>
       <c r="M89" s="5"/>
       <c r="N89" s="5">
-        <f t="shared" ref="N89:S89" si="46">SUM(N68:N87)</f>
+        <f t="shared" ref="N89" si="46">SUM(N68:N87)</f>
         <v>87411</v>
       </c>
       <c r="O89" s="5"/>
@@ -18613,7 +18608,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7B60D45-40A7-4AEF-8152-6E6E2D19E14F}">
-  <dimension ref="A1:AI75"/>
+  <dimension ref="A1:AI92"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -18746,7 +18741,7 @@
       </c>
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A2">
+      <c r="A2" s="9">
         <v>1881</v>
       </c>
       <c r="B2" s="1">
@@ -18838,7 +18833,7 @@
       </c>
     </row>
     <row r="3" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A3">
+      <c r="A3" s="9">
         <f t="shared" ref="A3:A15" si="0">A4-1</f>
         <v>1882</v>
       </c>
@@ -18928,7 +18923,7 @@
       </c>
     </row>
     <row r="4" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A4">
+      <c r="A4" s="9">
         <f t="shared" si="0"/>
         <v>1883</v>
       </c>
@@ -19018,7 +19013,7 @@
       </c>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A5">
+      <c r="A5" s="9">
         <f t="shared" si="0"/>
         <v>1884</v>
       </c>
@@ -19108,7 +19103,7 @@
       </c>
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A6">
+      <c r="A6" s="9">
         <f t="shared" si="0"/>
         <v>1885</v>
       </c>
@@ -19198,7 +19193,7 @@
       </c>
     </row>
     <row r="7" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A7">
+      <c r="A7" s="9">
         <f t="shared" si="0"/>
         <v>1886</v>
       </c>
@@ -19288,7 +19283,7 @@
       </c>
     </row>
     <row r="8" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A8">
+      <c r="A8" s="9">
         <f t="shared" si="0"/>
         <v>1887</v>
       </c>
@@ -19375,7 +19370,7 @@
       </c>
     </row>
     <row r="9" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A9">
+      <c r="A9" s="9">
         <f t="shared" si="0"/>
         <v>1888</v>
       </c>
@@ -19462,7 +19457,7 @@
       </c>
     </row>
     <row r="10" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A10">
+      <c r="A10" s="9">
         <f t="shared" si="0"/>
         <v>1889</v>
       </c>
@@ -19540,7 +19535,7 @@
       </c>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A11">
+      <c r="A11" s="9">
         <f t="shared" si="0"/>
         <v>1890</v>
       </c>
@@ -19618,7 +19613,7 @@
       </c>
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A12">
+      <c r="A12" s="9">
         <f t="shared" si="0"/>
         <v>1891</v>
       </c>
@@ -19696,7 +19691,7 @@
       </c>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A13">
+      <c r="A13" s="9">
         <f t="shared" si="0"/>
         <v>1892</v>
       </c>
@@ -19774,7 +19769,7 @@
       </c>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A14">
+      <c r="A14" s="9">
         <f t="shared" si="0"/>
         <v>1893</v>
       </c>
@@ -19852,7 +19847,7 @@
       </c>
     </row>
     <row r="15" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A15">
+      <c r="A15" s="9">
         <f t="shared" si="0"/>
         <v>1894</v>
       </c>
@@ -19930,7 +19925,7 @@
       </c>
     </row>
     <row r="16" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A16">
+      <c r="A16" s="9">
         <f>A17-1</f>
         <v>1895</v>
       </c>
@@ -20008,7 +20003,7 @@
       </c>
     </row>
     <row r="17" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A17">
+      <c r="A17" s="9">
         <v>1896</v>
       </c>
       <c r="B17" s="1">
@@ -20103,7 +20098,7 @@
       </c>
     </row>
     <row r="18" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A18">
+      <c r="A18" s="9">
         <f>A17+1</f>
         <v>1897</v>
       </c>
@@ -20199,7 +20194,7 @@
       </c>
     </row>
     <row r="19" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A19">
+      <c r="A19" s="9">
         <f t="shared" ref="A19:A36" si="1">A18+1</f>
         <v>1898</v>
       </c>
@@ -20295,7 +20290,7 @@
       </c>
     </row>
     <row r="20" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A20">
+      <c r="A20" s="9">
         <f t="shared" si="1"/>
         <v>1899</v>
       </c>
@@ -20391,7 +20386,7 @@
       </c>
     </row>
     <row r="21" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A21">
+      <c r="A21" s="9">
         <f t="shared" si="1"/>
         <v>1900</v>
       </c>
@@ -20487,7 +20482,7 @@
       </c>
     </row>
     <row r="22" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A22">
+      <c r="A22" s="9">
         <f t="shared" si="1"/>
         <v>1901</v>
       </c>
@@ -20583,7 +20578,7 @@
       </c>
     </row>
     <row r="23" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A23">
+      <c r="A23" s="9">
         <f t="shared" si="1"/>
         <v>1902</v>
       </c>
@@ -20679,7 +20674,7 @@
       </c>
     </row>
     <row r="24" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A24">
+      <c r="A24" s="9">
         <f t="shared" si="1"/>
         <v>1903</v>
       </c>
@@ -20775,7 +20770,7 @@
       </c>
     </row>
     <row r="25" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A25">
+      <c r="A25" s="9">
         <f t="shared" si="1"/>
         <v>1904</v>
       </c>
@@ -20871,7 +20866,7 @@
       </c>
     </row>
     <row r="26" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A26">
+      <c r="A26" s="9">
         <f t="shared" si="1"/>
         <v>1905</v>
       </c>
@@ -20967,7 +20962,7 @@
       </c>
     </row>
     <row r="27" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A27">
+      <c r="A27" s="9">
         <f t="shared" si="1"/>
         <v>1906</v>
       </c>
@@ -21063,7 +21058,7 @@
       </c>
     </row>
     <row r="28" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A28">
+      <c r="A28" s="9">
         <f t="shared" si="1"/>
         <v>1907</v>
       </c>
@@ -21159,7 +21154,7 @@
       </c>
     </row>
     <row r="29" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A29">
+      <c r="A29" s="9">
         <f t="shared" si="1"/>
         <v>1908</v>
       </c>
@@ -21255,7 +21250,7 @@
       </c>
     </row>
     <row r="30" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A30">
+      <c r="A30" s="9">
         <f t="shared" si="1"/>
         <v>1909</v>
       </c>
@@ -21351,7 +21346,7 @@
       </c>
     </row>
     <row r="31" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A31">
+      <c r="A31" s="9">
         <f t="shared" si="1"/>
         <v>1910</v>
       </c>
@@ -21447,7 +21442,7 @@
       </c>
     </row>
     <row r="32" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A32">
+      <c r="A32" s="9">
         <f t="shared" si="1"/>
         <v>1911</v>
       </c>
@@ -21543,7 +21538,7 @@
       </c>
     </row>
     <row r="33" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A33">
+      <c r="A33" s="9">
         <f t="shared" si="1"/>
         <v>1912</v>
       </c>
@@ -21639,7 +21634,7 @@
       </c>
     </row>
     <row r="34" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A34">
+      <c r="A34" s="9">
         <f t="shared" si="1"/>
         <v>1913</v>
       </c>
@@ -21735,7 +21730,7 @@
       </c>
     </row>
     <row r="35" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A35">
+      <c r="A35" s="9">
         <f t="shared" si="1"/>
         <v>1914</v>
       </c>
@@ -21831,7 +21826,7 @@
       </c>
     </row>
     <row r="36" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A36">
+      <c r="A36" s="9">
         <f t="shared" si="1"/>
         <v>1915</v>
       </c>
@@ -22049,7 +22044,7 @@
       </c>
     </row>
     <row r="46" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
+      <c r="A46" s="9" t="s">
         <v>50</v>
       </c>
       <c r="B46" s="1">
@@ -22186,7 +22181,7 @@
       </c>
     </row>
     <row r="47" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
+      <c r="A47" s="9" t="s">
         <v>4</v>
       </c>
       <c r="B47" s="1">
@@ -22323,7 +22318,7 @@
       </c>
     </row>
     <row r="48" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
+      <c r="A48" s="9" t="s">
         <v>51</v>
       </c>
       <c r="B48" s="1">
@@ -22459,8 +22454,11 @@
         <v>932892</v>
       </c>
     </row>
+    <row r="49" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A49" s="9"/>
+    </row>
     <row r="50" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
+      <c r="A50" s="9" t="s">
         <v>50</v>
       </c>
       <c r="H50" s="1">
@@ -22565,7 +22563,7 @@
       </c>
     </row>
     <row r="51" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
+      <c r="A51" s="9" t="s">
         <v>4</v>
       </c>
       <c r="H51" s="1">
@@ -22670,7 +22668,7 @@
       </c>
     </row>
     <row r="52" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
+      <c r="A52" s="9" t="s">
         <v>51</v>
       </c>
       <c r="H52" s="1">
@@ -22775,67 +22773,3718 @@
       </c>
     </row>
     <row r="54" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A54" s="9">
+        <v>1881</v>
+      </c>
       <c r="B54" s="1"/>
+      <c r="H54" s="1">
+        <f>H2+B2</f>
+        <v>54846</v>
+      </c>
+      <c r="I54" s="1">
+        <f>I2+C2</f>
+        <v>21252</v>
+      </c>
+      <c r="J54" s="1">
+        <f>J2</f>
+        <v>-366</v>
+      </c>
+      <c r="K54" s="1">
+        <f t="shared" ref="K54:Q54" si="12">K2</f>
+        <v>-294</v>
+      </c>
+      <c r="L54" s="1">
+        <f t="shared" si="12"/>
+        <v>7</v>
+      </c>
+      <c r="M54" s="1">
+        <f t="shared" si="12"/>
+        <v>-159</v>
+      </c>
+      <c r="N54" s="1">
+        <f t="shared" si="12"/>
+        <v>-3</v>
+      </c>
+      <c r="O54" s="1">
+        <f t="shared" si="12"/>
+        <v>-55</v>
+      </c>
+      <c r="P54" s="1">
+        <f t="shared" si="12"/>
+        <v>58</v>
+      </c>
+      <c r="Q54" s="1">
+        <f t="shared" si="12"/>
+        <v>-76</v>
+      </c>
+      <c r="R54" s="1">
+        <f>R2+D2</f>
+        <v>1011</v>
+      </c>
+      <c r="S54" s="1">
+        <f t="shared" ref="S54:AE69" si="13">S2</f>
+        <v>598</v>
+      </c>
+      <c r="T54" s="1">
+        <f t="shared" si="13"/>
+        <v>-18</v>
+      </c>
+      <c r="U54" s="1">
+        <f t="shared" si="13"/>
+        <v>122</v>
+      </c>
+      <c r="V54" s="1">
+        <f t="shared" si="13"/>
+        <v>-27</v>
+      </c>
+      <c r="W54" s="1">
+        <f t="shared" si="13"/>
+        <v>6</v>
+      </c>
+      <c r="X54" s="1">
+        <f t="shared" si="13"/>
+        <v>-2</v>
+      </c>
+      <c r="Y54" s="1">
+        <f t="shared" si="13"/>
+        <v>26</v>
+      </c>
+      <c r="Z54" s="1">
+        <f>Z2+E2</f>
+        <v>-942</v>
+      </c>
+      <c r="AA54" s="1">
+        <f>AA2+F2</f>
+        <v>2104</v>
+      </c>
+      <c r="AB54" s="1">
+        <f t="shared" si="13"/>
+        <v>890</v>
+      </c>
+      <c r="AC54" s="1">
+        <f t="shared" si="13"/>
+        <v>-2</v>
+      </c>
+      <c r="AD54" s="1">
+        <f t="shared" si="13"/>
+        <v>20</v>
+      </c>
+      <c r="AE54" s="1">
+        <f>AE2+G2</f>
+        <v>17</v>
+      </c>
+      <c r="AG54" s="1">
+        <f>SUM(H54:AE54)</f>
+        <v>79013</v>
+      </c>
     </row>
     <row r="55" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A55" s="9">
+        <v>1882</v>
+      </c>
       <c r="B55" s="1"/>
+      <c r="H55" s="1">
+        <f t="shared" ref="H55:H88" si="14">H3+B3</f>
+        <v>50504</v>
+      </c>
+      <c r="I55" s="1">
+        <f t="shared" ref="I55:I88" si="15">I3+C3</f>
+        <v>41842</v>
+      </c>
+      <c r="J55" s="1">
+        <f t="shared" ref="J55:Q88" si="16">J3</f>
+        <v>-493</v>
+      </c>
+      <c r="K55" s="1">
+        <f t="shared" si="16"/>
+        <v>599</v>
+      </c>
+      <c r="L55" s="1">
+        <f t="shared" si="16"/>
+        <v>-11</v>
+      </c>
+      <c r="M55" s="1">
+        <f t="shared" si="16"/>
+        <v>-781</v>
+      </c>
+      <c r="N55" s="1">
+        <f t="shared" si="16"/>
+        <v>79</v>
+      </c>
+      <c r="O55" s="1">
+        <f t="shared" si="16"/>
+        <v>-56</v>
+      </c>
+      <c r="P55" s="1">
+        <f t="shared" si="16"/>
+        <v>387</v>
+      </c>
+      <c r="Q55" s="1">
+        <f t="shared" si="16"/>
+        <v>-2</v>
+      </c>
+      <c r="R55" s="1">
+        <f t="shared" ref="R55:R88" si="17">R3+D3</f>
+        <v>1428</v>
+      </c>
+      <c r="S55" s="1">
+        <f t="shared" si="13"/>
+        <v>419</v>
+      </c>
+      <c r="T55" s="1">
+        <f t="shared" si="13"/>
+        <v>-21</v>
+      </c>
+      <c r="U55" s="1">
+        <f t="shared" si="13"/>
+        <v>17</v>
+      </c>
+      <c r="V55" s="1">
+        <f t="shared" si="13"/>
+        <v>5</v>
+      </c>
+      <c r="W55" s="1">
+        <f t="shared" si="13"/>
+        <v>4</v>
+      </c>
+      <c r="X55" s="1">
+        <f t="shared" si="13"/>
+        <v>-2</v>
+      </c>
+      <c r="Y55" s="1">
+        <f t="shared" si="13"/>
+        <v>-3</v>
+      </c>
+      <c r="Z55" s="1">
+        <f t="shared" ref="Z55:Z88" si="18">Z3+E3</f>
+        <v>7068</v>
+      </c>
+      <c r="AA55" s="1">
+        <f t="shared" ref="AA55:AA88" si="19">AA3+F3</f>
+        <v>10</v>
+      </c>
+      <c r="AB55" s="1">
+        <f t="shared" si="13"/>
+        <v>3081</v>
+      </c>
+      <c r="AC55" s="1">
+        <f t="shared" si="13"/>
+        <v>35</v>
+      </c>
+      <c r="AD55" s="1">
+        <f t="shared" si="13"/>
+        <v>2</v>
+      </c>
+      <c r="AE55" s="1">
+        <f t="shared" ref="AE55:AE88" si="20">AE3+G3</f>
+        <v>67</v>
+      </c>
+      <c r="AG55" s="1">
+        <f t="shared" ref="AG55:AG88" si="21">SUM(H55:AE55)</f>
+        <v>104178</v>
+      </c>
     </row>
     <row r="56" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A56" s="9">
+        <v>1883</v>
+      </c>
       <c r="B56" s="1"/>
+      <c r="H56" s="1">
+        <f t="shared" si="14"/>
+        <v>30582</v>
+      </c>
+      <c r="I56" s="1">
+        <f t="shared" si="15"/>
+        <v>35166</v>
+      </c>
+      <c r="J56" s="1">
+        <f t="shared" si="16"/>
+        <v>1223</v>
+      </c>
+      <c r="K56" s="1">
+        <f t="shared" si="16"/>
+        <v>154</v>
+      </c>
+      <c r="L56" s="1">
+        <f t="shared" si="16"/>
+        <v>88</v>
+      </c>
+      <c r="M56" s="1">
+        <f t="shared" si="16"/>
+        <v>93</v>
+      </c>
+      <c r="N56" s="1">
+        <f t="shared" si="16"/>
+        <v>-1</v>
+      </c>
+      <c r="O56" s="1">
+        <f t="shared" si="16"/>
+        <v>-6</v>
+      </c>
+      <c r="P56" s="1">
+        <f t="shared" si="16"/>
+        <v>34</v>
+      </c>
+      <c r="Q56" s="1">
+        <f t="shared" si="16"/>
+        <v>90</v>
+      </c>
+      <c r="R56" s="1">
+        <f t="shared" si="17"/>
+        <v>173</v>
+      </c>
+      <c r="S56" s="1">
+        <f t="shared" si="13"/>
+        <v>279</v>
+      </c>
+      <c r="T56" s="1">
+        <f t="shared" si="13"/>
+        <v>46</v>
+      </c>
+      <c r="U56" s="1">
+        <f t="shared" si="13"/>
+        <v>78</v>
+      </c>
+      <c r="V56" s="1">
+        <f t="shared" si="13"/>
+        <v>85</v>
+      </c>
+      <c r="W56" s="1">
+        <f t="shared" si="13"/>
+        <v>2</v>
+      </c>
+      <c r="X56" s="1">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="Y56" s="1">
+        <f t="shared" si="13"/>
+        <v>10</v>
+      </c>
+      <c r="Z56" s="1">
+        <f t="shared" si="18"/>
+        <v>4546</v>
+      </c>
+      <c r="AA56" s="1">
+        <f t="shared" si="19"/>
+        <v>-3</v>
+      </c>
+      <c r="AB56" s="1">
+        <f t="shared" si="13"/>
+        <v>4826</v>
+      </c>
+      <c r="AC56" s="1">
+        <f t="shared" si="13"/>
+        <v>-6</v>
+      </c>
+      <c r="AD56" s="1">
+        <f t="shared" si="13"/>
+        <v>-7</v>
+      </c>
+      <c r="AE56" s="1">
+        <f t="shared" si="20"/>
+        <v>49</v>
+      </c>
+      <c r="AG56" s="1">
+        <f t="shared" si="21"/>
+        <v>77501</v>
+      </c>
     </row>
     <row r="57" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A57" s="9">
+        <v>1884</v>
+      </c>
       <c r="B57" s="1"/>
+      <c r="H57" s="1">
+        <f t="shared" si="14"/>
+        <v>32918</v>
+      </c>
+      <c r="I57" s="1">
+        <f t="shared" si="15"/>
+        <v>37989</v>
+      </c>
+      <c r="J57" s="1">
+        <f t="shared" si="16"/>
+        <v>281</v>
+      </c>
+      <c r="K57" s="1">
+        <f t="shared" si="16"/>
+        <v>-371</v>
+      </c>
+      <c r="L57" s="1">
+        <f t="shared" si="16"/>
+        <v>59</v>
+      </c>
+      <c r="M57" s="1">
+        <f t="shared" si="16"/>
+        <v>29</v>
+      </c>
+      <c r="N57" s="1">
+        <f t="shared" si="16"/>
+        <v>45</v>
+      </c>
+      <c r="O57" s="1">
+        <f t="shared" si="16"/>
+        <v>12</v>
+      </c>
+      <c r="P57" s="1">
+        <f t="shared" si="16"/>
+        <v>102</v>
+      </c>
+      <c r="Q57" s="1">
+        <f t="shared" si="16"/>
+        <v>83</v>
+      </c>
+      <c r="R57" s="1">
+        <f t="shared" si="17"/>
+        <v>2443</v>
+      </c>
+      <c r="S57" s="1">
+        <f t="shared" si="13"/>
+        <v>298</v>
+      </c>
+      <c r="T57" s="1">
+        <f t="shared" si="13"/>
+        <v>67</v>
+      </c>
+      <c r="U57" s="1">
+        <f t="shared" si="13"/>
+        <v>-83</v>
+      </c>
+      <c r="V57" s="1">
+        <f t="shared" si="13"/>
+        <v>17</v>
+      </c>
+      <c r="W57" s="1">
+        <f t="shared" si="13"/>
+        <v>-24</v>
+      </c>
+      <c r="X57" s="1">
+        <f t="shared" si="13"/>
+        <v>9</v>
+      </c>
+      <c r="Y57" s="1">
+        <f t="shared" si="13"/>
+        <v>26</v>
+      </c>
+      <c r="Z57" s="1">
+        <f t="shared" si="18"/>
+        <v>6357</v>
+      </c>
+      <c r="AA57" s="1">
+        <f t="shared" si="19"/>
+        <v>-8</v>
+      </c>
+      <c r="AB57" s="1">
+        <f t="shared" si="13"/>
+        <v>2773</v>
+      </c>
+      <c r="AC57" s="1">
+        <f t="shared" si="13"/>
+        <v>-7</v>
+      </c>
+      <c r="AD57" s="1">
+        <f t="shared" si="13"/>
+        <v>-85</v>
+      </c>
+      <c r="AE57" s="1">
+        <f t="shared" si="20"/>
+        <v>105</v>
+      </c>
+      <c r="AG57" s="1">
+        <f t="shared" si="21"/>
+        <v>83035</v>
+      </c>
     </row>
     <row r="58" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A58" s="9">
+        <v>1885</v>
+      </c>
       <c r="B58" s="1"/>
+      <c r="H58" s="1">
+        <f t="shared" si="14"/>
+        <v>65433</v>
+      </c>
+      <c r="I58" s="1">
+        <f t="shared" si="15"/>
+        <v>44759</v>
+      </c>
+      <c r="J58" s="1">
+        <f t="shared" si="16"/>
+        <v>2181</v>
+      </c>
+      <c r="K58" s="1">
+        <f t="shared" si="16"/>
+        <v>537</v>
+      </c>
+      <c r="L58" s="1">
+        <f t="shared" si="16"/>
+        <v>145</v>
+      </c>
+      <c r="M58" s="1">
+        <f t="shared" si="16"/>
+        <v>218</v>
+      </c>
+      <c r="N58" s="1">
+        <f t="shared" si="16"/>
+        <v>63</v>
+      </c>
+      <c r="O58" s="1">
+        <f t="shared" si="16"/>
+        <v>-43</v>
+      </c>
+      <c r="P58" s="1">
+        <f t="shared" si="16"/>
+        <v>-121</v>
+      </c>
+      <c r="Q58" s="1">
+        <f t="shared" si="16"/>
+        <v>-90</v>
+      </c>
+      <c r="R58" s="1">
+        <f t="shared" si="17"/>
+        <v>453</v>
+      </c>
+      <c r="S58" s="1">
+        <f t="shared" si="13"/>
+        <v>39</v>
+      </c>
+      <c r="T58" s="1">
+        <f t="shared" si="13"/>
+        <v>17</v>
+      </c>
+      <c r="U58" s="1">
+        <f t="shared" si="13"/>
+        <v>358</v>
+      </c>
+      <c r="V58" s="1">
+        <f t="shared" si="13"/>
+        <v>13</v>
+      </c>
+      <c r="W58" s="1">
+        <f t="shared" si="13"/>
+        <v>-19</v>
+      </c>
+      <c r="X58" s="1">
+        <f t="shared" si="13"/>
+        <v>-3</v>
+      </c>
+      <c r="Y58" s="1">
+        <f t="shared" si="13"/>
+        <v>31</v>
+      </c>
+      <c r="Z58" s="1">
+        <f t="shared" si="18"/>
+        <v>4602</v>
+      </c>
+      <c r="AA58" s="1">
+        <f t="shared" si="19"/>
+        <v>-20</v>
+      </c>
+      <c r="AB58" s="1">
+        <f t="shared" si="13"/>
+        <v>3934</v>
+      </c>
+      <c r="AC58" s="1">
+        <f t="shared" si="13"/>
+        <v>4</v>
+      </c>
+      <c r="AD58" s="1">
+        <f t="shared" si="13"/>
+        <v>-34</v>
+      </c>
+      <c r="AE58" s="1">
+        <f t="shared" si="20"/>
+        <v>64</v>
+      </c>
+      <c r="AG58" s="1">
+        <f t="shared" si="21"/>
+        <v>122521</v>
+      </c>
     </row>
     <row r="59" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A59" s="9">
+        <v>1886</v>
+      </c>
       <c r="B59" s="1"/>
+      <c r="H59" s="1">
+        <f t="shared" si="14"/>
+        <v>55165</v>
+      </c>
+      <c r="I59" s="1">
+        <f t="shared" si="15"/>
+        <v>40607</v>
+      </c>
+      <c r="J59" s="1">
+        <f t="shared" si="16"/>
+        <v>285</v>
+      </c>
+      <c r="K59" s="1">
+        <f t="shared" si="16"/>
+        <v>229</v>
+      </c>
+      <c r="L59" s="1">
+        <f t="shared" si="16"/>
+        <v>414</v>
+      </c>
+      <c r="M59" s="1">
+        <f t="shared" si="16"/>
+        <v>223</v>
+      </c>
+      <c r="N59" s="1">
+        <f t="shared" si="16"/>
+        <v>-93</v>
+      </c>
+      <c r="O59" s="1">
+        <f t="shared" si="16"/>
+        <v>11</v>
+      </c>
+      <c r="P59" s="1">
+        <f t="shared" si="16"/>
+        <v>317</v>
+      </c>
+      <c r="Q59" s="1">
+        <f t="shared" si="16"/>
+        <v>-8</v>
+      </c>
+      <c r="R59" s="1">
+        <f t="shared" si="17"/>
+        <v>646</v>
+      </c>
+      <c r="S59" s="1">
+        <f t="shared" si="13"/>
+        <v>879</v>
+      </c>
+      <c r="T59" s="1">
+        <f t="shared" si="13"/>
+        <v>43</v>
+      </c>
+      <c r="U59" s="1">
+        <f t="shared" si="13"/>
+        <v>150</v>
+      </c>
+      <c r="V59" s="1">
+        <f t="shared" si="13"/>
+        <v>44</v>
+      </c>
+      <c r="W59" s="1">
+        <f t="shared" si="13"/>
+        <v>17</v>
+      </c>
+      <c r="X59" s="1">
+        <f t="shared" si="13"/>
+        <v>-6</v>
+      </c>
+      <c r="Y59" s="1">
+        <f t="shared" si="13"/>
+        <v>4</v>
+      </c>
+      <c r="Z59" s="1">
+        <f t="shared" si="18"/>
+        <v>14035</v>
+      </c>
+      <c r="AA59" s="1">
+        <f t="shared" si="19"/>
+        <v>-24</v>
+      </c>
+      <c r="AB59" s="1">
+        <f t="shared" si="13"/>
+        <v>3094</v>
+      </c>
+      <c r="AC59" s="1">
+        <f t="shared" si="13"/>
+        <v>-8</v>
+      </c>
+      <c r="AD59" s="1">
+        <f t="shared" si="13"/>
+        <v>17</v>
+      </c>
+      <c r="AE59" s="1">
+        <f t="shared" si="20"/>
+        <v>-309</v>
+      </c>
+      <c r="AG59" s="1">
+        <f t="shared" si="21"/>
+        <v>115732</v>
+      </c>
     </row>
     <row r="60" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A60" s="9">
+        <v>1887</v>
+      </c>
       <c r="B60" s="1"/>
+      <c r="H60" s="1">
+        <f t="shared" si="14"/>
+        <v>40077</v>
+      </c>
+      <c r="I60" s="1">
+        <f t="shared" si="15"/>
+        <v>17654</v>
+      </c>
+      <c r="J60" s="1">
+        <f t="shared" si="16"/>
+        <v>-898</v>
+      </c>
+      <c r="K60" s="1">
+        <f t="shared" si="16"/>
+        <v>-429</v>
+      </c>
+      <c r="L60" s="1">
+        <f t="shared" si="16"/>
+        <v>-76</v>
+      </c>
+      <c r="M60" s="1">
+        <f t="shared" si="16"/>
+        <v>-294</v>
+      </c>
+      <c r="N60" s="1">
+        <f t="shared" si="16"/>
+        <v>-121</v>
+      </c>
+      <c r="O60" s="1">
+        <f t="shared" si="16"/>
+        <v>-27</v>
+      </c>
+      <c r="P60" s="1">
+        <f t="shared" si="16"/>
+        <v>93</v>
+      </c>
+      <c r="Q60" s="1">
+        <f t="shared" si="16"/>
+        <v>-6</v>
+      </c>
+      <c r="R60" s="1">
+        <f t="shared" si="17"/>
+        <v>125</v>
+      </c>
+      <c r="S60" s="1">
+        <f t="shared" si="13"/>
+        <v>312</v>
+      </c>
+      <c r="T60" s="1">
+        <f t="shared" si="13"/>
+        <v>-20</v>
+      </c>
+      <c r="U60" s="1">
+        <f t="shared" si="13"/>
+        <v>-37</v>
+      </c>
+      <c r="V60" s="1">
+        <f t="shared" si="13"/>
+        <v>13</v>
+      </c>
+      <c r="W60" s="1">
+        <f t="shared" si="13"/>
+        <v>-5</v>
+      </c>
+      <c r="X60" s="1">
+        <f t="shared" si="13"/>
+        <v>-17</v>
+      </c>
+      <c r="Y60" s="1">
+        <f t="shared" si="13"/>
+        <v>22</v>
+      </c>
+      <c r="Z60" s="1">
+        <f t="shared" si="18"/>
+        <v>8123</v>
+      </c>
+      <c r="AA60" s="1">
+        <f t="shared" si="19"/>
+        <v>-99</v>
+      </c>
+      <c r="AB60" s="1">
+        <f t="shared" si="13"/>
+        <v>2183</v>
+      </c>
+      <c r="AC60" s="1">
+        <f t="shared" si="13"/>
+        <v>-5</v>
+      </c>
+      <c r="AD60" s="1">
+        <f t="shared" si="13"/>
+        <v>-38</v>
+      </c>
+      <c r="AE60" s="1">
+        <f t="shared" si="20"/>
+        <v>-215</v>
+      </c>
+      <c r="AG60" s="1">
+        <f t="shared" si="21"/>
+        <v>66315</v>
+      </c>
     </row>
     <row r="61" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A61" s="9">
+        <v>1888</v>
+      </c>
       <c r="B61" s="1"/>
+      <c r="H61" s="1">
+        <f t="shared" si="14"/>
+        <v>68160</v>
+      </c>
+      <c r="I61" s="1">
+        <f t="shared" si="15"/>
+        <v>15619</v>
+      </c>
+      <c r="J61" s="1">
+        <f t="shared" si="16"/>
+        <v>-112</v>
+      </c>
+      <c r="K61" s="1">
+        <f t="shared" si="16"/>
+        <v>243</v>
+      </c>
+      <c r="L61" s="1">
+        <f t="shared" si="16"/>
+        <v>-75</v>
+      </c>
+      <c r="M61" s="1">
+        <f t="shared" si="16"/>
+        <v>5</v>
+      </c>
+      <c r="N61" s="1">
+        <f t="shared" si="16"/>
+        <v>74</v>
+      </c>
+      <c r="O61" s="1">
+        <f t="shared" si="16"/>
+        <v>8</v>
+      </c>
+      <c r="P61" s="1">
+        <f t="shared" si="16"/>
+        <v>174</v>
+      </c>
+      <c r="Q61" s="1">
+        <f t="shared" si="16"/>
+        <v>79</v>
+      </c>
+      <c r="R61" s="1">
+        <f t="shared" si="17"/>
+        <v>16</v>
+      </c>
+      <c r="S61" s="1">
+        <f t="shared" si="13"/>
+        <v>661</v>
+      </c>
+      <c r="T61" s="1">
+        <f t="shared" si="13"/>
+        <v>44</v>
+      </c>
+      <c r="U61" s="1">
+        <f t="shared" si="13"/>
+        <v>30</v>
+      </c>
+      <c r="V61" s="1">
+        <f t="shared" si="13"/>
+        <v>11</v>
+      </c>
+      <c r="W61" s="1">
+        <f t="shared" si="13"/>
+        <v>-6</v>
+      </c>
+      <c r="X61" s="1">
+        <f t="shared" si="13"/>
+        <v>-12</v>
+      </c>
+      <c r="Y61" s="1">
+        <f t="shared" si="13"/>
+        <v>-9</v>
+      </c>
+      <c r="Z61" s="1">
+        <f t="shared" si="18"/>
+        <v>6129</v>
+      </c>
+      <c r="AA61" s="1">
+        <f t="shared" si="19"/>
+        <v>-34</v>
+      </c>
+      <c r="AB61" s="1">
+        <f t="shared" si="13"/>
+        <v>5927</v>
+      </c>
+      <c r="AC61" s="1">
+        <f t="shared" si="13"/>
+        <v>-3</v>
+      </c>
+      <c r="AD61" s="1">
+        <f t="shared" si="13"/>
+        <v>-71</v>
+      </c>
+      <c r="AE61" s="1">
+        <f t="shared" si="20"/>
+        <v>42</v>
+      </c>
+      <c r="AG61" s="1">
+        <f t="shared" si="21"/>
+        <v>96900</v>
+      </c>
     </row>
     <row r="62" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A62" s="9">
+        <v>1889</v>
+      </c>
       <c r="B62" s="1"/>
+      <c r="H62" s="1">
+        <f t="shared" si="14"/>
+        <v>17395</v>
+      </c>
+      <c r="I62" s="1">
+        <f t="shared" si="15"/>
+        <v>16643</v>
+      </c>
+      <c r="J62" s="1">
+        <f t="shared" si="16"/>
+        <v>400</v>
+      </c>
+      <c r="K62" s="1">
+        <f t="shared" si="16"/>
+        <v>1075</v>
+      </c>
+      <c r="L62" s="1">
+        <f t="shared" si="16"/>
+        <v>920</v>
+      </c>
+      <c r="M62" s="1">
+        <f t="shared" si="16"/>
+        <v>252</v>
+      </c>
+      <c r="N62" s="1">
+        <f t="shared" si="16"/>
+        <v>-52</v>
+      </c>
+      <c r="O62" s="1">
+        <f t="shared" si="16"/>
+        <v>30</v>
+      </c>
+      <c r="P62" s="1">
+        <f t="shared" si="16"/>
+        <v>-25</v>
+      </c>
+      <c r="Q62" s="1">
+        <f t="shared" si="16"/>
+        <v>4</v>
+      </c>
+      <c r="R62" s="1">
+        <f t="shared" si="17"/>
+        <v>335</v>
+      </c>
+      <c r="S62" s="1">
+        <f t="shared" si="13"/>
+        <v>296</v>
+      </c>
+      <c r="T62" s="1">
+        <f t="shared" si="13"/>
+        <v>-9</v>
+      </c>
+      <c r="U62" s="1">
+        <f t="shared" si="13"/>
+        <v>162</v>
+      </c>
+      <c r="V62" s="1">
+        <f t="shared" si="13"/>
+        <v>-11</v>
+      </c>
+      <c r="W62" s="1">
+        <f t="shared" si="13"/>
+        <v>36</v>
+      </c>
+      <c r="X62" s="1">
+        <f t="shared" si="13"/>
+        <v>12</v>
+      </c>
+      <c r="Y62" s="1">
+        <f t="shared" si="13"/>
+        <v>-2</v>
+      </c>
+      <c r="Z62" s="1">
+        <f t="shared" si="18"/>
+        <v>8526</v>
+      </c>
+      <c r="AA62" s="1">
+        <f t="shared" si="19"/>
+        <v>-100</v>
+      </c>
+      <c r="AB62" s="1">
+        <f t="shared" si="13"/>
+        <v>2995</v>
+      </c>
+      <c r="AC62" s="1">
+        <f t="shared" si="13"/>
+        <v>5</v>
+      </c>
+      <c r="AD62" s="1">
+        <f t="shared" si="13"/>
+        <v>23</v>
+      </c>
+      <c r="AE62" s="1">
+        <f t="shared" si="20"/>
+        <v>-19</v>
+      </c>
+      <c r="AG62" s="1">
+        <f t="shared" si="21"/>
+        <v>48891</v>
+      </c>
     </row>
     <row r="63" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A63" s="9">
+        <v>1890</v>
+      </c>
       <c r="B63" s="1"/>
+      <c r="H63" s="1">
+        <f t="shared" si="14"/>
+        <v>32800</v>
+      </c>
+      <c r="I63" s="1">
+        <f t="shared" si="15"/>
+        <v>15833</v>
+      </c>
+      <c r="J63" s="1">
+        <f t="shared" si="16"/>
+        <v>1581</v>
+      </c>
+      <c r="K63" s="1">
+        <f t="shared" si="16"/>
+        <v>868</v>
+      </c>
+      <c r="L63" s="1">
+        <f t="shared" si="16"/>
+        <v>290</v>
+      </c>
+      <c r="M63" s="1">
+        <f t="shared" si="16"/>
+        <v>446</v>
+      </c>
+      <c r="N63" s="1">
+        <f t="shared" si="16"/>
+        <v>113</v>
+      </c>
+      <c r="O63" s="1">
+        <f t="shared" si="16"/>
+        <v>12</v>
+      </c>
+      <c r="P63" s="1">
+        <f t="shared" si="16"/>
+        <v>1378</v>
+      </c>
+      <c r="Q63" s="1">
+        <f t="shared" si="16"/>
+        <v>9</v>
+      </c>
+      <c r="R63" s="1">
+        <f t="shared" si="17"/>
+        <v>612</v>
+      </c>
+      <c r="S63" s="1">
+        <f t="shared" si="13"/>
+        <v>426</v>
+      </c>
+      <c r="T63" s="1">
+        <f t="shared" si="13"/>
+        <v>21</v>
+      </c>
+      <c r="U63" s="1">
+        <f t="shared" si="13"/>
+        <v>291</v>
+      </c>
+      <c r="V63" s="1">
+        <f t="shared" si="13"/>
+        <v>-34</v>
+      </c>
+      <c r="W63" s="1">
+        <f t="shared" si="13"/>
+        <v>25</v>
+      </c>
+      <c r="X63" s="1">
+        <f t="shared" si="13"/>
+        <v>-24</v>
+      </c>
+      <c r="Y63" s="1">
+        <f t="shared" si="13"/>
+        <v>41</v>
+      </c>
+      <c r="Z63" s="1">
+        <f t="shared" si="18"/>
+        <v>12580</v>
+      </c>
+      <c r="AA63" s="1">
+        <f t="shared" si="19"/>
+        <v>-89</v>
+      </c>
+      <c r="AB63" s="1">
+        <f t="shared" si="13"/>
+        <v>3372</v>
+      </c>
+      <c r="AC63" s="1">
+        <f t="shared" si="13"/>
+        <v>-2</v>
+      </c>
+      <c r="AD63" s="1">
+        <f t="shared" si="13"/>
+        <v>-295</v>
+      </c>
+      <c r="AE63" s="1">
+        <f t="shared" si="20"/>
+        <v>-706</v>
+      </c>
+      <c r="AG63" s="1">
+        <f t="shared" si="21"/>
+        <v>69548</v>
+      </c>
     </row>
     <row r="64" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A64" s="9">
+        <v>1891</v>
+      </c>
       <c r="B64" s="1"/>
-    </row>
-    <row r="65" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="H64" s="1">
+        <f t="shared" si="14"/>
+        <v>-11339</v>
+      </c>
+      <c r="I64" s="1">
+        <f t="shared" si="15"/>
+        <v>19882</v>
+      </c>
+      <c r="J64" s="1">
+        <f t="shared" si="16"/>
+        <v>-526</v>
+      </c>
+      <c r="K64" s="1">
+        <f t="shared" si="16"/>
+        <v>851</v>
+      </c>
+      <c r="L64" s="1">
+        <f t="shared" si="16"/>
+        <v>581</v>
+      </c>
+      <c r="M64" s="1">
+        <f t="shared" si="16"/>
+        <v>39</v>
+      </c>
+      <c r="N64" s="1">
+        <f t="shared" si="16"/>
+        <v>-98</v>
+      </c>
+      <c r="O64" s="1">
+        <f t="shared" si="16"/>
+        <v>-2</v>
+      </c>
+      <c r="P64" s="1">
+        <f t="shared" si="16"/>
+        <v>879</v>
+      </c>
+      <c r="Q64" s="1">
+        <f t="shared" si="16"/>
+        <v>100</v>
+      </c>
+      <c r="R64" s="1">
+        <f t="shared" si="17"/>
+        <v>-275</v>
+      </c>
+      <c r="S64" s="1">
+        <f t="shared" si="13"/>
+        <v>201</v>
+      </c>
+      <c r="T64" s="1">
+        <f t="shared" si="13"/>
+        <v>85</v>
+      </c>
+      <c r="U64" s="1">
+        <f t="shared" si="13"/>
+        <v>240</v>
+      </c>
+      <c r="V64" s="1">
+        <f t="shared" si="13"/>
+        <v>31</v>
+      </c>
+      <c r="W64" s="1">
+        <f t="shared" si="13"/>
+        <v>-2</v>
+      </c>
+      <c r="X64" s="1">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="Y64" s="1">
+        <f t="shared" si="13"/>
+        <v>4</v>
+      </c>
+      <c r="Z64" s="1">
+        <f t="shared" si="18"/>
+        <v>7662</v>
+      </c>
+      <c r="AA64" s="1">
+        <f t="shared" si="19"/>
+        <v>-122</v>
+      </c>
+      <c r="AB64" s="1">
+        <f t="shared" si="13"/>
+        <v>3159</v>
+      </c>
+      <c r="AC64" s="1">
+        <f t="shared" si="13"/>
+        <v>3</v>
+      </c>
+      <c r="AD64" s="1">
+        <f t="shared" si="13"/>
+        <v>-343</v>
+      </c>
+      <c r="AE64" s="1">
+        <f t="shared" si="20"/>
+        <v>-470</v>
+      </c>
+      <c r="AG64" s="1">
+        <f t="shared" si="21"/>
+        <v>20540</v>
+      </c>
+    </row>
+    <row r="65" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A65" s="9">
+        <v>1892</v>
+      </c>
       <c r="B65" s="1"/>
-    </row>
-    <row r="66" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="H65" s="1">
+        <f t="shared" si="14"/>
+        <v>3616</v>
+      </c>
+      <c r="I65" s="1">
+        <f t="shared" si="15"/>
+        <v>9892</v>
+      </c>
+      <c r="J65" s="1">
+        <f t="shared" si="16"/>
+        <v>-999</v>
+      </c>
+      <c r="K65" s="1">
+        <f t="shared" si="16"/>
+        <v>416</v>
+      </c>
+      <c r="L65" s="1">
+        <f t="shared" si="16"/>
+        <v>224</v>
+      </c>
+      <c r="M65" s="1">
+        <f t="shared" si="16"/>
+        <v>-391</v>
+      </c>
+      <c r="N65" s="1">
+        <f t="shared" si="16"/>
+        <v>-9</v>
+      </c>
+      <c r="O65" s="1">
+        <f t="shared" si="16"/>
+        <v>17</v>
+      </c>
+      <c r="P65" s="1">
+        <f t="shared" si="16"/>
+        <v>899</v>
+      </c>
+      <c r="Q65" s="1">
+        <f t="shared" si="16"/>
+        <v>101</v>
+      </c>
+      <c r="R65" s="1">
+        <f t="shared" si="17"/>
+        <v>-287</v>
+      </c>
+      <c r="S65" s="1">
+        <f t="shared" si="13"/>
+        <v>214</v>
+      </c>
+      <c r="T65" s="1">
+        <f t="shared" si="13"/>
+        <v>118</v>
+      </c>
+      <c r="U65" s="1">
+        <f t="shared" si="13"/>
+        <v>199</v>
+      </c>
+      <c r="V65" s="1">
+        <f t="shared" si="13"/>
+        <v>10</v>
+      </c>
+      <c r="W65" s="1">
+        <f t="shared" si="13"/>
+        <v>14</v>
+      </c>
+      <c r="X65" s="1">
+        <f t="shared" si="13"/>
+        <v>34</v>
+      </c>
+      <c r="Y65" s="1">
+        <f t="shared" si="13"/>
+        <v>2</v>
+      </c>
+      <c r="Z65" s="1">
+        <f t="shared" si="18"/>
+        <v>16360</v>
+      </c>
+      <c r="AA65" s="1">
+        <f t="shared" si="19"/>
+        <v>-201</v>
+      </c>
+      <c r="AB65" s="1">
+        <f t="shared" si="13"/>
+        <v>-164</v>
+      </c>
+      <c r="AC65" s="1">
+        <f t="shared" si="13"/>
+        <v>5</v>
+      </c>
+      <c r="AD65" s="1">
+        <f t="shared" si="13"/>
+        <v>-250</v>
+      </c>
+      <c r="AE65" s="1">
+        <f t="shared" si="20"/>
+        <v>-16</v>
+      </c>
+      <c r="AG65" s="1">
+        <f t="shared" si="21"/>
+        <v>29804</v>
+      </c>
+    </row>
+    <row r="66" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A66" s="9">
+        <v>1893</v>
+      </c>
       <c r="B66" s="1"/>
-    </row>
-    <row r="67" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="H66" s="1">
+        <f t="shared" si="14"/>
+        <v>26811</v>
+      </c>
+      <c r="I66" s="1">
+        <f t="shared" si="15"/>
+        <v>3749</v>
+      </c>
+      <c r="J66" s="1">
+        <f t="shared" si="16"/>
+        <v>-127</v>
+      </c>
+      <c r="K66" s="1">
+        <f t="shared" si="16"/>
+        <v>1811</v>
+      </c>
+      <c r="L66" s="1">
+        <f t="shared" si="16"/>
+        <v>284</v>
+      </c>
+      <c r="M66" s="1">
+        <f t="shared" si="16"/>
+        <v>76</v>
+      </c>
+      <c r="N66" s="1">
+        <f t="shared" si="16"/>
+        <v>699</v>
+      </c>
+      <c r="O66" s="1">
+        <f t="shared" si="16"/>
+        <v>69</v>
+      </c>
+      <c r="P66" s="1">
+        <f t="shared" si="16"/>
+        <v>351</v>
+      </c>
+      <c r="Q66" s="1">
+        <f t="shared" si="16"/>
+        <v>178</v>
+      </c>
+      <c r="R66" s="1">
+        <f t="shared" si="17"/>
+        <v>69</v>
+      </c>
+      <c r="S66" s="1">
+        <f t="shared" si="13"/>
+        <v>4</v>
+      </c>
+      <c r="T66" s="1">
+        <f t="shared" si="13"/>
+        <v>-31</v>
+      </c>
+      <c r="U66" s="1">
+        <f t="shared" si="13"/>
+        <v>275</v>
+      </c>
+      <c r="V66" s="1">
+        <f t="shared" si="13"/>
+        <v>29</v>
+      </c>
+      <c r="W66" s="1">
+        <f t="shared" si="13"/>
+        <v>-32</v>
+      </c>
+      <c r="X66" s="1">
+        <f t="shared" si="13"/>
+        <v>-3</v>
+      </c>
+      <c r="Y66" s="1">
+        <f t="shared" si="13"/>
+        <v>15</v>
+      </c>
+      <c r="Z66" s="1">
+        <f t="shared" si="18"/>
+        <v>12664</v>
+      </c>
+      <c r="AA66" s="1">
+        <f t="shared" si="19"/>
+        <v>385</v>
+      </c>
+      <c r="AB66" s="1">
+        <f t="shared" si="13"/>
+        <v>5813</v>
+      </c>
+      <c r="AC66" s="1">
+        <f t="shared" si="13"/>
+        <v>13</v>
+      </c>
+      <c r="AD66" s="1">
+        <f t="shared" si="13"/>
+        <v>-393</v>
+      </c>
+      <c r="AE66" s="1">
+        <f t="shared" si="20"/>
+        <v>44</v>
+      </c>
+      <c r="AG66" s="1">
+        <f t="shared" si="21"/>
+        <v>52753</v>
+      </c>
+    </row>
+    <row r="67" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A67" s="9">
+        <v>1894</v>
+      </c>
       <c r="B67" s="1"/>
-    </row>
-    <row r="68" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="H67" s="1">
+        <f t="shared" si="14"/>
+        <v>5875</v>
+      </c>
+      <c r="I67" s="1">
+        <f t="shared" si="15"/>
+        <v>5078</v>
+      </c>
+      <c r="J67" s="1">
+        <f t="shared" si="16"/>
+        <v>-1092</v>
+      </c>
+      <c r="K67" s="1">
+        <f t="shared" si="16"/>
+        <v>871</v>
+      </c>
+      <c r="L67" s="1">
+        <f t="shared" si="16"/>
+        <v>430</v>
+      </c>
+      <c r="M67" s="1">
+        <f t="shared" si="16"/>
+        <v>-10</v>
+      </c>
+      <c r="N67" s="1">
+        <f t="shared" si="16"/>
+        <v>-314</v>
+      </c>
+      <c r="O67" s="1">
+        <f t="shared" si="16"/>
+        <v>40</v>
+      </c>
+      <c r="P67" s="1">
+        <f t="shared" si="16"/>
+        <v>1153</v>
+      </c>
+      <c r="Q67" s="1">
+        <f t="shared" si="16"/>
+        <v>103</v>
+      </c>
+      <c r="R67" s="1">
+        <f t="shared" si="17"/>
+        <v>385</v>
+      </c>
+      <c r="S67" s="1">
+        <f t="shared" si="13"/>
+        <v>398</v>
+      </c>
+      <c r="T67" s="1">
+        <f t="shared" si="13"/>
+        <v>99</v>
+      </c>
+      <c r="U67" s="1">
+        <f t="shared" si="13"/>
+        <v>390</v>
+      </c>
+      <c r="V67" s="1">
+        <f t="shared" si="13"/>
+        <v>-4</v>
+      </c>
+      <c r="W67" s="1">
+        <f t="shared" si="13"/>
+        <v>52</v>
+      </c>
+      <c r="X67" s="1">
+        <f t="shared" si="13"/>
+        <v>25</v>
+      </c>
+      <c r="Y67" s="1">
+        <f t="shared" si="13"/>
+        <v>16</v>
+      </c>
+      <c r="Z67" s="1">
+        <f t="shared" si="18"/>
+        <v>14190</v>
+      </c>
+      <c r="AA67" s="1">
+        <f t="shared" si="19"/>
+        <v>537</v>
+      </c>
+      <c r="AB67" s="1">
+        <f t="shared" si="13"/>
+        <v>2051</v>
+      </c>
+      <c r="AC67" s="1">
+        <f t="shared" si="13"/>
+        <v>6</v>
+      </c>
+      <c r="AD67" s="1">
+        <f t="shared" si="13"/>
+        <v>-143</v>
+      </c>
+      <c r="AE67" s="1">
+        <f t="shared" si="20"/>
+        <v>4552</v>
+      </c>
+      <c r="AG67" s="1">
+        <f t="shared" si="21"/>
+        <v>34688</v>
+      </c>
+    </row>
+    <row r="68" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A68" s="9">
+        <v>1895</v>
+      </c>
       <c r="B68" s="1"/>
-    </row>
-    <row r="69" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="H68" s="1">
+        <f t="shared" si="14"/>
+        <v>-85110</v>
+      </c>
+      <c r="I68" s="1">
+        <f t="shared" si="15"/>
+        <v>15846</v>
+      </c>
+      <c r="J68" s="1">
+        <f t="shared" si="16"/>
+        <v>-144</v>
+      </c>
+      <c r="K68" s="1">
+        <f t="shared" si="16"/>
+        <v>1033</v>
+      </c>
+      <c r="L68" s="1">
+        <f t="shared" si="16"/>
+        <v>1080</v>
+      </c>
+      <c r="M68" s="1">
+        <f t="shared" si="16"/>
+        <v>347</v>
+      </c>
+      <c r="N68" s="1">
+        <f t="shared" si="16"/>
+        <v>25</v>
+      </c>
+      <c r="O68" s="1">
+        <f t="shared" si="16"/>
+        <v>-57</v>
+      </c>
+      <c r="P68" s="1">
+        <f t="shared" si="16"/>
+        <v>597</v>
+      </c>
+      <c r="Q68" s="1">
+        <f t="shared" si="16"/>
+        <v>8</v>
+      </c>
+      <c r="R68" s="1">
+        <f t="shared" si="17"/>
+        <v>356</v>
+      </c>
+      <c r="S68" s="1">
+        <f t="shared" si="13"/>
+        <v>107</v>
+      </c>
+      <c r="T68" s="1">
+        <f t="shared" si="13"/>
+        <v>36</v>
+      </c>
+      <c r="U68" s="1">
+        <f t="shared" si="13"/>
+        <v>204</v>
+      </c>
+      <c r="V68" s="1">
+        <f t="shared" si="13"/>
+        <v>15</v>
+      </c>
+      <c r="W68" s="1">
+        <f t="shared" si="13"/>
+        <v>22</v>
+      </c>
+      <c r="X68" s="1">
+        <f t="shared" si="13"/>
+        <v>-4</v>
+      </c>
+      <c r="Y68" s="1">
+        <f t="shared" si="13"/>
+        <v>22</v>
+      </c>
+      <c r="Z68" s="1">
+        <f t="shared" si="18"/>
+        <v>16096</v>
+      </c>
+      <c r="AA68" s="1">
+        <f t="shared" si="19"/>
+        <v>59</v>
+      </c>
+      <c r="AB68" s="1">
+        <f t="shared" si="13"/>
+        <v>4906</v>
+      </c>
+      <c r="AC68" s="1">
+        <f t="shared" si="13"/>
+        <v>12</v>
+      </c>
+      <c r="AD68" s="1">
+        <f t="shared" si="13"/>
+        <v>-228</v>
+      </c>
+      <c r="AE68" s="1">
+        <f t="shared" si="20"/>
+        <v>4320</v>
+      </c>
+      <c r="AG68" s="1">
+        <f t="shared" si="21"/>
+        <v>-40452</v>
+      </c>
+    </row>
+    <row r="69" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A69" s="9">
+        <v>1896</v>
+      </c>
       <c r="B69" s="1"/>
-    </row>
-    <row r="70" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="H69" s="1">
+        <f t="shared" si="14"/>
+        <v>23460</v>
+      </c>
+      <c r="I69" s="1">
+        <f t="shared" si="15"/>
+        <v>3179</v>
+      </c>
+      <c r="J69" s="1">
+        <f t="shared" si="16"/>
+        <v>-978</v>
+      </c>
+      <c r="K69" s="1">
+        <f t="shared" si="16"/>
+        <v>-902</v>
+      </c>
+      <c r="L69" s="1">
+        <f t="shared" si="16"/>
+        <v>251</v>
+      </c>
+      <c r="M69" s="1">
+        <f t="shared" si="16"/>
+        <v>426</v>
+      </c>
+      <c r="N69" s="1">
+        <f t="shared" si="16"/>
+        <v>1415</v>
+      </c>
+      <c r="O69" s="1">
+        <f t="shared" si="16"/>
+        <v>-110</v>
+      </c>
+      <c r="P69" s="1">
+        <f t="shared" si="16"/>
+        <v>354</v>
+      </c>
+      <c r="Q69" s="1">
+        <f t="shared" si="16"/>
+        <v>174</v>
+      </c>
+      <c r="R69" s="1">
+        <f t="shared" si="17"/>
+        <v>289</v>
+      </c>
+      <c r="S69" s="1">
+        <f t="shared" si="13"/>
+        <v>331</v>
+      </c>
+      <c r="T69" s="1">
+        <f t="shared" si="13"/>
+        <v>51</v>
+      </c>
+      <c r="U69" s="1">
+        <f t="shared" si="13"/>
+        <v>526</v>
+      </c>
+      <c r="V69" s="1">
+        <f t="shared" si="13"/>
+        <v>129</v>
+      </c>
+      <c r="W69" s="1">
+        <f t="shared" si="13"/>
+        <v>62</v>
+      </c>
+      <c r="X69" s="1">
+        <f t="shared" si="13"/>
+        <v>-44</v>
+      </c>
+      <c r="Y69" s="1">
+        <f t="shared" si="13"/>
+        <v>25</v>
+      </c>
+      <c r="Z69" s="1">
+        <f t="shared" si="18"/>
+        <v>12095</v>
+      </c>
+      <c r="AA69" s="1">
+        <f t="shared" si="19"/>
+        <v>1431</v>
+      </c>
+      <c r="AB69" s="1">
+        <f t="shared" si="13"/>
+        <v>4771</v>
+      </c>
+      <c r="AC69" s="1">
+        <f t="shared" si="13"/>
+        <v>13</v>
+      </c>
+      <c r="AD69" s="1">
+        <f t="shared" si="13"/>
+        <v>-2081</v>
+      </c>
+      <c r="AE69" s="1">
+        <f t="shared" si="20"/>
+        <v>2834</v>
+      </c>
+      <c r="AG69" s="1">
+        <f t="shared" si="21"/>
+        <v>47701</v>
+      </c>
+    </row>
+    <row r="70" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A70" s="9">
+        <v>1897</v>
+      </c>
       <c r="B70" s="1"/>
-    </row>
-    <row r="71" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="H70" s="1">
+        <f t="shared" si="14"/>
+        <v>26567</v>
+      </c>
+      <c r="I70" s="1">
+        <f t="shared" si="15"/>
+        <v>9153</v>
+      </c>
+      <c r="J70" s="1">
+        <f t="shared" si="16"/>
+        <v>2018</v>
+      </c>
+      <c r="K70" s="1">
+        <f t="shared" si="16"/>
+        <v>1013</v>
+      </c>
+      <c r="L70" s="1">
+        <f t="shared" si="16"/>
+        <v>515</v>
+      </c>
+      <c r="M70" s="1">
+        <f t="shared" si="16"/>
+        <v>524</v>
+      </c>
+      <c r="N70" s="1">
+        <f t="shared" si="16"/>
+        <v>1418</v>
+      </c>
+      <c r="O70" s="1">
+        <f t="shared" si="16"/>
+        <v>90</v>
+      </c>
+      <c r="P70" s="1">
+        <f t="shared" si="16"/>
+        <v>484</v>
+      </c>
+      <c r="Q70" s="1">
+        <f t="shared" si="16"/>
+        <v>-4</v>
+      </c>
+      <c r="R70" s="1">
+        <f t="shared" si="17"/>
+        <v>455</v>
+      </c>
+      <c r="S70" s="1">
+        <f t="shared" ref="S70:AE85" si="22">S18</f>
+        <v>308</v>
+      </c>
+      <c r="T70" s="1">
+        <f t="shared" si="22"/>
+        <v>290</v>
+      </c>
+      <c r="U70" s="1">
+        <f t="shared" si="22"/>
+        <v>414</v>
+      </c>
+      <c r="V70" s="1">
+        <f t="shared" si="22"/>
+        <v>75</v>
+      </c>
+      <c r="W70" s="1">
+        <f t="shared" si="22"/>
+        <v>117</v>
+      </c>
+      <c r="X70" s="1">
+        <f t="shared" si="22"/>
+        <v>40</v>
+      </c>
+      <c r="Y70" s="1">
+        <f t="shared" si="22"/>
+        <v>-40</v>
+      </c>
+      <c r="Z70" s="1">
+        <f t="shared" si="18"/>
+        <v>26624</v>
+      </c>
+      <c r="AA70" s="1">
+        <f t="shared" si="19"/>
+        <v>1039</v>
+      </c>
+      <c r="AB70" s="1">
+        <f t="shared" si="22"/>
+        <v>4740</v>
+      </c>
+      <c r="AC70" s="1">
+        <f t="shared" si="22"/>
+        <v>16</v>
+      </c>
+      <c r="AD70" s="1">
+        <f t="shared" si="22"/>
+        <v>60</v>
+      </c>
+      <c r="AE70" s="1">
+        <f t="shared" si="20"/>
+        <v>3481</v>
+      </c>
+      <c r="AG70" s="1">
+        <f t="shared" si="21"/>
+        <v>79397</v>
+      </c>
+    </row>
+    <row r="71" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A71" s="9">
+        <v>1898</v>
+      </c>
       <c r="B71" s="1"/>
-    </row>
-    <row r="72" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="H71" s="1">
+        <f t="shared" si="14"/>
+        <v>19680</v>
+      </c>
+      <c r="I71" s="1">
+        <f t="shared" si="15"/>
+        <v>14479</v>
+      </c>
+      <c r="J71" s="1">
+        <f t="shared" si="16"/>
+        <v>2061</v>
+      </c>
+      <c r="K71" s="1">
+        <f t="shared" si="16"/>
+        <v>2034</v>
+      </c>
+      <c r="L71" s="1">
+        <f t="shared" si="16"/>
+        <v>415</v>
+      </c>
+      <c r="M71" s="1">
+        <f t="shared" si="16"/>
+        <v>383</v>
+      </c>
+      <c r="N71" s="1">
+        <f t="shared" si="16"/>
+        <v>1838</v>
+      </c>
+      <c r="O71" s="1">
+        <f t="shared" si="16"/>
+        <v>13</v>
+      </c>
+      <c r="P71" s="1">
+        <f t="shared" si="16"/>
+        <v>636</v>
+      </c>
+      <c r="Q71" s="1">
+        <f t="shared" si="16"/>
+        <v>161</v>
+      </c>
+      <c r="R71" s="1">
+        <f t="shared" si="17"/>
+        <v>746</v>
+      </c>
+      <c r="S71" s="1">
+        <f t="shared" si="22"/>
+        <v>424</v>
+      </c>
+      <c r="T71" s="1">
+        <f t="shared" si="22"/>
+        <v>-171</v>
+      </c>
+      <c r="U71" s="1">
+        <f t="shared" si="22"/>
+        <v>582</v>
+      </c>
+      <c r="V71" s="1">
+        <f t="shared" si="22"/>
+        <v>223</v>
+      </c>
+      <c r="W71" s="1">
+        <f t="shared" si="22"/>
+        <v>189</v>
+      </c>
+      <c r="X71" s="1">
+        <f t="shared" si="22"/>
+        <v>-38</v>
+      </c>
+      <c r="Y71" s="1">
+        <f t="shared" si="22"/>
+        <v>30</v>
+      </c>
+      <c r="Z71" s="1">
+        <f t="shared" si="18"/>
+        <v>26612</v>
+      </c>
+      <c r="AA71" s="1">
+        <f t="shared" si="19"/>
+        <v>1050</v>
+      </c>
+      <c r="AB71" s="1">
+        <f t="shared" si="22"/>
+        <v>9956</v>
+      </c>
+      <c r="AC71" s="1">
+        <f t="shared" si="22"/>
+        <v>64</v>
+      </c>
+      <c r="AD71" s="1">
+        <f t="shared" si="22"/>
+        <v>-14</v>
+      </c>
+      <c r="AE71" s="1">
+        <f t="shared" si="20"/>
+        <v>2289</v>
+      </c>
+      <c r="AG71" s="1">
+        <f t="shared" si="21"/>
+        <v>83642</v>
+      </c>
+    </row>
+    <row r="72" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A72" s="9">
+        <v>1899</v>
+      </c>
       <c r="B72" s="1"/>
-    </row>
-    <row r="73" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="H72" s="1">
+        <f t="shared" si="14"/>
+        <v>39526</v>
+      </c>
+      <c r="I72" s="1">
+        <f t="shared" si="15"/>
+        <v>8689</v>
+      </c>
+      <c r="J72" s="1">
+        <f t="shared" si="16"/>
+        <v>506</v>
+      </c>
+      <c r="K72" s="1">
+        <f t="shared" si="16"/>
+        <v>1122</v>
+      </c>
+      <c r="L72" s="1">
+        <f t="shared" si="16"/>
+        <v>554</v>
+      </c>
+      <c r="M72" s="1">
+        <f t="shared" si="16"/>
+        <v>202</v>
+      </c>
+      <c r="N72" s="1">
+        <f t="shared" si="16"/>
+        <v>277</v>
+      </c>
+      <c r="O72" s="1">
+        <f t="shared" si="16"/>
+        <v>131</v>
+      </c>
+      <c r="P72" s="1">
+        <f t="shared" si="16"/>
+        <v>274</v>
+      </c>
+      <c r="Q72" s="1">
+        <f t="shared" si="16"/>
+        <v>183</v>
+      </c>
+      <c r="R72" s="1">
+        <f t="shared" si="17"/>
+        <v>410</v>
+      </c>
+      <c r="S72" s="1">
+        <f t="shared" si="22"/>
+        <v>18</v>
+      </c>
+      <c r="T72" s="1">
+        <f t="shared" si="22"/>
+        <v>159</v>
+      </c>
+      <c r="U72" s="1">
+        <f t="shared" si="22"/>
+        <v>695</v>
+      </c>
+      <c r="V72" s="1">
+        <f t="shared" si="22"/>
+        <v>62</v>
+      </c>
+      <c r="W72" s="1">
+        <f t="shared" si="22"/>
+        <v>-23</v>
+      </c>
+      <c r="X72" s="1">
+        <f t="shared" si="22"/>
+        <v>11</v>
+      </c>
+      <c r="Y72" s="1">
+        <f t="shared" si="22"/>
+        <v>46</v>
+      </c>
+      <c r="Z72" s="1">
+        <f t="shared" si="18"/>
+        <v>31058</v>
+      </c>
+      <c r="AA72" s="1">
+        <f t="shared" si="19"/>
+        <v>1474</v>
+      </c>
+      <c r="AB72" s="1">
+        <f t="shared" si="22"/>
+        <v>8199</v>
+      </c>
+      <c r="AC72" s="1">
+        <f t="shared" si="22"/>
+        <v>-4</v>
+      </c>
+      <c r="AD72" s="1">
+        <f t="shared" si="22"/>
+        <v>-148</v>
+      </c>
+      <c r="AE72" s="1">
+        <f t="shared" si="20"/>
+        <v>1733</v>
+      </c>
+      <c r="AG72" s="1">
+        <f t="shared" si="21"/>
+        <v>95154</v>
+      </c>
+    </row>
+    <row r="73" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A73" s="9">
+        <v>1900</v>
+      </c>
       <c r="B73" s="1"/>
-    </row>
-    <row r="75" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="H73" s="1">
+        <f t="shared" si="14"/>
+        <v>28424</v>
+      </c>
+      <c r="I73" s="1">
+        <f t="shared" si="15"/>
+        <v>11790</v>
+      </c>
+      <c r="J73" s="1">
+        <f t="shared" si="16"/>
+        <v>160</v>
+      </c>
+      <c r="K73" s="1">
+        <f t="shared" si="16"/>
+        <v>506</v>
+      </c>
+      <c r="L73" s="1">
+        <f t="shared" si="16"/>
+        <v>250</v>
+      </c>
+      <c r="M73" s="1">
+        <f t="shared" si="16"/>
+        <v>-268</v>
+      </c>
+      <c r="N73" s="1">
+        <f t="shared" si="16"/>
+        <v>598</v>
+      </c>
+      <c r="O73" s="1">
+        <f t="shared" si="16"/>
+        <v>-117</v>
+      </c>
+      <c r="P73" s="1">
+        <f t="shared" si="16"/>
+        <v>161</v>
+      </c>
+      <c r="Q73" s="1">
+        <f t="shared" si="16"/>
+        <v>604</v>
+      </c>
+      <c r="R73" s="1">
+        <f t="shared" si="17"/>
+        <v>378</v>
+      </c>
+      <c r="S73" s="1">
+        <f t="shared" si="22"/>
+        <v>268</v>
+      </c>
+      <c r="T73" s="1">
+        <f t="shared" si="22"/>
+        <v>204</v>
+      </c>
+      <c r="U73" s="1">
+        <f t="shared" si="22"/>
+        <v>233</v>
+      </c>
+      <c r="V73" s="1">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="W73" s="1">
+        <f t="shared" si="22"/>
+        <v>20</v>
+      </c>
+      <c r="X73" s="1">
+        <f t="shared" si="22"/>
+        <v>27</v>
+      </c>
+      <c r="Y73" s="1">
+        <f t="shared" si="22"/>
+        <v>34</v>
+      </c>
+      <c r="Z73" s="1">
+        <f t="shared" si="18"/>
+        <v>10021</v>
+      </c>
+      <c r="AA73" s="1">
+        <f t="shared" si="19"/>
+        <v>1237</v>
+      </c>
+      <c r="AB73" s="1">
+        <f t="shared" si="22"/>
+        <v>8448</v>
+      </c>
+      <c r="AC73" s="1">
+        <f t="shared" si="22"/>
+        <v>-207</v>
+      </c>
+      <c r="AD73" s="1">
+        <f t="shared" si="22"/>
+        <v>-215</v>
+      </c>
+      <c r="AE73" s="1">
+        <f t="shared" si="20"/>
+        <v>-4</v>
+      </c>
+      <c r="AG73" s="1">
+        <f t="shared" si="21"/>
+        <v>62552</v>
+      </c>
+    </row>
+    <row r="74" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A74" s="9">
+        <v>1901</v>
+      </c>
+      <c r="H74" s="1">
+        <f t="shared" si="14"/>
+        <v>36675</v>
+      </c>
+      <c r="I74" s="1">
+        <f t="shared" si="15"/>
+        <v>13699</v>
+      </c>
+      <c r="J74" s="1">
+        <f t="shared" si="16"/>
+        <v>1178</v>
+      </c>
+      <c r="K74" s="1">
+        <f t="shared" si="16"/>
+        <v>103</v>
+      </c>
+      <c r="L74" s="1">
+        <f t="shared" si="16"/>
+        <v>373</v>
+      </c>
+      <c r="M74" s="1">
+        <f t="shared" si="16"/>
+        <v>89</v>
+      </c>
+      <c r="N74" s="1">
+        <f t="shared" si="16"/>
+        <v>236</v>
+      </c>
+      <c r="O74" s="1">
+        <f t="shared" si="16"/>
+        <v>13</v>
+      </c>
+      <c r="P74" s="1">
+        <f t="shared" si="16"/>
+        <v>270</v>
+      </c>
+      <c r="Q74" s="1">
+        <f t="shared" si="16"/>
+        <v>978</v>
+      </c>
+      <c r="R74" s="1">
+        <f t="shared" si="17"/>
+        <v>495</v>
+      </c>
+      <c r="S74" s="1">
+        <f t="shared" si="22"/>
+        <v>284</v>
+      </c>
+      <c r="T74" s="1">
+        <f t="shared" si="22"/>
+        <v>183</v>
+      </c>
+      <c r="U74" s="1">
+        <f t="shared" si="22"/>
+        <v>322</v>
+      </c>
+      <c r="V74" s="1">
+        <f t="shared" si="22"/>
+        <v>-11</v>
+      </c>
+      <c r="W74" s="1">
+        <f t="shared" si="22"/>
+        <v>-7</v>
+      </c>
+      <c r="X74" s="1">
+        <f t="shared" si="22"/>
+        <v>5</v>
+      </c>
+      <c r="Y74" s="1">
+        <f t="shared" si="22"/>
+        <v>32</v>
+      </c>
+      <c r="Z74" s="1">
+        <f t="shared" si="18"/>
+        <v>16538</v>
+      </c>
+      <c r="AA74" s="1">
+        <f t="shared" si="19"/>
+        <v>23761</v>
+      </c>
+      <c r="AB74" s="1">
+        <f t="shared" si="22"/>
+        <v>3584</v>
+      </c>
+      <c r="AC74" s="1">
+        <f t="shared" si="22"/>
+        <v>1622</v>
+      </c>
+      <c r="AD74" s="1">
+        <f t="shared" si="22"/>
+        <v>-392</v>
+      </c>
+      <c r="AE74" s="1">
+        <f t="shared" si="20"/>
+        <v>-1432</v>
+      </c>
+      <c r="AG74" s="1">
+        <f t="shared" si="21"/>
+        <v>98598</v>
+      </c>
+    </row>
+    <row r="75" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A75" s="9">
+        <v>1902</v>
+      </c>
       <c r="B75" s="1"/>
+      <c r="H75" s="1">
+        <f t="shared" si="14"/>
+        <v>18122</v>
+      </c>
+      <c r="I75" s="1">
+        <f t="shared" si="15"/>
+        <v>15376</v>
+      </c>
+      <c r="J75" s="1">
+        <f t="shared" si="16"/>
+        <v>439</v>
+      </c>
+      <c r="K75" s="1">
+        <f t="shared" si="16"/>
+        <v>485</v>
+      </c>
+      <c r="L75" s="1">
+        <f t="shared" si="16"/>
+        <v>191</v>
+      </c>
+      <c r="M75" s="1">
+        <f t="shared" si="16"/>
+        <v>62</v>
+      </c>
+      <c r="N75" s="1">
+        <f t="shared" si="16"/>
+        <v>213</v>
+      </c>
+      <c r="O75" s="1">
+        <f t="shared" si="16"/>
+        <v>198</v>
+      </c>
+      <c r="P75" s="1">
+        <f t="shared" si="16"/>
+        <v>333</v>
+      </c>
+      <c r="Q75" s="1">
+        <f t="shared" si="16"/>
+        <v>942</v>
+      </c>
+      <c r="R75" s="1">
+        <f t="shared" si="17"/>
+        <v>1228</v>
+      </c>
+      <c r="S75" s="1">
+        <f t="shared" si="22"/>
+        <v>367</v>
+      </c>
+      <c r="T75" s="1">
+        <f t="shared" si="22"/>
+        <v>166</v>
+      </c>
+      <c r="U75" s="1">
+        <f t="shared" si="22"/>
+        <v>198</v>
+      </c>
+      <c r="V75" s="1">
+        <f t="shared" si="22"/>
+        <v>-19</v>
+      </c>
+      <c r="W75" s="1">
+        <f t="shared" si="22"/>
+        <v>85</v>
+      </c>
+      <c r="X75" s="1">
+        <f t="shared" si="22"/>
+        <v>-34</v>
+      </c>
+      <c r="Y75" s="1">
+        <f t="shared" si="22"/>
+        <v>-36</v>
+      </c>
+      <c r="Z75" s="1">
+        <f t="shared" si="18"/>
+        <v>21988</v>
+      </c>
+      <c r="AA75" s="1">
+        <f t="shared" si="19"/>
+        <v>27566</v>
+      </c>
+      <c r="AB75" s="1">
+        <f t="shared" si="22"/>
+        <v>7913</v>
+      </c>
+      <c r="AC75" s="1">
+        <f t="shared" si="22"/>
+        <v>2264</v>
+      </c>
+      <c r="AD75" s="1">
+        <f t="shared" si="22"/>
+        <v>-247</v>
+      </c>
+      <c r="AE75" s="1">
+        <f t="shared" si="20"/>
+        <v>-1763</v>
+      </c>
+      <c r="AG75" s="1">
+        <f t="shared" si="21"/>
+        <v>96037</v>
+      </c>
+    </row>
+    <row r="76" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A76" s="9">
+        <v>1903</v>
+      </c>
+      <c r="H76" s="1">
+        <f t="shared" si="14"/>
+        <v>24435</v>
+      </c>
+      <c r="I76" s="1">
+        <f t="shared" si="15"/>
+        <v>11465</v>
+      </c>
+      <c r="J76" s="1">
+        <f t="shared" si="16"/>
+        <v>-8</v>
+      </c>
+      <c r="K76" s="1">
+        <f t="shared" si="16"/>
+        <v>651</v>
+      </c>
+      <c r="L76" s="1">
+        <f t="shared" si="16"/>
+        <v>355</v>
+      </c>
+      <c r="M76" s="1">
+        <f t="shared" si="16"/>
+        <v>118</v>
+      </c>
+      <c r="N76" s="1">
+        <f t="shared" si="16"/>
+        <v>84</v>
+      </c>
+      <c r="O76" s="1">
+        <f t="shared" si="16"/>
+        <v>194</v>
+      </c>
+      <c r="P76" s="1">
+        <f t="shared" si="16"/>
+        <v>375</v>
+      </c>
+      <c r="Q76" s="1">
+        <f t="shared" si="16"/>
+        <v>813</v>
+      </c>
+      <c r="R76" s="1">
+        <f t="shared" si="17"/>
+        <v>448</v>
+      </c>
+      <c r="S76" s="1">
+        <f t="shared" si="22"/>
+        <v>314</v>
+      </c>
+      <c r="T76" s="1">
+        <f t="shared" si="22"/>
+        <v>249</v>
+      </c>
+      <c r="U76" s="1">
+        <f t="shared" si="22"/>
+        <v>377</v>
+      </c>
+      <c r="V76" s="1">
+        <f t="shared" si="22"/>
+        <v>30</v>
+      </c>
+      <c r="W76" s="1">
+        <f t="shared" si="22"/>
+        <v>24</v>
+      </c>
+      <c r="X76" s="1">
+        <f t="shared" si="22"/>
+        <v>-4</v>
+      </c>
+      <c r="Y76" s="1">
+        <f t="shared" si="22"/>
+        <v>20</v>
+      </c>
+      <c r="Z76" s="1">
+        <f t="shared" si="18"/>
+        <v>23983</v>
+      </c>
+      <c r="AA76" s="1">
+        <f t="shared" si="19"/>
+        <v>5252</v>
+      </c>
+      <c r="AB76" s="1">
+        <f t="shared" si="22"/>
+        <v>10102</v>
+      </c>
+      <c r="AC76" s="1">
+        <f t="shared" si="22"/>
+        <v>2079</v>
+      </c>
+      <c r="AD76" s="1">
+        <f t="shared" si="22"/>
+        <v>-447</v>
+      </c>
+      <c r="AE76" s="1">
+        <f t="shared" si="20"/>
+        <v>1191</v>
+      </c>
+      <c r="AG76" s="1">
+        <f t="shared" si="21"/>
+        <v>82100</v>
+      </c>
+    </row>
+    <row r="77" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A77" s="9">
+        <v>1904</v>
+      </c>
+      <c r="H77" s="1">
+        <f t="shared" si="14"/>
+        <v>13711</v>
+      </c>
+      <c r="I77" s="1">
+        <f t="shared" si="15"/>
+        <v>16264</v>
+      </c>
+      <c r="J77" s="1">
+        <f t="shared" si="16"/>
+        <v>190</v>
+      </c>
+      <c r="K77" s="1">
+        <f t="shared" si="16"/>
+        <v>924</v>
+      </c>
+      <c r="L77" s="1">
+        <f t="shared" si="16"/>
+        <v>110</v>
+      </c>
+      <c r="M77" s="1">
+        <f t="shared" si="16"/>
+        <v>-164</v>
+      </c>
+      <c r="N77" s="1">
+        <f t="shared" si="16"/>
+        <v>63</v>
+      </c>
+      <c r="O77" s="1">
+        <f t="shared" si="16"/>
+        <v>168</v>
+      </c>
+      <c r="P77" s="1">
+        <f t="shared" si="16"/>
+        <v>-192</v>
+      </c>
+      <c r="Q77" s="1">
+        <f t="shared" si="16"/>
+        <v>402</v>
+      </c>
+      <c r="R77" s="1">
+        <f t="shared" si="17"/>
+        <v>247</v>
+      </c>
+      <c r="S77" s="1">
+        <f t="shared" si="22"/>
+        <v>333</v>
+      </c>
+      <c r="T77" s="1">
+        <f t="shared" si="22"/>
+        <v>53</v>
+      </c>
+      <c r="U77" s="1">
+        <f t="shared" si="22"/>
+        <v>83</v>
+      </c>
+      <c r="V77" s="1">
+        <f t="shared" si="22"/>
+        <v>-85</v>
+      </c>
+      <c r="W77" s="1">
+        <f t="shared" si="22"/>
+        <v>-55</v>
+      </c>
+      <c r="X77" s="1">
+        <f t="shared" si="22"/>
+        <v>-44</v>
+      </c>
+      <c r="Y77" s="1">
+        <f t="shared" si="22"/>
+        <v>4</v>
+      </c>
+      <c r="Z77" s="1">
+        <f t="shared" si="18"/>
+        <v>14727</v>
+      </c>
+      <c r="AA77" s="1">
+        <f t="shared" si="19"/>
+        <v>1849</v>
+      </c>
+      <c r="AB77" s="1">
+        <f t="shared" si="22"/>
+        <v>9855</v>
+      </c>
+      <c r="AC77" s="1">
+        <f t="shared" si="22"/>
+        <v>-459</v>
+      </c>
+      <c r="AD77" s="1">
+        <f t="shared" si="22"/>
+        <v>-257</v>
+      </c>
+      <c r="AE77" s="1">
+        <f t="shared" si="20"/>
+        <v>-3052</v>
+      </c>
+      <c r="AG77" s="1">
+        <f t="shared" si="21"/>
+        <v>54675</v>
+      </c>
+    </row>
+    <row r="78" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A78" s="9">
+        <v>1905</v>
+      </c>
+      <c r="H78" s="1">
+        <f t="shared" si="14"/>
+        <v>17314</v>
+      </c>
+      <c r="I78" s="1">
+        <f t="shared" si="15"/>
+        <v>-19790</v>
+      </c>
+      <c r="J78" s="1">
+        <f t="shared" si="16"/>
+        <v>368</v>
+      </c>
+      <c r="K78" s="1">
+        <f t="shared" si="16"/>
+        <v>286</v>
+      </c>
+      <c r="L78" s="1">
+        <f t="shared" si="16"/>
+        <v>409</v>
+      </c>
+      <c r="M78" s="1">
+        <f t="shared" si="16"/>
+        <v>-104</v>
+      </c>
+      <c r="N78" s="1">
+        <f t="shared" si="16"/>
+        <v>-498</v>
+      </c>
+      <c r="O78" s="1">
+        <f t="shared" si="16"/>
+        <v>-78</v>
+      </c>
+      <c r="P78" s="1">
+        <f t="shared" si="16"/>
+        <v>-161</v>
+      </c>
+      <c r="Q78" s="1">
+        <f t="shared" si="16"/>
+        <v>671</v>
+      </c>
+      <c r="R78" s="1">
+        <f t="shared" si="17"/>
+        <v>210</v>
+      </c>
+      <c r="S78" s="1">
+        <f t="shared" si="22"/>
+        <v>-4</v>
+      </c>
+      <c r="T78" s="1">
+        <f t="shared" si="22"/>
+        <v>-289</v>
+      </c>
+      <c r="U78" s="1">
+        <f t="shared" si="22"/>
+        <v>208</v>
+      </c>
+      <c r="V78" s="1">
+        <f t="shared" si="22"/>
+        <v>48</v>
+      </c>
+      <c r="W78" s="1">
+        <f t="shared" si="22"/>
+        <v>-70</v>
+      </c>
+      <c r="X78" s="1">
+        <f t="shared" si="22"/>
+        <v>-28</v>
+      </c>
+      <c r="Y78" s="1">
+        <f t="shared" si="22"/>
+        <v>8</v>
+      </c>
+      <c r="Z78" s="1">
+        <f t="shared" si="18"/>
+        <v>7588</v>
+      </c>
+      <c r="AA78" s="1">
+        <f t="shared" si="19"/>
+        <v>-379</v>
+      </c>
+      <c r="AB78" s="1">
+        <f t="shared" si="22"/>
+        <v>3277</v>
+      </c>
+      <c r="AC78" s="1">
+        <f t="shared" si="22"/>
+        <v>155</v>
+      </c>
+      <c r="AD78" s="1">
+        <f t="shared" si="22"/>
+        <v>-61</v>
+      </c>
+      <c r="AE78" s="1">
+        <f t="shared" si="20"/>
+        <v>-14</v>
+      </c>
+      <c r="AG78" s="1">
+        <f t="shared" si="21"/>
+        <v>9066</v>
+      </c>
+    </row>
+    <row r="79" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A79" s="9">
+        <v>1906</v>
+      </c>
+      <c r="H79" s="1">
+        <f t="shared" si="14"/>
+        <v>33711</v>
+      </c>
+      <c r="I79" s="1">
+        <f t="shared" si="15"/>
+        <v>-82671</v>
+      </c>
+      <c r="J79" s="1">
+        <f t="shared" si="16"/>
+        <v>184</v>
+      </c>
+      <c r="K79" s="1">
+        <f t="shared" si="16"/>
+        <v>849</v>
+      </c>
+      <c r="L79" s="1">
+        <f t="shared" si="16"/>
+        <v>194</v>
+      </c>
+      <c r="M79" s="1">
+        <f t="shared" si="16"/>
+        <v>-127</v>
+      </c>
+      <c r="N79" s="1">
+        <f t="shared" si="16"/>
+        <v>57</v>
+      </c>
+      <c r="O79" s="1">
+        <f t="shared" si="16"/>
+        <v>92</v>
+      </c>
+      <c r="P79" s="1">
+        <f t="shared" si="16"/>
+        <v>33</v>
+      </c>
+      <c r="Q79" s="1">
+        <f t="shared" si="16"/>
+        <v>1234</v>
+      </c>
+      <c r="R79" s="1">
+        <f t="shared" si="17"/>
+        <v>409</v>
+      </c>
+      <c r="S79" s="1">
+        <f t="shared" si="22"/>
+        <v>501</v>
+      </c>
+      <c r="T79" s="1">
+        <f t="shared" si="22"/>
+        <v>146</v>
+      </c>
+      <c r="U79" s="1">
+        <f t="shared" si="22"/>
+        <v>108</v>
+      </c>
+      <c r="V79" s="1">
+        <f t="shared" si="22"/>
+        <v>58</v>
+      </c>
+      <c r="W79" s="1">
+        <f t="shared" si="22"/>
+        <v>19</v>
+      </c>
+      <c r="X79" s="1">
+        <f t="shared" si="22"/>
+        <v>4</v>
+      </c>
+      <c r="Y79" s="1">
+        <f t="shared" si="22"/>
+        <v>20</v>
+      </c>
+      <c r="Z79" s="1">
+        <f t="shared" si="18"/>
+        <v>34123</v>
+      </c>
+      <c r="AA79" s="1">
+        <f t="shared" si="19"/>
+        <v>16572</v>
+      </c>
+      <c r="AB79" s="1">
+        <f t="shared" si="22"/>
+        <v>7674</v>
+      </c>
+      <c r="AC79" s="1">
+        <f t="shared" si="22"/>
+        <v>4211</v>
+      </c>
+      <c r="AD79" s="1">
+        <f t="shared" si="22"/>
+        <v>-444</v>
+      </c>
+      <c r="AE79" s="1">
+        <f t="shared" si="20"/>
+        <v>3450</v>
+      </c>
+      <c r="AG79" s="1">
+        <f t="shared" si="21"/>
+        <v>20407</v>
+      </c>
+    </row>
+    <row r="80" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A80" s="9">
+        <v>1907</v>
+      </c>
+      <c r="H80" s="1">
+        <f t="shared" si="14"/>
+        <v>17598</v>
+      </c>
+      <c r="I80" s="1">
+        <f t="shared" si="15"/>
+        <v>11905</v>
+      </c>
+      <c r="J80" s="1">
+        <f t="shared" si="16"/>
+        <v>-37</v>
+      </c>
+      <c r="K80" s="1">
+        <f t="shared" si="16"/>
+        <v>1500</v>
+      </c>
+      <c r="L80" s="1">
+        <f t="shared" si="16"/>
+        <v>553</v>
+      </c>
+      <c r="M80" s="1">
+        <f t="shared" si="16"/>
+        <v>-67</v>
+      </c>
+      <c r="N80" s="1">
+        <f t="shared" si="16"/>
+        <v>614</v>
+      </c>
+      <c r="O80" s="1">
+        <f t="shared" si="16"/>
+        <v>230</v>
+      </c>
+      <c r="P80" s="1">
+        <f t="shared" si="16"/>
+        <v>214</v>
+      </c>
+      <c r="Q80" s="1">
+        <f t="shared" si="16"/>
+        <v>-13</v>
+      </c>
+      <c r="R80" s="1">
+        <f t="shared" si="17"/>
+        <v>375</v>
+      </c>
+      <c r="S80" s="1">
+        <f t="shared" si="22"/>
+        <v>714</v>
+      </c>
+      <c r="T80" s="1">
+        <f t="shared" si="22"/>
+        <v>140</v>
+      </c>
+      <c r="U80" s="1">
+        <f t="shared" si="22"/>
+        <v>445</v>
+      </c>
+      <c r="V80" s="1">
+        <f t="shared" si="22"/>
+        <v>83</v>
+      </c>
+      <c r="W80" s="1">
+        <f t="shared" si="22"/>
+        <v>149</v>
+      </c>
+      <c r="X80" s="1">
+        <f t="shared" si="22"/>
+        <v>-13</v>
+      </c>
+      <c r="Y80" s="1">
+        <f t="shared" si="22"/>
+        <v>-25</v>
+      </c>
+      <c r="Z80" s="1">
+        <f t="shared" si="18"/>
+        <v>16182</v>
+      </c>
+      <c r="AA80" s="1">
+        <f t="shared" si="19"/>
+        <v>27703</v>
+      </c>
+      <c r="AB80" s="1">
+        <f t="shared" si="22"/>
+        <v>14572</v>
+      </c>
+      <c r="AC80" s="1">
+        <f t="shared" si="22"/>
+        <v>1280</v>
+      </c>
+      <c r="AD80" s="1">
+        <f t="shared" si="22"/>
+        <v>-415</v>
+      </c>
+      <c r="AE80" s="1">
+        <f t="shared" si="20"/>
+        <v>9635</v>
+      </c>
+      <c r="AG80" s="1">
+        <f t="shared" si="21"/>
+        <v>103322</v>
+      </c>
+    </row>
+    <row r="81" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A81" s="9">
+        <v>1908</v>
+      </c>
+      <c r="H81" s="1">
+        <f t="shared" si="14"/>
+        <v>23538</v>
+      </c>
+      <c r="I81" s="1">
+        <f t="shared" si="15"/>
+        <v>10199</v>
+      </c>
+      <c r="J81" s="1">
+        <f t="shared" si="16"/>
+        <v>266</v>
+      </c>
+      <c r="K81" s="1">
+        <f t="shared" si="16"/>
+        <v>2407</v>
+      </c>
+      <c r="L81" s="1">
+        <f t="shared" si="16"/>
+        <v>271</v>
+      </c>
+      <c r="M81" s="1">
+        <f t="shared" si="16"/>
+        <v>323</v>
+      </c>
+      <c r="N81" s="1">
+        <f t="shared" si="16"/>
+        <v>487</v>
+      </c>
+      <c r="O81" s="1">
+        <f t="shared" si="16"/>
+        <v>213</v>
+      </c>
+      <c r="P81" s="1">
+        <f t="shared" si="16"/>
+        <v>-16</v>
+      </c>
+      <c r="Q81" s="1">
+        <f t="shared" si="16"/>
+        <v>433</v>
+      </c>
+      <c r="R81" s="1">
+        <f t="shared" si="17"/>
+        <v>1101</v>
+      </c>
+      <c r="S81" s="1">
+        <f t="shared" si="22"/>
+        <v>174</v>
+      </c>
+      <c r="T81" s="1">
+        <f t="shared" si="22"/>
+        <v>459</v>
+      </c>
+      <c r="U81" s="1">
+        <f t="shared" si="22"/>
+        <v>343</v>
+      </c>
+      <c r="V81" s="1">
+        <f t="shared" si="22"/>
+        <v>-70</v>
+      </c>
+      <c r="W81" s="1">
+        <f t="shared" si="22"/>
+        <v>102</v>
+      </c>
+      <c r="X81" s="1">
+        <f t="shared" si="22"/>
+        <v>65</v>
+      </c>
+      <c r="Y81" s="1">
+        <f t="shared" si="22"/>
+        <v>-17</v>
+      </c>
+      <c r="Z81" s="1">
+        <f t="shared" si="18"/>
+        <v>14617</v>
+      </c>
+      <c r="AA81" s="1">
+        <f t="shared" si="19"/>
+        <v>13337</v>
+      </c>
+      <c r="AB81" s="1">
+        <f t="shared" si="22"/>
+        <v>13278</v>
+      </c>
+      <c r="AC81" s="1">
+        <f t="shared" si="22"/>
+        <v>170</v>
+      </c>
+      <c r="AD81" s="1">
+        <f t="shared" si="22"/>
+        <v>-227</v>
+      </c>
+      <c r="AE81" s="1">
+        <f t="shared" si="20"/>
+        <v>856</v>
+      </c>
+      <c r="AG81" s="1">
+        <f t="shared" si="21"/>
+        <v>82309</v>
+      </c>
+    </row>
+    <row r="82" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A82" s="9">
+        <v>1909</v>
+      </c>
+      <c r="H82" s="1">
+        <f t="shared" si="14"/>
+        <v>34466</v>
+      </c>
+      <c r="I82" s="1">
+        <f t="shared" si="15"/>
+        <v>6329</v>
+      </c>
+      <c r="J82" s="1">
+        <f t="shared" si="16"/>
+        <v>859</v>
+      </c>
+      <c r="K82" s="1">
+        <f t="shared" si="16"/>
+        <v>1210</v>
+      </c>
+      <c r="L82" s="1">
+        <f t="shared" si="16"/>
+        <v>444</v>
+      </c>
+      <c r="M82" s="1">
+        <f t="shared" si="16"/>
+        <v>-112</v>
+      </c>
+      <c r="N82" s="1">
+        <f t="shared" si="16"/>
+        <v>578</v>
+      </c>
+      <c r="O82" s="1">
+        <f t="shared" si="16"/>
+        <v>430</v>
+      </c>
+      <c r="P82" s="1">
+        <f t="shared" si="16"/>
+        <v>397</v>
+      </c>
+      <c r="Q82" s="1">
+        <f t="shared" si="16"/>
+        <v>118</v>
+      </c>
+      <c r="R82" s="1">
+        <f t="shared" si="17"/>
+        <v>2190</v>
+      </c>
+      <c r="S82" s="1">
+        <f t="shared" si="22"/>
+        <v>517</v>
+      </c>
+      <c r="T82" s="1">
+        <f t="shared" si="22"/>
+        <v>580</v>
+      </c>
+      <c r="U82" s="1">
+        <f t="shared" si="22"/>
+        <v>474</v>
+      </c>
+      <c r="V82" s="1">
+        <f t="shared" si="22"/>
+        <v>33</v>
+      </c>
+      <c r="W82" s="1">
+        <f t="shared" si="22"/>
+        <v>81</v>
+      </c>
+      <c r="X82" s="1">
+        <f t="shared" si="22"/>
+        <v>26</v>
+      </c>
+      <c r="Y82" s="1">
+        <f t="shared" si="22"/>
+        <v>27</v>
+      </c>
+      <c r="Z82" s="1">
+        <f t="shared" si="18"/>
+        <v>20199</v>
+      </c>
+      <c r="AA82" s="1">
+        <f t="shared" si="19"/>
+        <v>16459</v>
+      </c>
+      <c r="AB82" s="1">
+        <f t="shared" si="22"/>
+        <v>22675</v>
+      </c>
+      <c r="AC82" s="1">
+        <f t="shared" si="22"/>
+        <v>916</v>
+      </c>
+      <c r="AD82" s="1">
+        <f t="shared" si="22"/>
+        <v>131</v>
+      </c>
+      <c r="AE82" s="1">
+        <f t="shared" si="20"/>
+        <v>1072</v>
+      </c>
+      <c r="AG82" s="1">
+        <f t="shared" si="21"/>
+        <v>110099</v>
+      </c>
+    </row>
+    <row r="83" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A83" s="9">
+        <v>1910</v>
+      </c>
+      <c r="H83" s="1">
+        <f t="shared" si="14"/>
+        <v>-31709</v>
+      </c>
+      <c r="I83" s="1">
+        <f t="shared" si="15"/>
+        <v>6158</v>
+      </c>
+      <c r="J83" s="1">
+        <f t="shared" si="16"/>
+        <v>1491</v>
+      </c>
+      <c r="K83" s="1">
+        <f t="shared" si="16"/>
+        <v>3119</v>
+      </c>
+      <c r="L83" s="1">
+        <f t="shared" si="16"/>
+        <v>671</v>
+      </c>
+      <c r="M83" s="1">
+        <f t="shared" si="16"/>
+        <v>405</v>
+      </c>
+      <c r="N83" s="1">
+        <f t="shared" si="16"/>
+        <v>387</v>
+      </c>
+      <c r="O83" s="1">
+        <f t="shared" si="16"/>
+        <v>522</v>
+      </c>
+      <c r="P83" s="1">
+        <f t="shared" si="16"/>
+        <v>441</v>
+      </c>
+      <c r="Q83" s="1">
+        <f t="shared" si="16"/>
+        <v>1345</v>
+      </c>
+      <c r="R83" s="1">
+        <f t="shared" si="17"/>
+        <v>967</v>
+      </c>
+      <c r="S83" s="1">
+        <f t="shared" si="22"/>
+        <v>278</v>
+      </c>
+      <c r="T83" s="1">
+        <f t="shared" si="22"/>
+        <v>455</v>
+      </c>
+      <c r="U83" s="1">
+        <f t="shared" si="22"/>
+        <v>725</v>
+      </c>
+      <c r="V83" s="1">
+        <f t="shared" si="22"/>
+        <v>121</v>
+      </c>
+      <c r="W83" s="1">
+        <f t="shared" si="22"/>
+        <v>63</v>
+      </c>
+      <c r="X83" s="1">
+        <f t="shared" si="22"/>
+        <v>28</v>
+      </c>
+      <c r="Y83" s="1">
+        <f t="shared" si="22"/>
+        <v>17</v>
+      </c>
+      <c r="Z83" s="1">
+        <f t="shared" si="18"/>
+        <v>24406</v>
+      </c>
+      <c r="AA83" s="1">
+        <f t="shared" si="19"/>
+        <v>19707</v>
+      </c>
+      <c r="AB83" s="1">
+        <f t="shared" si="22"/>
+        <v>18263</v>
+      </c>
+      <c r="AC83" s="1">
+        <f t="shared" si="22"/>
+        <v>-754</v>
+      </c>
+      <c r="AD83" s="1">
+        <f t="shared" si="22"/>
+        <v>-475</v>
+      </c>
+      <c r="AE83" s="1">
+        <f t="shared" si="20"/>
+        <v>6898</v>
+      </c>
+      <c r="AG83" s="1">
+        <f t="shared" si="21"/>
+        <v>53529</v>
+      </c>
+    </row>
+    <row r="84" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A84" s="9">
+        <v>1911</v>
+      </c>
+      <c r="H84" s="1">
+        <f t="shared" si="14"/>
+        <v>18233</v>
+      </c>
+      <c r="I84" s="1">
+        <f t="shared" si="15"/>
+        <v>14467</v>
+      </c>
+      <c r="J84" s="1">
+        <f t="shared" si="16"/>
+        <v>885</v>
+      </c>
+      <c r="K84" s="1">
+        <f t="shared" si="16"/>
+        <v>1388</v>
+      </c>
+      <c r="L84" s="1">
+        <f t="shared" si="16"/>
+        <v>301</v>
+      </c>
+      <c r="M84" s="1">
+        <f t="shared" si="16"/>
+        <v>393</v>
+      </c>
+      <c r="N84" s="1">
+        <f t="shared" si="16"/>
+        <v>632</v>
+      </c>
+      <c r="O84" s="1">
+        <f t="shared" si="16"/>
+        <v>844</v>
+      </c>
+      <c r="P84" s="1">
+        <f t="shared" si="16"/>
+        <v>312</v>
+      </c>
+      <c r="Q84" s="1">
+        <f t="shared" si="16"/>
+        <v>394</v>
+      </c>
+      <c r="R84" s="1">
+        <f t="shared" si="17"/>
+        <v>278</v>
+      </c>
+      <c r="S84" s="1">
+        <f t="shared" si="22"/>
+        <v>556</v>
+      </c>
+      <c r="T84" s="1">
+        <f t="shared" si="22"/>
+        <v>831</v>
+      </c>
+      <c r="U84" s="1">
+        <f t="shared" si="22"/>
+        <v>652</v>
+      </c>
+      <c r="V84" s="1">
+        <f t="shared" si="22"/>
+        <v>-1</v>
+      </c>
+      <c r="W84" s="1">
+        <f t="shared" si="22"/>
+        <v>73</v>
+      </c>
+      <c r="X84" s="1">
+        <f t="shared" si="22"/>
+        <v>35</v>
+      </c>
+      <c r="Y84" s="1">
+        <f t="shared" si="22"/>
+        <v>-34</v>
+      </c>
+      <c r="Z84" s="1">
+        <f t="shared" si="18"/>
+        <v>32555</v>
+      </c>
+      <c r="AA84" s="1">
+        <f t="shared" si="19"/>
+        <v>-3710</v>
+      </c>
+      <c r="AB84" s="1">
+        <f t="shared" si="22"/>
+        <v>23277</v>
+      </c>
+      <c r="AC84" s="1">
+        <f t="shared" si="22"/>
+        <v>1293</v>
+      </c>
+      <c r="AD84" s="1">
+        <f t="shared" si="22"/>
+        <v>-519</v>
+      </c>
+      <c r="AE84" s="1">
+        <f t="shared" si="20"/>
+        <v>521</v>
+      </c>
+      <c r="AG84" s="1">
+        <f t="shared" si="21"/>
+        <v>93656</v>
+      </c>
+    </row>
+    <row r="85" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A85" s="9">
+        <v>1912</v>
+      </c>
+      <c r="H85" s="1">
+        <f t="shared" si="14"/>
+        <v>26741</v>
+      </c>
+      <c r="I85" s="1">
+        <f t="shared" si="15"/>
+        <v>6329</v>
+      </c>
+      <c r="J85" s="1">
+        <f t="shared" si="16"/>
+        <v>1428</v>
+      </c>
+      <c r="K85" s="1">
+        <f t="shared" si="16"/>
+        <v>1654</v>
+      </c>
+      <c r="L85" s="1">
+        <f t="shared" si="16"/>
+        <v>281</v>
+      </c>
+      <c r="M85" s="1">
+        <f t="shared" si="16"/>
+        <v>264</v>
+      </c>
+      <c r="N85" s="1">
+        <f t="shared" si="16"/>
+        <v>255</v>
+      </c>
+      <c r="O85" s="1">
+        <f t="shared" si="16"/>
+        <v>675</v>
+      </c>
+      <c r="P85" s="1">
+        <f t="shared" si="16"/>
+        <v>125</v>
+      </c>
+      <c r="Q85" s="1">
+        <f t="shared" si="16"/>
+        <v>-3643</v>
+      </c>
+      <c r="R85" s="1">
+        <f t="shared" si="17"/>
+        <v>688</v>
+      </c>
+      <c r="S85" s="1">
+        <f t="shared" si="22"/>
+        <v>-447</v>
+      </c>
+      <c r="T85" s="1">
+        <f t="shared" si="22"/>
+        <v>1010</v>
+      </c>
+      <c r="U85" s="1">
+        <f t="shared" si="22"/>
+        <v>845</v>
+      </c>
+      <c r="V85" s="1">
+        <f t="shared" si="22"/>
+        <v>-171</v>
+      </c>
+      <c r="W85" s="1">
+        <f t="shared" si="22"/>
+        <v>11</v>
+      </c>
+      <c r="X85" s="1">
+        <f t="shared" si="22"/>
+        <v>-9</v>
+      </c>
+      <c r="Y85" s="1">
+        <f t="shared" si="22"/>
+        <v>-130</v>
+      </c>
+      <c r="Z85" s="1">
+        <f t="shared" si="18"/>
+        <v>49934</v>
+      </c>
+      <c r="AA85" s="1">
+        <f t="shared" si="19"/>
+        <v>19789</v>
+      </c>
+      <c r="AB85" s="1">
+        <f t="shared" si="22"/>
+        <v>7686</v>
+      </c>
+      <c r="AC85" s="1">
+        <f t="shared" si="22"/>
+        <v>1699</v>
+      </c>
+      <c r="AD85" s="1">
+        <f t="shared" si="22"/>
+        <v>10</v>
+      </c>
+      <c r="AE85" s="1">
+        <f t="shared" si="20"/>
+        <v>-351</v>
+      </c>
+      <c r="AG85" s="1">
+        <f t="shared" si="21"/>
+        <v>114673</v>
+      </c>
+    </row>
+    <row r="86" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A86" s="9">
+        <v>1913</v>
+      </c>
+      <c r="H86" s="1">
+        <f t="shared" si="14"/>
+        <v>20449</v>
+      </c>
+      <c r="I86" s="1">
+        <f t="shared" si="15"/>
+        <v>10229</v>
+      </c>
+      <c r="J86" s="1">
+        <f t="shared" si="16"/>
+        <v>2768</v>
+      </c>
+      <c r="K86" s="1">
+        <f t="shared" si="16"/>
+        <v>2244</v>
+      </c>
+      <c r="L86" s="1">
+        <f t="shared" si="16"/>
+        <v>936</v>
+      </c>
+      <c r="M86" s="1">
+        <f t="shared" si="16"/>
+        <v>941</v>
+      </c>
+      <c r="N86" s="1">
+        <f t="shared" si="16"/>
+        <v>1258</v>
+      </c>
+      <c r="O86" s="1">
+        <f t="shared" ref="K86:Q88" si="23">O34</f>
+        <v>1699</v>
+      </c>
+      <c r="P86" s="1">
+        <f t="shared" si="23"/>
+        <v>383</v>
+      </c>
+      <c r="Q86" s="1">
+        <f t="shared" si="23"/>
+        <v>1792</v>
+      </c>
+      <c r="R86" s="1">
+        <f t="shared" si="17"/>
+        <v>520</v>
+      </c>
+      <c r="S86" s="1">
+        <f t="shared" ref="S86:AE86" si="24">S34</f>
+        <v>263</v>
+      </c>
+      <c r="T86" s="1">
+        <f t="shared" si="24"/>
+        <v>1330</v>
+      </c>
+      <c r="U86" s="1">
+        <f t="shared" si="24"/>
+        <v>478</v>
+      </c>
+      <c r="V86" s="1">
+        <f t="shared" si="24"/>
+        <v>17</v>
+      </c>
+      <c r="W86" s="1">
+        <f t="shared" si="24"/>
+        <v>116</v>
+      </c>
+      <c r="X86" s="1">
+        <f t="shared" si="24"/>
+        <v>45</v>
+      </c>
+      <c r="Y86" s="1">
+        <f t="shared" si="24"/>
+        <v>250</v>
+      </c>
+      <c r="Z86" s="1">
+        <f t="shared" si="18"/>
+        <v>60806</v>
+      </c>
+      <c r="AA86" s="1">
+        <f t="shared" si="19"/>
+        <v>56725</v>
+      </c>
+      <c r="AB86" s="1">
+        <f t="shared" si="24"/>
+        <v>16316</v>
+      </c>
+      <c r="AC86" s="1">
+        <f t="shared" si="24"/>
+        <v>814</v>
+      </c>
+      <c r="AD86" s="1">
+        <f t="shared" si="24"/>
+        <v>137</v>
+      </c>
+      <c r="AE86" s="1">
+        <f t="shared" si="20"/>
+        <v>5688</v>
+      </c>
+      <c r="AG86" s="1">
+        <f t="shared" si="21"/>
+        <v>186204</v>
+      </c>
+    </row>
+    <row r="87" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A87" s="9">
+        <v>1914</v>
+      </c>
+      <c r="H87" s="1">
+        <f t="shared" si="14"/>
+        <v>450</v>
+      </c>
+      <c r="I87" s="1">
+        <f t="shared" si="15"/>
+        <v>10782</v>
+      </c>
+      <c r="J87" s="1">
+        <f t="shared" si="16"/>
+        <v>-1098</v>
+      </c>
+      <c r="K87" s="1">
+        <f t="shared" si="23"/>
+        <v>-28</v>
+      </c>
+      <c r="L87" s="1">
+        <f t="shared" si="23"/>
+        <v>889</v>
+      </c>
+      <c r="M87" s="1">
+        <f t="shared" si="23"/>
+        <v>-273</v>
+      </c>
+      <c r="N87" s="1">
+        <f t="shared" si="23"/>
+        <v>423</v>
+      </c>
+      <c r="O87" s="1">
+        <f t="shared" si="23"/>
+        <v>694</v>
+      </c>
+      <c r="P87" s="1">
+        <f t="shared" si="23"/>
+        <v>-331</v>
+      </c>
+      <c r="Q87" s="1">
+        <f t="shared" si="23"/>
+        <v>1577</v>
+      </c>
+      <c r="R87" s="1">
+        <f t="shared" si="17"/>
+        <v>424</v>
+      </c>
+      <c r="S87" s="1">
+        <f t="shared" ref="S87:AE87" si="25">S35</f>
+        <v>865</v>
+      </c>
+      <c r="T87" s="1">
+        <f t="shared" si="25"/>
+        <v>557</v>
+      </c>
+      <c r="U87" s="1">
+        <f t="shared" si="25"/>
+        <v>12</v>
+      </c>
+      <c r="V87" s="1">
+        <f t="shared" si="25"/>
+        <v>-14</v>
+      </c>
+      <c r="W87" s="1">
+        <f t="shared" si="25"/>
+        <v>43</v>
+      </c>
+      <c r="X87" s="1">
+        <f t="shared" si="25"/>
+        <v>7</v>
+      </c>
+      <c r="Y87" s="1">
+        <f t="shared" si="25"/>
+        <v>45</v>
+      </c>
+      <c r="Z87" s="1">
+        <f t="shared" si="18"/>
+        <v>50658</v>
+      </c>
+      <c r="AA87" s="1">
+        <f t="shared" si="19"/>
+        <v>23184</v>
+      </c>
+      <c r="AB87" s="1">
+        <f t="shared" si="25"/>
+        <v>10755</v>
+      </c>
+      <c r="AC87" s="1">
+        <f t="shared" si="25"/>
+        <v>300</v>
+      </c>
+      <c r="AD87" s="1">
+        <f t="shared" si="25"/>
+        <v>34</v>
+      </c>
+      <c r="AE87" s="1">
+        <f t="shared" si="20"/>
+        <v>-330</v>
+      </c>
+      <c r="AG87" s="1">
+        <f t="shared" si="21"/>
+        <v>99625</v>
+      </c>
+    </row>
+    <row r="88" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A88" s="9">
+        <v>1915</v>
+      </c>
+      <c r="H88" s="1">
+        <f t="shared" si="14"/>
+        <v>-7327</v>
+      </c>
+      <c r="I88" s="1">
+        <f t="shared" si="15"/>
+        <v>-1094</v>
+      </c>
+      <c r="J88" s="1">
+        <f t="shared" si="16"/>
+        <v>-138</v>
+      </c>
+      <c r="K88" s="1">
+        <f t="shared" si="23"/>
+        <v>-88</v>
+      </c>
+      <c r="L88" s="1">
+        <f t="shared" si="23"/>
+        <v>43</v>
+      </c>
+      <c r="M88" s="1">
+        <f t="shared" si="23"/>
+        <v>48</v>
+      </c>
+      <c r="N88" s="1">
+        <f t="shared" si="23"/>
+        <v>96</v>
+      </c>
+      <c r="O88" s="1">
+        <f t="shared" si="23"/>
+        <v>-4</v>
+      </c>
+      <c r="P88" s="1">
+        <f t="shared" si="23"/>
+        <v>-24</v>
+      </c>
+      <c r="Q88" s="1">
+        <f t="shared" si="23"/>
+        <v>859</v>
+      </c>
+      <c r="R88" s="1">
+        <f t="shared" si="17"/>
+        <v>-30</v>
+      </c>
+      <c r="S88" s="1">
+        <f t="shared" ref="S88:AE88" si="26">S36</f>
+        <v>-442</v>
+      </c>
+      <c r="T88" s="1">
+        <f t="shared" si="26"/>
+        <v>23</v>
+      </c>
+      <c r="U88" s="1">
+        <f t="shared" si="26"/>
+        <v>67</v>
+      </c>
+      <c r="V88" s="1">
+        <f t="shared" si="26"/>
+        <v>34</v>
+      </c>
+      <c r="W88" s="1">
+        <f t="shared" si="26"/>
+        <v>10</v>
+      </c>
+      <c r="X88" s="1">
+        <f t="shared" si="26"/>
+        <v>-1</v>
+      </c>
+      <c r="Y88" s="1">
+        <f t="shared" si="26"/>
+        <v>33</v>
+      </c>
+      <c r="Z88" s="1">
+        <f t="shared" si="18"/>
+        <v>20497</v>
+      </c>
+      <c r="AA88" s="1">
+        <f t="shared" si="19"/>
+        <v>36286</v>
+      </c>
+      <c r="AB88" s="1">
+        <f t="shared" si="26"/>
+        <v>464</v>
+      </c>
+      <c r="AC88" s="1">
+        <f t="shared" si="26"/>
+        <v>1509</v>
+      </c>
+      <c r="AD88" s="1">
+        <f t="shared" si="26"/>
+        <v>79</v>
+      </c>
+      <c r="AE88" s="1">
+        <f t="shared" si="20"/>
+        <v>-1622</v>
+      </c>
+      <c r="AG88" s="1">
+        <f t="shared" si="21"/>
+        <v>49278</v>
+      </c>
+    </row>
+    <row r="90" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="AG90" s="1">
+        <f>SUM(AG54:AG68)</f>
+        <v>960967</v>
+      </c>
+    </row>
+    <row r="91" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="AG91" s="1">
+        <f>SUM(AG69:AG88)</f>
+        <v>1622024</v>
+      </c>
+    </row>
+    <row r="92" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="AG92" s="1">
+        <f>AG91+AG90</f>
+        <v>2582991</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
